--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -3266,7 +3266,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>399.84 - 409.23 DR DEMAND</t>
+          <t>399.83 - 409.23 DR DEMAND</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>10163.48 - 10582.66 DR DEMAND</t>
+          <t>10163.49 - 10582.66 DR DEMAND</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P120"/>
+  <dimension ref="A1:P116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,17 +513,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JINDALSAW</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jindal Saw Ltd.</t>
+          <t>Craftsman Automation Ltd.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -532,26 +532,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>281.25</v>
+        <v>10937</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>279.0 - 281.75 DR DEMAND</t>
+          <t>10927.0 - 10999.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>310.0 - 320.0 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>11.5 / 10 SUPER COMBO</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -593,17 +593,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NEULANDLAB</t>
+          <t>FLUOROCHEM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Neuland Laboratories Ltd.</t>
+          <t>Gujarat Fluorochemicals Ltd.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -612,26 +612,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>22625</v>
+        <v>4471.8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22550.0 - 22660.0 DR DEMAND</t>
+          <t>4458.15 - 4536.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10163.48 - 10582.66 DR DEMAND</t>
+          <t>2923.16 - 3026.3 DR DEMAND</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>10.5 / 10 HIGH COMBO</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -673,17 +673,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VIJAYA</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vijaya Diagnostic Centre Ltd.</t>
+          <t>Grasim Industries Ltd.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -692,26 +692,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1438.3</v>
+        <v>3173.1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1438.01 - 1450.49 DR DEMAND</t>
+          <t>3105.33 - 3128.25 DR DEMAND</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>846.83 - 860.21 DR DEMAND</t>
+          <t>2494.13 - 2528.69 DR DEMAND</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -741,29 +741,29 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>BUY READY</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FLUOROCHEM</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gujarat Fluorochemicals Ltd.</t>
+          <t>ICICI Bank Ltd.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4533.6</v>
+        <v>1347.6</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4461.1 - 4539.0 DR DEMAND</t>
+          <t>1320.37 - 1327.11 DR DEMAND</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2925.1 - 3028.3 DR DEMAND</t>
+          <t>1457.77 - 1476.07 RD SUPPLY</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -816,34 +816,34 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>BUY READY</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>NEULANDLAB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Central Depository Services (India) Ltd.</t>
+          <t>Neuland Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -852,21 +852,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1299</v>
+        <v>22665</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1289.24 - 1299.55 DR DEMAND</t>
+          <t>22550.0 - 22660.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1730.38 - 1955.87 RD SUPPLY</t>
+          <t>10163.48 - 10582.66 DR DEMAND</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -891,34 +891,34 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>BUY READY</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consumer Products Ltd.</t>
+          <t>Chambal Fertilizers &amp; Chemicals Ltd.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -932,26 +932,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1000.1</v>
+        <v>413.9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1090.5 - 1095.0 RD SUPPLY</t>
+          <t>401.4 - 407.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>998.75 - 1006.29 DR DEMAND</t>
+          <t>404.75 - 434.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -976,34 +976,34 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>BUY READY</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Enterprise Ltd.</t>
+          <t>Bajaj Auto Ltd.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1012,28 +1012,28 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>8696.5</v>
+        <v>11500</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>8544.05 - 8590.0 DR DEMAND</t>
+          <t>11379.0 - 11424.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>6.5 B</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9501.0 - 9716.0 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>9.0 A+</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>11.0 / 10 SUPER COMBO</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1073,17 +1073,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MRPL</t>
+          <t>MRF</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mangalore Refinery &amp; Petrochemicals Ltd.</t>
+          <t>MRF Ltd.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1092,21 +1092,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>166.11</v>
+        <v>124585</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>161.2 - 162.96 DR DEMAND</t>
+          <t>123389.63 - 123833.86 DR DEMAND</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>96.88 - 103.61 DR DEMAND</t>
+          <t>101787.0 - 105025.92 DR DEMAND</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>11.0 / 10 SUPER COMBO</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1153,17 +1153,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Torrent Pharmaceuticals Ltd.</t>
+          <t>CESC Ltd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1172,21 +1172,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4812.5</v>
+        <v>141.56</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4695.1 - 4750.0 DR DEMAND</t>
+          <t>168.0 - 170.92 RD SUPPLY</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3068.54 - 3119.39 DR DEMAND</t>
+          <t>133.19 - 139.44 DR DEMAND</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1206,17 +1206,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>11.0 / 10 SUPER COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1233,17 +1233,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>LALPATHLAB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Grasim Industries Ltd.</t>
+          <t>Dr. Lal Path Labs Ltd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1252,26 +1252,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3187</v>
+        <v>1924.7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3105.33 - 3128.25 DR DEMAND</t>
+          <t>1870.0 - 1890.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2494.13 - 2528.7 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1291,12 +1291,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>10.5 / 10 HIGH COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1313,17 +1313,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Craftsman Automation Ltd.</t>
+          <t>Tata Consumer Products Ltd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1332,41 +1332,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>11040</v>
+        <v>1013.7</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10927.0 - 10999.0 DR DEMAND</t>
+          <t>1090.5 - 1095.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>7.5 A</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>998.75 - 1006.29 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>7.0 A</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>TIMKEN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Indus Towers Ltd.</t>
+          <t>Timken India Ltd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1412,21 +1412,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>375.6</v>
+        <v>3185.1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>368.7 - 372.0 DR DEMAND</t>
+          <t>3091.2 - 3126.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>427.61 - 433.1 RD SUPPLY</t>
+          <t>2177.68 - 2425.42 DR DEMAND</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1473,17 +1473,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KEC</t>
+          <t>JBMA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kec International Ltd.</t>
+          <t>JBM Auto Ltd.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1492,26 +1492,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>397.55</v>
+        <v>593.6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>389.15 - 393.2 DR DEMAND</t>
+          <t>585.0 - 586.05 DR DEMAND</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1178.75 - 1289.99 RD SUPPLY</t>
+          <t>716.95 - 764.17 RD SUPPLY</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1553,17 +1553,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>MGL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bajaj Auto Ltd.</t>
+          <t>Mahanagar Gas Ltd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1572,11 +1572,11 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>11593</v>
+        <v>1071.2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>11379.0 - 11424.0 DR DEMAND</t>
+          <t>1054.52 - 1061.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1586,17 +1586,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9501.0 - 9716.0 DR DEMAND</t>
+          <t>885.65 - 912.91 DR DEMAND</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1633,17 +1633,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MRF</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MRF Ltd.</t>
+          <t>Power Finance Corporation Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1652,26 +1652,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>125010</v>
+        <v>344.95</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>123389.63 - 123833.86 DR DEMAND</t>
+          <t>343.3 - 344.9 DR DEMAND</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>101787.0 - 105025.93 DR DEMAND</t>
+          <t>329.74 - 339.39 DR DEMAND</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1713,17 +1713,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CESC Ltd.</t>
+          <t>PB Fintech Ltd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1732,21 +1732,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>141.67</v>
+        <v>1765</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>168.0 - 170.92 RD SUPPLY</t>
+          <t>1710.1 - 1736.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>133.19 - 139.44 DR DEMAND</t>
+          <t>2108.85 - 2246.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1756,17 +1756,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1793,17 +1793,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>RITES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bank of India</t>
+          <t>RITES Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1812,11 +1812,11 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>137.81</v>
+        <v>207.93</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>134.01 - 135.12 DR DEMAND</t>
+          <t>202.92 - 204.92 DR DEMAND</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>86.59 - 88.92 DR DEMAND</t>
+          <t>217.6 - 229.47 RD SUPPLY</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1873,17 +1873,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bharat Heavy Electricals Ltd.</t>
+          <t>Amara Raja Energy &amp; Mobility Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1892,36 +1892,36 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>410.6</v>
+        <v>795.3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>402.15 - 405.0 DR DEMAND</t>
+          <t>789.12 - 791.56 DR DEMAND</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>204.46 - 207.34 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1953,17 +1953,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Canara Bank</t>
+          <t>Bajaj Finserv Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1972,26 +1972,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>123.2</v>
+        <v>1859.2</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>120.5 - 121.15 DR DEMAND</t>
+          <t>1832.1 - 1837.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>73.46 - 75.61 DR DEMAND</t>
+          <t>1991.7 - 2073.13 RD SUPPLY</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2033,17 +2033,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GALLANTT</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gallantt Ispat Ltd.</t>
+          <t>Bajaj Finance Ltd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2052,21 +2052,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>524.95</v>
+        <v>1015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>513.1 - 521.2 DR DEMAND</t>
+          <t>1001.3 - 1012.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>861.85 - 948.0 RD SUPPLY</t>
+          <t>783.09 - 796.65 DR DEMAND</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2081,12 +2081,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2113,17 +2113,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GPIL</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Godawari Power &amp; Ispat Ltd.</t>
+          <t>Computer Age Management Services Ltd.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2132,21 +2132,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>236.49</v>
+        <v>714.95</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>232.9 - 235.43 DR DEMAND</t>
+          <t>700.15 - 705.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>220.3 - 234.23 DR DEMAND</t>
+          <t>591.51 - 613.37 DR DEMAND</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2193,17 +2193,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MGL</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mahanagar Gas Ltd.</t>
+          <t>CG Power and Industrial Solutions Ltd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2212,36 +2212,36 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1080.1</v>
+        <v>880</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1054.52 - 1061.5 DR DEMAND</t>
+          <t>794.1 - 800.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>885.65 - 912.91 DR DEMAND</t>
+          <t>814.85 - 863.4 DR DEMAND</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2273,12 +2273,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>CHOICEIN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Power Finance Corporation Ltd.</t>
+          <t>Choice International Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2292,26 +2292,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>346</v>
+        <v>738</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>343.3 - 344.9 DR DEMAND</t>
+          <t>721.6 - 725.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>329.74 - 339.39 DR DEMAND</t>
+          <t>840.3 - 860.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2353,17 +2353,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>APARINDS</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Apar Industries Ltd.</t>
+          <t>Coforge Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2372,26 +2372,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>17075</v>
+        <v>1793</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>16442.91 - 16754.83 DR DEMAND</t>
+          <t>1762.2 - 1773.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>13236.05 - 14298.36 DR DEMAND</t>
+          <t>1985.3 - 2021.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2433,17 +2433,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DEVYANI</t>
+          <t>DOMS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Devyani International Ltd.</t>
+          <t>DOMS Industries Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2452,11 +2452,11 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>136.69</v>
+        <v>2121.6</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>133.75 - 135.0 DR DEMAND</t>
+          <t>2061.3 - 2085.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2466,17 +2466,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>91.55 - 94.59 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2513,17 +2513,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JYOTICNC</t>
+          <t>FIVESTAR</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jyoti CNC Automation Ltd.</t>
+          <t>Five-Star Business Finance Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2532,11 +2532,11 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>967.7</v>
+        <v>530.95</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>948.05 - 955.65 DR DEMAND</t>
+          <t>518.5 - 524.85 DR DEMAND</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>580.1 - 596.0 DR DEMAND</t>
+          <t>412.05 - 443.54 DR DEMAND</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2593,17 +2593,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>INDIAMART</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Navin Fluorine International Ltd.</t>
+          <t>Indiamart Intermesh Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2612,36 +2612,36 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>8160.5</v>
+        <v>1662.7</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>8110.0 - 8151.0 DR DEMAND</t>
+          <t>1624.1 - 1637.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4173.89 - 4245.43 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>75.41</v>
+        <v>75.2</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1703.1</v>
+        <v>1687.4</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2833,17 +2833,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PTCIL</t>
+          <t>OLAELEC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PTC Industries Ltd.</t>
+          <t>Ola Electric Mobility Ltd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2852,36 +2852,36 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>22500</v>
+        <v>36.79</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>22055.0 - 22385.0 DR DEMAND</t>
+          <t>36.05 - 36.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>11902.0 - 12721.0 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2913,12 +2913,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RAMCOCEM</t>
+          <t>PTCIL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The Ramco Cements Ltd.</t>
+          <t>PTC Industries Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2932,31 +2932,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>863.15</v>
+        <v>22670</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>856.75 - 860.55 DR DEMAND</t>
+          <t>22055.0 - 22385.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>836.02 - 868.83 DR DEMAND</t>
+          <t>11902.0 - 12721.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2993,17 +2993,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SBI Cards and Payment Services Ltd.</t>
+          <t>Torrent Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3012,11 +3012,11 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>618.1</v>
+        <v>4875</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>610.0 - 611.0 DR DEMAND</t>
+          <t>4755.5 - 4810.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3026,17 +3026,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>565.45 - 593.2 DR DEMAND</t>
+          <t>3068.54 - 3119.39 DR DEMAND</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1389.5</v>
+        <v>1390</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3153,17 +3153,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Indraprastha Gas Ltd.</t>
+          <t>Gujarat Mineral Development Corporation Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3172,11 +3172,11 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>148.77</v>
+        <v>549.15</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>147.45 - 147.94 DR DEMAND</t>
+          <t>535.05 - 543.35 DR DEMAND</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>141.74 - 145.62 DR DEMAND</t>
+          <t>736.15 - 771.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3233,17 +3233,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>GPIL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Axis Bank Ltd.</t>
+          <t>Godawari Power &amp; Ispat Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3252,26 +3252,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1241</v>
+        <v>238.39</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1372.94 - 1376.64 RD SUPPLY</t>
+          <t>232.9 - 235.43 DR DEMAND</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1208.6 - 1229.5 DR DEMAND</t>
+          <t>220.3 - 234.23 DR DEMAND</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3313,17 +3313,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>OLECTRA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bharti Airtel Ltd.</t>
+          <t>Olectra Greentech Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3332,28 +3332,28 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1835</v>
+        <v>1186.2</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1813.0 - 1814.7 DR DEMAND</t>
+          <t>1155.0 - 1168.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
+          <t>5.5 B</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>1508.5 - 1556.0 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>1527.35 - 1537.83 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>6.5 B</t>
-        </is>
-      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -3371,12 +3371,12 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3393,17 +3393,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CCL Products (I) Ltd.</t>
+          <t>Persistent Systems Ltd.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3412,36 +3412,36 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1065.5</v>
+        <v>5473</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>961.32 - 966.71 DR DEMAND</t>
+          <t>5390.5 - 5410.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
+          <t>5.5 B</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>4229.81 - 4311.53 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
           <t>8.5 A</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>1040.1 - 1050.87 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>5.0 C</t>
-        </is>
-      </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3473,17 +3473,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CROMPTON</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Crompton Greaves Consumer Electricals Ltd.</t>
+          <t>Axis Bank Ltd.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3492,11 +3492,11 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>223.4</v>
+        <v>1240</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>219.51 - 220.94 DR DEMAND</t>
+          <t>1372.94 - 1376.64 RD SUPPLY</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>214.82 - 218.82 DR DEMAND</t>
+          <t>1208.6 - 1229.5 DR DEMAND</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3553,17 +3553,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DEEPAKNTR</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Deepak Nitrite Ltd.</t>
+          <t>Bajaj Holdings &amp; Investment Ltd.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3572,31 +3572,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1590.5</v>
+        <v>11010</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1542.95 - 1564.16 DR DEMAND</t>
+          <t>10922.0 - 10990.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>8482.6 - 8638.66 DR DEMAND</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3633,17 +3633,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ENDURANCE</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Endurance Technologies Ltd.</t>
+          <t>Bharti Airtel Ltd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3652,26 +3652,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2628.4</v>
+        <v>1836</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2538.15 - 2615.93 DR DEMAND</t>
+          <t>1813.0 - 1814.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1661.59 - 1735.99 DR DEMAND</t>
+          <t>1527.35 - 1537.83 DR DEMAND</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3713,17 +3713,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mankind Pharma Ltd.</t>
+          <t>CCL Products (I) Ltd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3732,26 +3732,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2246</v>
+        <v>1062.3</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2222.0 - 2237.2 DR DEMAND</t>
+          <t>961.32 - 966.71 DR DEMAND</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1909.7 - 2005.8 DR DEMAND</t>
+          <t>1040.1 - 1050.87 DR DEMAND</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3761,17 +3761,17 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3793,12 +3793,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>CROMPTON</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PG Electroplast Ltd.</t>
+          <t>Crompton Greaves Consumer Electricals Ltd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3812,11 +3812,11 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>523.85</v>
+        <v>225.1</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>513.0 - 515.25 DR DEMAND</t>
+          <t>219.51 - 220.94 DR DEMAND</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3826,12 +3826,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>811.74 - 836.08 RD SUPPLY</t>
+          <t>214.82 - 218.82 DR DEMAND</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3873,17 +3873,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BAJAJHFL</t>
+          <t>BATAINDIA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bajaj Housing Finance Ltd.</t>
+          <t>Bata India Ltd.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3892,26 +3892,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>82.95999999999999</v>
+        <v>636.65</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>82.4 - 82.82 DR DEMAND</t>
+          <t>626.3 - 630.65 DR DEMAND</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>685.67 - 743.46 RD SUPPLY</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1937.8</v>
+        <v>1929.8</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4033,17 +4033,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ERIS</t>
+          <t>GICRE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Eris Lifesciences Ltd.</t>
+          <t>General Insurance Corporation of India</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4052,16 +4052,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1303.2</v>
+        <v>339.8</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1288.9 - 1301.0 DR DEMAND</t>
+          <t>334.14 - 335.25 DR DEMAND</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4113,17 +4113,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GICRE</t>
+          <t>J&amp;KBANK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>General Insurance Corporation of India</t>
+          <t>Jammu &amp; Kashmir Bank Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4132,11 +4132,11 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>337.75</v>
+        <v>147.28</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>334.14 - 335.25 DR DEMAND</t>
+          <t>144.0 - 144.44 DR DEMAND</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -4146,12 +4146,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>108.0 - 110.01 DR DEMAND</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4193,17 +4193,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>LALPATHLAB</t>
+          <t>MRPL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dr. Lal Path Labs Ltd.</t>
+          <t>Mangalore Refinery &amp; Petrochemicals Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4212,11 +4212,11 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1895.7</v>
+        <v>163.77</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1855.7 - 1877.5 DR DEMAND</t>
+          <t>161.2 - 162.96 DR DEMAND</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4226,17 +4226,17 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>96.88 - 103.61 DR DEMAND</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4246,12 +4246,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>87.59</v>
+        <v>87.58</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>432.45</v>
+        <v>432.8</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4433,17 +4433,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SCHAEFFLER</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Schaeffler India Ltd.</t>
+          <t>SBI Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4452,28 +4452,28 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3898.9</v>
+        <v>1766.9</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>3811.1 - 3860.2 DR DEMAND</t>
+          <t>2106.67 - 2129.04 RD SUPPLY</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
+          <t>6.0 B</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>1700.4 - 1765.7 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
           <t>4.5 C</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>3489.69 - 3548.8 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>8.5 A</t>
-        </is>
-      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4532,7 +4532,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>256</v>
+        <v>257.45</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4593,17 +4593,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AWL</t>
+          <t>BELRISE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AWL Agri Business Ltd.</t>
+          <t>Belrise Industries Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4612,16 +4612,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>181.94</v>
+        <v>229.37</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>180.27 - 181.44 DR DEMAND</t>
+          <t>225.81 - 226.91 DR DEMAND</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4673,17 +4673,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BELRISE</t>
+          <t>CONCORDBIO</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Belrise Industries Ltd.</t>
+          <t>Concord Biotech Ltd.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4692,16 +4692,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229.35</v>
+        <v>1461.1</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>225.81 - 226.91 DR DEMAND</t>
+          <t>1426.9 - 1439.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4753,17 +4753,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CENTRALBK</t>
+          <t>FACT</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Central Bank of India</t>
+          <t>Fertilisers and Chemicals Travancore Ltd.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4772,11 +4772,11 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>30.39</v>
+        <v>759.8</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>30.1 - 30.17 DR DEMAND</t>
+          <t>738.0 - 749.15 DR DEMAND</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>35.83 - 36.93 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4833,17 +4833,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CONCORDBIO</t>
+          <t>IDBI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Concord Biotech Ltd.</t>
+          <t>IDBI Bank Ltd.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>PVTBANK</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4852,11 +4852,11 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1453.8</v>
+        <v>81.89</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1426.9 - 1439.6 DR DEMAND</t>
+          <t>80.17 - 80.53 DR DEMAND</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4866,17 +4866,17 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>91.3 - 96.25 RD SUPPLY</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4913,17 +4913,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RITES Ltd.</t>
+          <t>Indraprastha Gas Ltd.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4932,11 +4932,11 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>204.92</v>
+        <v>148.67</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>202.22 - 203.29 DR DEMAND</t>
+          <t>147.45 - 147.94 DR DEMAND</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>217.6 - 229.47 RD SUPPLY</t>
+          <t>141.74 - 145.62 DR DEMAND</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4993,17 +4993,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>RRKABEL</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>R R Kabel Ltd.</t>
+          <t>Navin Fluorine International Ltd.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5012,11 +5012,11 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2397.4</v>
+        <v>8220</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2330.2 - 2378.3 DR DEMAND</t>
+          <t>8110.0 - 8151.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2942.6 - 2983.8 RD SUPPLY</t>
+          <t>4173.89 - 4245.43 DR DEMAND</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5073,12 +5073,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TECHNOE</t>
+          <t>RRKABEL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Techno Electric &amp; Engineering Company Ltd.</t>
+          <t>R R Kabel Ltd.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5092,36 +5092,36 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>971.05</v>
+        <v>2390.5</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1023.27 - 1034.04 RD SUPPLY</t>
+          <t>2330.2 - 2378.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>863.77 - 967.52 DR DEMAND</t>
+          <t>2942.6 - 2983.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5153,17 +5153,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>SOBHA</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bata India Ltd.</t>
+          <t>Sobha Ltd.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5172,26 +5172,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>630.65</v>
+        <v>1189.4</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>625.59 - 627.84 DR DEMAND</t>
+          <t>1374.0 - 1378.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>685.67 - 743.46 RD SUPPLY</t>
+          <t>1125.39 - 1182.55 DR DEMAND</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5233,17 +5233,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>TECHNOE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dixon Technologies (India) Ltd.</t>
+          <t>Techno Electric &amp; Engineering Company Ltd.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5252,26 +5252,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>13181</v>
+        <v>984.7</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>12848.0 - 12934.0 DR DEMAND</t>
+          <t>1023.27 - 1034.04 RD SUPPLY</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>14850.0 - 15000.0 RD SUPPLY</t>
+          <t>863.77 - 967.52 DR DEMAND</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5332,7 +5332,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>314.4</v>
+        <v>314.9</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1535</v>
+        <v>1545.6</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5473,17 +5473,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MEDANTA</t>
+          <t>AWL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Global Health Ltd.</t>
+          <t>AWL Agri Business Ltd.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5492,11 +5492,11 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1404.6</v>
+        <v>184.04</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1382.71 - 1393.91 DR DEMAND</t>
+          <t>180.27 - 181.44 DR DEMAND</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1480.9 - 1544.0 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5553,17 +5553,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>CREDITACC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Oracle Financial Services Software Ltd.</t>
+          <t>CreditAccess Grameen Ltd.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5572,11 +5572,11 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>11510</v>
+        <v>1370.8</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>11318.0 - 11420.0 DR DEMAND</t>
+          <t>1354.1 - 1370.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5586,22 +5586,22 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1602.0 - 1634.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5633,17 +5633,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SBFC</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SBFC Finance Ltd.</t>
+          <t>Indian Hotels Co. Ltd.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5652,11 +5652,11 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>93.66</v>
+        <v>726.65</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>91.55 - 92.77 DR DEMAND</t>
+          <t>706.05 - 713.55 DR DEMAND</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5666,17 +5666,17 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>871.1 - 888.32 RD SUPPLY</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5713,17 +5713,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tata Steel Ltd.</t>
+          <t>Oracle Financial Services Software Ltd.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5732,11 +5732,11 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>183</v>
+        <v>11620</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>182.01 - 182.63 DR DEMAND</t>
+          <t>11318.0 - 11420.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5746,22 +5746,22 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>156.83 - 164.57 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5793,17 +5793,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>VMM</t>
+          <t>SBFC</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Vishal Mega Mart Ltd.</t>
+          <t>SBFC Finance Ltd.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5812,16 +5812,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100.97</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>98.77 - 99.68 DR DEMAND</t>
+          <t>91.55 - 92.77 DR DEMAND</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5873,17 +5873,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>VMM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Ltd.</t>
+          <t>Vishal Mega Mart Ltd.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5892,36 +5892,36 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1107.5</v>
+        <v>101.24</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1094.12 - 1098.81 DR DEMAND</t>
+          <t>98.77 - 99.68 DR DEMAND</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>855.18 - 875.51 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5953,17 +5953,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>CENTRALBK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Bharat Forge Ltd.</t>
+          <t>Central Bank of India</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5972,11 +5972,11 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1885</v>
+        <v>30.4</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1830.45 - 1850.39 DR DEMAND</t>
+          <t>30.1 - 30.17 DR DEMAND</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5986,12 +5986,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1605.33 - 1669.53 DR DEMAND</t>
+          <t>35.83 - 36.93 RD SUPPLY</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6033,12 +6033,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>POLYMED</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Granules India Ltd.</t>
+          <t>Poly Medicure Ltd.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6052,11 +6052,11 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>835.6</v>
+        <v>1712.7</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>822.0 - 825.7 DR DEMAND</t>
+          <t>1647.83 - 1688.54 DR DEMAND</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>419.84 - 453.47 DR DEMAND</t>
+          <t>1297.34 - 1337.36 DR DEMAND</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6113,12 +6113,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>POLYMED</t>
+          <t>ERIS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Poly Medicure Ltd.</t>
+          <t>Eris Lifesciences Ltd.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -6132,11 +6132,11 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1704.6</v>
+        <v>1310.7</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1647.83 - 1688.54 DR DEMAND</t>
+          <t>1288.9 - 1301.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6146,17 +6146,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1297.34 - 1337.36 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>3.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>813.3</v>
+        <v>818.25</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6273,17 +6273,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NIACL</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The New India Assurance Company Ltd.</t>
+          <t>Bharat Electronics Ltd.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6292,31 +6292,31 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>184.19</v>
+        <v>395.45</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>182.41 - 185.45 DR DEMAND</t>
+          <t>411.55 - 416.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>378.32 - 397.37 DR DEMAND</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -6353,17 +6353,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Amara Raja Energy &amp; Mobility Ltd.</t>
+          <t>Indus Towers Ltd.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6372,26 +6372,26 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>791.55</v>
+        <v>381.35</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>789.12 - 791.56 DR DEMAND</t>
+          <t>368.7 - 372.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>376.63 - 395.08 DR DEMAND</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -6433,17 +6433,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>RAMCOCEM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Bajaj Finance Ltd.</t>
+          <t>The Ramco Cements Ltd.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6452,26 +6452,26 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1006.2</v>
+        <v>858.95</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1001.3 - 1012.8 DR DEMAND</t>
+          <t>856.75 - 860.55 DR DEMAND</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>783.09 - 796.65 DR DEMAND</t>
+          <t>836.02 - 868.83 DR DEMAND</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -6513,17 +6513,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>BAJAJHFL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Bharat Electronics Ltd.</t>
+          <t>Bajaj Housing Finance Ltd.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6532,26 +6532,26 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>385.75</v>
+        <v>82.7</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>411.55 - 416.0 RD SUPPLY</t>
+          <t>82.4 - 82.82 DR DEMAND</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>378.32 - 397.37 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -6593,17 +6593,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>DCMSHRIRAM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Coforge Ltd.</t>
+          <t>DCM Shriram Ltd.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6612,36 +6612,36 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1766.7</v>
+        <v>984</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1762.2 - 1773.0 DR DEMAND</t>
+          <t>981.47 - 992.13 DR DEMAND</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>1985.3 - 2021.2 RD SUPPLY</t>
+          <t>942.52 - 977.88 DR DEMAND</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -6673,17 +6673,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>SAMMAANCAP</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CG Power and Industrial Solutions Ltd.</t>
+          <t>Sammaan Capital Ltd.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -6692,26 +6692,26 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>851.55</v>
+        <v>142.22</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>794.1 - 800.0 DR DEMAND</t>
+          <t>159.2 - 161.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>814.85 - 863.4 DR DEMAND</t>
+          <t>134.75 - 144.61 DR DEMAND</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -6753,17 +6753,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PNB Housing Finance Ltd.</t>
+          <t>Dalmia Bharat Ltd.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -6772,31 +6772,31 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1134</v>
+        <v>1693.3</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1132.8 - 1142.0 DR DEMAND</t>
+          <t>1683.0 - 1730.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>723.95 - 749.2 DR DEMAND</t>
+          <t>2397.36 - 2484.34 RD SUPPLY</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -6833,12 +6833,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>HOMEFIRST</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Bajaj Holdings &amp; Investment Ltd.</t>
+          <t>Home First Finance Company India Ltd.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6848,32 +6848,32 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>EQUILIBRIUM</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>10930</v>
+        <v>1173.3</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>10922.0 - 10990.0 DR DEMAND</t>
+          <t>1151.9 - 1160.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
+          <t>2.5 C</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>1184.37 - 1233.14 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
           <t>4.0 C</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>8482.6 - 8638.66 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>6.0 B</t>
-        </is>
-      </c>
       <c r="J81" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
@@ -6891,12 +6891,12 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>4.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -6906,24 +6906,24 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CONFLICT</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BAYERCROP</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Bayer Cropscience Ltd.</t>
+          <t>Dr. Reddy's Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -6932,26 +6932,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3938.6</v>
+        <v>1175</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>3936.0 - 3960.8 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1141.16 - 1182.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -6961,22 +6961,22 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>3.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -6993,12 +6993,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DCMSHRIRAM</t>
+          <t>FIRSTCRY</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DCM Shriram Ltd.</t>
+          <t>Brainbees Solutions Ltd.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -7012,26 +7012,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>986.3</v>
+        <v>169.25</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>981.47 - 992.13 DR DEMAND</t>
+          <t>168.15 - 170.82 DR DEMAND</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>942.52 - 977.88 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>3.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -7073,45 +7073,45 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SAMMAANCAP</t>
+          <t>3MINDIA</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Sammaan Capital Ltd.</t>
+          <t>3M India Ltd.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>142.19</v>
+        <v>32530</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>159.2 - 161.0 RD SUPPLY</t>
+          <t>32710.0 - 32895.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>134.75 - 144.61 DR DEMAND</t>
+          <t>28319.86 - 29690.02 DR DEMAND</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -7131,67 +7131,67 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>USHAMART</t>
+          <t>CANFINHOME</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Usha Martin Ltd.</t>
+          <t>Can Fin Homes Ltd.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>478.85</v>
+        <v>774.4</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>477.8 - 481.3 DR DEMAND</t>
+          <t>790.0 - 791.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>274.28 - 291.22 DR DEMAND</t>
+          <t>545.13 - 563.82 DR DEMAND</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -7211,67 +7211,67 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ZFCVINDIA</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ZF Commercial Vehicle Control Systems India Ltd.</t>
+          <t>REC Ltd.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2461.5</v>
+        <v>310.5</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2446.9 - 2468.9 DR DEMAND</t>
+          <t>314.0 - 315.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2046.79 - 2067.08 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -7291,67 +7291,67 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Dalmia Bharat Ltd.</t>
+          <t>Dabur India Ltd.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1693.6</v>
+        <v>384.55</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1683.0 - 1730.6 DR DEMAND</t>
+          <t>386.85 - 390.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2397.36 - 2484.34 RD SUPPLY</t>
+          <t>518.65 - 536.39 RD SUPPLY</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -7371,34 +7371,34 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FACT</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Fertilisers and Chemicals Travancore Ltd.</t>
+          <t>Hindustan Unilever Ltd.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -7408,20 +7408,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>749</v>
+        <v>1942.2</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>738.0 - 749.15 DR DEMAND</t>
+          <t>1962.0 - 1977.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7451,67 +7451,67 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SOBHA</t>
+          <t>HONAUT</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Sobha Ltd.</t>
+          <t>Honeywell Automation India Ltd.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1181.8</v>
+        <v>33915</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1374.0 - 1378.0 RD SUPPLY</t>
+          <t>34590.0 - 34870.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1125.39 - 1182.55 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -7531,34 +7531,34 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Chambal Fertilizers &amp; Chemicals Ltd.</t>
+          <t>Nestle India Ltd.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -7568,30 +7568,30 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>409.1</v>
+        <v>1370.6</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>487.44 - 491.19 RD SUPPLY</t>
+          <t>1384.5 - 1397.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>404.75 - 434.2 DR DEMAND</t>
+          <t>1153.85 - 1169.18 DR DEMAND</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -7611,34 +7611,34 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>VTL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Indian Hotels Co. Ltd.</t>
+          <t>Vardhman Textiles Ltd.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -7648,40 +7648,40 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>713.4</v>
+        <v>561.3</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>706.05 - 713.55 DR DEMAND</t>
+          <t>571.75 - 577.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>871.1 - 888.32 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -7691,77 +7691,77 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>HOMEFIRST</t>
+          <t>BLUEDART</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Home First Finance Company India Ltd.</t>
+          <t>Blue Dart Express Ltd.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1175.9</v>
+        <v>4811.3</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1151.9 - 1160.0 DR DEMAND</t>
+          <t>4850.5 - 4868.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1184.37 - 1233.14 RD SUPPLY</t>
+          <t>5465.7 - 5775.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -7776,72 +7776,72 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>4.0 / 10 SOLID</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>CONFLICT</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FIRSTCRY</t>
+          <t>GLAXO</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Brainbees Solutions Ltd.</t>
+          <t>Glaxosmithkline Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>170.02</v>
+        <v>2799.9</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>168.15 - 170.82 DR DEMAND</t>
+          <t>2856.2 - 2878.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1849.2 - 1903.26 DR DEMAND</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7851,39 +7851,39 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>3.5 / 10 SOLID</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EIHOTEL</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EIH Ltd.</t>
+          <t>HDFC Bank Ltd.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -7892,26 +7892,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>292.1</v>
+        <v>713</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>295.75 - 307.5 RD SUPPLY</t>
+          <t>721.5 - 725.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>398.09 - 432.84 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -7953,17 +7953,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>URBANCO</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Urban Company Ltd.</t>
+          <t>HDFC Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -7972,31 +7972,31 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>164.56</v>
+        <v>557</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>166.98 - 167.8 RD SUPPLY</t>
+          <t>561.0 - 561.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>811.41 - 817.84 RD SUPPLY</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -8033,17 +8033,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Dabur India Ltd.</t>
+          <t>LIC Housing Finance Ltd.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8052,31 +8052,31 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>382</v>
+        <v>545.9</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>386.85 - 390.95 RD SUPPLY</t>
+          <t>485.45 - 490.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>518.65 - 536.39 RD SUPPLY</t>
+          <t>554.86 - 559.52 RD SUPPLY</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -8113,17 +8113,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>APARINDS</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Hindustan Unilever Ltd.</t>
+          <t>Apar Industries Ltd.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8132,11 +8132,11 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1962</v>
+        <v>17801</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>1980.0 - 1990.8 RD SUPPLY</t>
+          <t>18137.03 - 18401.11 RD SUPPLY</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -8146,17 +8146,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>13236.05 - 14298.36 DR DEMAND</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -8193,17 +8193,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>EMAMILTD</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Exide Industries Ltd.</t>
+          <t>Emami Ltd.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8212,41 +8212,41 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>415.5</v>
+        <v>376.1</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>420.85 - 424.0 RD SUPPLY</t>
+          <t>376.65 - 379.35 RD SUPPLY</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>444.5 - 477.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -8273,17 +8273,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>LLOYDSME</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Lloyds Metals And Energy Ltd.</t>
+          <t>Titan Company Ltd.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -8292,21 +8292,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1812.3</v>
+        <v>4841</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1848.7 - 1859.4 RD SUPPLY</t>
+          <t>4908.5 - 4921.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1042.28 - 1072.36 DR DEMAND</t>
+          <t>3949.84 - 4061.57 DR DEMAND</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -8353,17 +8353,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EMAMILTD</t>
+          <t>CANHLIFE</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Emami Ltd.</t>
+          <t>Canara HSBC Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8372,36 +8372,36 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>369.3</v>
+        <v>155.36</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>376.65 - 379.35 RD SUPPLY</t>
+          <t>158.5 - 161.05 RD SUPPLY</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>444.5 - 477.0 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -8433,17 +8433,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Indegene Ltd.</t>
+          <t>Radico Khaitan Ltd</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -8452,26 +8452,26 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>573.2</v>
+        <v>4380</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>581.8 - 584.85 RD SUPPLY</t>
+          <t>4460.0 - 4485.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>412.19 - 432.7 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -8532,7 +8532,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2206.2</v>
+        <v>2207.4</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8593,17 +8593,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Jubilant Foodworks Ltd.</t>
+          <t>IDFC First Bank Ltd.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -8612,11 +8612,11 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>471</v>
+        <v>86.33</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>408.55 - 410.0 DR DEMAND</t>
+          <t>87.81 - 88.1 RD SUPPLY</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>477.24 - 497.34 RD SUPPLY</t>
+          <t>57.91 - 58.68 DR DEMAND</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -8673,17 +8673,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Varun Beverages Ltd.</t>
+          <t>Exide Industries Ltd.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -8692,36 +8692,36 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>410.4</v>
+        <v>418.6</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>415.0 - 416.95 RD SUPPLY</t>
+          <t>420.85 - 424.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>520.87 - 531.92 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -8753,17 +8753,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ACMESOLAR</t>
+          <t>LGEINDIA</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ACME Solar Holdings Ltd.</t>
+          <t>LG Electronics India Ltd.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -8772,11 +8772,11 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>418</v>
+        <v>1652.9</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>422.8 - 430.5 RD SUPPLY</t>
+          <t>1672.2 - 1680.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -8833,17 +8833,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CANHLIFE</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Canara HSBC Life Insurance Company Ltd.</t>
+          <t>Punjab National Bank</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -8852,26 +8852,26 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>153.92</v>
+        <v>116.47</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>154.16 - 154.71 RD SUPPLY</t>
+          <t>117.95 - 118.25 RD SUPPLY</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>80.71 - 82.53 DR DEMAND</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>4.5 / 10 SUPPLY</t>
+          <t>3.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -8913,17 +8913,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BALRAMCHIN</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Ltd.</t>
+          <t>City Union Bank Ltd.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>PVTBANK</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -8932,26 +8932,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>682.6</v>
+        <v>231.82</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>695.95 - 738.95 RD SUPPLY</t>
+          <t>235.93 - 243.1 RD SUPPLY</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>415.9 - 440.91 DR DEMAND</t>
+          <t>177.59 - 189.81 DR DEMAND</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -8961,7 +8961,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🔴 4 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>3.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -8993,17 +8993,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>RAINBOW</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Emcure Pharmaceuticals Ltd.</t>
+          <t>Rainbow Childrens Medicare Ltd.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9012,26 +9012,26 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1931.9</v>
+        <v>1473.4</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>1834.83 - 1851.1 DR DEMAND</t>
+          <t>1478.5 - 1485.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>1962.18 - 2044.02 RD SUPPLY</t>
+          <t>1550.0 - 1610.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -9041,12 +9041,12 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>2.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -9073,12 +9073,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>RAINBOW</t>
+          <t>CAPLIPOINT</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Rainbow Childrens Medicare Ltd.</t>
+          <t>Caplin Point Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -9092,11 +9092,11 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1457.2</v>
+        <v>2596.6</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>1465.0 - 1471.0 RD SUPPLY</t>
+          <t>1703.23 - 1716.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>1550.0 - 1610.0 RD SUPPLY</t>
+          <t>2503.19 - 2628.59 RD SUPPLY</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -9136,34 +9136,34 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TATAINVEST</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Punjab National Bank</t>
+          <t>Tata Investment Corporation Ltd.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9172,26 +9172,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>116.8</v>
+        <v>719.3</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>117.95 - 118.25 RD SUPPLY</t>
+          <t>716.11 - 737.89 RD SUPPLY</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>80.71 - 82.53 DR DEMAND</t>
+          <t>655.32 - 737.89 RD SUPPLY</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🔴 6 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -9216,34 +9216,34 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>3.5 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>EIHOTEL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Castrol India Ltd.</t>
+          <t>EIH Ltd.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9252,36 +9252,36 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>188.84</v>
+        <v>299.9</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>189.0 - 190.45 RD SUPPLY</t>
+          <t>295.75 - 307.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>144.37 - 156.26 DR DEMAND</t>
+          <t>398.09 - 432.84 RD SUPPLY</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -9296,29 +9296,29 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>3.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PVR INOX Ltd.</t>
+          <t>Jubilant Foodworks Ltd.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -9332,26 +9332,26 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1254.6</v>
+        <v>480.2</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>1255.3 - 1267.5 RD SUPPLY</t>
+          <t>408.55 - 410.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>907.4 - 918.6 DR DEMAND</t>
+          <t>477.24 - 497.34 RD SUPPLY</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -9376,34 +9376,34 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>3.0 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FIVESTAR</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Five-Star Business Finance Ltd.</t>
+          <t>Kajaria Ceramics Ltd.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -9412,11 +9412,11 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>549.4</v>
+        <v>1217.2</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>550.2 - 552.95 RD SUPPLY</t>
+          <t>1060.5 - 1072.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>412.05 - 443.54 DR DEMAND</t>
+          <t>1187.65 - 1246.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -9456,34 +9456,34 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2.5 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CAPLIPOINT</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Caplin Point Laboratories Ltd.</t>
+          <t>Varun Beverages Ltd.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -9492,11 +9492,11 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2583</v>
+        <v>415.45</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>1703.23 - 1716.1 DR DEMAND</t>
+          <t>415.0 - 416.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -9506,22 +9506,22 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2503.19 - 2628.59 RD SUPPLY</t>
+          <t>520.87 - 531.92 RD SUPPLY</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -9553,17 +9553,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Radico Khaitan Ltd</t>
+          <t>Phoenix Mills Ltd.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -9572,36 +9572,36 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4466</v>
+        <v>1872.2</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>4460.0 - 4485.0 RD SUPPLY</t>
+          <t>2090.43 - 2097.12 RD SUPPLY</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1851.05 - 1990.36 RD SUPPLY</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>3.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -9633,12 +9633,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AEGISLOG</t>
+          <t>AEGISVOPAK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Aegis Logistics Ltd.</t>
+          <t>Aegis Vopak Terminals Ltd.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -9652,16 +9652,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1381.2</v>
+        <v>310.7</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>1365.3 - 1385.0 RD SUPPLY</t>
+          <t>303.3 - 311.49 RD SUPPLY</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -9681,12 +9681,12 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>3.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -9705,326 +9705,6 @@
         </is>
       </c>
       <c r="P116" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>KAJARIACER</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Kajaria Ceramics Ltd.</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>CONSUMPTION</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-      <c r="E117" t="n">
-        <v>1215.9</v>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>1060.5 - 1072.6 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>2.5 C</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>1187.65 - 1246.8 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>5.0 C</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>1W UP • 20 EMA BULLISH</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>🟡 1 TEST (TESTED)</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>NORMAL VOL</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>+0.0 PTS</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>5.0 / 10 SUPPLY</t>
-        </is>
-      </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>SUPPLY TEST</t>
-        </is>
-      </c>
-      <c r="P117" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>PCBL</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>PCBL Chemical Ltd.</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-      <c r="E118" t="n">
-        <v>317.1</v>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>308.15 - 309.8 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>6.0 B</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>305.14 - 326.1 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>5.0 C</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>1W UP • 20 EMA BULLISH</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>🟡 1 TEST (TESTED)</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>NORMAL VOL</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>+0.0 PTS</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>5.0 / 10 SUPPLY</t>
-        </is>
-      </c>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>SUPPLY TEST</t>
-        </is>
-      </c>
-      <c r="P118" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>TATAINVEST</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Tata Investment Corporation Ltd.</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>FINSERVICE</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-      <c r="E119" t="n">
-        <v>681.95</v>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>716.11 - 737.89 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>3.5 C</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>655.32 - 737.89 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>4.0 C</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>1W UP • 20 EMA BULLISH</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>🟡 1 TEST (TESTED)</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>+0.0 PTS</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>4.0 / 10 SUPPLY</t>
-        </is>
-      </c>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>SUPPLY TEST</t>
-        </is>
-      </c>
-      <c r="P119" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Phoenix Mills Ltd.</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>REALTY</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-      <c r="E120" t="n">
-        <v>1855</v>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2090.43 - 2097.12 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>6.0 B</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>1851.05 - 1990.36 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>2.5 C</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>🔴 2 TESTS (WEAK)</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>NORMAL VOL</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>+0.0 PTS</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>3.5 / 10 SUPPLY</t>
-        </is>
-      </c>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>SUPPLY TEST</t>
-        </is>
-      </c>
-      <c r="P120" t="inlineStr">
         <is>
           <t>IN</t>
         </is>

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P116"/>
+  <dimension ref="A1:P108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,17 +513,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>BDL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Craftsman Automation Ltd.</t>
+          <t>Bharat Dynamics Ltd.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -532,36 +532,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10937</v>
+        <v>1196.6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10927.0 - 10999.0 DR DEMAND</t>
+          <t>1086.0 - 1096.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>4.0 C</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1155.2 - 1204.6 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>7.0 A</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -593,17 +593,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FLUOROCHEM</t>
+          <t>TIMKEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Gujarat Fluorochemicals Ltd.</t>
+          <t>Timken India Ltd.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -612,11 +612,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4471.8</v>
+        <v>3124.2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4458.15 - 4536.0 DR DEMAND</t>
+          <t>3091.2 - 3126.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -626,17 +626,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2923.16 - 3026.3 DR DEMAND</t>
+          <t>2177.68 - 2425.42 DR DEMAND</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -673,17 +673,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Grasim Industries Ltd.</t>
+          <t>Torrent Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -692,26 +692,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3173.1</v>
+        <v>4840</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3105.33 - 3128.25 DR DEMAND</t>
+          <t>4695.1 - 4750.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2494.13 - 2528.69 DR DEMAND</t>
+          <t>3068.54 - 3119.39 DR DEMAND</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -731,12 +731,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>10.5 / 10 HIGH COMBO</t>
+          <t>11.0 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1347.6</v>
+        <v>1338.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -833,17 +833,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NEULANDLAB</t>
+          <t>TMPV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Neuland Laboratories Ltd.</t>
+          <t>Tata Motors Passenger Vehicles Ltd.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -852,11 +852,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>22665</v>
+        <v>303.8</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22550.0 - 22660.0 DR DEMAND</t>
+          <t>299.3 - 301.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -866,17 +866,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10163.48 - 10582.66 DR DEMAND</t>
+          <t>391.75 - 404.64 RD SUPPLY</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>413.9</v>
+        <v>414.9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -993,17 +993,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bajaj Auto Ltd.</t>
+          <t>Indus Towers Ltd.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1012,31 +1012,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>11500</v>
+        <v>375.9</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>11379.0 - 11424.0 DR DEMAND</t>
+          <t>368.7 - 372.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>9.0 A+</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>427.61 - 433.1 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>6.5 B</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>9501.0 - 9716.0 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>9.0 A+</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1073,17 +1073,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MRF</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MRF Ltd.</t>
+          <t>Cholamandalam Investment and Finance Company Ltd.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1092,31 +1092,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>124585</v>
+        <v>1800</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>123389.63 - 123833.86 DR DEMAND</t>
+          <t>1756.3 - 1765.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>101787.0 - 105025.92 DR DEMAND</t>
+          <t>1298.89 - 1354.17 DR DEMAND</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1153,17 +1153,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>CPPLUS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CESC Ltd.</t>
+          <t>Aditya Infotech Ltd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1172,31 +1172,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>141.56</v>
+        <v>3355.1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>168.0 - 170.92 RD SUPPLY</t>
+          <t>3251.0 - 3303.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>133.19 - 139.44 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1233,17 +1233,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LALPATHLAB</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dr. Lal Path Labs Ltd.</t>
+          <t>CESC Ltd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1252,31 +1252,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1924.7</v>
+        <v>141.53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1870.0 - 1890.6 DR DEMAND</t>
+          <t>168.0 - 170.92 RD SUPPLY</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>7.5 A</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>133.19 - 139.44 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>7.0 A</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1313,17 +1313,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consumer Products Ltd.</t>
+          <t>Craftsman Automation Ltd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1332,41 +1332,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1013.7</v>
+        <v>11138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1090.5 - 1095.0 RD SUPPLY</t>
+          <t>10927.0 - 10999.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>998.75 - 1006.29 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TIMKEN</t>
+          <t>MGL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Timken India Ltd.</t>
+          <t>Mahanagar Gas Ltd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1412,21 +1412,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3185.1</v>
+        <v>1081.7</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3091.2 - 3126.6 DR DEMAND</t>
+          <t>1054.52 - 1061.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2177.68 - 2425.42 DR DEMAND</t>
+          <t>885.65 - 912.91 DR DEMAND</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1473,17 +1473,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JBMA</t>
+          <t>NIACL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JBM Auto Ltd.</t>
+          <t>The New India Assurance Company Ltd.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1492,36 +1492,36 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>593.6</v>
+        <v>187.66</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>585.0 - 586.05 DR DEMAND</t>
+          <t>182.41 - 185.45 DR DEMAND</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>716.95 - 764.17 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1553,17 +1553,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MGL</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mahanagar Gas Ltd.</t>
+          <t>PB Fintech Ltd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1572,36 +1572,36 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1071.2</v>
+        <v>1743</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1054.52 - 1061.5 DR DEMAND</t>
+          <t>1710.1 - 1736.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>885.65 - 912.91 DR DEMAND</t>
+          <t>2108.85 - 2246.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1633,17 +1633,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>INDIAMART</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Power Finance Corporation Ltd.</t>
+          <t>Indiamart Intermesh Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1652,26 +1652,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>344.95</v>
+        <v>1646.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>343.3 - 344.9 DR DEMAND</t>
+          <t>1624.1 - 1637.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>329.74 - 339.39 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1681,22 +1681,22 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1713,17 +1713,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>OLAELEC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PB Fintech Ltd.</t>
+          <t>Ola Electric Mobility Ltd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1732,41 +1732,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1765</v>
+        <v>36.39</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1710.1 - 1736.0 DR DEMAND</t>
+          <t>36.05 - 36.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2108.85 - 2246.9 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1793,12 +1793,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>PTCIL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RITES Ltd.</t>
+          <t>PTC Industries Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1812,36 +1812,36 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>207.93</v>
+        <v>22805</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>202.92 - 204.92 DR DEMAND</t>
+          <t>22055.0 - 22385.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>217.6 - 229.47 RD SUPPLY</t>
+          <t>11902.0 - 12721.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1873,17 +1873,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Amara Raja Energy &amp; Mobility Ltd.</t>
+          <t>United Spirits Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1892,11 +1892,11 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>795.3</v>
+        <v>1371</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>789.12 - 791.56 DR DEMAND</t>
+          <t>1368.1 - 1370.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1595.35 - 1664.74 RD SUPPLY</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1953,17 +1953,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>RAMCOCEM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bajaj Finserv Ltd.</t>
+          <t>The Ramco Cements Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1972,26 +1972,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1859.2</v>
+        <v>869.75</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1832.1 - 1837.0 DR DEMAND</t>
+          <t>856.75 - 860.55 DR DEMAND</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1991.7 - 2073.13 RD SUPPLY</t>
+          <t>836.02 - 868.83 DR DEMAND</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2033,17 +2033,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bajaj Finance Ltd.</t>
+          <t>CCL Products (I) Ltd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2052,26 +2052,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1015</v>
+        <v>1065.6</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1001.3 - 1012.8 DR DEMAND</t>
+          <t>961.32 - 966.71 DR DEMAND</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>783.09 - 796.65 DR DEMAND</t>
+          <t>1040.1 - 1050.87 DR DEMAND</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2113,17 +2113,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>DEEPAKNTR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Computer Age Management Services Ltd.</t>
+          <t>Deepak Nitrite Ltd.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2132,26 +2132,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>714.95</v>
+        <v>1586.3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>700.15 - 705.7 DR DEMAND</t>
+          <t>1542.95 - 1564.16 DR DEMAND</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>591.51 - 613.37 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2193,17 +2193,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>SWIGGY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CG Power and Industrial Solutions Ltd.</t>
+          <t>Swiggy Ltd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2212,36 +2212,36 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>880</v>
+        <v>273.05</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>794.1 - 800.0 DR DEMAND</t>
+          <t>269.45 - 270.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>814.85 - 863.4 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2273,17 +2273,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CHOICEIN</t>
+          <t>BATAINDIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Choice International Ltd.</t>
+          <t>Bata India Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2292,26 +2292,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>738</v>
+        <v>638.3</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>721.6 - 725.5 DR DEMAND</t>
+          <t>626.3 - 630.65 DR DEMAND</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>840.3 - 860.5 RD SUPPLY</t>
+          <t>685.67 - 743.46 RD SUPPLY</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2326,17 +2326,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2353,17 +2353,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>DCMSHRIRAM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Coforge Ltd.</t>
+          <t>DCM Shriram Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2372,36 +2372,36 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1793</v>
+        <v>995</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1762.2 - 1773.0 DR DEMAND</t>
+          <t>981.47 - 992.13 DR DEMAND</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1985.3 - 2021.2 RD SUPPLY</t>
+          <t>942.52 - 977.88 DR DEMAND</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 5 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2433,17 +2433,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DOMS</t>
+          <t>ERIS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DOMS Industries Ltd.</t>
+          <t>Eris Lifesciences Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2452,16 +2452,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2121.6</v>
+        <v>1321.3</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2061.3 - 2085.2 DR DEMAND</t>
+          <t>1288.9 - 1301.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2481,22 +2481,22 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2513,17 +2513,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FIVESTAR</t>
+          <t>J&amp;KBANK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Five-Star Business Finance Ltd.</t>
+          <t>Jammu &amp; Kashmir Bank Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2532,41 +2532,41 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>530.95</v>
+        <v>146.58</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>518.5 - 524.85 DR DEMAND</t>
+          <t>144.0 - 144.44 DR DEMAND</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>412.05 - 443.54 DR DEMAND</t>
+          <t>108.0 - 110.01 DR DEMAND</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2593,17 +2593,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>INDIAMART</t>
+          <t>MRF</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Indiamart Intermesh Ltd.</t>
+          <t>MRF Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2612,26 +2612,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1662.7</v>
+        <v>125670</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1624.1 - 1637.7 DR DEMAND</t>
+          <t>123389.63 - 123833.86 DR DEMAND</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>101786.99 - 105025.93 DR DEMAND</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2641,22 +2641,22 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2673,17 +2673,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>MRPL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NHPC Ltd.</t>
+          <t>Mangalore Refinery &amp; Petrochemicals Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2692,28 +2692,28 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>75.2</v>
+        <v>165.38</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>74.3 - 74.82 DR DEMAND</t>
+          <t>161.2 - 162.96 DR DEMAND</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>4.5 C</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>96.88 - 103.61 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>67.83 - 70.98 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>6.0 B</t>
-        </is>
-      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2753,17 +2753,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nuvama Wealth Management Ltd.</t>
+          <t>Amara Raja Energy &amp; Mobility Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2772,16 +2772,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1687.4</v>
+        <v>796</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1644.4 - 1670.1 DR DEMAND</t>
+          <t>789.12 - 791.56 DR DEMAND</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2833,17 +2833,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>OLAELEC</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ola Electric Mobility Ltd.</t>
+          <t>Dalmia Bharat Ltd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2852,28 +2852,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>36.79</v>
+        <v>1761.4</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>36.05 - 36.2 DR DEMAND</t>
+          <t>1683.0 - 1730.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>4.0 C</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2397.36 - 2484.34 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2913,17 +2913,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PTCIL</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PTC Industries Ltd.</t>
+          <t>Indraprastha Gas Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2932,31 +2932,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>22670</v>
+        <v>148.56</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>22055.0 - 22385.0 DR DEMAND</t>
+          <t>147.45 - 147.94 DR DEMAND</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>11902.0 - 12721.0 DR DEMAND</t>
+          <t>141.74 - 145.62 DR DEMAND</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2993,17 +2993,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Torrent Pharmaceuticals Ltd.</t>
+          <t>Power Finance Corporation Ltd.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3012,11 +3012,11 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4875</v>
+        <v>342.55</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4755.5 - 4810.0 DR DEMAND</t>
+          <t>431.25 - 433.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3026,22 +3026,22 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3068.54 - 3119.39 DR DEMAND</t>
+          <t>329.74 - 339.39 DR DEMAND</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3073,17 +3073,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>United Spirits Ltd.</t>
+          <t>Dixon Technologies (India) Ltd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3092,26 +3092,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1390</v>
+        <v>13005</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1368.1 - 1370.0 DR DEMAND</t>
+          <t>12848.0 - 12934.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1595.35 - 1664.74 RD SUPPLY</t>
+          <t>14850.0 - 15000.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3153,17 +3153,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>CREDITACC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Gujarat Mineral Development Corporation Ltd.</t>
+          <t>CreditAccess Grameen Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3172,26 +3172,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>549.15</v>
+        <v>1387.6</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>535.05 - 543.35 DR DEMAND</t>
+          <t>1354.1 - 1370.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>736.15 - 771.9 RD SUPPLY</t>
+          <t>1602.0 - 1634.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3233,17 +3233,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GPIL</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Godawari Power &amp; Ispat Ltd.</t>
+          <t>Tata Steel Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3252,11 +3252,11 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>238.39</v>
+        <v>185.54</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>232.9 - 235.43 DR DEMAND</t>
+          <t>182.01 - 182.63 DR DEMAND</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>220.3 - 234.23 DR DEMAND</t>
+          <t>156.83 - 164.57 DR DEMAND</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🔴 4 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3313,17 +3313,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>OLECTRA</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Olectra Greentech Ltd.</t>
+          <t>Torrent Power Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3332,26 +3332,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1186.2</v>
+        <v>1258.8</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1155.0 - 1168.0 DR DEMAND</t>
+          <t>1518.74 - 1522.83 RD SUPPLY</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1508.5 - 1556.0 RD SUPPLY</t>
+          <t>1186.52 - 1241.27 DR DEMAND</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3393,17 +3393,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>NEULANDLAB</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Persistent Systems Ltd.</t>
+          <t>Neuland Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3412,26 +3412,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5473</v>
+        <v>22840</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>5390.5 - 5410.0 DR DEMAND</t>
+          <t>22419.0 - 22510.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4229.81 - 4311.53 DR DEMAND</t>
+          <t>10163.48 - 10582.66 DR DEMAND</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3473,17 +3473,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Axis Bank Ltd.</t>
+          <t>Dr. Reddy's Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3492,26 +3492,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1240</v>
+        <v>1185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1372.94 - 1376.64 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1208.6 - 1229.5 DR DEMAND</t>
+          <t>1141.16 - 1182.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3521,22 +3521,22 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>3.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3553,17 +3553,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>FIRSTCRY</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bajaj Holdings &amp; Investment Ltd.</t>
+          <t>Brainbees Solutions Ltd.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3572,36 +3572,36 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>11010</v>
+        <v>172.15</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>10922.0 - 10990.0 DR DEMAND</t>
+          <t>168.15 - 170.82 DR DEMAND</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>8482.6 - 8638.66 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>3.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3633,17 +3633,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>ANURAS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bharti Airtel Ltd.</t>
+          <t>Anupam Rasayan India Ltd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3652,21 +3652,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1836</v>
+        <v>1207.7</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1813.0 - 1814.7 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1527.35 - 1537.83 DR DEMAND</t>
+          <t>1192.3 - 1207.8 DR DEMAND</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3691,39 +3691,39 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>GPIL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CCL Products (I) Ltd.</t>
+          <t>Godawari Power &amp; Ispat Ltd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3732,26 +3732,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1062.3</v>
+        <v>233.47</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>961.32 - 966.71 DR DEMAND</t>
+          <t>232.9 - 235.43 DR DEMAND</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1040.1 - 1050.87 DR DEMAND</t>
+          <t>220.3 - 234.23 DR DEMAND</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CROMPTON</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Crompton Greaves Consumer Electricals Ltd.</t>
+          <t>NATCO Pharma Ltd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3812,26 +3812,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>225.1</v>
+        <v>813.4</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>219.51 - 220.94 DR DEMAND</t>
+          <t>950.09 - 963.22 RD SUPPLY</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>214.82 - 218.82 DR DEMAND</t>
+          <t>803.32 - 821.11 DR DEMAND</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3856,34 +3856,34 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bata India Ltd.</t>
+          <t>Bajaj Auto Ltd.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3892,36 +3892,36 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>636.65</v>
+        <v>11414</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>626.3 - 630.65 DR DEMAND</t>
+          <t>11379.0 - 11424.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>685.67 - 743.46 RD SUPPLY</t>
+          <t>9501.0 - 9716.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3931,67 +3931,67 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>COROMANDEL</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Coromandel International Ltd.</t>
+          <t>Bharat Electronics Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>EQUILIBRIUM</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1929.8</v>
+        <v>393.3</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1898.45 - 1912.04 DR DEMAND</t>
+          <t>397.4 - 399.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1704.84 - 1751.89 DR DEMAND</t>
+          <t>378.32 - 397.37 DR DEMAND</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4011,34 +4011,34 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>CONFLICT</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GICRE</t>
+          <t>SAMMAANCAP</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>General Insurance Corporation of India</t>
+          <t>Sammaan Capital Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4052,28 +4052,28 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>339.8</v>
+        <v>143.92</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>334.14 - 335.25 DR DEMAND</t>
+          <t>159.2 - 161.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
+          <t>6.0 B</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>134.75 - 144.61 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
           <t>4.5 C</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -4101,29 +4101,29 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>J&amp;KBANK</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir Bank Ltd.</t>
+          <t>SBI Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4132,28 +4132,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>147.28</v>
+        <v>1731</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>144.0 - 144.44 DR DEMAND</t>
+          <t>2106.67 - 2129.04 RD SUPPLY</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
+          <t>6.0 B</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>1700.4 - 1765.7 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
           <t>4.5 C</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>108.0 - 110.01 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>7.0 A</t>
-        </is>
-      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -4181,29 +4181,29 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MRPL</t>
+          <t>SBFC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mangalore Refinery &amp; Petrochemicals Ltd.</t>
+          <t>SBFC Finance Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4212,26 +4212,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>163.77</v>
+        <v>92.36</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>161.2 - 162.96 DR DEMAND</t>
+          <t>91.55 - 92.77 DR DEMAND</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>96.88 - 103.61 DR DEMAND</t>
+          <t>98.82 - 104.39 RD SUPPLY</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4256,29 +4256,29 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NTPCGREEN</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NTPC Green Energy Ltd.</t>
+          <t>NTPC Ltd.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4288,25 +4288,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>87.58</v>
+        <v>323.65</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>85.31 - 85.89 DR DEMAND</t>
+          <t>329.8 - 331.3 RD SUPPLY</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>109.85 - 119.95 RD SUPPLY</t>
+          <t>394.88 - 409.97 RD SUPPLY</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4331,17 +4331,17 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4353,12 +4353,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>POONAWALLA</t>
+          <t>AIIL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Poonawalla Fincorp Ltd.</t>
+          <t>Authum Investment &amp; Infrastructure Ltd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4368,40 +4368,40 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>432.8</v>
+        <v>559</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>425.0 - 428.45 DR DEMAND</t>
+          <t>568.95 - 579.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>370.05 - 382.85 DR DEMAND</t>
+          <t>629.8 - 683.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4411,17 +4411,17 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -4433,12 +4433,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>CANFINHOME</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SBI Life Insurance Company Ltd.</t>
+          <t>Can Fin Homes Ltd.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4448,32 +4448,32 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1766.9</v>
+        <v>778.5</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2106.67 - 2129.04 RD SUPPLY</t>
+          <t>790.0 - 791.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
+          <t>7.5 A</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>545.13 - 563.82 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>1700.4 - 1765.7 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>4.5 C</t>
-        </is>
-      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4491,17 +4491,17 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -4513,45 +4513,45 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>INOXWIND</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Vedanta Ltd.</t>
+          <t>Inox Wind Ltd.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>257.45</v>
+        <v>76.8</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>249.7 - 253.05 DR DEMAND</t>
+          <t>78.13 - 78.59 RD SUPPLY</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>155.13 - 159.3 RD SUPPLY</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4571,17 +4571,17 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -4593,55 +4593,55 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BELRISE</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Belrise Industries Ltd.</t>
+          <t>Marico Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229.37</v>
+        <v>803.9</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>225.81 - 226.91 DR DEMAND</t>
+          <t>820.05 - 822.45 RD SUPPLY</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>705.08 - 721.7 DR DEMAND</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4651,17 +4651,17 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -4673,75 +4673,75 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CONCORDBIO</t>
+          <t>NTPCGREEN</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Concord Biotech Ltd.</t>
+          <t>NTPC Green Energy Ltd.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1461.1</v>
+        <v>88.55</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1426.9 - 1439.6 DR DEMAND</t>
+          <t>89.39 - 89.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>109.85 - 119.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -4753,12 +4753,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FACT</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fertilisers and Chemicals Travancore Ltd.</t>
+          <t>Tata Consumer Products Ltd.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4768,30 +4768,30 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>759.8</v>
+        <v>996</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>738.0 - 749.15 DR DEMAND</t>
+          <t>1016.2 - 1020.3 RD SUPPLY</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>869.05 - 898.68 DR DEMAND</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4801,27 +4801,27 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -4833,45 +4833,45 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>IDBI</t>
+          <t>BAJAJHFL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IDBI Bank Ltd.</t>
+          <t>Bajaj Housing Finance Ltd.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PVTBANK</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>81.89</v>
+        <v>85.58</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>80.17 - 80.53 DR DEMAND</t>
+          <t>85.71 - 85.79 RD SUPPLY</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>91.3 - 96.25 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4881,27 +4881,27 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -4913,45 +4913,45 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>BIKAJI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Indraprastha Gas Ltd.</t>
+          <t>Bikaji Foods International Ltd.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>148.67</v>
+        <v>580.25</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>147.45 - 147.94 DR DEMAND</t>
+          <t>583.7 - 590.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>141.74 - 145.62 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4971,17 +4971,17 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -4993,55 +4993,55 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Navin Fluorine International Ltd.</t>
+          <t>GMR Airports Ltd.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>8220</v>
+        <v>99.3</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>8110.0 - 8151.0 DR DEMAND</t>
+          <t>100.44 - 100.66 RD SUPPLY</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4173.89 - 4245.43 DR DEMAND</t>
+          <t>112.74 - 115.64 RD SUPPLY</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5073,55 +5073,55 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>RRKABEL</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>R R Kabel Ltd.</t>
+          <t>Hindustan Unilever Ltd.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2390.5</v>
+        <v>1932</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2330.2 - 2378.3 DR DEMAND</t>
+          <t>1962.0 - 1977.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2942.6 - 2983.8 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5131,17 +5131,17 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5153,45 +5153,45 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SOBHA</t>
+          <t>LEMONTREE</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sobha Ltd.</t>
+          <t>Lemon Tree Hotels Ltd.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1189.4</v>
+        <v>106.47</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1374.0 - 1378.0 RD SUPPLY</t>
+          <t>108.53 - 108.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1125.39 - 1182.55 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5211,17 +5211,17 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5233,45 +5233,45 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TECHNOE</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Techno Electric &amp; Engineering Company Ltd.</t>
+          <t>Mahindra &amp; Mahindra Ltd.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>984.7</v>
+        <v>3052</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1023.27 - 1034.04 RD SUPPLY</t>
+          <t>3082.0 - 3127.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>863.77 - 967.52 DR DEMAND</t>
+          <t>3465.0 - 3534.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5291,17 +5291,17 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -5313,45 +5313,45 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>IGIL</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>International Gemological Institute Ltd.</t>
+          <t>Maruti Suzuki India Ltd.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>314.9</v>
+        <v>12103</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>309.47 - 310.95 DR DEMAND</t>
+          <t>12350.0 - 12458.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>14709.27 - 15305.29 RD SUPPLY</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5361,27 +5361,27 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -5393,45 +5393,45 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AFFLE</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Affle 3i Ltd.</t>
+          <t>Sun Pharmaceutical Industries Ltd.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1545.6</v>
+        <v>1837.3</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1489.2 - 1519.2 DR DEMAND</t>
+          <t>1867.3 - 1877.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1251.3 - 1335.3 DR DEMAND</t>
+          <t>1569.37 - 1580.86 DR DEMAND</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5441,27 +5441,27 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -5473,35 +5473,35 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWL</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AWL Agri Business Ltd.</t>
+          <t>Alkem Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>184.04</v>
+        <v>5466.5</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>180.27 - 181.44 DR DEMAND</t>
+          <t>5475.0 - 5510.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5516,32 +5516,32 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -5553,55 +5553,55 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CREDITACC</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CreditAccess Grameen Ltd.</t>
+          <t>Bharat Heavy Electricals Ltd.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1370.8</v>
+        <v>439.9</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1354.1 - 1370.8 DR DEMAND</t>
+          <t>445.0 - 446.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1602.0 - 1634.0 RD SUPPLY</t>
+          <t>204.46 - 207.34 DR DEMAND</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5611,17 +5611,17 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -5633,75 +5633,75 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>CHOICEIN</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Indian Hotels Co. Ltd.</t>
+          <t>Choice International Ltd.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>726.65</v>
+        <v>763.85</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>706.05 - 713.55 DR DEMAND</t>
+          <t>770.4 - 775.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>871.1 - 888.32 RD SUPPLY</t>
+          <t>840.3 - 860.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -5713,35 +5713,35 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>HDBFS</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Oracle Financial Services Software Ltd.</t>
+          <t>HDB Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>11620</v>
+        <v>698.4</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>11318.0 - 11420.0 DR DEMAND</t>
+          <t>700.0 - 701.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5771,17 +5771,17 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -5793,12 +5793,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SBFC</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SBFC Finance Ltd.</t>
+          <t>HDFC Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5808,30 +5808,30 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>93.31999999999999</v>
+        <v>550.95</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>91.55 - 92.77 DR DEMAND</t>
+          <t>561.0 - 561.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>811.41 - 817.84 RD SUPPLY</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5851,17 +5851,17 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -5873,55 +5873,55 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>VMM</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Vishal Mega Mart Ltd.</t>
+          <t>LIC Housing Finance Ltd.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>101.24</v>
+        <v>548.15</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>98.77 - 99.68 DR DEMAND</t>
+          <t>485.45 - 490.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>554.86 - 559.52 RD SUPPLY</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -5953,55 +5953,55 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CENTRALBK</t>
+          <t>LLOYDSME</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Central Bank of India</t>
+          <t>Lloyds Metals And Energy Ltd.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>30.4</v>
+        <v>1826.7</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>30.1 - 30.17 DR DEMAND</t>
+          <t>1848.7 - 1859.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>35.83 - 36.93 RD SUPPLY</t>
+          <t>1042.28 - 1072.36 DR DEMAND</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6011,17 +6011,17 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -6033,55 +6033,55 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>POLYMED</t>
+          <t>ZEEL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Poly Medicure Ltd.</t>
+          <t>Zee Entertainment Enterprises Ltd.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1712.7</v>
+        <v>78.62</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1647.83 - 1688.54 DR DEMAND</t>
+          <t>80.0 - 83.66 RD SUPPLY</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1297.34 - 1337.36 DR DEMAND</t>
+          <t>66.41 - 70.46 DR DEMAND</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -6091,17 +6091,17 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -6113,45 +6113,45 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ERIS</t>
+          <t>BBTC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Eris Lifesciences Ltd.</t>
+          <t>Bombay Burmah Trading Corporation Ltd.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1310.7</v>
+        <v>1512.1</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1288.9 - 1301.0 DR DEMAND</t>
+          <t>1539.0 - 1545.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1962.03 - 2114.67 RD SUPPLY</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6161,27 +6161,27 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>3.5 / 10 SOLID</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -6193,45 +6193,45 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>BHARTIHEXA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NATCO Pharma Ltd.</t>
+          <t>Bharti Hexacom Ltd.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>818.25</v>
+        <v>1540.1</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>950.09 - 963.22 RD SUPPLY</t>
+          <t>1546.1 - 1567.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>803.32 - 821.11 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6241,77 +6241,77 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>SCHNEIDER</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Bharat Electronics Ltd.</t>
+          <t>Schneider Electric Infrastructure Ltd.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>395.45</v>
+        <v>1213.5</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>411.55 - 416.0 RD SUPPLY</t>
+          <t>1232.4 - 1235.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>378.32 - 397.37 DR DEMAND</t>
+          <t>540.0 - 575.5 DR DEMAND</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -6331,72 +6331,72 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Indus Towers Ltd.</t>
+          <t>Supreme Industries Ltd.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>381.35</v>
+        <v>3580.3</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>368.7 - 372.0 DR DEMAND</t>
+          <t>3605.0 - 3661.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>376.63 - 395.08 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -6406,77 +6406,77 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>RAMCOCEM</t>
+          <t>HOMEFIRST</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The Ramco Cements Ltd.</t>
+          <t>Home First Finance Company India Ltd.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>858.95</v>
+        <v>1241.3</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>856.75 - 860.55 DR DEMAND</t>
+          <t>1265.0 - 1284.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>836.02 - 868.83 DR DEMAND</t>
+          <t>889.54 - 900.59 DR DEMAND</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -6486,39 +6486,39 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BAJAJHFL</t>
+          <t>TATAINVEST</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Bajaj Housing Finance Ltd.</t>
+          <t>Tata Investment Corporation Ltd.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6528,40 +6528,40 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>82.7</v>
+        <v>702.35</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>82.4 - 82.82 DR DEMAND</t>
+          <t>716.11 - 737.89 RD SUPPLY</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>655.32 - 737.89 RD SUPPLY</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 6 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6571,77 +6571,77 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DCMSHRIRAM</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DCM Shriram Ltd.</t>
+          <t>Apollo Hospitals Enterprise Ltd.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>984</v>
+        <v>8944.5</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>981.47 - 992.13 DR DEMAND</t>
+          <t>9000.0 - 9024.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>942.52 - 977.88 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6651,52 +6651,52 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SAMMAANCAP</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sammaan Capital Ltd.</t>
+          <t>Adani Total Gas Ltd.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>142.22</v>
+        <v>660.7</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>159.2 - 161.0 RD SUPPLY</t>
+          <t>666.5 - 687.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -6706,17 +6706,17 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>134.75 - 144.61 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -6726,82 +6726,82 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dalmia Bharat Ltd.</t>
+          <t>Central Depository Services (India) Ltd.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1693.3</v>
+        <v>1390</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1683.0 - 1730.6 DR DEMAND</t>
+          <t>1415.0 - 1438.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2397.36 - 2484.34 RD SUPPLY</t>
+          <t>1730.38 - 1955.87 RD SUPPLY</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6811,62 +6811,62 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HOMEFIRST</t>
+          <t>JSWINFRA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Home First Finance Company India Ltd.</t>
+          <t>JSW Infrastructure Ltd.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1173.3</v>
+        <v>348.25</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1151.9 - 1160.0 DR DEMAND</t>
+          <t>349.7 - 355.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>1184.37 - 1233.14 RD SUPPLY</t>
+          <t>216.99 - 253.34 DR DEMAND</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6881,12 +6881,12 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6896,29 +6896,29 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>4.0 / 10 SOLID</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>CONFLICT</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>MEDANTA</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories Ltd.</t>
+          <t>Global Health Ltd.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6928,40 +6928,40 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1175</v>
+        <v>1499.4</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
+          <t>1520.5 - 1544.0 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>6.0 B</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
           <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>1141.16 - 1182.0 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>2.5 C</t>
-        </is>
-      </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6971,77 +6971,77 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>3.5 / 10 SOLID</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FIRSTCRY</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Brainbees Solutions Ltd.</t>
+          <t>Narayana Hrudayalaya Ltd.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>169.25</v>
+        <v>1928.5</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>168.15 - 170.82 DR DEMAND</t>
+          <t>1932.1 - 1940.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>2170.07 - 2359.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -7051,39 +7051,39 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>3.5 / 10 SOLID</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3MINDIA</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>3M India Ltd.</t>
+          <t>UPL Ltd.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7092,26 +7092,26 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>32530</v>
+        <v>580</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>32710.0 - 32895.0 RD SUPPLY</t>
+          <t>589.3 - 591.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>28319.86 - 29690.02 DR DEMAND</t>
+          <t>557.75 - 565.72 DR DEMAND</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7153,12 +7153,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CANFINHOME</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Can Fin Homes Ltd.</t>
+          <t>Life Insurance Corporation of India</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -7172,26 +7172,26 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>774.4</v>
+        <v>407.7</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>790.0 - 791.95 RD SUPPLY</t>
+          <t>452.84 - 457.74 RD SUPPLY</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>545.13 - 563.82 DR DEMAND</t>
+          <t>414.97 - 443.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -7233,17 +7233,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>CARBORUNIV</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>REC Ltd.</t>
+          <t>Carborundum Universal Ltd.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7252,41 +7252,41 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>310.5</v>
+        <v>1124.4</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>314.0 - 315.5 RD SUPPLY</t>
+          <t>1139.4 - 1151.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1181.58 - 1303.79 RD SUPPLY</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -7313,17 +7313,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>RAINBOW</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Dabur India Ltd.</t>
+          <t>Rainbow Childrens Medicare Ltd.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7332,36 +7332,36 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>384.55</v>
+        <v>1454.7</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>386.85 - 390.95 RD SUPPLY</t>
+          <t>1465.0 - 1471.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>518.65 - 536.39 RD SUPPLY</t>
+          <t>1550.0 - 1610.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -7393,17 +7393,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>TBOTEK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Hindustan Unilever Ltd.</t>
+          <t>TBO Tek Ltd.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7412,36 +7412,36 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1942.2</v>
+        <v>1710.6</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1962.0 - 1977.0 RD SUPPLY</t>
+          <t>1733.7 - 1743.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1004.2 - 1057.3 DR DEMAND</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -7473,17 +7473,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>HONAUT</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Honeywell Automation India Ltd.</t>
+          <t>Zydus Lifesciences Ltd.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -7492,41 +7492,41 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>33915</v>
+        <v>1160</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>34590.0 - 34870.0 RD SUPPLY</t>
+          <t>1161.7 - 1167.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>855.18 - 875.51 DR DEMAND</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -7553,17 +7553,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Nestle India Ltd.</t>
+          <t>Container Corporation of India Ltd.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -7572,41 +7572,41 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1370.6</v>
+        <v>504.55</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1384.5 - 1397.0 RD SUPPLY</t>
+          <t>447.08 - 450.02 DR DEMAND</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1153.85 - 1169.18 DR DEMAND</t>
+          <t>507.3 - 535.36 RD SUPPLY</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>3.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -7633,17 +7633,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>VTL</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Vardhman Textiles Ltd.</t>
+          <t>Punjab National Bank</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -7652,36 +7652,36 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>561.3</v>
+        <v>117.27</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>571.75 - 577.0 RD SUPPLY</t>
+          <t>117.95 - 118.25 RD SUPPLY</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>80.71 - 82.53 DR DEMAND</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>3.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -7713,17 +7713,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BLUEDART</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Blue Dart Express Ltd.</t>
+          <t>City Union Bank Ltd.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>PVTBANK</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -7732,36 +7732,36 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4811.3</v>
+        <v>235.79</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>4850.5 - 4868.9 RD SUPPLY</t>
+          <t>235.93 - 243.1 RD SUPPLY</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>5465.7 - 5775.5 RD SUPPLY</t>
+          <t>177.59 - 189.81 DR DEMAND</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 4 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>3.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -7793,17 +7793,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>HONASA</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Glaxosmithkline Pharmaceuticals Ltd.</t>
+          <t>Honasa Consumer Ltd.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -7812,26 +7812,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2799.9</v>
+        <v>479.55</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2856.2 - 2878.0 RD SUPPLY</t>
+          <t>483.8 - 488.71 RD SUPPLY</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1849.2 - 1903.26 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>3.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -7873,17 +7873,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>HDFC Bank Ltd.</t>
+          <t>Sona BLW Precision Forgings Ltd.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -7892,41 +7892,41 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>713</v>
+        <v>808</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>721.5 - 725.4 RD SUPPLY</t>
+          <t>821.9 - 824.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>399.83 - 409.23 DR DEMAND</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>3.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -7953,17 +7953,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>TECHNOE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>HDFC Life Insurance Company Ltd.</t>
+          <t>Techno Electric &amp; Engineering Company Ltd.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -7972,21 +7972,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>557</v>
+        <v>1030.45</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>561.0 - 561.95 RD SUPPLY</t>
+          <t>1023.27 - 1034.04 RD SUPPLY</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>811.41 - 817.84 RD SUPPLY</t>
+          <t>863.77 - 967.52 DR DEMAND</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -8016,34 +8016,34 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LIC Housing Finance Ltd.</t>
+          <t>APL Apollo Tubes Ltd.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8052,26 +8052,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>545.9</v>
+        <v>2270.1</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>485.45 - 490.0 DR DEMAND</t>
+          <t>2241.37 - 2272.25 RD SUPPLY</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>554.86 - 559.52 RD SUPPLY</t>
+          <t>2226.02 - 2292.57 RD SUPPLY</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -8101,29 +8101,29 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>APARINDS</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Apar Industries Ltd.</t>
+          <t>Patanjali Foods Ltd.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8132,36 +8132,36 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>17801</v>
+        <v>367</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>18137.03 - 18401.11 RD SUPPLY</t>
+          <t>365.0 - 367.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>13236.05 - 14298.36 DR DEMAND</t>
+          <t>598.95 - 605.96 RD SUPPLY</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -8181,29 +8181,29 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EMAMILTD</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Emami Ltd.</t>
+          <t>Emcure Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8212,36 +8212,36 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>376.1</v>
+        <v>2003.8</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>376.65 - 379.35 RD SUPPLY</t>
+          <t>1834.83 - 1851.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
+          <t>8.5 A</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>1962.18 - 2044.02 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>444.5 - 477.0 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>7.0 A</t>
-        </is>
-      </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -8256,34 +8256,34 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Titan Company Ltd.</t>
+          <t>Petronet LNG Ltd.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -8292,26 +8292,26 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4841</v>
+        <v>292.6</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>4908.5 - 4921.5 RD SUPPLY</t>
+          <t>290.95 - 293.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>3949.84 - 4061.57 DR DEMAND</t>
+          <t>232.67 - 245.62 DR DEMAND</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8336,34 +8336,34 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CANHLIFE</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Canara HSBC Life Insurance Company Ltd.</t>
+          <t>Kajaria Ceramics Ltd.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8372,26 +8372,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>155.36</v>
+        <v>1202.7</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>158.5 - 161.05 RD SUPPLY</t>
+          <t>1060.5 - 1072.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1187.65 - 1246.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -8416,29 +8416,29 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>SPLPETRO</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Radico Khaitan Ltd</t>
+          <t>Supreme Petrochem Ltd.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -8452,26 +8452,26 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4380</v>
+        <v>865.7</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>4460.0 - 4485.0 RD SUPPLY</t>
+          <t>688.05 - 691.15 DR DEMAND</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>854.83 - 887.11 RD SUPPLY</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8496,34 +8496,34 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ANANDRATHI</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Anand Rathi Wealth Ltd.</t>
+          <t>Adani Green Energy Ltd.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -8532,26 +8532,26 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2207.4</v>
+        <v>1334.5</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2212.4 - 2222.0 RD SUPPLY</t>
+          <t>1330.6 - 1346.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>1710.6 - 1725.35 DR DEMAND</t>
+          <t>765.0 - 814.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8576,34 +8576,34 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>JSWDULUX</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>IDFC First Bank Ltd.</t>
+          <t>JSW Dulux Ltd.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -8612,26 +8612,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>86.33</v>
+        <v>3188.8</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>87.81 - 88.1 RD SUPPLY</t>
+          <t>3169.9 - 3195.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>57.91 - 58.68 DR DEMAND</t>
+          <t>2862.0 - 2938.8 DR DEMAND</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 5 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -8656,34 +8656,34 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Exide Industries Ltd.</t>
+          <t>Clean Science and Technology Ltd.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -8692,28 +8692,28 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>418.6</v>
+        <v>851.9</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>420.85 - 424.0 RD SUPPLY</t>
+          <t>846.0 - 858.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
+          <t>4.0 C</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>1538.62 - 1583.15 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
           <t>5.5 B</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J104" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8736,34 +8736,34 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>LGEINDIA</t>
+          <t>SCHAEFFLER</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LG Electronics India Ltd.</t>
+          <t>Schaeffler India Ltd.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -8772,26 +8772,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1652.9</v>
+        <v>4217.6</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>1672.2 - 1680.0 RD SUPPLY</t>
+          <t>4196.0 - 4235.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>3489.69 - 3548.8 DR DEMAND</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 7 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8816,34 +8816,34 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>4.5 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Punjab National Bank</t>
+          <t>Phoenix Mills Ltd.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -8852,31 +8852,31 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>116.47</v>
+        <v>1877.9</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>117.95 - 118.25 RD SUPPLY</t>
+          <t>2090.43 - 2097.12 RD SUPPLY</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>80.71 - 82.53 DR DEMAND</t>
+          <t>1851.05 - 1990.36 RD SUPPLY</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -8901,29 +8901,29 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>City Union Bank Ltd.</t>
+          <t>Aegis Logistics Ltd.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PVTBANK</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -8932,11 +8932,11 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>231.82</v>
+        <v>1415.4</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>235.93 - 243.1 RD SUPPLY</t>
+          <t>1383.9 - 1434.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>177.59 - 189.81 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -8961,7 +8961,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🔴 5 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8981,29 +8981,29 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>RAINBOW</t>
+          <t>POONAWALLA</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Rainbow Childrens Medicare Ltd.</t>
+          <t>Poonawalla Fincorp Ltd.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9012,26 +9012,26 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1473.4</v>
+        <v>479.4</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>1478.5 - 1485.2 RD SUPPLY</t>
+          <t>425.0 - 428.45 DR DEMAND</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>1550.0 - 1610.0 RD SUPPLY</t>
+          <t>454.8 - 503.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -9056,655 +9056,15 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2.5 / 10 SUPPLY</t>
+          <t>3.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
-        <is>
-          <t>NEAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>CAPLIPOINT</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Caplin Point Laboratories Ltd.</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>HEALTHCARE</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-      <c r="E109" t="n">
-        <v>2596.6</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>1703.23 - 1716.1 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>4.0 C</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>2503.19 - 2628.59 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>7.0 A</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>1W UP • 20 EMA BULLISH</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>🟢 0 TESTS (FRESH)</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>NORMAL VOL</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>+0.0 PTS</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>7.0 / 10 SUPPLY</t>
-        </is>
-      </c>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>SUPPLY TEST</t>
-        </is>
-      </c>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>TATAINVEST</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Tata Investment Corporation Ltd.</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>FINSERVICE</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-      <c r="E110" t="n">
-        <v>719.3</v>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>716.11 - 737.89 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>5.0 C</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>655.32 - 737.89 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>4.0 C</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>1W UP • 20 EMA BULLISH</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>🔴 6 TESTS (WEAK)</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>🔥 1.8x HIGH VOL</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>+0.0 PTS</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>6.5 / 10 SUPPLY</t>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>SUPPLY TEST</t>
-        </is>
-      </c>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>EIHOTEL</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>EIH Ltd.</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>CONSUMPTION</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-      <c r="E111" t="n">
-        <v>299.9</v>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>295.75 - 307.5 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>5.0 C</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>398.09 - 432.84 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>4.0 C</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>🟡 1 TEST (TESTED)</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>NORMAL VOL</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>+0.0 PTS</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr">
-        <is>
-          <t>6.0 / 10 SUPPLY</t>
-        </is>
-      </c>
-      <c r="O111" t="inlineStr">
-        <is>
-          <t>SUPPLY TEST</t>
-        </is>
-      </c>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>JUBLFOOD</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Jubilant Foodworks Ltd.</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>CONSUMPTION</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-      <c r="E112" t="n">
-        <v>480.2</v>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>408.55 - 410.0 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>6.0 B</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>477.24 - 497.34 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>5.5 B</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>1W UP • 20 EMA BULLISH</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>🟡 1 TEST (TESTED)</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>NORMAL VOL</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>+0.0 PTS</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>5.5 / 10 SUPPLY</t>
-        </is>
-      </c>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>SUPPLY TEST</t>
-        </is>
-      </c>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>KAJARIACER</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Kajaria Ceramics Ltd.</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>CONSUMPTION</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-      <c r="E113" t="n">
-        <v>1217.2</v>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>1060.5 - 1072.6 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>2.5 C</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>1187.65 - 1246.8 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>5.0 C</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>1W UP • 20 EMA BULLISH</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>🟡 1 TEST (TESTED)</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>NORMAL VOL</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>+0.0 PTS</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>5.0 / 10 SUPPLY</t>
-        </is>
-      </c>
-      <c r="O113" t="inlineStr">
-        <is>
-          <t>SUPPLY TEST</t>
-        </is>
-      </c>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>VBL</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Varun Beverages Ltd.</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-      <c r="E114" t="n">
-        <v>415.45</v>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>415.0 - 416.95 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>4.0 C</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>520.87 - 531.92 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>6.0 B</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>🔴 2 TESTS (WEAK)</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>NORMAL VOL</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>+0.0 PTS</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>5.0 / 10 SUPPLY</t>
-        </is>
-      </c>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>SUPPLY TEST</t>
-        </is>
-      </c>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Phoenix Mills Ltd.</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>REALTY</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-      <c r="E115" t="n">
-        <v>1872.2</v>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2090.43 - 2097.12 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>6.0 B</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>1851.05 - 1990.36 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>2.5 C</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>🔴 2 TESTS (WEAK)</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>NORMAL VOL</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>+0.0 PTS</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>3.5 / 10 SUPPLY</t>
-        </is>
-      </c>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>SUPPLY TEST</t>
-        </is>
-      </c>
-      <c r="P115" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>AEGISVOPAK</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Aegis Vopak Terminals Ltd.</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>OIL</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-      <c r="E116" t="n">
-        <v>310.7</v>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>303.3 - 311.49 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>3.0 C</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>1W UP • 20 EMA BULLISH</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>🔴 3 TESTS (WEAK)</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>+0.0 PTS</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>3.0 / 10 SUPPLY</t>
-        </is>
-      </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>SUPPLY TEST</t>
-        </is>
-      </c>
-      <c r="P116" t="inlineStr">
         <is>
           <t>IN</t>
         </is>

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>300.05</v>
+        <v>300.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -593,17 +593,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BDL</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bharat Dynamics Ltd.</t>
+          <t>Castrol India Ltd.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -612,31 +612,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1168</v>
+        <v>193.23</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1085.64 - 1096.23 DR DEMAND</t>
+          <t>193.15 - 193.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1154.81 - 1204.2 DR DEMAND</t>
+          <t>144.37 - 156.26 DR DEMAND</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -673,17 +673,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ANTHEM</t>
+          <t>BDL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Anthem Biosciences Ltd.</t>
+          <t>Bharat Dynamics Ltd.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -692,31 +692,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>891.7</v>
+        <v>1161</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>871.0 - 874.7 DR DEMAND</t>
+          <t>1085.64 - 1096.23 DR DEMAND</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1154.81 - 1204.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -731,34 +731,34 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>11.0 / 10 SUPER COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>BUY READY</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Colgate Palmolive (India) Ltd.</t>
+          <t>CCL Products (I) Ltd.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -772,26 +772,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1869</v>
+        <v>1043.2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1836.9 - 1840.3 DR DEMAND</t>
+          <t>961.32 - 966.71 DR DEMAND</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2228.23 - 2274.78 RD SUPPLY</t>
+          <t>1040.1 - 1050.87 DR DEMAND</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -816,34 +816,34 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>11.0 / 10 SUPER COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>BUY READY</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>ANTHEM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ICICI Bank Ltd.</t>
+          <t>Anthem Biosciences Ltd.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -852,31 +852,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1339.6</v>
+        <v>881.9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1320.37 - 1327.11 DR DEMAND</t>
+          <t>871.0 - 874.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1457.77 - 1476.07 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>10.5 / 10 HIGH COMBO</t>
+          <t>11.0 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -913,17 +913,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AEGISVOPAK</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aegis Vopak Terminals Ltd.</t>
+          <t>ICICI Bank Ltd.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -932,31 +932,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>301.4</v>
+        <v>1340</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>288.9 - 295.85 DR DEMAND</t>
+          <t>1320.37 - 1327.11 DR DEMAND</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1457.77 - 1476.07 RD SUPPLY</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -993,17 +993,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>TENNIND</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Abbott India Ltd.</t>
+          <t>Tenneco Clean Air India Ltd.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1012,31 +1012,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>27225</v>
+        <v>518.6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>26815.0 - 26960.0 DR DEMAND</t>
+          <t>510.0 - 513.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>25135.0 - 25850.0 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1073,17 +1073,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FLUOROCHEM</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gujarat Fluorochemicals Ltd.</t>
+          <t>City Union Bank Ltd.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>PVTBANK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1092,26 +1092,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4487.2</v>
+        <v>225.34</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4432.6 - 4471.8 DR DEMAND</t>
+          <t>220.0 - 222.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2923.16 - 3026.3 DR DEMAND</t>
+          <t>177.59 - 189.81 DR DEMAND</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1153,17 +1153,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NEULANDLAB</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Neuland Laboratories Ltd.</t>
+          <t>One 97 Communications Ltd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1172,26 +1172,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>22550</v>
+        <v>1775</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22123.0 - 22216.0 DR DEMAND</t>
+          <t>1752.7 - 1763.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10163.48 - 10582.66 DR DEMAND</t>
+          <t>651.5 - 700.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1233,17 +1233,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sona BLW Precision Forgings Ltd.</t>
+          <t>Tata Consultancy Services Ltd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1252,21 +1252,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>809</v>
+        <v>2089.6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>793.2 - 795.25 DR DEMAND</t>
+          <t>2053.34 - 2057.72 DR DEMAND</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>399.83 - 409.23 DR DEMAND</t>
+          <t>1966.02 - 2020.42 DR DEMAND</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1291,12 +1291,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1313,17 +1313,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JINDALSAW</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jindal Saw Ltd.</t>
+          <t>Aditya Birla Capital Ltd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1332,26 +1332,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>286.45</v>
+        <v>402.45</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>275.7 - 281.25 DR DEMAND</t>
+          <t>394.65 - 397.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>310.0 - 320.0 RD SUPPLY</t>
+          <t>287.7 - 292.25 DR DEMAND</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RAINBOW</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rainbow Childrens Medicare Ltd.</t>
+          <t>Petronet LNG Ltd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1412,21 +1412,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1430.9</v>
+        <v>285.85</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1402.2 - 1404.8 DR DEMAND</t>
+          <t>280.3 - 281.75 DR DEMAND</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1550.0 - 1610.0 RD SUPPLY</t>
+          <t>232.67 - 245.62 DR DEMAND</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1473,17 +1473,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bank of India</t>
+          <t>Aurobindo Pharma Ltd.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1492,31 +1492,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>137.01</v>
+        <v>1721.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>134.01 - 135.12 DR DEMAND</t>
+          <t>1689.3 - 1700.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>86.59 - 88.92 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1553,17 +1553,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Canara Bank</t>
+          <t>ITC Ltd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1572,26 +1572,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>122.9</v>
+        <v>270.15</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>120.5 - 121.15 DR DEMAND</t>
+          <t>264.75 - 265.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>73.46 - 75.61 DR DEMAND</t>
+          <t>306.55 - 309.47 RD SUPPLY</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1633,12 +1633,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CROMPTON</t>
+          <t>SAPPHIRE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Crompton Greaves Consumer Electricals Ltd.</t>
+          <t>Sapphire Foods India Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1652,31 +1652,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222</v>
+        <v>231.48</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>219.51 - 220.94 DR DEMAND</t>
+          <t>228.0 - 230.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>139.91 - 150.42 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>214.82 - 218.82 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>6.0 B</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1713,17 +1713,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GRAVITA</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gravita India Ltd.</t>
+          <t>Ambuja Cements Ltd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1732,11 +1732,11 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1564.9</v>
+        <v>392.75</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1540.0 - 1544.5 DR DEMAND</t>
+          <t>385.15 - 386.9 DR DEMAND</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1746,12 +1746,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1266.9 - 1318.1 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1793,17 +1793,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HDBFS</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HDB Financial Services Ltd.</t>
+          <t>Ashok Leyland Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1812,11 +1812,11 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>674.55</v>
+        <v>162.89</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>662.4 - 664.7 DR DEMAND</t>
+          <t>159.8 - 160.75 DR DEMAND</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>207.56 - 211.81 RD SUPPLY</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1873,17 +1873,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JBMA</t>
+          <t>GRAVITA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JBM Auto Ltd.</t>
+          <t>Gravita India Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1892,11 +1892,11 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>593.15</v>
+        <v>1561.1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>585.0 - 586.05 DR DEMAND</t>
+          <t>1540.0 - 1544.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>716.95 - 764.17 RD SUPPLY</t>
+          <t>1266.9 - 1318.1 DR DEMAND</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1953,17 +1953,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LALPATHLAB</t>
+          <t>HDBFS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dr. Lal Path Labs Ltd.</t>
+          <t>HDB Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1972,11 +1972,11 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1909.8</v>
+        <v>670.8</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1885.0 - 1896.9 DR DEMAND</t>
+          <t>662.4 - 664.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2033,17 +2033,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Narayana Hrudayalaya Ltd.</t>
+          <t>Shree Cement Ltd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2052,26 +2052,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1883.3</v>
+        <v>22500</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1850.5 - 1858.5 DR DEMAND</t>
+          <t>22165.0 - 22200.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2170.07 - 2359.4 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1551.6</v>
+        <v>1557</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2193,17 +2193,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>VTL</t>
+          <t>WAAREEENER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vardhman Textiles Ltd.</t>
+          <t>Waaree Energies Ltd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2212,16 +2212,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>551.2</v>
+        <v>2512</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>538.48 - 540.86 DR DEMAND</t>
+          <t>2470.0 - 2473.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2273,17 +2273,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>WAAREEENER</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Waaree Energies Ltd.</t>
+          <t>Coforge Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2292,51 +2292,51 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2494.8</v>
+        <v>1782.4</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2470.0 - 2473.0 DR DEMAND</t>
+          <t>1762.2 - 1773.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1985.3 - 2021.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2353,17 +2353,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Coforge Ltd.</t>
+          <t>Manappuram Finance Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2372,11 +2372,11 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1803</v>
+        <v>320.4</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1762.2 - 1773.0 DR DEMAND</t>
+          <t>313.8 - 315.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2386,22 +2386,22 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1985.3 - 2021.2 RD SUPPLY</t>
+          <t>244.06 - 249.98 DR DEMAND</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2433,17 +2433,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>RAINBOW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Manappuram Finance Ltd.</t>
+          <t>Rainbow Childrens Medicare Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2452,28 +2452,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>319.3</v>
+        <v>1406.5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>313.8 - 315.1 DR DEMAND</t>
+          <t>1402.2 - 1404.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>1550.0 - 1610.0 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>244.06 - 249.98 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>7.0 A</t>
-        </is>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2513,17 +2513,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NHPC Ltd.</t>
+          <t>ACC Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2532,26 +2532,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>76.01000000000001</v>
+        <v>1251.4</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>74.3 - 74.82 DR DEMAND</t>
+          <t>1234.8 - 1238.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>67.83 - 70.98 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2593,17 +2593,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Axis Bank Ltd.</t>
+          <t>Bharti Airtel Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2612,26 +2612,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1242.7</v>
+        <v>1833.2</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1372.94 - 1376.64 RD SUPPLY</t>
+          <t>1813.0 - 1817.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1208.6 - 1229.5 DR DEMAND</t>
+          <t>1527.35 - 1537.83 DR DEMAND</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2651,12 +2651,12 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2673,17 +2673,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>FLUOROCHEM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dalmia Bharat Ltd.</t>
+          <t>Gujarat Fluorochemicals Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2692,36 +2692,36 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1741.6</v>
+        <v>4476.4</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1683.0 - 1730.6 DR DEMAND</t>
+          <t>4432.6 - 4471.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2397.36 - 2484.34 RD SUPPLY</t>
+          <t>2923.16 - 3026.3 DR DEMAND</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2753,17 +2753,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>NCC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PG Electroplast Ltd.</t>
+          <t>NCC Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2772,26 +2772,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>520.2</v>
+        <v>136.05</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>512.76 - 515.01 DR DEMAND</t>
+          <t>133.75 - 134.41 DR DEMAND</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>811.36 - 835.69 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2833,17 +2833,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RITES Ltd.</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2852,26 +2852,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>203.6</v>
+        <v>994.1</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>200.24 - 202.21 DR DEMAND</t>
+          <t>981.3 - 987.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>214.72 - 226.44 RD SUPPLY</t>
+          <t>933.9 - 964.4 DR DEMAND</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2913,17 +2913,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BAJAJHFL</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bajaj Housing Finance Ltd.</t>
+          <t>Torrent Power Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2932,26 +2932,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>83.12</v>
+        <v>1259.4</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>82.4 - 82.82 DR DEMAND</t>
+          <t>1232.0 - 1250.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1186.52 - 1241.27 DR DEMAND</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2993,17 +2993,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>COROMANDEL</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Coromandel International Ltd.</t>
+          <t>Axis Bank Ltd.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3012,26 +3012,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1944.9</v>
+        <v>1243.2</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1898.45 - 1912.04 DR DEMAND</t>
+          <t>1372.94 - 1376.64 RD SUPPLY</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1704.84 - 1751.89 DR DEMAND</t>
+          <t>1208.6 - 1229.5 DR DEMAND</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3073,12 +3073,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GICRE</t>
+          <t>CANHLIFE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>General Insurance Corporation of India</t>
+          <t>Canara HSBC Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3092,16 +3092,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>341.2</v>
+        <v>151.63</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>334.14 - 335.25 DR DEMAND</t>
+          <t>148.1 - 149.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3153,17 +3153,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>J&amp;KBANK</t>
+          <t>CROMPTON</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir Bank Ltd.</t>
+          <t>Crompton Greaves Consumer Electricals Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3172,26 +3172,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>145.94</v>
+        <v>223.43</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>144.0 - 144.44 DR DEMAND</t>
+          <t>219.51 - 220.94 DR DEMAND</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>108.0 - 110.01 DR DEMAND</t>
+          <t>214.82 - 218.82 DR DEMAND</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3233,17 +3233,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MGL</t>
+          <t>LALPATHLAB</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mahanagar Gas Ltd.</t>
+          <t>Dr. Lal Path Labs Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3252,31 +3252,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1067.3</v>
+        <v>1924.3</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1054.52 - 1061.5 DR DEMAND</t>
+          <t>1885.0 - 1896.9 DR DEMAND</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>885.65 - 912.91 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3291,12 +3291,12 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3313,17 +3313,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MRPL</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mangalore Refinery &amp; Petrochemicals Ltd.</t>
+          <t>Mazagoan Dock Shipbuilders Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3332,26 +3332,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>164.44</v>
+        <v>2211.5</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>161.2 - 162.96 DR DEMAND</t>
+          <t>2176.0 - 2209.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>96.88 - 103.61 DR DEMAND</t>
+          <t>1900.61 - 2111.67 DR DEMAND</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3393,17 +3393,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Amara Raja Energy &amp; Mobility Ltd.</t>
+          <t>PG Electroplast Ltd.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3412,26 +3412,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>793.2</v>
+        <v>521.15</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>789.12 - 791.56 DR DEMAND</t>
+          <t>512.76 - 515.01 DR DEMAND</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>811.36 - 835.69 RD SUPPLY</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3473,17 +3473,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>RITES</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Indraprastha Gas Ltd.</t>
+          <t>RITES Ltd.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3492,26 +3492,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>146.68</v>
+        <v>204.05</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>158.04 - 159.5 RD SUPPLY</t>
+          <t>200.24 - 202.21 DR DEMAND</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>141.74 - 145.62 DR DEMAND</t>
+          <t>214.72 - 226.44 RD SUPPLY</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3553,17 +3553,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Power Finance Corporation Ltd.</t>
+          <t>Sun Pharmaceutical Industries Ltd.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3572,11 +3572,11 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>345.8</v>
+        <v>1865</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>431.25 - 433.95 RD SUPPLY</t>
+          <t>1842.3 - 1846.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>329.74 - 339.39 DR DEMAND</t>
+          <t>1569.37 - 1580.86 DR DEMAND</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3633,17 +3633,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RAMCOCEM</t>
+          <t>BAJAJHFL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Ramco Cements Ltd.</t>
+          <t>Bajaj Housing Finance Ltd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3652,26 +3652,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>883.5</v>
+        <v>83.52</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>856.75 - 860.55 DR DEMAND</t>
+          <t>82.4 - 82.82 DR DEMAND</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>836.02 - 868.83 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3713,17 +3713,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TIMKEN</t>
+          <t>LATENTVIEW</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Timken India Ltd.</t>
+          <t>Latent View Analytics Ltd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3732,21 +3732,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3178.5</v>
+        <v>253.4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>3091.2 - 3126.6 DR DEMAND</t>
+          <t>249.65 - 250.55 DR DEMAND</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2177.68 - 2425.42 DR DEMAND</t>
+          <t>316.2 - 324.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3793,17 +3793,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bata India Ltd.</t>
+          <t>Indraprastha Gas Ltd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3812,26 +3812,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>631.75</v>
+        <v>147.09</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>625.59 - 627.84 DR DEMAND</t>
+          <t>158.04 - 159.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>685.67 - 743.46 RD SUPPLY</t>
+          <t>141.74 - 145.62 DR DEMAND</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3873,17 +3873,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bharti Airtel Ltd.</t>
+          <t>Power Finance Corporation Ltd.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3892,26 +3892,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1817.2</v>
+        <v>346</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1813.0 - 1814.7 DR DEMAND</t>
+          <t>431.25 - 433.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1527.35 - 1537.83 DR DEMAND</t>
+          <t>329.74 - 339.39 DR DEMAND</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3953,17 +3953,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>RAMCOCEM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dixon Technologies (India) Ltd.</t>
+          <t>The Ramco Cements Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3972,26 +3972,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>13084</v>
+        <v>885.05</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>12838.12 - 12924.05 DR DEMAND</t>
+          <t>856.75 - 860.55 DR DEMAND</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>14838.58 - 14988.47 RD SUPPLY</t>
+          <t>836.02 - 868.83 DR DEMAND</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4033,17 +4033,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NIACL</t>
+          <t>BATAINDIA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The New India Assurance Company Ltd.</t>
+          <t>Bata India Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4052,36 +4052,36 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>187.41</v>
+        <v>637.2</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>182.41 - 185.45 DR DEMAND</t>
+          <t>625.59 - 627.84 DR DEMAND</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>685.67 - 743.46 RD SUPPLY</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4113,17 +4113,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AWL</t>
+          <t>DCMSHRIRAM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AWL Agri Business Ltd.</t>
+          <t>DCM Shriram Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4132,26 +4132,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>183.1</v>
+        <v>980</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>180.27 - 181.44 DR DEMAND</t>
+          <t>1296.87 - 1319.98 RD SUPPLY</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>942.52 - 977.88 DR DEMAND</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4193,12 +4193,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DCMSHRIRAM</t>
+          <t>INDIAMART</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DCM Shriram Ltd.</t>
+          <t>Indiamart Intermesh Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4212,26 +4212,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>979.3</v>
+        <v>1652.4</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1296.87 - 1319.98 RD SUPPLY</t>
+          <t>1624.1 - 1637.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>942.52 - 977.88 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1675.7</v>
+        <v>1688.2</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4353,17 +4353,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tata Steel Ltd.</t>
+          <t>Dalmia Bharat Ltd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4372,26 +4372,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>184.97</v>
+        <v>1744</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>182.01 - 182.63 DR DEMAND</t>
+          <t>1683.0 - 1730.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>156.83 - 164.57 DR DEMAND</t>
+          <t>2397.36 - 2484.34 RD SUPPLY</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4433,17 +4433,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>SBFC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NATCO Pharma Ltd.</t>
+          <t>SBFC Finance Ltd.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4452,26 +4452,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>815.05</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>950.09 - 963.22 RD SUPPLY</t>
+          <t>90.01 - 90.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>803.32 - 821.11 DR DEMAND</t>
+          <t>98.82 - 104.39 RD SUPPLY</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4491,67 +4491,67 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TATAINVEST</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tata Investment Corporation Ltd.</t>
+          <t>Abbott India Ltd.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>682.25</v>
+        <v>26935</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>666.0 - 676.1 DR DEMAND</t>
+          <t>26815.0 - 26960.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>655.32 - 737.89 RD SUPPLY</t>
+          <t>24406.02 - 25223.54 DR DEMAND</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4586,24 +4586,24 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CONFLICT</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>United Breweries Ltd.</t>
+          <t>Indus Towers Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4612,26 +4612,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1215.2</v>
+        <v>384.8</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1213.5 - 1216.8 DR DEMAND</t>
+          <t>368.7 - 372.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1426.85 - 1453.66 RD SUPPLY</t>
+          <t>376.63 - 395.08 DR DEMAND</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4673,47 +4673,47 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>GPIL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Torrent Power Ltd.</t>
+          <t>Godawari Power &amp; Ispat Ltd.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>EQUILIBRIUM</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1246.3</v>
+        <v>234.68</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1232.0 - 1250.0 DR DEMAND</t>
+          <t>239.0 - 239.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
+          <t>7.5 A</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>220.3 - 234.23 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
           <t>4.0 C</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>1186.52 - 1241.27 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>3.0 C</t>
-        </is>
-      </c>
       <c r="J54" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4746,47 +4746,47 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CONFLICT</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>GESHIP</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CCL Products (I) Ltd.</t>
+          <t>Great Eastern Shipping Co. Ltd.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>EQUILIBRIUM</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1050</v>
+        <v>1483.8</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>961.32 - 966.71 DR DEMAND</t>
+          <t>1458.0 - 1462.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1040.1 - 1050.87 DR DEMAND</t>
+          <t>1468.8 - 1519.65 RD SUPPLY</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4826,62 +4826,62 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CONFLICT</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FIVESTAR</t>
+          <t>ANURAS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Five-Star Business Finance Ltd.</t>
+          <t>Anupam Rasayan India Ltd.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>EQUILIBRIUM</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>524.85</v>
+        <v>1193.4</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>518.5 - 524.85 DR DEMAND</t>
+          <t>1207.7 - 1219.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>412.05 - 443.54 DR DEMAND</t>
+          <t>1190.79 - 1206.27 DR DEMAND</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4906,19 +4906,19 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CONFLICT</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>PTCIL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Grasim Industries Ltd.</t>
+          <t>PTC Industries Ltd.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4932,36 +4932,36 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3128.2</v>
+        <v>22355</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>3105.33 - 3128.25 DR DEMAND</t>
+          <t>22055.0 - 22385.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2494.13 - 2528.7 DR DEMAND</t>
+          <t>11902.0 - 12721.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4993,45 +4993,45 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>SAMMAANCAP</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Indus Towers Ltd.</t>
+          <t>Sammaan Capital Ltd.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>382.1</v>
+        <v>144.48</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>381.35 - 384.75 RD SUPPLY</t>
+          <t>159.2 - 161.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>376.63 - 395.08 DR DEMAND</t>
+          <t>134.75 - 144.61 DR DEMAND</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5066,24 +5066,24 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>CONFLICT</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>KEC</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Kec International Ltd.</t>
+          <t>SBI Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5092,26 +5092,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>391.55</v>
+        <v>1760</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>389.15 - 393.2 DR DEMAND</t>
+          <t>2106.67 - 2129.04 RD SUPPLY</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1178.75 - 1289.99 RD SUPPLY</t>
+          <t>1700.4 - 1765.7 DR DEMAND</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5153,45 +5153,45 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mazagoan Dock Shipbuilders Ltd.</t>
+          <t>Bharat Electronics Ltd.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>EQUILIBRIUM</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2204</v>
+        <v>396.05</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2176.0 - 2209.0 DR DEMAND</t>
+          <t>397.4 - 399.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1900.61 - 2111.67 DR DEMAND</t>
+          <t>378.32 - 397.37 DR DEMAND</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5226,19 +5226,19 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CONFLICT</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ANURAS</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Anupam Rasayan India Ltd.</t>
+          <t>Chambal Fertilizers &amp; Chemicals Ltd.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5248,30 +5248,30 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1197.9</v>
+        <v>419.6</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1207.7 - 1219.0 RD SUPPLY</t>
+          <t>401.4 - 407.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1190.79 - 1206.27 DR DEMAND</t>
+          <t>404.75 - 434.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5281,22 +5281,22 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5306,19 +5306,19 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>CONFLICT</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>TATAINVEST</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Computer Age Management Services Ltd.</t>
+          <t>Tata Investment Corporation Ltd.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5328,25 +5328,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>EQUILIBRIUM</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>704</v>
+        <v>674.3</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>700.15 - 705.7 DR DEMAND</t>
+          <t>666.0 - 676.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>591.51 - 613.37 DR DEMAND</t>
+          <t>655.32 - 737.89 RD SUPPLY</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5386,24 +5386,24 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CONFLICT</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SAMMAANCAP</t>
+          <t>NEULANDLAB</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Sammaan Capital Ltd.</t>
+          <t>Neuland Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5412,36 +5412,36 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>142.36</v>
+        <v>22490</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>159.2 - 161.0 RD SUPPLY</t>
+          <t>22419.0 - 22510.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>134.75 - 144.61 DR DEMAND</t>
+          <t>10163.48 - 10582.66 DR DEMAND</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5451,12 +5451,12 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5473,45 +5473,45 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SBI Life Insurance Company Ltd.</t>
+          <t>NTPC Ltd.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1756.3</v>
+        <v>326</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2106.67 - 2129.04 RD SUPPLY</t>
+          <t>329.8 - 331.3 RD SUPPLY</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1700.4 - 1765.7 DR DEMAND</t>
+          <t>394.88 - 409.97 RD SUPPLY</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5531,67 +5531,67 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>TECHNOE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>UPL Ltd.</t>
+          <t>Techno Electric &amp; Engineering Company Ltd.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>559.9</v>
+        <v>1012.05</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>589.3 - 591.0 RD SUPPLY</t>
+          <t>1023.27 - 1034.04 RD SUPPLY</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>557.75 - 565.72 DR DEMAND</t>
+          <t>863.77 - 967.52 DR DEMAND</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5611,67 +5611,67 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Bharat Electronics Ltd.</t>
+          <t>Voltas Ltd.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>397.9</v>
+        <v>1130</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>397.4 - 399.2 RD SUPPLY</t>
+          <t>1143.0 - 1158.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>378.32 - 397.37 DR DEMAND</t>
+          <t>1425.92 - 1533.08 RD SUPPLY</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5696,72 +5696,72 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>CONFLICT</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>GPIL</t>
+          <t>AIIL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Godawari Power &amp; Ispat Ltd.</t>
+          <t>Authum Investment &amp; Infrastructure Ltd.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>232.89</v>
+        <v>561.45</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>227.37 - 228.05 DR DEMAND</t>
+          <t>568.95 - 579.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>220.3 - 234.23 DR DEMAND</t>
+          <t>629.8 - 683.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5771,77 +5771,77 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PTCIL</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PTC Industries Ltd.</t>
+          <t>Alkem Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>22130</v>
+        <v>5417.5</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>22055.0 - 22385.0 DR DEMAND</t>
+          <t>5475.0 - 5510.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>11902.0 - 12721.0 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5851,67 +5851,67 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Bajaj Finance Ltd.</t>
+          <t>Atul Ltd.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1008.8</v>
+        <v>6118</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1001.3 - 1012.8 DR DEMAND</t>
+          <t>6199.0 - 6234.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>783.09 - 796.65 DR DEMAND</t>
+          <t>5107.21 - 5250.52 DR DEMAND</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5931,67 +5931,67 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Chambal Fertilizers &amp; Chemicals Ltd.</t>
+          <t>ICICI Lombard General Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>418.5</v>
+        <v>1500.6</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>401.4 - 407.5 DR DEMAND</t>
+          <t>1511.0 - 1514.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>404.75 - 434.2 DR DEMAND</t>
+          <t>1894.31 - 1975.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6011,67 +6011,67 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CREDITACC</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CreditAccess Grameen Ltd.</t>
+          <t>Indian Railway Finance Corporation Ltd.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1357.9</v>
+        <v>81</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1354.1 - 1370.8 DR DEMAND</t>
+          <t>81.5 - 81.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1602.0 - 1634.0 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -6091,67 +6091,67 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>INDIAMART</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Indiamart Intermesh Ltd.</t>
+          <t>Larsen &amp; Toubro Ltd.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1635.2</v>
+        <v>3929.9</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1624.1 - 1637.7 DR DEMAND</t>
+          <t>3999.0 - 4004.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>3256.29 - 3470.21 DR DEMAND</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -6171,67 +6171,67 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SBFC</t>
+          <t>MRF</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SBFC Finance Ltd.</t>
+          <t>MRF Ltd.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>90.41</v>
+        <v>124580</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>90.01 - 90.5 DR DEMAND</t>
+          <t>125780.0 - 126500.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>98.82 - 104.39 RD SUPPLY</t>
+          <t>101787.0 - 105025.92 DR DEMAND</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -6251,39 +6251,39 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NTPC Ltd.</t>
+          <t>REC Ltd.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6292,26 +6292,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>327.8</v>
+        <v>311.5</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>329.8 - 331.3 RD SUPPLY</t>
+          <t>314.0 - 315.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>394.88 - 409.97 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -6353,17 +6353,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TECHNOE</t>
+          <t>BSOFT</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Techno Electric &amp; Engineering Company Ltd.</t>
+          <t>Birlasoft Ltd.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6372,26 +6372,26 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1005.65</v>
+        <v>281.1</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1023.27 - 1034.04 RD SUPPLY</t>
+          <t>284.15 - 284.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>863.77 - 967.52 DR DEMAND</t>
+          <t>421.73 - 438.51 RD SUPPLY</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -6433,17 +6433,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Jubilant Foodworks Ltd.</t>
+          <t>CESC Ltd.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6452,31 +6452,31 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>491.1</v>
+        <v>142.56</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>500.0 - 503.6 RD SUPPLY</t>
+          <t>144.0 - 144.33 RD SUPPLY</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>477.24 - 497.34 RD SUPPLY</t>
+          <t>133.19 - 139.44 DR DEMAND</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>9.0 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -6513,12 +6513,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>INOXWIND</t>
+          <t>ESCORTS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Inox Wind Ltd.</t>
+          <t>Escorts Kubota Ltd.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6532,26 +6532,26 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>77.90000000000001</v>
+        <v>2796.9</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>78.13 - 78.59 RD SUPPLY</t>
+          <t>2833.9 - 2859.3 RD SUPPLY</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>155.13 - 159.3 RD SUPPLY</t>
+          <t>2679.78 - 2709.64 DR DEMAND</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -6593,17 +6593,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Indian Railway Finance Corporation Ltd.</t>
+          <t>GMR Airports Ltd.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6612,26 +6612,26 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>80</v>
+        <v>99.14</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>81.5 - 81.7 RD SUPPLY</t>
+          <t>100.44 - 100.66 RD SUPPLY</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>112.74 - 115.64 RD SUPPLY</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -6673,17 +6673,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MRF</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MRF Ltd.</t>
+          <t>Hindustan Unilever Ltd.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -6692,26 +6692,26 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>124770</v>
+        <v>1950</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>125780.0 - 126500.0 RD SUPPLY</t>
+          <t>1980.0 - 1990.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>101786.99 - 105025.92 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -6753,17 +6753,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Ltd.</t>
+          <t>Maruti Suzuki India Ltd.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -6772,26 +6772,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2105</v>
+        <v>12230</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2135.1 - 2145.0 RD SUPPLY</t>
+          <t>12350.0 - 12458.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>1966.02 - 2020.42 DR DEMAND</t>
+          <t>14709.27 - 15305.29 RD SUPPLY</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -6833,17 +6833,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>TRITURBINE</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Berger Paints India Ltd.</t>
+          <t>Triveni Turbine Ltd.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -6852,11 +6852,11 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>452.6</v>
+        <v>562.1</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>460.8 - 463.0 RD SUPPLY</t>
+          <t>567.8 - 572.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>560.77 - 590.09 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -6913,17 +6913,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BSOFT</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Birlasoft Ltd.</t>
+          <t>United Breweries Ltd.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -6932,11 +6932,11 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>281.15</v>
+        <v>1242.3</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>284.15 - 284.9 RD SUPPLY</t>
+          <t>1251.5 - 1260.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>421.73 - 438.51 RD SUPPLY</t>
+          <t>1426.85 - 1453.66 RD SUPPLY</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -6993,17 +6993,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CESC Ltd.</t>
+          <t>Grasim Industries Ltd.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7012,31 +7012,31 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>142.52</v>
+        <v>3188.5</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>144.0 - 144.33 RD SUPPLY</t>
+          <t>3209.2 - 3217.3 RD SUPPLY</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>133.19 - 139.44 DR DEMAND</t>
+          <t>2494.13 - 2528.69 DR DEMAND</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -7073,12 +7073,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ESCORTS</t>
+          <t>RHIM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Escorts Kubota Ltd.</t>
+          <t>RHI MAGNESITA INDIA LTD.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7092,31 +7092,31 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2793.6</v>
+        <v>388.85</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2833.9 - 2859.3 RD SUPPLY</t>
+          <t>390.95 - 392.34 RD SUPPLY</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2679.78 - 2709.64 DR DEMAND</t>
+          <t>320.92 - 335.62 DR DEMAND</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7153,17 +7153,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>GRSE</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Garden Reach Shipbuilders &amp; Engineers Ltd.</t>
+          <t>Dixon Technologies (India) Ltd.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7172,11 +7172,11 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2399.7</v>
+        <v>13200</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2411.8 - 2430.0 RD SUPPLY</t>
+          <t>13364.0 - 13434.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -7186,17 +7186,17 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1173.27 - 1243.67 DR DEMAND</t>
+          <t>14838.58 - 14988.47 RD SUPPLY</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -7233,17 +7233,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>IKS</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Inventurus Knowledge Solutions Ltd.</t>
+          <t>Max Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7252,31 +7252,31 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1869.2</v>
+        <v>1562.9</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1870.0 - 1876.2 RD SUPPLY</t>
+          <t>1574.9 - 1591.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>1858.0 - 1933.0 RD SUPPLY</t>
+          <t>950.0 - 998.1 DR DEMAND</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -7313,17 +7313,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>INTELLECT</t>
+          <t>NTPCGREEN</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Intellect Design Arena Ltd.</t>
+          <t>NTPC Green Energy Ltd.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7332,11 +7332,11 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>647.75</v>
+        <v>95.42</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>660.5 - 668.0 RD SUPPLY</t>
+          <t>97.29 - 97.71 RD SUPPLY</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -7346,17 +7346,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>109.85 - 119.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -7393,17 +7393,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>WHIRLPOOL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Maruti Suzuki India Ltd.</t>
+          <t>Whirlpool of India Ltd.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7412,11 +7412,11 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>12190</v>
+        <v>865.25</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>12350.0 - 12458.0 RD SUPPLY</t>
+          <t>872.23 - 888.69 RD SUPPLY</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -7426,17 +7426,17 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>14709.27 - 15305.29 RD SUPPLY</t>
+          <t>766.42 - 785.01 DR DEMAND</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -7473,17 +7473,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SONATSOFTW</t>
+          <t>WOCKPHARMA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Sonata Software Ltd.</t>
+          <t>Wockhardt Ltd.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -7492,11 +7492,11 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>284.45</v>
+        <v>2329.7</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>287.95 - 291.95 RD SUPPLY</t>
+          <t>1967.3 - 2021.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -7506,17 +7506,17 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>2377.0 - 2422.3 RD SUPPLY</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -7553,17 +7553,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries Ltd.</t>
+          <t>Zydus Wellness Ltd.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -7572,11 +7572,11 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1846.4</v>
+        <v>531</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1869.0 - 1891.5 RD SUPPLY</t>
+          <t>534.5 - 537.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -7586,17 +7586,17 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1569.37 - 1580.86 DR DEMAND</t>
+          <t>297.16 - 310.71 DR DEMAND</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -7633,17 +7633,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SWANCORP</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Swan Corp Ltd.</t>
+          <t>Anant Raj Ltd.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -7652,31 +7652,31 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>302.75</v>
+        <v>631.8</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>304.15 - 306.35 RD SUPPLY</t>
+          <t>641.0 - 644.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>721.5 - 809.23 RD SUPPLY</t>
+          <t>855.56 - 945.21 RD SUPPLY</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -7713,12 +7713,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>CONCORDBIO</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Syngene International Ltd.</t>
+          <t>Concord Biotech Ltd.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -7732,31 +7732,31 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>377.5</v>
+        <v>1560.3</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>385.15 - 387.05 RD SUPPLY</t>
+          <t>1588.0 - 1592.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>711.99 - 726.54 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -7793,17 +7793,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>GICRE</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>UltraTech Cement Ltd.</t>
+          <t>General Insurance Corporation of India</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -7812,26 +7812,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>11000</v>
+        <v>344.15</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>11100.0 - 11146.0 RD SUPPLY</t>
+          <t>351.0 - 353.25 RD SUPPLY</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>9784.84 - 9863.33 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -7873,17 +7873,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>GRAPHITE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Castrol India Ltd.</t>
+          <t>Graphite India Ltd.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -7892,26 +7892,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>195.61</v>
+        <v>821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>197.14 - 197.85 RD SUPPLY</t>
+          <t>834.7 - 838.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>144.37 - 156.26 DR DEMAND</t>
+          <t>551.99 - 610.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -7953,17 +7953,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DOMS</t>
+          <t>J&amp;KBANK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DOMS Industries Ltd.</t>
+          <t>Jammu &amp; Kashmir Bank Ltd.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -7972,26 +7972,26 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2098.8</v>
+        <v>149.25</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2121.6 - 2140.0 RD SUPPLY</t>
+          <t>151.37 - 152.17 RD SUPPLY</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>108.0 - 110.01 DR DEMAND</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -8033,12 +8033,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>LTF</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>HDFC Life Insurance Company Ltd.</t>
+          <t>L&amp;T Finance Ltd.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -8052,11 +8052,11 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>559.2</v>
+        <v>310</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>561.0 - 561.95 RD SUPPLY</t>
+          <t>312.8 - 314.3 RD SUPPLY</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -8066,17 +8066,17 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>811.41 - 817.84 RD SUPPLY</t>
+          <t>127.67 - 131.25 DR DEMAND</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -8113,17 +8113,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CIEINDIA</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CIE Automotive India Ltd.</t>
+          <t>APL Apollo Tubes Ltd.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8132,36 +8132,36 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>390.6</v>
+        <v>2195</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>396.8 - 398.1 RD SUPPLY</t>
+          <t>1935.05 - 1937.54 DR DEMAND</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
+          <t>7.5 A</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2226.02 - 2292.57 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>479.0 - 504.0 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>4.0 C</t>
-        </is>
-      </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -8193,17 +8193,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>BERGEPAINT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ITC Ltd.</t>
+          <t>Berger Paints India Ltd.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8212,26 +8212,26 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>265.8</v>
+        <v>459.75</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>267.9 - 268.25 RD SUPPLY</t>
+          <t>460.8 - 463.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>306.55 - 309.47 RD SUPPLY</t>
+          <t>560.77 - 590.09 RD SUPPLY</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -8273,17 +8273,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>BLUEDART</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Bank of Maharashtra</t>
+          <t>Blue Dart Express Ltd.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -8292,36 +8292,36 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>82.40000000000001</v>
+        <v>4799.5</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>83.54 - 83.7 RD SUPPLY</t>
+          <t>4850.5 - 4868.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>91.75 - 94.5 RD SUPPLY</t>
+          <t>5465.7 - 5775.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -8353,17 +8353,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>GRSE</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Max Financial Services Ltd.</t>
+          <t>Garden Reach Shipbuilders &amp; Engineers Ltd.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8372,28 +8372,28 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1554.2</v>
+        <v>2380.6</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1574.9 - 1591.8 RD SUPPLY</t>
+          <t>2411.8 - 2430.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
+          <t>5.0 C</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>1173.27 - 1243.67 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>950.0 - 998.1 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>6.0 B</t>
-        </is>
-      </c>
       <c r="J100" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -8401,7 +8401,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -8433,17 +8433,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SCHNEIDER</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Schneider Electric Infrastructure Ltd.</t>
+          <t>Hero MotoCorp Ltd.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -8452,11 +8452,11 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1214.2</v>
+        <v>5394</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>1232.4 - 1235.7 RD SUPPLY</t>
+          <t>5424.0 - 5443.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>540.0 - 575.5 DR DEMAND</t>
+          <t>5627.23 - 5755.34 RD SUPPLY</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -8513,17 +8513,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BEML</t>
+          <t>JSWINFRA</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BEML Ltd.</t>
+          <t>JSW Infrastructure Ltd.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -8532,26 +8532,26 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2096.8</v>
+        <v>363.6</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2138.41 - 2142.39 RD SUPPLY</t>
+          <t>369.0 - 375.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>1159.43 - 1211.03 DR DEMAND</t>
+          <t>216.99 - 253.34 DR DEMAND</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -8593,17 +8593,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CENTRALBK</t>
+          <t>KIMS</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Central Bank of India</t>
+          <t>Krishna Institute of Medical Sciences Ltd.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -8612,31 +8612,31 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>31.37</v>
+        <v>798.05</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>31.73 - 32.4 RD SUPPLY</t>
+          <t>811.8 - 819.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>35.83 - 36.93 RD SUPPLY</t>
+          <t>748.3 - 753.1 DR DEMAND</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -8673,12 +8673,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>GESHIP</t>
+          <t>LGEINDIA</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Great Eastern Shipping Co. Ltd.</t>
+          <t>LG Electronics India Ltd.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -8692,26 +8692,26 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1462</v>
+        <v>1694.2</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>1490.0 - 1495.1 RD SUPPLY</t>
+          <t>1696.9 - 1706.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>762.54 - 775.16 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -8753,17 +8753,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>GRAPHITE</t>
+          <t>LTFOODS</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Graphite India Ltd.</t>
+          <t>LT Foods Ltd.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -8772,21 +8772,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>827.75</v>
+        <v>430</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>834.7 - 838.0 RD SUPPLY</t>
+          <t>430.8 - 433.45 RD SUPPLY</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>551.99 - 610.0 DR DEMAND</t>
+          <t>285.59 - 341.87 DR DEMAND</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -8833,17 +8833,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>RAILTEL</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Railtel Corporation Of India Ltd.</t>
+          <t>Mahindra &amp; Mahindra Ltd.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -8852,26 +8852,26 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>263.9</v>
+        <v>3035</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>266.0 - 267.7 RD SUPPLY</t>
+          <t>3082.0 - 3127.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>3465.0 - 3534.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -8913,17 +8913,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>3MINDIA</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>3M India Ltd.</t>
+          <t>Narayana Hrudayalaya Ltd.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -8932,11 +8932,11 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>34220</v>
+        <v>1919.3</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>34890.0 - 35095.0 RD SUPPLY</t>
+          <t>1932.1 - 1940.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>28319.86 - 29690.02 DR DEMAND</t>
+          <t>2170.07 - 2359.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -8961,7 +8961,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8993,17 +8993,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AARTIIND</t>
+          <t>NIVABUPA</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Aarti Industries Ltd.</t>
+          <t>Niva Bupa Health Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9012,16 +9012,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>496</v>
+        <v>80.23</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>502.7 - 503.75 RD SUPPLY</t>
+          <t>81.5 - 83.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -9073,12 +9073,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>NUVOCO</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>APL Apollo Tubes Ltd.</t>
+          <t>Nuvoco Vistas Corporation Ltd.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -9092,21 +9092,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2195</v>
+        <v>344.75</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>1935.05 - 1937.54 DR DEMAND</t>
+          <t>283.4 - 285.05 DR DEMAND</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2226.02 - 2292.57 RD SUPPLY</t>
+          <t>348.65 - 365.75 RD SUPPLY</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -9153,17 +9153,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BLUEDART</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Blue Dart Express Ltd.</t>
+          <t>Punjab National Bank</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9172,36 +9172,36 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4786.6</v>
+        <v>118.3</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>4850.5 - 4868.9 RD SUPPLY</t>
+          <t>118.45 - 118.74 RD SUPPLY</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>5465.7 - 5775.5 RD SUPPLY</t>
+          <t>80.71 - 82.53 DR DEMAND</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -9233,17 +9233,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>SWIGGY</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Hero MotoCorp Ltd.</t>
+          <t>Swiggy Ltd.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9252,11 +9252,11 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5373</v>
+        <v>278.5</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>5424.0 - 5443.0 RD SUPPLY</t>
+          <t>284.1 - 285.55 RD SUPPLY</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>5627.23 - 5755.34 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -9313,17 +9313,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Hindustan Unilever Ltd.</t>
+          <t>Syngene International Ltd.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -9332,11 +9332,11 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1933.8</v>
+        <v>381.85</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>1962.0 - 1977.0 RD SUPPLY</t>
+          <t>385.15 - 387.05 RD SUPPLY</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>711.99 - 726.54 RD SUPPLY</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -9393,17 +9393,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>LGEINDIA</t>
+          <t>TATACAP</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>LG Electronics India Ltd.</t>
+          <t>Tata Capital Ltd.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -9412,16 +9412,16 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1663.7</v>
+        <v>350.05</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>1696.9 - 1706.9 RD SUPPLY</t>
+          <t>351.35 - 355.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -9436,17 +9436,17 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9473,17 +9473,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>USHAMART</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Ltd.</t>
+          <t>Usha Martin Ltd.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -9492,36 +9492,36 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3044.5</v>
+        <v>535.05</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>3082.0 - 3127.8 RD SUPPLY</t>
+          <t>541.0 - 542.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>3465.0 - 3534.6 RD SUPPLY</t>
+          <t>274.28 - 291.22 DR DEMAND</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -9553,12 +9553,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Nestle India Ltd.</t>
+          <t>Varun Beverages Ltd.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -9572,11 +9572,11 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1363.9</v>
+        <v>436.15</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>1384.5 - 1397.0 RD SUPPLY</t>
+          <t>439.3 - 443.3 RD SUPPLY</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -9586,12 +9586,12 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>1153.85 - 1169.18 DR DEMAND</t>
+          <t>396.2 - 400.45 DR DEMAND</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -9633,17 +9633,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>NIVABUPA</t>
+          <t>CENTRALBK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Niva Bupa Health Insurance Company Ltd.</t>
+          <t>Central Bank of India</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -9652,26 +9652,26 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>80.83</v>
+        <v>31.63</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>81.5 - 83.9 RD SUPPLY</t>
+          <t>31.73 - 32.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>35.83 - 36.93 RD SUPPLY</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -9713,17 +9713,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>PAGEIND</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Page Industries Ltd.</t>
+          <t>Capri Global Capital Ltd.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -9732,16 +9732,16 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>37150</v>
+        <v>268.6</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>37164.81 - 37483.06 RD SUPPLY</t>
+          <t>272.95 - 273.65 RD SUPPLY</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -9756,17 +9756,17 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -9776,7 +9776,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -9793,17 +9793,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>IGIL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Punjab National Bank</t>
+          <t>International Gemological Institute Ltd.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -9812,36 +9812,36 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>117</v>
+        <v>331.65</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>118.45 - 118.74 RD SUPPLY</t>
+          <t>332.25 - 337.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>80.71 - 82.53 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -9873,12 +9873,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SWIGGY</t>
+          <t>LEMONTREE</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Swiggy Ltd.</t>
+          <t>Lemon Tree Hotels Ltd.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -9892,16 +9892,16 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>284.05</v>
+        <v>107.92</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>284.1 - 285.55 RD SUPPLY</t>
+          <t>108.53 - 108.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -9936,7 +9936,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -9953,17 +9953,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>USHAMART</t>
+          <t>MGL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Usha Martin Ltd.</t>
+          <t>Mahanagar Gas Ltd.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -9972,41 +9972,41 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>531.3</v>
+        <v>1092.8</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>541.0 - 542.6 RD SUPPLY</t>
+          <t>1103.2 - 1109.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>274.28 - 291.22 DR DEMAND</t>
+          <t>885.65 - 912.91 DR DEMAND</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -10033,17 +10033,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>WELCORP</t>
+          <t>CEATLTD</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Welspun Corp Ltd.</t>
+          <t>Ceat Ltd.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -10052,36 +10052,36 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2731.5</v>
+        <v>3432.2</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2776.9 - 2784.8 RD SUPPLY</t>
+          <t>3471.2 - 3529.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>658.55 - 760.86 DR DEMAND</t>
+          <t>2297.7 - 2483.48 DR DEMAND</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -10113,17 +10113,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Adani Green Energy Ltd.</t>
+          <t>Life Insurance Corporation of India</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -10132,26 +10132,26 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1304</v>
+        <v>407.5</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>1330.6 - 1346.8 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>765.0 - 814.2 DR DEMAND</t>
+          <t>414.97 - 443.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -10193,17 +10193,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>POLYMED</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Coal India Ltd.</t>
+          <t>Poly Medicure Ltd.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10212,26 +10212,26 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>428</v>
+        <v>1726.6</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>434.23 - 436.47 RD SUPPLY</t>
+          <t>1728.0 - 1748.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1297.34 - 1337.36 DR DEMAND</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -10273,17 +10273,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>IGIL</t>
+          <t>SWANCORP</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>International Gemological Institute Ltd.</t>
+          <t>Swan Corp Ltd.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -10292,26 +10292,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>326.95</v>
+        <v>300.05</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>332.25 - 337.9 RD SUPPLY</t>
+          <t>304.15 - 306.35 RD SUPPLY</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>721.5 - 809.23 RD SUPPLY</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -10353,12 +10353,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>LEMONTREE</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Lemon Tree Hotels Ltd.</t>
+          <t>Indian Hotels Co. Ltd.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -10372,11 +10372,11 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>107.51</v>
+        <v>743.7</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>108.53 - 108.8 RD SUPPLY</t>
+          <t>752.3 - 754.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -10386,17 +10386,17 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>871.1 - 888.32 RD SUPPLY</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -10433,17 +10433,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RKFORGE</t>
+          <t>3MINDIA</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ramkrishna Forgings Ltd.</t>
+          <t>3M India Ltd.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -10452,26 +10452,26 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>716.25</v>
+        <v>34615</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>725.0 - 728.0 RD SUPPLY</t>
+          <t>34890.0 - 35095.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>459.41 - 465.85 DR DEMAND</t>
+          <t>28319.86 - 29690.02 DR DEMAND</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -10513,17 +10513,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>POLYMED</t>
+          <t>FIVESTAR</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Poly Medicure Ltd.</t>
+          <t>Five-Star Business Finance Ltd.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -10532,26 +10532,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1699</v>
+        <v>549.7</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>1728.0 - 1748.0 RD SUPPLY</t>
+          <t>550.2 - 552.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>1297.34 - 1337.36 DR DEMAND</t>
+          <t>412.05 - 443.54 DR DEMAND</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -10593,17 +10593,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>JYOTICNC</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Enterprise Ltd.</t>
+          <t>Jyoti CNC Automation Ltd.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -10612,26 +10612,26 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>8835.5</v>
+        <v>1100.8</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>9000.0 - 9024.0 RD SUPPLY</t>
+          <t>1113.85 - 1134.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>580.1 - 596.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>4.5 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -10673,17 +10673,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>MEDANTA</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Clean Science and Technology Ltd.</t>
+          <t>Global Health Ltd.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -10692,11 +10692,11 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>833.2</v>
+        <v>1496.1</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>846.0 - 858.7 RD SUPPLY</t>
+          <t>1520.5 - 1544.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -10706,12 +10706,12 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>1538.62 - 1583.15 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -10753,17 +10753,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>TBOTEK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>LIC Housing Finance Ltd.</t>
+          <t>TBO Tek Ltd.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -10772,11 +10772,11 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>565</v>
+        <v>1704.5</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>574.07 - 586.43 RD SUPPLY</t>
+          <t>1733.7 - 1743.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -10786,12 +10786,12 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>449.87 - 485.5 DR DEMAND</t>
+          <t>1004.2 - 1057.3 DR DEMAND</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -10833,12 +10833,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TBOTEK</t>
+          <t>JSWDULUX</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TBO Tek Ltd.</t>
+          <t>JSW Dulux Ltd.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -10852,26 +10852,26 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1703.7</v>
+        <v>3160.9</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>1733.7 - 1743.9 RD SUPPLY</t>
+          <t>3169.9 - 3195.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>1004.2 - 1057.3 DR DEMAND</t>
+          <t>2862.0 - 2938.8 DR DEMAND</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 6 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>3.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -10913,17 +10913,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>JSWDULUX</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>JSW Dulux Ltd.</t>
+          <t>Mankind Pharma Ltd.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -10932,11 +10932,11 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3137.1</v>
+        <v>2465</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>3169.9 - 3195.0 RD SUPPLY</t>
+          <t>2483.0 - 2497.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2862.0 - 2938.8 DR DEMAND</t>
+          <t>1909.7 - 2005.8 DR DEMAND</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>🔴 6 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -10993,17 +10993,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>CHALET</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Mankind Pharma Ltd.</t>
+          <t>Chalet Hotels Ltd.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -11012,26 +11012,26 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2480</v>
+        <v>884.05</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2483.0 - 2497.9 RD SUPPLY</t>
+          <t>898.87 - 912.96 RD SUPPLY</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>1909.7 - 2005.8 DR DEMAND</t>
+          <t>972.81 - 1050.08 RD SUPPLY</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🔴 4 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>3.5 / 10 SUPPLY</t>
+          <t>3.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -11073,17 +11073,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Indian Hotels Co. Ltd.</t>
+          <t>LIC Housing Finance Ltd.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -11092,26 +11092,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>736.25</v>
+        <v>572.5</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>751.2 - 757.4 RD SUPPLY</t>
+          <t>574.07 - 586.43 RD SUPPLY</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>871.1 - 888.32 RD SUPPLY</t>
+          <t>449.87 - 485.5 DR DEMAND</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🔴 4 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -11136,7 +11136,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2.5 / 10 SUPPLY</t>
+          <t>3.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -11153,17 +11153,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>LLOYDSME</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Lloyds Metals And Energy Ltd.</t>
+          <t>Clean Science and Technology Ltd.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11172,26 +11172,26 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1857.4</v>
+        <v>836.6</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>1848.7 - 1859.4 RD SUPPLY</t>
+          <t>846.0 - 858.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>1042.28 - 1072.36 DR DEMAND</t>
+          <t>1538.62 - 1583.15 RD SUPPLY</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -11216,34 +11216,34 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>2.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>COHANCE</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Anant Raj Ltd.</t>
+          <t>Cohance Lifesciences Ltd.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -11252,26 +11252,26 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>610.1</v>
+        <v>461.45</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>606.15 - 611.7 RD SUPPLY</t>
+          <t>462.35 - 467.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>855.56 - 945.21 RD SUPPLY</t>
+          <t>1229.95 - 1328.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -11281,7 +11281,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -11296,34 +11296,34 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>2.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Saregama India Ltd</t>
+          <t>HDFC Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -11332,31 +11332,31 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>503.35</v>
+        <v>561.5</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>500.0 - 506.6 RD SUPPLY</t>
+          <t>561.0 - 561.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>811.41 - 817.84 RD SUPPLY</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -11393,17 +11393,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ASAHIINDIA</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Asahi India Glass Ltd.</t>
+          <t>Jubilant Foodworks Ltd.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -11412,26 +11412,26 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>965.15</v>
+        <v>483.3</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>961.05 - 968.0 RD SUPPLY</t>
+          <t>408.55 - 410.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>477.24 - 497.34 RD SUPPLY</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -11473,17 +11473,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>SPLPETRO</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Emcure Pharmaceuticals Ltd.</t>
+          <t>Supreme Petrochem Ltd.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -11492,26 +11492,26 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1975</v>
+        <v>882.2</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>1834.83 - 1851.1 DR DEMAND</t>
+          <t>688.05 - 691.15 DR DEMAND</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>1962.18 - 2044.02 RD SUPPLY</t>
+          <t>854.83 - 887.11 RD SUPPLY</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -11553,17 +11553,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SUNDARMFIN</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Sundaram Finance Ltd.</t>
+          <t>Emcure Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -11572,28 +11572,28 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4751.9</v>
+        <v>1981.7</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>4751.3 - 4790.0 RD SUPPLY</t>
+          <t>1834.83 - 1851.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
+          <t>8.5 A</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>1962.18 - 2044.02 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>5480.6 - 5612.41 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>8.0 A</t>
-        </is>
-      </c>
       <c r="J140" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -11633,17 +11633,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Glaxosmithkline Pharmaceuticals Ltd.</t>
+          <t>IDFC First Bank Ltd.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -11652,26 +11652,26 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2873.6</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2856.2 - 2878.0 RD SUPPLY</t>
+          <t>87.81 - 88.1 RD SUPPLY</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>1849.2 - 1903.26 DR DEMAND</t>
+          <t>57.91 - 58.68 DR DEMAND</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -11681,12 +11681,12 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -11713,17 +11713,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Gabriel India Ltd.</t>
+          <t>Nestle India Ltd.</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -11732,11 +11732,11 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1471.4</v>
+        <v>1387.2</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>1469.0 - 1484.4 RD SUPPLY</t>
+          <t>1384.5 - 1397.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -11746,17 +11746,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>794.06 - 824.64 DR DEMAND</t>
+          <t>1153.85 - 1169.18 DR DEMAND</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -11766,7 +11766,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -11776,7 +11776,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -11793,12 +11793,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>PAGEIND</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Kajaria Ceramics Ltd.</t>
+          <t>Page Industries Ltd.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -11812,31 +11812,31 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1183.6</v>
+        <v>37340</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>1055.21 - 1067.25 DR DEMAND</t>
+          <t>37164.81 - 37483.06 RD SUPPLY</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>1181.73 - 1240.58 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -11873,17 +11873,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SPLPETRO</t>
+          <t>GLAXO</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Supreme Petrochem Ltd.</t>
+          <t>Glaxosmithkline Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -11892,26 +11892,26 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>864.75</v>
+        <v>2876.9</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>688.05 - 691.15 DR DEMAND</t>
+          <t>2856.2 - 2878.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>854.83 - 887.11 RD SUPPLY</t>
+          <t>1849.2 - 1903.26 DR DEMAND</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11936,7 +11936,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -11953,17 +11953,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CARBORUNIV</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Carborundum Universal Ltd.</t>
+          <t>Kajaria Ceramics Ltd.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -11972,26 +11972,26 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1211.3</v>
+        <v>1216.4</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>990.84 - 995.43 DR DEMAND</t>
+          <t>1175.7 - 1183.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>1181.58 - 1303.79 RD SUPPLY</t>
+          <t>1181.73 - 1240.58 RD SUPPLY</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -12033,17 +12033,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>HOMEFIRST</t>
+          <t>CARBORUNIV</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Home First Finance Company India Ltd.</t>
+          <t>Carborundum Universal Ltd.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -12052,21 +12052,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1212.5</v>
+        <v>1264.5</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>1151.9 - 1160.0 DR DEMAND</t>
+          <t>990.84 - 995.43 DR DEMAND</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>1184.37 - 1233.14 RD SUPPLY</t>
+          <t>1181.58 - 1303.79 RD SUPPLY</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -12113,17 +12113,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>HOMEFIRST</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Ltd.</t>
+          <t>Home First Finance Company India Ltd.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -12132,21 +12132,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1162.3</v>
+        <v>1205.8</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>1161.7 - 1167.7 RD SUPPLY</t>
+          <t>1151.9 - 1160.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>855.18 - 875.51 DR DEMAND</t>
+          <t>1184.37 - 1233.14 RD SUPPLY</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -12193,17 +12193,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>POONAWALLA</t>
+          <t>HONASA</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Poonawalla Fincorp Ltd.</t>
+          <t>Honasa Consumer Ltd.</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -12212,26 +12212,26 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>471.9</v>
+        <v>484.9</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>425.0 - 428.45 DR DEMAND</t>
+          <t>483.8 - 488.71 RD SUPPLY</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>454.8 - 503.0 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>3.0 / 10 SUPPLY</t>
+          <t>3.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -12273,17 +12273,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>POONAWALLA</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Phoenix Mills Ltd.</t>
+          <t>Poonawalla Fincorp Ltd.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -12292,26 +12292,26 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1953.4</v>
+        <v>478.85</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2090.43 - 2097.12 RD SUPPLY</t>
+          <t>425.0 - 428.45 DR DEMAND</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>1851.05 - 1990.36 RD SUPPLY</t>
+          <t>454.8 - 503.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2.5 / 10 SUPPLY</t>
+          <t>3.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P99"/>
+  <dimension ref="A1:P101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,17 +513,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ABSLAMC</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aditya Birla Sun Life AMC Ltd.</t>
+          <t>Axis Bank Ltd.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -532,11 +532,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>955.9</v>
+        <v>1226</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>955.16 - 963.07 DR DEMAND</t>
+          <t>1175.0 - 1186.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>721.52 - 740.88 DR DEMAND</t>
+          <t>1208.6 - 1229.5 DR DEMAND</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -593,17 +593,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Axis Bank Ltd.</t>
+          <t>CESC Ltd.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -612,21 +612,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1212.1</v>
+        <v>133.85</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1175.0 - 1186.5 DR DEMAND</t>
+          <t>144.0 - 144.33 RD SUPPLY</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1208.6 - 1229.5 DR DEMAND</t>
+          <t>133.19 - 139.44 DR DEMAND</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -673,17 +673,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CESC Ltd.</t>
+          <t>Glenmark Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -692,31 +692,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>133.87</v>
+        <v>2334.7</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>144.0 - 144.33 RD SUPPLY</t>
+          <t>2292.0 - 2325.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>133.19 - 139.44 DR DEMAND</t>
+          <t>1331.41 - 1376.45 DR DEMAND</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -726,44 +726,44 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>BUY READY</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gabriel India Ltd.</t>
+          <t>Anant Raj Ltd.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -772,21 +772,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1303.9</v>
+        <v>598.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1281.6 - 1290.3 DR DEMAND</t>
+          <t>594.0 - 595.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>794.06 - 824.64 DR DEMAND</t>
+          <t>855.56 - 945.21 RD SUPPLY</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>11.5 / 10 SUPER COMBO</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -833,17 +833,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mazagoan Dock Shipbuilders Ltd.</t>
+          <t>Chambal Fertilizers &amp; Chemicals Ltd.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -852,21 +852,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2087.1</v>
+        <v>409.25</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2053.69 - 2061.48 DR DEMAND</t>
+          <t>401.4 - 407.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1900.61 - 2111.67 DR DEMAND</t>
+          <t>404.75 - 434.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>11.5 / 10 SUPER COMBO</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -913,17 +913,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Enterprise Ltd.</t>
+          <t>Craftsman Automation Ltd.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>8659</v>
+        <v>10417</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8544.05 - 8590.0 DR DEMAND</t>
+          <t>10205.0 - 10251.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -966,17 +966,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>11.0 / 10 SUPER COMBO</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -993,17 +993,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>HBLENGINE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Divi's Laboratories Ltd.</t>
+          <t>HBL Engineering Ltd.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1012,26 +1012,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>9431</v>
+        <v>794.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9312.5 - 9330.0 DR DEMAND</t>
+          <t>773.65 - 784.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5624.31 - 5922.58 DR DEMAND</t>
+          <t>647.1 - 656.44 DR DEMAND</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>11.0 / 10 SUPER COMBO</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1073,17 +1073,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VIJAYA</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vijaya Diagnostic Centre Ltd.</t>
+          <t>Jindal Stainless Ltd.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1092,26 +1092,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1475</v>
+        <v>747.4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1438.01 - 1450.49 DR DEMAND</t>
+          <t>736.0 - 738.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>846.83 - 860.21 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>10.5 / 10 HIGH COMBO</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1153,17 +1153,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>CHOLAHLDNG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anant Raj Ltd.</t>
+          <t>Cholamandalam Financial Holdings Ltd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1172,31 +1172,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>602.3</v>
+        <v>1386.2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>594.0 - 595.2 DR DEMAND</t>
+          <t>1341.0 - 1361.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>855.56 - 945.21 RD SUPPLY</t>
+          <t>1358.29 - 1396.78 DR DEMAND</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1233,17 +1233,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chambal Fertilizers &amp; Chemicals Ltd.</t>
+          <t>Granules India Ltd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1252,31 +1252,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>413.55</v>
+        <v>846.55</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>401.4 - 407.5 DR DEMAND</t>
+          <t>829.0 - 835.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>404.75 - 434.2 DR DEMAND</t>
+          <t>419.84 - 453.47 DR DEMAND</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1291,12 +1291,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1313,17 +1313,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>City Union Bank Ltd.</t>
+          <t>Hindalco Industries Ltd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PVTBANK</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1332,31 +1332,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>214.91</v>
+        <v>941.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>211.34 - 212.2 DR DEMAND</t>
+          <t>935.1 - 936.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>177.59 - 189.81 DR DEMAND</t>
+          <t>766.15 - 804.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jindal Stainless Ltd.</t>
+          <t>SBI Cards and Payment Services Ltd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1412,31 +1412,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>738.3</v>
+        <v>578.05</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>736.0 - 738.0 DR DEMAND</t>
+          <t>565.45 - 568.25 DR DEMAND</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>565.45 - 593.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>178.75</v>
+        <v>177.68</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1553,17 +1553,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kfin Technologies Ltd.</t>
+          <t>Infosys Ltd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1572,26 +1572,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>838.2</v>
+        <v>994.1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>826.8 - 836.62 DR DEMAND</t>
+          <t>982.4 - 985.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1329.97 - 1360.84 RD SUPPLY</t>
+          <t>982.4 - 1000.4 DR DEMAND</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1633,17 +1633,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LTTS</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>Kfin Technologies Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1652,26 +1652,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3081.6</v>
+        <v>840</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3030.0 - 3047.7 DR DEMAND</t>
+          <t>826.8 - 836.62 DR DEMAND</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2976.44 - 3086.89 DR DEMAND</t>
+          <t>1329.97 - 1360.84 RD SUPPLY</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1686,17 +1686,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1713,17 +1713,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FSN E-Commerce Ventures Ltd.</t>
+          <t>Welspun Corp Ltd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1732,26 +1732,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>327.35</v>
+        <v>2717</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>322.7 - 323.75 DR DEMAND</t>
+          <t>2675.0 - 2692.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>232.05 - 235.0 DR DEMAND</t>
+          <t>658.55 - 760.86 DR DEMAND</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1793,12 +1793,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>COROMANDEL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SRF Ltd.</t>
+          <t>Coromandel International Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1812,26 +1812,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2420.1</v>
+        <v>1758.2</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2376.78 - 2395.25 DR DEMAND</t>
+          <t>1704.84 - 1749.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3066.4 - 3131.26 RD SUPPLY</t>
+          <t>1704.84 - 1751.89 DR DEMAND</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1873,17 +1873,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AAVAS</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aavas Financiers Ltd.</t>
+          <t>NATCO Pharma Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1892,26 +1892,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1248.4</v>
+        <v>827.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1242.7 - 1246.1 DR DEMAND</t>
+          <t>845.0 - 851.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1060.4 - 1078.0 DR DEMAND</t>
+          <t>803.32 - 821.11 DR DEMAND</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1953,17 +1953,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>POLYMED</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Amber Enterprises India Ltd.</t>
+          <t>Poly Medicure Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1972,31 +1972,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6606.5</v>
+        <v>1673.8</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>6151.0 - 6170.5 DR DEMAND</t>
+          <t>1635.65 - 1644.33 DR DEMAND</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6120.0 - 6549.0 DR DEMAND</t>
+          <t>1297.34 - 1337.36 DR DEMAND</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2033,17 +2033,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CENTRALBK</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Central Bank of India</t>
+          <t>Tube Investments of India Ltd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2052,26 +2052,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>30.04</v>
+        <v>2375</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>29.32 - 29.62 DR DEMAND</t>
+          <t>2161.89 - 2177.97 DR DEMAND</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>35.83 - 36.93 RD SUPPLY</t>
+          <t>2161.89 - 2330.75 DR DEMAND</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2113,12 +2113,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bharti Airtel Ltd.</t>
+          <t>Amber Enterprises India Ltd.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2132,26 +2132,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1771.2</v>
+        <v>6672.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1748.99 - 1753.04 DR DEMAND</t>
+          <t>6151.0 - 6170.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1527.35 - 1537.83 DR DEMAND</t>
+          <t>6120.0 - 6549.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2193,17 +2193,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>CHOICEIN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bharat Heavy Electricals Ltd.</t>
+          <t>Choice International Ltd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2212,36 +2212,36 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>413.35</v>
+        <v>726.25</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>406.0 - 410.6 DR DEMAND</t>
+          <t>721.6 - 725.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>6.0 B</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>840.3 - 860.5 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>4.5 C</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>204.46 - 207.34 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>7.5 A</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2273,17 +2273,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>KIMS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Petronet LNG Ltd.</t>
+          <t>Krishna Institute of Medical Sciences Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2292,51 +2292,51 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>282.95</v>
+        <v>746.4</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>280.3 - 281.75 DR DEMAND</t>
+          <t>725.4 - 735.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>232.67 - 245.62 DR DEMAND</t>
+          <t>474.05 - 496.35 DR DEMAND</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2353,17 +2353,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>POLYMED</t>
+          <t>OLAELEC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Poly Medicure Ltd.</t>
+          <t>Ola Electric Mobility Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2372,26 +2372,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1644.7</v>
+        <v>36.92</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1635.65 - 1644.33 DR DEMAND</t>
+          <t>36.05 - 36.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1297.34 - 1337.36 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2433,17 +2433,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>State Bank of India</t>
+          <t>UltraTech Cement Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2452,26 +2452,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>964.7</v>
+        <v>10956</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1108.0 - 1124.5 RD SUPPLY</t>
+          <t>10800.0 - 10829.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>933.9 - 964.4 DR DEMAND</t>
+          <t>9784.84 - 9863.33 DR DEMAND</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2513,17 +2513,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>ZFCVINDIA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capri Global Capital Ltd.</t>
+          <t>ZF Commercial Vehicle Control Systems India Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2532,36 +2532,36 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>246.9</v>
+        <v>2341</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>243.67 - 244.62 DR DEMAND</t>
+          <t>2285.0 - 2297.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>2046.79 - 2067.08 DR DEMAND</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2593,12 +2593,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vodafone Idea Ltd.</t>
+          <t>Bharti Airtel Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2612,26 +2612,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>13.56</v>
+        <v>1757</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>13.46 - 13.51 DR DEMAND</t>
+          <t>1748.99 - 1753.04 DR DEMAND</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>8.13 - 8.53 DR DEMAND</t>
+          <t>1527.35 - 1537.83 DR DEMAND</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2673,17 +2673,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Infosys Ltd.</t>
+          <t>Bharat Heavy Electricals Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2692,36 +2692,36 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1015.4</v>
+        <v>415.5</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>982.4 - 985.3 DR DEMAND</t>
+          <t>406.0 - 410.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>982.4 - 1000.4 DR DEMAND</t>
+          <t>204.46 - 207.34 DR DEMAND</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2753,17 +2753,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NLC India Ltd.</t>
+          <t>Petronet LNG Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2772,31 +2772,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>255.75</v>
+        <v>284.5</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>254.06 - 255.11 DR DEMAND</t>
+          <t>280.3 - 281.75 DR DEMAND</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>217.4 - 220.48 DR DEMAND</t>
+          <t>232.67 - 245.62 DR DEMAND</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2833,17 +2833,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tata Communications Ltd.</t>
+          <t>RBL Bank Ltd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>PVTBANK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2852,36 +2852,36 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1654.7</v>
+        <v>403.35</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1640.2 - 1649.3 DR DEMAND</t>
+          <t>401.1 - 402.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1310.58 - 1335.75 DR DEMAND</t>
+          <t>286.46 - 290.25 DR DEMAND</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2913,17 +2913,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Ltd.</t>
+          <t>Capri Global Capital Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2932,36 +2932,36 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2032.4</v>
+        <v>247.45</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1966.02 - 1971.79 DR DEMAND</t>
+          <t>243.67 - 244.62 DR DEMAND</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1966.02 - 2020.42 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2993,17 +2993,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ZENSARTECH</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Zensar Technolgies Ltd.</t>
+          <t>Delhivery Ltd.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3012,11 +3012,11 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>429</v>
+        <v>409.7</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>416.15 - 422.4 DR DEMAND</t>
+          <t>405.05 - 407.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3026,12 +3026,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>510.15 - 553.1 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3073,17 +3073,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AIAENG</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AIA Engineering Ltd.</t>
+          <t>Max Healthcare Institute Ltd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3092,26 +3092,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3835.7</v>
+        <v>929.8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>3778.0 - 3805.8 DR DEMAND</t>
+          <t>918.17 - 923.96 DR DEMAND</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>5062.37 - 5160.6 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3121,22 +3121,22 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3153,17 +3153,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SCHAEFFLER</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Schaeffler India Ltd.</t>
+          <t>Tata Communications Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3172,26 +3172,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3920</v>
+        <v>1656.2</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>3811.1 - 3860.2 DR DEMAND</t>
+          <t>1640.2 - 1649.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3489.69 - 3548.8 DR DEMAND</t>
+          <t>1310.58 - 1335.75 DR DEMAND</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3201,22 +3201,22 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3233,17 +3233,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ashok Leyland Ltd.</t>
+          <t>Tata Consultancy Services Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3252,26 +3252,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>153.44</v>
+        <v>2050.6</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>150.3 - 151.46 DR DEMAND</t>
+          <t>1966.02 - 1971.79 DR DEMAND</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>207.56 - 211.81 RD SUPPLY</t>
+          <t>1966.02 - 2020.42 DR DEMAND</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3291,12 +3291,12 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3313,17 +3313,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>AIAENG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HDFC Life Insurance Company Ltd.</t>
+          <t>AIA Engineering Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3332,26 +3332,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>523.55</v>
+        <v>3869</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>508.7 - 514.0 DR DEMAND</t>
+          <t>3778.0 - 3805.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>811.41 - 817.84 RD SUPPLY</t>
+          <t>5062.37 - 5160.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3393,17 +3393,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>ESCORTS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Navin Fluorine International Ltd.</t>
+          <t>Escorts Kubota Ltd.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3412,36 +3412,36 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>8234.5</v>
+        <v>2715.2</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>8110.0 - 8151.0 DR DEMAND</t>
+          <t>2855.7 - 2866.3 RD SUPPLY</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4173.89 - 4245.43 DR DEMAND</t>
+          <t>2679.78 - 2709.64 DR DEMAND</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3473,12 +3473,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Saregama India Ltd</t>
+          <t>Vodafone Idea Ltd.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3492,31 +3492,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>493.45</v>
+        <v>12.95</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>484.5 - 488.2 DR DEMAND</t>
+          <t>12.79 - 12.89 DR DEMAND</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>8.13 - 8.53 DR DEMAND</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3553,12 +3553,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>IFCI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BSE Ltd.</t>
+          <t>IFCI Ltd.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3572,26 +3572,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3200</v>
+        <v>68.77</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>3085.1 - 3161.0 DR DEMAND</t>
+          <t>68.15 - 68.52 DR DEMAND</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2563.45 - 2625.28 DR DEMAND</t>
+          <t>46.4 - 47.88 DR DEMAND</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3601,12 +3601,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3633,12 +3633,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ENDURANCE</t>
+          <t>SCHAEFFLER</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Endurance Technologies Ltd.</t>
+          <t>Schaeffler India Ltd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3652,26 +3652,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2654.8</v>
+        <v>3897.1</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2538.15 - 2615.93 DR DEMAND</t>
+          <t>3811.1 - 3860.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1661.59 - 1735.99 DR DEMAND</t>
+          <t>3489.69 - 3548.8 DR DEMAND</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3713,17 +3713,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Indian Hotels Co. Ltd.</t>
+          <t>Ashok Leyland Ltd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3732,51 +3732,51 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>714.35</v>
+        <v>154.19</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>706.05 - 713.55 DR DEMAND</t>
+          <t>150.3 - 151.46 DR DEMAND</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>871.1 - 888.32 RD SUPPLY</t>
+          <t>207.56 - 211.81 RD SUPPLY</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3793,17 +3793,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kalyan Jewellers India Ltd.</t>
+          <t>Navin Fluorine International Ltd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3812,11 +3812,11 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>568.85</v>
+        <v>8245</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>560.16 - 562.31 DR DEMAND</t>
+          <t>8110.0 - 8151.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3826,12 +3826,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>590.56 - 613.39 RD SUPPLY</t>
+          <t>4173.89 - 4245.43 DR DEMAND</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3873,17 +3873,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MEDANTA</t>
+          <t>SCHNEIDER</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Global Health Ltd.</t>
+          <t>Schneider Electric Infrastructure Ltd.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3892,36 +3892,36 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1415.1</v>
+        <v>1203.4</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1382.71 - 1393.91 DR DEMAND</t>
+          <t>1186.4 - 1193.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>540.0 - 575.5 DR DEMAND</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3953,17 +3953,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FACT</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Fertilisers and Chemicals Travancore Ltd.</t>
+          <t>Dixon Technologies (India) Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3972,26 +3972,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>757.2</v>
+        <v>13100</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>738.0 - 749.15 DR DEMAND</t>
+          <t>12838.12 - 12924.05 DR DEMAND</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>14838.58 - 14988.47 RD SUPPLY</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4001,22 +4001,22 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4033,17 +4033,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>UTIAMC</t>
+          <t>ENDURANCE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>UTI Asset Management Company Ltd.</t>
+          <t>Endurance Technologies Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4052,28 +4052,28 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>877.6</v>
+        <v>2656.5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1039.08 - 1043.74 RD SUPPLY</t>
+          <t>2538.15 - 2615.93 DR DEMAND</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
+          <t>3.5 C</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1661.59 - 1735.99 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
           <t>4.0 C</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>841.38 - 874.76 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2.5 C</t>
-        </is>
-      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4113,17 +4113,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ZENTEC</t>
+          <t>IGIL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Zen Technologies Ltd.</t>
+          <t>International Gemological Institute Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4132,26 +4132,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1619.8</v>
+        <v>315.9</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1581.47 - 1609.16 DR DEMAND</t>
+          <t>309.47 - 310.95 DR DEMAND</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>943.53 - 1043.28 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4193,17 +4193,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ECLERX</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bharat Electronics Ltd.</t>
+          <t>eClerx Services Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4212,36 +4212,36 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>387.75</v>
+        <v>1819.9</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>397.4 - 399.2 RD SUPPLY</t>
+          <t>1734.04 - 1810.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>378.32 - 397.37 DR DEMAND</t>
+          <t>1083.13 - 1256.54 DR DEMAND</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 4 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4251,39 +4251,39 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CHOLAHLDNG</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cholamandalam Financial Holdings Ltd.</t>
+          <t>Mazagoan Dock Shipbuilders Ltd.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4292,26 +4292,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1371.8</v>
+        <v>2113</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>2053.69 - 2061.48 DR DEMAND</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1358.29 - 1396.78 DR DEMAND</t>
+          <t>1900.61 - 2111.67 DR DEMAND</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>ONESOURCE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Indraprastha Gas Ltd.</t>
+          <t>Onesource Specialty Pharma Ltd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4372,26 +4372,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>142.02</v>
+        <v>1521.6</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>158.04 - 159.5 RD SUPPLY</t>
+          <t>1479.1 - 1501.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>141.74 - 145.62 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4401,49 +4401,49 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NCC</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NCC Ltd.</t>
+          <t>Tata Steel Ltd.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4452,26 +4452,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>128.27</v>
+        <v>184.3</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>128.02 - 128.95 DR DEMAND</t>
+          <t>182.01 - 182.63 DR DEMAND</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>156.83 - 164.57 DR DEMAND</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 4 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4496,34 +4496,34 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SCHNEIDER</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Schneider Electric Infrastructure Ltd.</t>
+          <t>Torrent Power Ltd.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4532,11 +4532,11 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1192.7</v>
+        <v>1245.9</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1186.4 - 1193.6 DR DEMAND</t>
+          <t>1211.5 - 1220.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>540.0 - 575.5 DR DEMAND</t>
+          <t>1186.52 - 1241.27 DR DEMAND</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4576,34 +4576,34 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>RAMCOCEM</t>
+          <t>VMM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Ramco Cements Ltd.</t>
+          <t>Vishal Mega Mart Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4612,26 +4612,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>844.25</v>
+        <v>101</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>951.15 - 986.61 RD SUPPLY</t>
+          <t>98.77 - 99.68 DR DEMAND</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>836.02 - 868.83 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4651,39 +4651,39 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>FACT</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RBL Bank Ltd.</t>
+          <t>Fertilisers and Chemicals Travancore Ltd.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PVTBANK</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4692,36 +4692,36 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>402</v>
+        <v>757.95</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>401.1 - 402.4 DR DEMAND</t>
+          <t>738.0 - 749.15 DR DEMAND</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>286.46 - 290.25 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4736,34 +4736,34 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Berger Paints India Ltd.</t>
+          <t>HDFC Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4772,26 +4772,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>448.2</v>
+        <v>521.2</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>444.35 - 449.4 DR DEMAND</t>
+          <t>508.7 - 514.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>560.77 - 590.09 RD SUPPLY</t>
+          <t>811.41 - 817.84 RD SUPPLY</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4811,39 +4811,39 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>UTIAMC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CG Power and Industrial Solutions Ltd.</t>
+          <t>UTI Asset Management Company Ltd.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4852,26 +4852,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>858.05</v>
+        <v>882.4</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>794.1 - 800.0 DR DEMAND</t>
+          <t>1039.08 - 1043.74 RD SUPPLY</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>814.85 - 863.4 DR DEMAND</t>
+          <t>841.38 - 874.76 DR DEMAND</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>JINDALSAW</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Jindal Saw Ltd.</t>
+          <t>Bharat Electronics Ltd.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4932,21 +4932,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>277.7</v>
+        <v>388.3</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>275.7 - 281.25 DR DEMAND</t>
+          <t>397.4 - 399.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>310.0 - 320.0 RD SUPPLY</t>
+          <t>378.32 - 397.37 DR DEMAND</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4993,55 +4993,55 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>FORTIS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Kajaria Ceramics Ltd.</t>
+          <t>Fortis Healthcare Ltd.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1190.5</v>
+        <v>770</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1175.7 - 1183.6 DR DEMAND</t>
+          <t>915.0 - 918.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
+          <t>7.5 A</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>765.99 - 794.16 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
           <t>7.0 A</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>1181.73 - 1240.58 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>5.0 C</t>
-        </is>
-      </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5066,57 +5066,57 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>CONFLICT</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PVR INOX Ltd.</t>
+          <t>Indraprastha Gas Ltd.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1190.1</v>
+        <v>145.61</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1159.9 - 1169.2 DR DEMAND</t>
+          <t>139.2 - 141.99 DR DEMAND</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1207.7 - 1249.7 RD SUPPLY</t>
+          <t>141.74 - 145.62 DR DEMAND</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5126,17 +5126,17 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5146,24 +5146,24 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>CONFLICT</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>NCC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SBI Cards and Payment Services Ltd.</t>
+          <t>NCC Ltd.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5172,11 +5172,11 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>581</v>
+        <v>128.88</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>565.45 - 568.25 DR DEMAND</t>
+          <t>128.02 - 128.95 DR DEMAND</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5186,12 +5186,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>565.45 - 593.2 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5233,12 +5233,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ESCORTS</t>
+          <t>RAMCOCEM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Escorts Kubota Ltd.</t>
+          <t>The Ramco Cements Ltd.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5252,26 +5252,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2706.2</v>
+        <v>845.55</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2855.7 - 2866.3 RD SUPPLY</t>
+          <t>951.15 - 986.61 RD SUPPLY</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2679.78 - 2709.64 DR DEMAND</t>
+          <t>836.02 - 868.83 DR DEMAND</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5313,17 +5313,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ITC Ltd.</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5332,26 +5332,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>265.1</v>
+        <v>959.5</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>264.75 - 265.8 DR DEMAND</t>
+          <t>1108.0 - 1124.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>306.55 - 309.47 RD SUPPLY</t>
+          <t>933.9 - 964.4 DR DEMAND</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5393,17 +5393,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SAMMAANCAP</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Sammaan Capital Ltd.</t>
+          <t>Torrent Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5412,31 +5412,31 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>136.48</v>
+        <v>4800</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>144.48 - 145.94 RD SUPPLY</t>
+          <t>4755.5 - 4810.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
+          <t>5.5 B</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>3068.54 - 3119.39 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
           <t>7.0 A</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>134.75 - 144.61 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>4.5 C</t>
-        </is>
-      </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -5451,12 +5451,12 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5473,17 +5473,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SBI Life Insurance Company Ltd.</t>
+          <t>CG Power and Industrial Solutions Ltd.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5492,26 +5492,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1735</v>
+        <v>854.2</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2106.67 - 2129.04 RD SUPPLY</t>
+          <t>794.1 - 800.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1700.4 - 1765.7 DR DEMAND</t>
+          <t>814.85 - 863.4 DR DEMAND</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5553,12 +5553,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>GPIL</t>
+          <t>JINDALSAW</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Godawari Power &amp; Ispat Ltd.</t>
+          <t>Jindal Saw Ltd.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5572,31 +5572,31 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221.35</v>
+        <v>277.7</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>239.0 - 239.6 RD SUPPLY</t>
+          <t>275.7 - 281.25 DR DEMAND</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>220.3 - 234.23 DR DEMAND</t>
+          <t>310.0 - 320.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5633,17 +5633,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Indian Bank</t>
+          <t>Federal Bank Ltd.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5652,26 +5652,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>795.25</v>
+        <v>317.4</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>769.25 - 772.4 DR DEMAND</t>
+          <t>317.12 - 318.41 DR DEMAND</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>748.11 - 819.79 DR DEMAND</t>
+          <t>171.04 - 175.95 DR DEMAND</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -5713,17 +5713,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>SAMMAANCAP</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Ltd.</t>
+          <t>Sammaan Capital Ltd.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5732,36 +5732,36 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1697.7</v>
+        <v>136.54</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1689.3 - 1700.0 DR DEMAND</t>
+          <t>144.48 - 145.94 RD SUPPLY</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>134.75 - 144.61 DR DEMAND</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -5793,17 +5793,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>GPIL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Torrent Power Ltd.</t>
+          <t>Godawari Power &amp; Ispat Ltd.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5812,11 +5812,11 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1220.2</v>
+        <v>222.34</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1518.74 - 1522.83 RD SUPPLY</t>
+          <t>239.0 - 239.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1186.52 - 1241.27 DR DEMAND</t>
+          <t>220.3 - 234.23 DR DEMAND</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -5873,17 +5873,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AFFLE</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Affle 3i Ltd.</t>
+          <t>Indian Bank</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5892,26 +5892,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1501</v>
+        <v>805.9</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1489.2 - 1519.2 DR DEMAND</t>
+          <t>769.25 - 772.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1251.3 - 1335.3 DR DEMAND</t>
+          <t>748.11 - 819.79 DR DEMAND</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>4.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -5953,17 +5953,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BLS</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BLS International Services Ltd.</t>
+          <t>BSE Ltd.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5972,26 +5972,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219.55</v>
+        <v>3092</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>218.42 - 221.26 DR DEMAND</t>
+          <t>3085.1 - 3161.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>393.86 - 423.45 RD SUPPLY</t>
+          <t>2563.45 - 2625.28 DR DEMAND</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6011,12 +6011,12 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>4.0 / 10 SOLID</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6033,17 +6033,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ECLERX</t>
+          <t>ZENSARTECH</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>eClerx Services Ltd.</t>
+          <t>Zensar Technolgies Ltd.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6052,26 +6052,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1769.7</v>
+        <v>422.1</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1734.04 - 1810.7 DR DEMAND</t>
+          <t>416.15 - 422.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1083.13 - 1256.54 DR DEMAND</t>
+          <t>510.15 - 553.1 RD SUPPLY</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>4.0 / 10 SOLID</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -6113,17 +6113,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>ZENTEC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Max Healthcare Institute Ltd.</t>
+          <t>Zen Technologies Ltd.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6132,26 +6132,26 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>982.1</v>
+        <v>1605.2</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>980.3 - 990.5 DR DEMAND</t>
+          <t>1581.47 - 1609.16 DR DEMAND</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>937.3 - 958.19 DR DEMAND</t>
+          <t>943.53 - 1043.28 DR DEMAND</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>4.0 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -6193,40 +6193,40 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>AFFLE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NTPC Ltd.</t>
+          <t>Affle 3i Ltd.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>323.5</v>
+        <v>1511</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>329.8 - 331.3 RD SUPPLY</t>
+          <t>1489.2 - 1519.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>394.88 - 409.97 RD SUPPLY</t>
+          <t>1251.3 - 1335.3 DR DEMAND</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -6251,39 +6251,39 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>4.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>AU Small Finance Bank Ltd.</t>
+          <t>Adani Green Energy Ltd.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6292,26 +6292,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1005.2</v>
+        <v>1278</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1018.0 - 1021.2 RD SUPPLY</t>
+          <t>1296.6 - 1299.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>830.84 - 841.88 DR DEMAND</t>
+          <t>765.0 - 814.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -6353,12 +6353,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Federal Bank Ltd.</t>
+          <t>AU Small Finance Bank Ltd.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6372,11 +6372,11 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>320.2</v>
+        <v>1010.3</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>325.65 - 327.3 RD SUPPLY</t>
+          <t>1018.0 - 1021.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>171.04 - 175.95 DR DEMAND</t>
+          <t>830.84 - 841.88 DR DEMAND</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6433,17 +6433,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HDFC Bank Ltd.</t>
+          <t>JSW Steel Ltd.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6452,11 +6452,11 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>722.7</v>
+        <v>1253.4</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>735.6 - 739.65 RD SUPPLY</t>
+          <t>1272.4 - 1275.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6466,12 +6466,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1096.2 - 1116.09 DR DEMAND</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -6513,17 +6513,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>IGIL</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>International Gemological Institute Ltd.</t>
+          <t>Alkem Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6532,16 +6532,16 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>324.3</v>
+        <v>5163.5</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>330.55 - 332.4 RD SUPPLY</t>
+          <t>5250.0 - 5306.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -6593,17 +6593,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>APOLLOTYRE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Indian Railway Finance Corporation Ltd.</t>
+          <t>Apollo Tyres Ltd.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6612,16 +6612,16 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>80.26000000000001</v>
+        <v>404.7</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>81.5 - 81.7 RD SUPPLY</t>
+          <t>412.9 - 429.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -6673,17 +6673,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>DOMS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>InterGlobe Aviation Ltd.</t>
+          <t>DOMS Industries Ltd.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -6692,11 +6692,11 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4872</v>
+        <v>2107</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>4940.0 - 4956.0 RD SUPPLY</t>
+          <t>2141.5 - 2147.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>5901.5 - 5970.0 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -6753,17 +6753,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>FORCEMOT</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Asian Paints Ltd.</t>
+          <t>Force Motors Ltd.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -6772,26 +6772,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2415</v>
+        <v>17054</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2444.0 - 2451.0 RD SUPPLY</t>
+          <t>17388.0 - 17430.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2083.96 - 2137.91 DR DEMAND</t>
+          <t>24271.95 - 26374.97 RD SUPPLY</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -6833,17 +6833,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>MRF</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LIC Housing Finance Ltd.</t>
+          <t>MRF Ltd.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -6852,36 +6852,36 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>548.5</v>
+        <v>125280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>485.45 - 490.0 DR DEMAND</t>
+          <t>125780.0 - 126500.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>554.86 - 559.52 RD SUPPLY</t>
+          <t>101787.0 - 105025.93 DR DEMAND</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -6913,17 +6913,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>THERMAX</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Torrent Pharmaceuticals Ltd.</t>
+          <t>Thermax Ltd.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -6932,31 +6932,31 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4894</v>
+        <v>3392.2</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>4988.5 - 4996.5 RD SUPPLY</t>
+          <t>3451.9 - 3464.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>3068.54 - 3119.39 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -6993,17 +6993,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Granules India Ltd.</t>
+          <t>Asian Paints Ltd.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7012,31 +7012,31 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>866.75</v>
+        <v>2402.6</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>870.0 - 875.0 RD SUPPLY</t>
+          <t>2444.0 - 2451.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>419.84 - 453.47 DR DEMAND</t>
+          <t>2083.96 - 2137.91 DR DEMAND</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -7073,17 +7073,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>GODIGIT</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Hyundai Motor India Ltd.</t>
+          <t>Go Digit General Insurance Ltd.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7092,31 +7092,31 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2100</v>
+        <v>260.05</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2115.0 - 2135.0 RD SUPPLY</t>
+          <t>263.25 - 267.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>322.75 - 333.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7153,17 +7153,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>KARURVYSYA</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JSW Steel Ltd.</t>
+          <t>Karur Vysya Bank Ltd.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>PVTBANK</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7172,26 +7172,26 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1272.4</v>
+        <v>324.8</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1297.8 - 1304.0 RD SUPPLY</t>
+          <t>327.95 - 328.65 RD SUPPLY</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1096.2 - 1116.09 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -7233,17 +7233,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Bandhan Bank Ltd.</t>
+          <t>Samvardhana Motherson International Ltd.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7252,26 +7252,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>185.31</v>
+        <v>163.26</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>187.7 - 188.23 RD SUPPLY</t>
+          <t>165.71 - 166.22 RD SUPPLY</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>76.38 - 78.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -7313,17 +7313,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TEGA</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tega Industries Ltd.</t>
+          <t>PNB Housing Finance Ltd.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7332,26 +7332,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2060.6</v>
+        <v>1120</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2091.6 - 2100.0 RD SUPPLY</t>
+          <t>1138.5 - 1149.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1234.96 - 1320.03 DR DEMAND</t>
+          <t>737.16 - 753.6 DR DEMAND</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -7412,7 +7412,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2188.6</v>
+        <v>2190.1</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7473,17 +7473,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>BERGEPAINT</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Emcure Pharmaceuticals Ltd.</t>
+          <t>Berger Paints India Ltd.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -7492,36 +7492,36 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1959.1</v>
+        <v>455.45</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1834.83 - 1851.1 DR DEMAND</t>
+          <t>458.35 - 459.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1962.18 - 2044.02 RD SUPPLY</t>
+          <t>560.77 - 590.09 RD SUPPLY</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -7553,17 +7553,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ICICIAMC</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ICICI Prudential Asset Management Company Ltd.</t>
+          <t>Emcure Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -7572,28 +7572,28 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3233</v>
+        <v>1943</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>3291.8 - 3305.0 RD SUPPLY</t>
+          <t>1834.83 - 1851.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
+          <t>8.5 A</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>1962.18 - 2044.02 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J90" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7633,17 +7633,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>RKFORGE</t>
+          <t>ITCHOTELS</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ramkrishna Forgings Ltd.</t>
+          <t>ITC Hotels Ltd.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -7652,36 +7652,36 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>714.65</v>
+        <v>164.13</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>725.0 - 728.0 RD SUPPLY</t>
+          <t>164.8 - 165.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>459.41 - 465.85 DR DEMAND</t>
+          <t>180.5 - 188.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -7713,17 +7713,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries Ltd.</t>
+          <t>Varun Beverages Ltd.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -7732,31 +7732,31 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1865</v>
+        <v>432</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1867.3 - 1877.2 RD SUPPLY</t>
+          <t>439.3 - 443.3 RD SUPPLY</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
+          <t>5.0 C</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>396.2 - 400.45 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
           <t>5.5 B</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>1569.37 - 1580.86 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>7.0 A</t>
-        </is>
-      </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -7793,17 +7793,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SPLPETRO</t>
+          <t>LLOYDSME</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Supreme Petrochem Ltd.</t>
+          <t>Lloyds Metals And Energy Ltd.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -7812,26 +7812,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>831.85</v>
+        <v>1884</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>688.05 - 691.15 DR DEMAND</t>
+          <t>1890.9 - 1911.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>836.67 - 965.13 RD SUPPLY</t>
+          <t>1042.28 - 1072.36 DR DEMAND</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>3.5 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -7873,17 +7873,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>COHANCE</t>
+          <t>LGEINDIA</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cohance Lifesciences Ltd.</t>
+          <t>LG Electronics India Ltd.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -7892,26 +7892,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>457.9</v>
+        <v>1723.5</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>462.35 - 467.2 RD SUPPLY</t>
+          <t>1737.1 - 1755.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1229.95 - 1328.0 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2.5 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -7972,7 +7972,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1010.15</v>
+        <v>1008.75</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -8033,17 +8033,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>LLOYDSME</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Lloyds Metals And Energy Ltd.</t>
+          <t>Sun TV Network Ltd.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8052,26 +8052,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1902.2</v>
+        <v>605</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1890.9 - 1911.0 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1741.0 - 1794.6 DR DEMAND</t>
+          <t>599.4 - 653.93 RD SUPPLY</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -8113,17 +8113,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CARBORUNIV</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Carborundum Universal Ltd.</t>
+          <t>PVR INOX Ltd.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8132,26 +8132,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1200.5</v>
+        <v>1242.7</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>990.84 - 995.43 DR DEMAND</t>
+          <t>1159.9 - 1169.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>1181.58 - 1303.79 RD SUPPLY</t>
+          <t>1207.7 - 1249.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -8193,17 +8193,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>LGEINDIA</t>
+          <t>RITES</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LG Electronics India Ltd.</t>
+          <t>RITES Ltd.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8212,31 +8212,31 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1739.2</v>
+        <v>209.05</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>1737.1 - 1755.0 RD SUPPLY</t>
+          <t>207.23 - 211.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>214.72 - 226.44 RD SUPPLY</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -8273,78 +8273,238 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>KAJARIACER</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Kajaria Ceramics Ltd.</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>CONSUMPTION</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>1235.1</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1175.7 - 1183.6 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>1181.73 - 1240.58 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>5.0 C</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>🟡 1 TEST (TESTED)</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>🔥 2.5x VOL EXPLOSION</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>5.0 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>CARBORUNIV</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Carborundum Universal Ltd.</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>1252.5</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>1194.0 - 1200.5 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>1181.58 - 1303.79 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>4.0 C</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>🟡 1 TEST (TESTED)</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>4.0 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
           <t>PHOENIXLTD</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>Phoenix Mills Ltd.</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>REALTY</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
       </c>
-      <c r="E99" t="n">
-        <v>1929</v>
-      </c>
-      <c r="F99" t="inlineStr">
+      <c r="E101" t="n">
+        <v>1935</v>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>1978.4 - 1990.6 RD SUPPLY</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>5.5 B</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>1851.05 - 1990.36 RD SUPPLY</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t>2.5 C</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="K101" t="inlineStr">
         <is>
           <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t>NORMAL VOL</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t>+0.0 PTS</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
+      <c r="N101" t="inlineStr">
         <is>
           <t>2.5 / 10 SUPPLY</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr">
+      <c r="O101" t="inlineStr">
         <is>
           <t>SUPPLY TEST</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
+      <c r="P101" t="inlineStr">
         <is>
           <t>IN</t>
         </is>

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P101"/>
+  <dimension ref="A1:P108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,17 +513,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Axis Bank Ltd.</t>
+          <t>Adani Enterprises Ltd.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -532,26 +532,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1226</v>
+        <v>2816.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1175.0 - 1186.5 DR DEMAND</t>
+          <t>2793.7 - 2831.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1208.6 - 1229.5 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>11.0 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -593,17 +593,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CESC Ltd.</t>
+          <t>Adani Ports and Special Economic Zone Ltd.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -612,31 +612,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>133.85</v>
+        <v>1737.8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>144.0 - 144.33 RD SUPPLY</t>
+          <t>1736.6 - 1743.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>133.19 - 139.44 DR DEMAND</t>
+          <t>1288.07 - 1307.09 DR DEMAND</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>11.0 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -673,17 +673,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>HBLENGINE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Glenmark Pharmaceuticals Ltd.</t>
+          <t>HBL Engineering Ltd.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -692,26 +692,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2334.7</v>
+        <v>779.35</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2292.0 - 2325.7 DR DEMAND</t>
+          <t>773.65 - 784.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1331.41 - 1376.45 DR DEMAND</t>
+          <t>647.1 - 656.44 DR DEMAND</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -726,44 +726,44 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>10.5 / 10 HIGH COMBO</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>BUY READY</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>AWL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Anant Raj Ltd.</t>
+          <t>AWL Agri Business Ltd.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -772,11 +772,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>598.9</v>
+        <v>175.43</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>594.0 - 595.2 DR DEMAND</t>
+          <t>174.69 - 176.18 DR DEMAND</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -786,17 +786,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>855.56 - 945.21 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -816,34 +816,34 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>BUY READY</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chambal Fertilizers &amp; Chemicals Ltd.</t>
+          <t>Kfin Technologies Ltd.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -852,28 +852,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>409.25</v>
+        <v>832</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>401.4 - 407.5 DR DEMAND</t>
+          <t>826.8 - 836.62 DR DEMAND</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1329.97 - 1360.84 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>6.5 B</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>404.75 - 434.2 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3.0 C</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -896,34 +896,34 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>BUY READY</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>SUMICHEM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Craftsman Automation Ltd.</t>
+          <t>Sumitomo Chemical India Ltd.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -932,31 +932,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10417</v>
+        <v>417.6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10205.0 - 10251.0 DR DEMAND</t>
+          <t>361.73 - 363.57 DR DEMAND</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>6.5 B</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>410.56 - 419.84 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>7.0 A</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -976,29 +976,29 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>BUY READY</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HBLENGINE</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HBL Engineering Ltd.</t>
+          <t>Mazagoan Dock Shipbuilders Ltd.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1012,31 +1012,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>794.5</v>
+        <v>2064</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>773.65 - 784.0 DR DEMAND</t>
+          <t>2053.69 - 2061.48 DR DEMAND</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>647.1 - 656.44 DR DEMAND</t>
+          <t>1900.61 - 2111.67 DR DEMAND</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1073,17 +1073,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>NTPCGREEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jindal Stainless Ltd.</t>
+          <t>NTPC Green Energy Ltd.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1092,31 +1092,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>747.4</v>
+        <v>91.09</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>736.0 - 738.0 DR DEMAND</t>
+          <t>89.65 - 89.99 DR DEMAND</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>109.85 - 119.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>11.0 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1153,17 +1153,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CHOLAHLDNG</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cholamandalam Financial Holdings Ltd.</t>
+          <t>Glenmark Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1172,31 +1172,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1386.2</v>
+        <v>2331</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1341.0 - 1361.0 DR DEMAND</t>
+          <t>2292.0 - 2325.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1358.29 - 1396.78 DR DEMAND</t>
+          <t>1331.41 - 1376.45 DR DEMAND</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1206,17 +1206,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1233,17 +1233,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>ASAHIINDIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Granules India Ltd.</t>
+          <t>Asahi India Glass Ltd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1252,26 +1252,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>846.55</v>
+        <v>944.25</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>829.0 - 835.6 DR DEMAND</t>
+          <t>925.1 - 929.29 DR DEMAND</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>419.84 - 453.47 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1291,12 +1291,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1313,17 +1313,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>BEML</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hindalco Industries Ltd.</t>
+          <t>BEML Ltd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1332,31 +1332,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>941.8</v>
+        <v>1962.3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>935.1 - 936.4 DR DEMAND</t>
+          <t>1914.23 - 1924.77 DR DEMAND</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>766.15 - 804.2 DR DEMAND</t>
+          <t>1159.43 - 1211.03 DR DEMAND</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SBI Cards and Payment Services Ltd.</t>
+          <t>Craftsman Automation Ltd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1412,31 +1412,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>578.05</v>
+        <v>10266</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>565.45 - 568.25 DR DEMAND</t>
+          <t>10205.0 - 10251.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>565.45 - 593.2 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1473,17 +1473,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWL</t>
+          <t>CHOLAHLDNG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AWL Agri Business Ltd.</t>
+          <t>Cholamandalam Financial Holdings Ltd.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1492,26 +1492,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>177.68</v>
+        <v>1369.6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>174.69 - 176.18 DR DEMAND</t>
+          <t>1341.0 - 1361.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1358.29 - 1396.78 DR DEMAND</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1553,17 +1553,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>CREDITACC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Infosys Ltd.</t>
+          <t>CreditAccess Grameen Ltd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1572,28 +1572,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>994.1</v>
+        <v>1239</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>982.4 - 985.3 DR DEMAND</t>
+          <t>1209.1 - 1216.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>7.5 A</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1602.0 - 1634.0 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>6.5 B</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>982.4 - 1000.4 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>6.0 B</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -1606,17 +1606,17 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1633,12 +1633,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>GICRE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kfin Technologies Ltd.</t>
+          <t>General Insurance Corporation of India</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1652,26 +1652,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>840</v>
+        <v>323.9</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>826.8 - 836.62 DR DEMAND</t>
+          <t>319.0 - 320.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1329.97 - 1360.84 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1713,17 +1713,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WELCORP</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Welspun Corp Ltd.</t>
+          <t>Hindalco Industries Ltd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1732,36 +1732,36 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2717</v>
+        <v>941.85</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2675.0 - 2692.2 DR DEMAND</t>
+          <t>935.1 - 936.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>658.55 - 760.86 DR DEMAND</t>
+          <t>766.15 - 804.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1793,17 +1793,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COROMANDEL</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Coromandel International Ltd.</t>
+          <t>Indraprastha Gas Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1812,26 +1812,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1758.2</v>
+        <v>142.79</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1704.84 - 1749.4 DR DEMAND</t>
+          <t>137.77 - 140.53 DR DEMAND</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1704.84 - 1751.89 DR DEMAND</t>
+          <t>140.28 - 144.12 DR DEMAND</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1873,17 +1873,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NATCO Pharma Ltd.</t>
+          <t>Power Grid Corporation of India Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1892,26 +1892,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>827.5</v>
+        <v>254.55</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>845.0 - 851.0 RD SUPPLY</t>
+          <t>248.1 - 250.01 DR DEMAND</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>803.32 - 821.11 DR DEMAND</t>
+          <t>238.36 - 241.78 DR DEMAND</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1953,17 +1953,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>POLYMED</t>
+          <t>REDINGTON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Poly Medicure Ltd.</t>
+          <t>Redington Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1972,26 +1972,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1673.8</v>
+        <v>397.95</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1635.65 - 1644.33 DR DEMAND</t>
+          <t>390.7 - 392.05 DR DEMAND</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1297.34 - 1337.36 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2033,12 +2033,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tube Investments of India Ltd.</t>
+          <t>Sona BLW Precision Forgings Ltd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2052,31 +2052,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2375</v>
+        <v>805</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2161.89 - 2177.97 DR DEMAND</t>
+          <t>793.2 - 795.25 DR DEMAND</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2161.89 - 2330.75 DR DEMAND</t>
+          <t>399.84 - 409.23 DR DEMAND</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2113,17 +2113,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Amber Enterprises India Ltd.</t>
+          <t>Aditya Birla Capital Ltd.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2132,21 +2132,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6672.5</v>
+        <v>375.05</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>6151.0 - 6170.5 DR DEMAND</t>
+          <t>368.6 - 369.95 DR DEMAND</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6120.0 - 6549.0 DR DEMAND</t>
+          <t>287.7 - 292.25 DR DEMAND</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2193,17 +2193,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CHOICEIN</t>
+          <t>EMAMILTD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Choice International Ltd.</t>
+          <t>Emami Ltd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2212,26 +2212,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>726.25</v>
+        <v>372.65</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>721.6 - 725.5 DR DEMAND</t>
+          <t>366.55 - 368.45 DR DEMAND</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>840.3 - 860.5 RD SUPPLY</t>
+          <t>444.5 - 477.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2273,17 +2273,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KIMS</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Krishna Institute of Medical Sciences Ltd.</t>
+          <t>Gland Pharma Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2292,11 +2292,11 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>746.4</v>
+        <v>2874.4</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>725.4 - 735.3 DR DEMAND</t>
+          <t>2792.4 - 2826.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>474.05 - 496.35 DR DEMAND</t>
+          <t>1256.51 - 1376.68 DR DEMAND</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2353,17 +2353,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OLAELEC</t>
+          <t>COROMANDEL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ola Electric Mobility Ltd.</t>
+          <t>Coromandel International Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2372,26 +2372,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>36.92</v>
+        <v>1763.6</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>36.05 - 36.2 DR DEMAND</t>
+          <t>1704.84 - 1749.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1704.84 - 1751.89 DR DEMAND</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2433,17 +2433,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>GABRIEL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>UltraTech Cement Ltd.</t>
+          <t>Gabriel India Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2452,31 +2452,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>10956</v>
+        <v>1315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>10800.0 - 10829.0 DR DEMAND</t>
+          <t>1294.0 - 1303.9 DR DEMAND</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>9784.84 - 9863.33 DR DEMAND</t>
+          <t>794.06 - 824.64 DR DEMAND</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2513,17 +2513,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ZFCVINDIA</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ZF Commercial Vehicle Control Systems India Ltd.</t>
+          <t>IDFC First Bank Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2532,28 +2532,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2341</v>
+        <v>80.39</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2285.0 - 2297.8 DR DEMAND</t>
+          <t>78.6 - 79.46 DR DEMAND</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>6.5 B</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>57.91 - 58.68 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2046.79 - 2067.08 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5.5 B</t>
-        </is>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2593,17 +2593,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>BBTC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bharti Airtel Ltd.</t>
+          <t>Bombay Burmah Trading Corporation Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1757</v>
+        <v>1334.2</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1748.99 - 1753.04 DR DEMAND</t>
+          <t>1314.6 - 1322.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>6.0 B</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1962.03 - 2114.67 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
           <t>6.5 B</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>1527.35 - 1537.83 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>6.5 B</t>
-        </is>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -2651,12 +2651,12 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2673,17 +2673,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bharat Heavy Electricals Ltd.</t>
+          <t>CG Power and Industrial Solutions Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2692,26 +2692,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>415.5</v>
+        <v>879</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>406.0 - 410.6 DR DEMAND</t>
+          <t>794.1 - 800.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>204.46 - 207.34 DR DEMAND</t>
+          <t>814.85 - 863.4 DR DEMAND</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2753,17 +2753,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Petronet LNG Ltd.</t>
+          <t>Dabur India Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2772,36 +2772,36 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>284.5</v>
+        <v>374.25</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>280.3 - 281.75 DR DEMAND</t>
+          <t>368.05 - 370.45 DR DEMAND</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>232.67 - 245.62 DR DEMAND</t>
+          <t>518.65 - 536.39 RD SUPPLY</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2833,17 +2833,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RBL Bank Ltd.</t>
+          <t>Hindustan Petroleum Corporation Ltd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PVTBANK</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2852,36 +2852,36 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>403.35</v>
+        <v>345</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>401.1 - 402.4 DR DEMAND</t>
+          <t>337.2 - 340.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>286.46 - 290.25 DR DEMAND</t>
+          <t>263.73 - 269.42 DR DEMAND</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2913,17 +2913,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capri Global Capital Ltd.</t>
+          <t>JSW Steel Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2932,41 +2932,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>247.45</v>
+        <v>1233</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>243.67 - 244.62 DR DEMAND</t>
+          <t>1218.0 - 1221.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1096.2 - 1116.09 DR DEMAND</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2993,17 +2993,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>KIMS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Delhivery Ltd.</t>
+          <t>Krishna Institute of Medical Sciences Ltd.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3012,26 +3012,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>409.7</v>
+        <v>736.25</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>405.05 - 407.5 DR DEMAND</t>
+          <t>725.4 - 735.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>474.05 - 496.35 DR DEMAND</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3073,17 +3073,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Max Healthcare Institute Ltd.</t>
+          <t>Lodha Developers Ltd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3092,11 +3092,11 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>929.8</v>
+        <v>1105.6</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>918.17 - 923.96 DR DEMAND</t>
+          <t>1091.8 - 1103.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>648.52 - 674.63 DR DEMAND</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3126,17 +3126,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3153,17 +3153,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tata Communications Ltd.</t>
+          <t>National Aluminium Co. Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3172,11 +3172,11 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1656.2</v>
+        <v>334.9</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1640.2 - 1649.3 DR DEMAND</t>
+          <t>331.16 - 333.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1310.58 - 1335.75 DR DEMAND</t>
+          <t>131.46 - 149.33 DR DEMAND</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3233,17 +3233,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>NCC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Ltd.</t>
+          <t>NCC Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3252,26 +3252,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2050.6</v>
+        <v>130.06</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1966.02 - 1971.79 DR DEMAND</t>
+          <t>128.02 - 128.95 DR DEMAND</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1966.02 - 2020.42 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3286,17 +3286,17 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3313,17 +3313,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AIAENG</t>
+          <t>RAINBOW</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AIA Engineering Ltd.</t>
+          <t>Rainbow Childrens Medicare Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3332,21 +3332,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3869</v>
+        <v>1279.8</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>3778.0 - 3805.8 DR DEMAND</t>
+          <t>1255.95 - 1260.24 DR DEMAND</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5062.37 - 5160.6 RD SUPPLY</t>
+          <t>1550.0 - 1610.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3393,17 +3393,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ESCORTS</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Escorts Kubota Ltd.</t>
+          <t>Petronet LNG Ltd.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3412,31 +3412,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2715.2</v>
+        <v>285.5</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2855.7 - 2866.3 RD SUPPLY</t>
+          <t>280.3 - 281.75 DR DEMAND</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2679.78 - 2709.64 DR DEMAND</t>
+          <t>232.67 - 245.62 DR DEMAND</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3473,17 +3473,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vodafone Idea Ltd.</t>
+          <t>Torrent Power Ltd.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3492,26 +3492,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>12.95</v>
+        <v>1242.9</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>12.79 - 12.89 DR DEMAND</t>
+          <t>1211.5 - 1220.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>8.13 - 8.53 DR DEMAND</t>
+          <t>1186.52 - 1241.27 DR DEMAND</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3553,17 +3553,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IFCI</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IFCI Ltd.</t>
+          <t>United Spirits Ltd.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3572,28 +3572,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>68.77</v>
+        <v>1335.1</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>68.15 - 68.52 DR DEMAND</t>
+          <t>1301.97 - 1310.41 DR DEMAND</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>5.5 B</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1595.35 - 1664.74 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
           <t>4.5 C</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>46.4 - 47.88 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>7.0 A</t>
-        </is>
-      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3633,17 +3633,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SCHAEFFLER</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Schaeffler India Ltd.</t>
+          <t>CRISIL Ltd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3652,31 +3652,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3897.1</v>
+        <v>4428.6</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>3811.1 - 3860.2 DR DEMAND</t>
+          <t>4325.1 - 4356.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3489.69 - 3548.8 DR DEMAND</t>
+          <t>3669.91 - 3717.29 DR DEMAND</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3713,17 +3713,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>JKTYRE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ashok Leyland Ltd.</t>
+          <t>JK Tyre &amp; Industries Ltd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3732,26 +3732,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>154.19</v>
+        <v>340.35</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>150.3 - 151.46 DR DEMAND</t>
+          <t>333.1 - 334.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>207.56 - 211.81 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3793,17 +3793,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Navin Fluorine International Ltd.</t>
+          <t>Max Healthcare Institute Ltd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3812,51 +3812,51 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>8245</v>
+        <v>940.95</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>8110.0 - 8151.0 DR DEMAND</t>
+          <t>918.17 - 923.96 DR DEMAND</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4173.89 - 4245.43 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3873,17 +3873,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SCHNEIDER</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Schneider Electric Infrastructure Ltd.</t>
+          <t>One 97 Communications Ltd.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3892,11 +3892,11 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1203.4</v>
+        <v>1656</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1186.4 - 1193.6 DR DEMAND</t>
+          <t>1624.4 - 1635.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3906,17 +3906,17 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>540.0 - 575.5 DR DEMAND</t>
+          <t>651.5 - 700.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3953,17 +3953,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>TATATECH</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dixon Technologies (India) Ltd.</t>
+          <t>Tata Technologies Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3972,26 +3972,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>13100</v>
+        <v>698.8</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>12838.12 - 12924.05 DR DEMAND</t>
+          <t>683.7 - 686.75 DR DEMAND</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>14838.58 - 14988.47 RD SUPPLY</t>
+          <t>835.0 - 891.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4033,17 +4033,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ENDURANCE</t>
+          <t>AIAENG</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Endurance Technologies Ltd.</t>
+          <t>AIA Engineering Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4052,26 +4052,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2656.5</v>
+        <v>3824.4</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2538.15 - 2615.93 DR DEMAND</t>
+          <t>3778.0 - 3805.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1661.59 - 1735.99 DR DEMAND</t>
+          <t>5062.37 - 5160.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4113,17 +4113,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>IGIL</t>
+          <t>CEMPRO</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>International Gemological Institute Ltd.</t>
+          <t>Cemindia Projects Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4132,11 +4132,11 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>315.9</v>
+        <v>1178.9</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>309.47 - 310.95 DR DEMAND</t>
+          <t>1153.8 - 1161.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -4146,12 +4146,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>474.17 - 485.07 DR DEMAND</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4193,17 +4193,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ECLERX</t>
+          <t>SCHAEFFLER</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>eClerx Services Ltd.</t>
+          <t>Schaeffler India Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4212,36 +4212,36 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1819.9</v>
+        <v>3885.6</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1734.04 - 1810.7 DR DEMAND</t>
+          <t>3811.1 - 3860.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1083.13 - 1256.54 DR DEMAND</t>
+          <t>3489.69 - 3548.8 DR DEMAND</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4273,17 +4273,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mazagoan Dock Shipbuilders Ltd.</t>
+          <t>Tube Investments of India Ltd.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4292,26 +4292,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2113</v>
+        <v>2340</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2053.69 - 2061.48 DR DEMAND</t>
+          <t>2161.89 - 2177.97 DR DEMAND</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1900.61 - 2111.67 DR DEMAND</t>
+          <t>2161.89 - 2330.75 DR DEMAND</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4353,17 +4353,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ONESOURCE</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Onesource Specialty Pharma Ltd.</t>
+          <t>Astral Ltd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4372,28 +4372,28 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1521.6</v>
+        <v>1344</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1479.1 - 1501.3 DR DEMAND</t>
+          <t>1540.5 - 1544.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
+          <t>6.0 B</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>1309.54 - 1333.5 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
           <t>4.0 C</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J50" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -4411,12 +4411,12 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4433,17 +4433,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tata Steel Ltd.</t>
+          <t>Capri Global Capital Ltd.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4452,11 +4452,11 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>184.3</v>
+        <v>249.23</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>182.01 - 182.63 DR DEMAND</t>
+          <t>243.67 - 244.62 DR DEMAND</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4466,22 +4466,22 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>156.83 - 164.57 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4513,17 +4513,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Torrent Power Ltd.</t>
+          <t>Eternal Ltd.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4532,36 +4532,36 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1245.9</v>
+        <v>313.9</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1211.5 - 1220.2 DR DEMAND</t>
+          <t>306.2 - 310.25 DR DEMAND</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
+          <t>4.0 C</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>194.8 - 201.7 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>1186.52 - 1241.27 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>3.0 C</t>
-        </is>
-      </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4593,12 +4593,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>VMM</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Vishal Mega Mart Ltd.</t>
+          <t>Indian Hotels Co. Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4612,11 +4612,11 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>101</v>
+        <v>718</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>98.77 - 99.68 DR DEMAND</t>
+          <t>706.05 - 713.55 DR DEMAND</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4626,22 +4626,22 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>871.1 - 888.32 RD SUPPLY</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 5 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4673,17 +4673,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FACT</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fertilisers and Chemicals Travancore Ltd.</t>
+          <t>NHPC Ltd.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4692,26 +4692,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>757.95</v>
+        <v>71.75</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>738.0 - 749.15 DR DEMAND</t>
+          <t>81.64 - 82.57 RD SUPPLY</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>67.83 - 70.98 DR DEMAND</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4753,17 +4753,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>RAMCOCEM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>HDFC Life Insurance Company Ltd.</t>
+          <t>The Ramco Cements Ltd.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4772,21 +4772,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>521.2</v>
+        <v>830.85</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>508.7 - 514.0 DR DEMAND</t>
+          <t>951.15 - 986.61 RD SUPPLY</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>811.41 - 817.84 RD SUPPLY</t>
+          <t>784.7 - 825.32 DR DEMAND</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4833,17 +4833,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>UTIAMC</t>
+          <t>IGIL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>UTI Asset Management Company Ltd.</t>
+          <t>International Gemological Institute Ltd.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4852,26 +4852,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>882.4</v>
+        <v>311.95</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1039.08 - 1043.74 RD SUPPLY</t>
+          <t>309.47 - 310.95 DR DEMAND</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>841.38 - 874.76 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4913,17 +4913,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bharat Electronics Ltd.</t>
+          <t>NATCO Pharma Ltd.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4932,26 +4932,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>388.3</v>
+        <v>821.3</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>397.4 - 399.2 RD SUPPLY</t>
+          <t>838.12 - 844.07 RD SUPPLY</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>378.32 - 397.37 DR DEMAND</t>
+          <t>803.32 - 821.11 DR DEMAND</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4971,39 +4971,39 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>POONAWALLA</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fortis Healthcare Ltd.</t>
+          <t>Poonawalla Fincorp Ltd.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5012,28 +5012,28 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>770</v>
+        <v>433.4</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>915.0 - 918.4 RD SUPPLY</t>
+          <t>425.0 - 428.45 DR DEMAND</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
+          <t>3.5 C</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>370.05 - 382.85 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
           <t>7.5 A</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>765.99 - 794.16 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>7.0 A</t>
-        </is>
-      </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -5041,49 +5041,49 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Indraprastha Gas Ltd.</t>
+          <t>Bharat Forge Ltd.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5092,26 +5092,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>145.61</v>
+        <v>1875</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>139.2 - 141.99 DR DEMAND</t>
+          <t>1830.45 - 1850.39 DR DEMAND</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>141.74 - 145.62 DR DEMAND</t>
+          <t>1605.33 - 1669.53 DR DEMAND</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 4 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5136,34 +5136,34 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NCC</t>
+          <t>MRPL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NCC Ltd.</t>
+          <t>Mangalore Refinery &amp; Petrochemicals Ltd.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5172,28 +5172,28 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>128.88</v>
+        <v>164.76</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>128.02 - 128.95 DR DEMAND</t>
+          <t>161.2 - 162.96 DR DEMAND</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
+          <t>3.0 C</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>96.88 - 103.61 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J60" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5216,34 +5216,34 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>RAMCOCEM</t>
+          <t>ONESOURCE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Ramco Cements Ltd.</t>
+          <t>Onesource Specialty Pharma Ltd.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5252,26 +5252,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>845.55</v>
+        <v>1508</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>951.15 - 986.61 RD SUPPLY</t>
+          <t>1479.1 - 1501.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>836.02 - 868.83 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5291,39 +5291,39 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>State Bank of India</t>
+          <t>Saregama India Ltd</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5332,36 +5332,36 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>959.5</v>
+        <v>494.75</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1108.0 - 1124.5 RD SUPPLY</t>
+          <t>484.5 - 488.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>933.9 - 964.4 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5371,39 +5371,39 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>TITAGARH</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Torrent Pharmaceuticals Ltd.</t>
+          <t>Titagarh Rail Systems Ltd.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5412,36 +5412,36 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4800</v>
+        <v>805.1</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>4755.5 - 4810.0 DR DEMAND</t>
+          <t>789.05 - 796.05 DR DEMAND</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>3068.54 - 3119.39 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5451,39 +5451,39 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>UTIAMC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CG Power and Industrial Solutions Ltd.</t>
+          <t>UTI Asset Management Company Ltd.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5492,26 +5492,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>854.2</v>
+        <v>883.7</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>794.1 - 800.0 DR DEMAND</t>
+          <t>1039.08 - 1043.74 RD SUPPLY</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>814.85 - 863.4 DR DEMAND</t>
+          <t>841.38 - 874.76 DR DEMAND</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5536,29 +5536,29 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>JINDALSAW</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Jindal Saw Ltd.</t>
+          <t>Shree Cement Ltd.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5572,36 +5572,36 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>277.7</v>
+        <v>21900</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>275.7 - 281.25 DR DEMAND</t>
+          <t>21550.0 - 21900.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>310.0 - 320.0 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5633,12 +5633,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Federal Bank Ltd.</t>
+          <t>AU Small Finance Bank Ltd.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5652,26 +5652,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>317.4</v>
+        <v>987</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>317.12 - 318.41 DR DEMAND</t>
+          <t>984.5 - 990.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>171.04 - 175.95 DR DEMAND</t>
+          <t>830.84 - 841.88 DR DEMAND</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -5713,17 +5713,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SAMMAANCAP</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sammaan Capital Ltd.</t>
+          <t>Bharat Electronics Ltd.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5732,26 +5732,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>136.54</v>
+        <v>383.1</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>144.48 - 145.94 RD SUPPLY</t>
+          <t>397.4 - 399.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>134.75 - 144.61 DR DEMAND</t>
+          <t>378.32 - 397.37 DR DEMAND</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -5793,17 +5793,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>GPIL</t>
+          <t>CIEINDIA</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Godawari Power &amp; Ispat Ltd.</t>
+          <t>CIE Automotive India Ltd.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5812,21 +5812,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222.34</v>
+        <v>376.35</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>239.0 - 239.6 RD SUPPLY</t>
+          <t>374.8 - 376.45 DR DEMAND</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>220.3 - 234.23 DR DEMAND</t>
+          <t>479.0 - 504.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -5873,17 +5873,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>FORTIS</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Indian Bank</t>
+          <t>Fortis Healthcare Ltd.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5892,26 +5892,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>805.9</v>
+        <v>785</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>769.25 - 772.4 DR DEMAND</t>
+          <t>915.0 - 918.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>748.11 - 819.79 DR DEMAND</t>
+          <t>765.99 - 794.16 DR DEMAND</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -5921,22 +5921,22 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -5953,17 +5953,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BSE Ltd.</t>
+          <t>Tata Steel Ltd.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5972,26 +5972,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3092</v>
+        <v>178</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>3085.1 - 3161.0 DR DEMAND</t>
+          <t>177.59 - 179.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2563.45 - 2625.28 DR DEMAND</t>
+          <t>156.83 - 164.57 DR DEMAND</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6033,17 +6033,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ZENSARTECH</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Zensar Technolgies Ltd.</t>
+          <t>Eicher Motors Ltd.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6052,21 +6052,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>422.1</v>
+        <v>6920</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>416.15 - 422.4 DR DEMAND</t>
+          <t>6870.55 - 7000.19 DR DEMAND</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>510.15 - 553.1 RD SUPPLY</t>
+          <t>5099.29 - 5210.66 DR DEMAND</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6081,22 +6081,22 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -6113,17 +6113,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ZENTEC</t>
+          <t>POLYMED</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Zen Technologies Ltd.</t>
+          <t>Poly Medicure Ltd.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6132,26 +6132,26 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1605.2</v>
+        <v>1638.1</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1581.47 - 1609.16 DR DEMAND</t>
+          <t>1635.65 - 1644.33 DR DEMAND</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>943.53 - 1043.28 DR DEMAND</t>
+          <t>1297.34 - 1337.36 DR DEMAND</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -6193,17 +6193,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AFFLE</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Affle 3i Ltd.</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6212,21 +6212,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1511</v>
+        <v>954.1</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1489.2 - 1519.2 DR DEMAND</t>
+          <t>1108.0 - 1124.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1251.3 - 1335.3 DR DEMAND</t>
+          <t>933.9 - 964.4 DR DEMAND</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>4.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -6273,55 +6273,55 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Adani Green Energy Ltd.</t>
+          <t>Torrent Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1278</v>
+        <v>4767.3</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1296.6 - 1299.6 RD SUPPLY</t>
+          <t>4755.5 - 4810.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>765.0 - 814.2 DR DEMAND</t>
+          <t>3068.54 - 3119.39 DR DEMAND</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6331,77 +6331,77 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AU Small Finance Bank Ltd.</t>
+          <t>Jindal Stainless Ltd.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1010.3</v>
+        <v>732.7</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1018.0 - 1021.2 RD SUPPLY</t>
+          <t>726.0 - 735.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>830.84 - 841.88 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6411,67 +6411,67 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JSW Steel Ltd.</t>
+          <t>Federal Bank Ltd.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1253.4</v>
+        <v>318.2</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1272.4 - 1275.9 RD SUPPLY</t>
+          <t>317.12 - 318.41 DR DEMAND</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1096.2 - 1116.09 DR DEMAND</t>
+          <t>171.04 - 175.95 DR DEMAND</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -6481,67 +6481,67 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Alkem Laboratories Ltd.</t>
+          <t>Vedanta Ltd.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5163.5</v>
+        <v>252.05</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>5250.0 - 5306.5 RD SUPPLY</t>
+          <t>249.7 - 253.05 DR DEMAND</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6571,67 +6571,67 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>APOLLOTYRE</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Apollo Tyres Ltd.</t>
+          <t>Ashok Leyland Ltd.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>404.7</v>
+        <v>150.48</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>412.9 - 429.0 RD SUPPLY</t>
+          <t>150.3 - 151.46 DR DEMAND</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>207.56 - 211.81 RD SUPPLY</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -6641,77 +6641,77 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DOMS</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DOMS Industries Ltd.</t>
+          <t>Axis Bank Ltd.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2107</v>
+        <v>1217.1</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2141.5 - 2147.0 RD SUPPLY</t>
+          <t>1175.0 - 1186.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1208.6 - 1229.5 DR DEMAND</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6731,67 +6731,67 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FORCEMOT</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Force Motors Ltd.</t>
+          <t>Indian Bank</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>17054</v>
+        <v>793.15</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>17388.0 - 17430.0 RD SUPPLY</t>
+          <t>769.25 - 772.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>24271.95 - 26374.97 RD SUPPLY</t>
+          <t>748.11 - 819.79 DR DEMAND</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6811,77 +6811,77 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MRF</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MRF Ltd.</t>
+          <t>Navin Fluorine International Ltd.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>125280</v>
+        <v>8136.5</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>125780.0 - 126500.0 RD SUPPLY</t>
+          <t>8110.0 - 8151.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>101787.0 - 105025.93 DR DEMAND</t>
+          <t>4173.89 - 4245.43 DR DEMAND</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6891,67 +6891,67 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>THERMAX</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Thermax Ltd.</t>
+          <t>Amber Enterprises India Ltd.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3392.2</v>
+        <v>6500</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>3451.9 - 3464.2 RD SUPPLY</t>
+          <t>6151.0 - 6170.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>6120.0 - 6549.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -6961,44 +6961,44 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ECLERX</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Asian Paints Ltd.</t>
+          <t>eClerx Services Ltd.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -7008,40 +7008,40 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2402.6</v>
+        <v>1802.9</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2444.0 - 2451.0 RD SUPPLY</t>
+          <t>1734.04 - 1810.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2083.96 - 2137.91 DR DEMAND</t>
+          <t>1083.13 - 1256.54 DR DEMAND</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 4 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -7051,67 +7051,67 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GODIGIT</t>
+          <t>ENDURANCE</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Go Digit General Insurance Ltd.</t>
+          <t>Endurance Technologies Ltd.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>260.05</v>
+        <v>2601.4</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>263.25 - 267.0 RD SUPPLY</t>
+          <t>2538.15 - 2615.93 DR DEMAND</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>322.75 - 333.9 RD SUPPLY</t>
+          <t>1661.59 - 1735.99 DR DEMAND</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -7131,57 +7131,57 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>KARURVYSYA</t>
+          <t>VMM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Karur Vysya Bank Ltd.</t>
+          <t>Vishal Mega Mart Ltd.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PVTBANK</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>324.8</v>
+        <v>99.5</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>327.95 - 328.65 RD SUPPLY</t>
+          <t>98.77 - 99.68 DR DEMAND</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7196,54 +7196,54 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Samvardhana Motherson International Ltd.</t>
+          <t>CCL Products (I) Ltd.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7252,31 +7252,31 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>163.26</v>
+        <v>1056.6</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>165.71 - 166.22 RD SUPPLY</t>
+          <t>1073.0 - 1079.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>76.38 - 78.2 DR DEMAND</t>
+          <t>991.4 - 1013.1 DR DEMAND</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -7313,17 +7313,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PNB Housing Finance Ltd.</t>
+          <t>HDFC Bank Ltd.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7332,31 +7332,31 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1120</v>
+        <v>721.2</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1138.5 - 1149.0 RD SUPPLY</t>
+          <t>735.6 - 739.65 RD SUPPLY</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>737.16 - 753.6 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -7393,17 +7393,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>APL Apollo Tubes Ltd.</t>
+          <t>Alkem Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7412,41 +7412,41 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2190.1</v>
+        <v>5220</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1935.05 - 1937.54 DR DEMAND</t>
+          <t>5250.0 - 5306.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2226.02 - 2292.57 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -7473,17 +7473,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>APOLLOTYRE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Berger Paints India Ltd.</t>
+          <t>Apollo Tyres Ltd.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -7492,26 +7492,26 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>455.45</v>
+        <v>404.75</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>458.35 - 459.0 RD SUPPLY</t>
+          <t>412.9 - 429.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>560.77 - 590.09 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -7553,17 +7553,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>CENTRALBK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Emcure Pharmaceuticals Ltd.</t>
+          <t>Central Bank of India</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -7572,31 +7572,31 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1943</v>
+        <v>30</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1834.83 - 1851.1 DR DEMAND</t>
+          <t>30.46 - 30.84 RD SUPPLY</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1962.18 - 2044.02 RD SUPPLY</t>
+          <t>35.83 - 36.93 RD SUPPLY</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -7633,17 +7633,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ITCHOTELS</t>
+          <t>MRF</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ITC Hotels Ltd.</t>
+          <t>MRF Ltd.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -7652,21 +7652,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>164.13</v>
+        <v>123715</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>164.8 - 165.4 RD SUPPLY</t>
+          <t>125780.0 - 126500.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>180.5 - 188.0 RD SUPPLY</t>
+          <t>101787.0 - 105025.92 DR DEMAND</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -7713,17 +7713,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>TECHNOE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Varun Beverages Ltd.</t>
+          <t>Techno Electric &amp; Engineering Company Ltd.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -7732,26 +7732,26 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>432</v>
+        <v>998.6</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>439.3 - 443.3 RD SUPPLY</t>
+          <t>1006.2 - 1016.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>396.2 - 400.45 DR DEMAND</t>
+          <t>863.77 - 967.52 DR DEMAND</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -7793,17 +7793,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LLOYDSME</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Lloyds Metals And Energy Ltd.</t>
+          <t>Asian Paints Ltd.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -7812,41 +7812,41 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1884</v>
+        <v>2407</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1890.9 - 1911.0 RD SUPPLY</t>
+          <t>2444.0 - 2451.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1042.28 - 1072.36 DR DEMAND</t>
+          <t>2083.96 - 2137.91 DR DEMAND</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -7873,17 +7873,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>LGEINDIA</t>
+          <t>KARURVYSYA</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LG Electronics India Ltd.</t>
+          <t>Karur Vysya Bank Ltd.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>PVTBANK</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -7892,16 +7892,16 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1723.5</v>
+        <v>325.3</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1737.1 - 1755.0 RD SUPPLY</t>
+          <t>327.95 - 328.65 RD SUPPLY</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7921,12 +7921,12 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -7953,12 +7953,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>TECHNOE</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Techno Electric &amp; Engineering Company Ltd.</t>
+          <t>Siemens Ltd.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -7972,31 +7972,31 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1008.75</v>
+        <v>3804</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1006.2 - 1016.2 RD SUPPLY</t>
+          <t>3877.0 - 3881.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>863.77 - 967.52 DR DEMAND</t>
+          <t>2891.79 - 2920.65 DR DEMAND</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -8016,34 +8016,34 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>KPIL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Sun TV Network Ltd.</t>
+          <t>Kalpataru Projects International Ltd.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8052,26 +8052,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>605</v>
+        <v>1356.4</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1381.8 - 1386.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>599.4 - 653.93 RD SUPPLY</t>
+          <t>1258.2 - 1289.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -8096,34 +8096,34 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PVR INOX Ltd.</t>
+          <t>Adani Green Energy Ltd.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8132,41 +8132,41 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1242.7</v>
+        <v>1276.1</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>1159.9 - 1169.2 DR DEMAND</t>
+          <t>1296.6 - 1299.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>1207.7 - 1249.7 RD SUPPLY</t>
+          <t>765.0 - 814.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -8176,34 +8176,34 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>BERGEPAINT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>RITES Ltd.</t>
+          <t>Berger Paints India Ltd.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8212,11 +8212,11 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>209.05</v>
+        <v>452.4</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>207.23 - 211.2 RD SUPPLY</t>
+          <t>458.35 - 459.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>214.72 - 226.44 RD SUPPLY</t>
+          <t>560.77 - 590.09 RD SUPPLY</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -8261,24 +8261,24 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>LEMONTREE</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Kajaria Ceramics Ltd.</t>
+          <t>Lemon Tree Hotels Ltd.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -8292,31 +8292,31 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1235.1</v>
+        <v>107.67</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1175.7 - 1183.6 DR DEMAND</t>
+          <t>108.53 - 108.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1181.73 - 1240.58 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -8336,29 +8336,29 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CARBORUNIV</t>
+          <t>APARINDS</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Carborundum Universal Ltd.</t>
+          <t>Apar Industries Ltd.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -8372,26 +8372,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1252.5</v>
+        <v>17648</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1194.0 - 1200.5 DR DEMAND</t>
+          <t>17804.0 - 18062.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1181.58 - 1303.79 RD SUPPLY</t>
+          <t>13236.05 - 14298.36 DR DEMAND</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -8421,90 +8421,650 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>EMCURE</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Emcure Pharmaceuticals Ltd.</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>1944.6</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>1834.83 - 1851.1 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>8.5 A</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>1962.18 - 2044.02 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>4.0 C</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>🟡 1 TEST (TESTED)</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>4.0 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>NEAR SUPPLY</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>NEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>LGEINDIA</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>LG Electronics India Ltd.</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>CONSUMPTION</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>1721.8</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>1737.1 - 1755.0 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>4.0 C</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>— NO ACTIVE ZONE —</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>🟡 1 TEST (TESTED)</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>4.0 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>NEAR SUPPLY</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>NEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>RITES</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>RITES Ltd.</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>209.48</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>207.23 - 211.2 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>5.0 C</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>214.72 - 226.44 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>5.0 C</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>1W DOWN • 20 EMA BEARISH</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>🟡 1 TEST (TESTED)</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>🔥 2.5x VOL EXPLOSION</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>6.0 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>KAJARIACER</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Kajaria Ceramics Ltd.</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>CONSUMPTION</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>1225.1</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>1175.7 - 1183.6 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>1181.73 - 1240.58 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>5.0 C</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>🟡 1 TEST (TESTED)</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>5.0 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>SUNTV</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Sun TV Network Ltd.</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>CONSUMPTION</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>599.9</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>— NO ACTIVE ZONE —</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>599.4 - 653.93 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>4.5 C</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>🟡 1 TEST (TESTED)</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>🔥 1.8x HIGH VOL</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>4.5 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>PVRINOX</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>PVR INOX Ltd.</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>CONSUMPTION</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>1215.3</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>1159.9 - 1169.2 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1207.7 - 1249.7 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>4.0 C</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>🟡 1 TEST (TESTED)</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>4.0 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>CARBORUNIV</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Carborundum Universal Ltd.</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>1239.7</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>1194.0 - 1200.5 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>1181.58 - 1303.79 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>2.5 C</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>🔴 2 TESTS (WEAK)</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>2.5 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
           <t>PHOENIXLTD</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>Phoenix Mills Ltd.</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>REALTY</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
       </c>
-      <c r="E101" t="n">
-        <v>1935</v>
-      </c>
-      <c r="F101" t="inlineStr">
+      <c r="E108" t="n">
+        <v>1930</v>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>1978.4 - 1990.6 RD SUPPLY</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t>5.5 B</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="H108" t="inlineStr">
         <is>
           <t>1851.05 - 1990.36 RD SUPPLY</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="I108" t="inlineStr">
         <is>
           <t>2.5 C</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="J108" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>🔴 2 TESTS (WEAK)</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>🔴 3 TESTS (WEAK)</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
         <is>
           <t>NORMAL VOL</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
+      <c r="M108" t="inlineStr">
         <is>
           <t>+0.0 PTS</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr">
+      <c r="N108" t="inlineStr">
         <is>
           <t>2.5 / 10 SUPPLY</t>
         </is>
       </c>
-      <c r="O101" t="inlineStr">
+      <c r="O108" t="inlineStr">
         <is>
           <t>SUPPLY TEST</t>
         </is>
       </c>
-      <c r="P101" t="inlineStr">
+      <c r="P108" t="inlineStr">
         <is>
           <t>IN</t>
         </is>

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -2066,7 +2066,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>399.84 - 409.23 DR DEMAND</t>
+          <t>399.83 - 409.23 DR DEMAND</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1595.35 - 1664.74 RD SUPPLY</t>
+          <t>1595.35 - 1664.73 RD SUPPLY</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>803.32 - 821.11 DR DEMAND</t>
+          <t>803.34 - 821.13 DR DEMAND</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>101787.0 - 105025.92 DR DEMAND</t>
+          <t>101787.0 - 105025.94 DR DEMAND</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -2066,7 +2066,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>399.83 - 409.23 DR DEMAND</t>
+          <t>399.84 - 409.23 DR DEMAND</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1595.35 - 1664.73 RD SUPPLY</t>
+          <t>1595.35 - 1664.74 RD SUPPLY</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>101787.0 - 105025.94 DR DEMAND</t>
+          <t>101787.0 - 105025.93 DR DEMAND</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P108"/>
+  <dimension ref="A1:P104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,17 +513,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Adani Enterprises Ltd.</t>
+          <t>Glenmark Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -532,31 +532,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2816.8</v>
+        <v>2311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2793.7 - 2831.1 DR DEMAND</t>
+          <t>2292.0 - 2325.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1331.41 - 1376.45 DR DEMAND</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -571,12 +571,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>11.0 / 10 SUPER COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -593,17 +593,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Adani Ports and Special Economic Zone Ltd.</t>
+          <t>CESC Ltd.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -612,31 +612,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1737.8</v>
+        <v>134.43</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1736.6 - 1743.7 DR DEMAND</t>
+          <t>144.0 - 144.33 RD SUPPLY</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1288.07 - 1307.09 DR DEMAND</t>
+          <t>133.19 - 139.44 DR DEMAND</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>11.0 / 10 SUPER COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -673,17 +673,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HBLENGINE</t>
+          <t>SUMICHEM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HBL Engineering Ltd.</t>
+          <t>Sumitomo Chemical India Ltd.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -692,31 +692,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>779.35</v>
+        <v>418.05</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>773.65 - 784.0 DR DEMAND</t>
+          <t>361.73 - 363.57 DR DEMAND</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>6.5 B</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>410.56 - 419.84 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>7.0 A</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>647.1 - 656.44 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7.5 A</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -753,17 +753,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AWL</t>
+          <t>NTPCGREEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AWL Agri Business Ltd.</t>
+          <t>NTPC Green Energy Ltd.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -772,26 +772,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>175.43</v>
+        <v>90.13</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>174.69 - 176.18 DR DEMAND</t>
+          <t>89.65 - 89.99 DR DEMAND</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>109.85 - 119.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -816,34 +816,34 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>11.0 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>BUY READY</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kfin Technologies Ltd.</t>
+          <t>Abbott India Ltd.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -852,26 +852,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>832</v>
+        <v>26115</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>826.8 - 836.62 DR DEMAND</t>
+          <t>25830.0 - 25910.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1329.97 - 1360.84 RD SUPPLY</t>
+          <t>24406.02 - 25223.54 DR DEMAND</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -891,39 +891,39 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>BUY READY</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SUMICHEM</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sumitomo Chemical India Ltd.</t>
+          <t>Craftsman Automation Ltd.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -932,31 +932,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>417.6</v>
+        <v>10348</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>361.73 - 363.57 DR DEMAND</t>
+          <t>10205.0 - 10251.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>410.56 - 419.84 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -976,34 +976,34 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>BUY READY</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mazagoan Dock Shipbuilders Ltd.</t>
+          <t>Hindalco Industries Ltd.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1012,26 +1012,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2064</v>
+        <v>940.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2053.69 - 2061.48 DR DEMAND</t>
+          <t>935.1 - 936.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1900.61 - 2111.67 DR DEMAND</t>
+          <t>766.15 - 804.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>11.5 / 10 SUPER COMBO</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1073,17 +1073,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NTPCGREEN</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NTPC Green Energy Ltd.</t>
+          <t>Indraprastha Gas Ltd.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1092,26 +1092,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>91.09</v>
+        <v>141.38</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>89.65 - 89.99 DR DEMAND</t>
+          <t>137.77 - 140.53 DR DEMAND</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>109.85 - 119.95 RD SUPPLY</t>
+          <t>140.28 - 144.12 DR DEMAND</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>11.0 / 10 SUPER COMBO</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1153,12 +1153,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Glenmark Pharmaceuticals Ltd.</t>
+          <t>Aurobindo Pharma Ltd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1172,26 +1172,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2331</v>
+        <v>1692.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2292.0 - 2325.7 DR DEMAND</t>
+          <t>1663.1 - 1674.9 DR DEMAND</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1331.41 - 1376.45 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>10.5 / 10 HIGH COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1233,17 +1233,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ASAHIINDIA</t>
+          <t>HOMEFIRST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Asahi India Glass Ltd.</t>
+          <t>Home First Finance Company India Ltd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1252,31 +1252,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>944.25</v>
+        <v>1111.5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>925.1 - 929.29 DR DEMAND</t>
+          <t>1075.1 - 1091.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>889.54 - 900.59 DR DEMAND</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1313,17 +1313,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BEML</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BEML Ltd.</t>
+          <t>Infosys Ltd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1332,31 +1332,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962.3</v>
+        <v>1013.85</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1914.23 - 1924.77 DR DEMAND</t>
+          <t>992.2 - 994.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1159.43 - 1211.03 DR DEMAND</t>
+          <t>982.4 - 1000.4 DR DEMAND</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1393,12 +1393,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>MINDACORP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Craftsman Automation Ltd.</t>
+          <t>Minda Corporation Ltd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1412,31 +1412,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>10266</v>
+        <v>659.6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10205.0 - 10251.0 DR DEMAND</t>
+          <t>637.05 - 647.85 DR DEMAND</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>451.85 - 473.12 DR DEMAND</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1473,17 +1473,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CHOLAHLDNG</t>
+          <t>CENTRALBK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cholamandalam Financial Holdings Ltd.</t>
+          <t>Central Bank of India</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1492,11 +1492,11 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1369.6</v>
+        <v>30.19</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1341.0 - 1361.0 DR DEMAND</t>
+          <t>29.32 - 29.62 DR DEMAND</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1358.29 - 1396.78 DR DEMAND</t>
+          <t>35.83 - 36.93 RD SUPPLY</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1553,12 +1553,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CREDITACC</t>
+          <t>CHOLAHLDNG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CreditAccess Grameen Ltd.</t>
+          <t>Cholamandalam Financial Holdings Ltd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1572,26 +1572,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1239</v>
+        <v>1424.6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1209.1 - 1216.3 DR DEMAND</t>
+          <t>1341.0 - 1361.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1602.0 - 1634.0 RD SUPPLY</t>
+          <t>1358.29 - 1396.78 DR DEMAND</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1633,17 +1633,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GICRE</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>General Insurance Corporation of India</t>
+          <t>Mazagoan Dock Shipbuilders Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1652,26 +1652,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>323.9</v>
+        <v>2101</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>319.0 - 320.0 DR DEMAND</t>
+          <t>2053.69 - 2061.48 DR DEMAND</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1900.61 - 2111.67 DR DEMAND</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1713,17 +1713,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hindalco Industries Ltd.</t>
+          <t>Prestige Estates Projects Ltd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1732,26 +1732,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>941.85</v>
+        <v>1467.7</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>935.1 - 936.4 DR DEMAND</t>
+          <t>1438.0 - 1445.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>766.15 - 804.2 DR DEMAND</t>
+          <t>1088.63 - 1125.08 DR DEMAND</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1793,17 +1793,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>INTELLECT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Indraprastha Gas Ltd.</t>
+          <t>Intellect Design Arena Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1812,26 +1812,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>142.79</v>
+        <v>601.4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>137.77 - 140.53 DR DEMAND</t>
+          <t>589.52 - 592.84 DR DEMAND</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>140.28 - 144.12 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1873,17 +1873,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>MSUMI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Power Grid Corporation of India Ltd.</t>
+          <t>Motherson Sumi Wiring India Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1892,26 +1892,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>254.55</v>
+        <v>33.31</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>248.1 - 250.01 DR DEMAND</t>
+          <t>32.7 - 32.89 DR DEMAND</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>238.36 - 241.78 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1953,17 +1953,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>REDINGTON</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Redington Ltd.</t>
+          <t>Torrent Power Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1972,36 +1972,36 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>397.95</v>
+        <v>1234.9</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>390.7 - 392.05 DR DEMAND</t>
+          <t>1211.5 - 1220.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1186.52 - 1241.27 DR DEMAND</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2033,17 +2033,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sona BLW Precision Forgings Ltd.</t>
+          <t>UPL Ltd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2052,31 +2052,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>805</v>
+        <v>509.55</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>793.2 - 795.25 DR DEMAND</t>
+          <t>496.05 - 502.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>399.84 - 409.23 DR DEMAND</t>
+          <t>483.85 - 489.19 DR DEMAND</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2113,17 +2113,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Aditya Birla Capital Ltd.</t>
+          <t>Axis Bank Ltd.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2132,26 +2132,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>375.05</v>
+        <v>1248</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>368.6 - 369.95 DR DEMAND</t>
+          <t>1175.0 - 1186.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>287.7 - 292.25 DR DEMAND</t>
+          <t>1208.6 - 1229.5 DR DEMAND</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2193,17 +2193,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EMAMILTD</t>
+          <t>JKTYRE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Emami Ltd.</t>
+          <t>JK Tyre &amp; Industries Ltd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2212,26 +2212,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>372.65</v>
+        <v>339.35</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>366.55 - 368.45 DR DEMAND</t>
+          <t>333.1 - 334.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>444.5 - 477.0 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2273,17 +2273,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gland Pharma Ltd.</t>
+          <t>Shree Cement Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2292,36 +2292,36 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2874.4</v>
+        <v>22210</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2792.4 - 2826.6 DR DEMAND</t>
+          <t>21550.0 - 21900.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1256.51 - 1376.68 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2353,17 +2353,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>COROMANDEL</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Coromandel International Ltd.</t>
+          <t>Syngene International Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2372,26 +2372,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1763.6</v>
+        <v>363.2</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1704.84 - 1749.4 DR DEMAND</t>
+          <t>355.55 - 357.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1704.84 - 1751.89 DR DEMAND</t>
+          <t>711.99 - 726.54 RD SUPPLY</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2433,17 +2433,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gabriel India Ltd.</t>
+          <t>Adani Enterprises Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2452,36 +2452,36 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1315</v>
+        <v>2849.9</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1294.0 - 1303.9 DR DEMAND</t>
+          <t>2793.7 - 2831.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>794.06 - 824.64 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2513,17 +2513,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IDFC First Bank Ltd.</t>
+          <t>Hero MotoCorp Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2532,26 +2532,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>80.39</v>
+        <v>5075</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>78.6 - 79.46 DR DEMAND</t>
+          <t>4982.0 - 5011.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>57.91 - 58.68 DR DEMAND</t>
+          <t>5627.23 - 5755.34 RD SUPPLY</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2593,17 +2593,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BBTC</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bombay Burmah Trading Corporation Ltd.</t>
+          <t>National Aluminium Co. Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2612,26 +2612,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1334.2</v>
+        <v>337.25</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1314.6 - 1322.0 DR DEMAND</t>
+          <t>331.16 - 333.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1962.03 - 2114.67 RD SUPPLY</t>
+          <t>131.46 - 149.33 DR DEMAND</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2673,17 +2673,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CG Power and Industrial Solutions Ltd.</t>
+          <t>Capri Global Capital Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2692,26 +2692,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>879</v>
+        <v>246.88</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>794.1 - 800.0 DR DEMAND</t>
+          <t>243.67 - 244.62 DR DEMAND</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>814.85 - 863.4 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2721,12 +2721,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2753,17 +2753,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dabur India Ltd.</t>
+          <t>Eicher Motors Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2772,26 +2772,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>374.25</v>
+        <v>7051</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>368.05 - 370.45 DR DEMAND</t>
+          <t>6870.55 - 7000.19 DR DEMAND</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>518.65 - 536.39 RD SUPPLY</t>
+          <t>5099.29 - 5210.66 DR DEMAND</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2833,17 +2833,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hindustan Petroleum Corporation Ltd.</t>
+          <t>Federal Bank Ltd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2852,28 +2852,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>345</v>
+        <v>320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>337.2 - 340.7 DR DEMAND</t>
+          <t>311.69 - 316.02 DR DEMAND</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>4.0 C</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>171.04 - 175.95 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>263.73 - 269.42 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>6.5 B</t>
-        </is>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2913,17 +2913,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>SOBHA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JSW Steel Ltd.</t>
+          <t>Sobha Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2932,26 +2932,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1233</v>
+        <v>1190.7</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1218.0 - 1221.0 DR DEMAND</t>
+          <t>1248.4 - 1251.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1096.2 - 1116.09 DR DEMAND</t>
+          <t>1125.39 - 1182.55 DR DEMAND</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2993,17 +2993,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>KIMS</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Krishna Institute of Medical Sciences Ltd.</t>
+          <t>Bharat Forge Ltd.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3012,28 +3012,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>736.25</v>
+        <v>1880</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>725.4 - 735.3 DR DEMAND</t>
+          <t>1830.45 - 1850.39 DR DEMAND</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
+          <t>3.0 C</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>1605.33 - 1669.53 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
           <t>7.0 A</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>474.05 - 496.35 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>8.0 A</t>
-        </is>
-      </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 4 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3073,17 +3073,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lodha Developers Ltd.</t>
+          <t>Tata Communications Ltd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3092,28 +3092,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1105.6</v>
+        <v>1681.8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1091.8 - 1103.0 DR DEMAND</t>
+          <t>1640.2 - 1649.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>4.0 C</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>1310.58 - 1335.75 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>648.52 - 674.63 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>6.5 B</t>
-        </is>
-      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3153,17 +3153,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>National Aluminium Co. Ltd.</t>
+          <t>Ashok Leyland Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3172,26 +3172,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>334.9</v>
+        <v>153.7</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>331.16 - 333.7 DR DEMAND</t>
+          <t>150.3 - 151.46 DR DEMAND</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>131.46 - 149.33 DR DEMAND</t>
+          <t>207.56 - 211.81 RD SUPPLY</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3233,17 +3233,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NCC</t>
+          <t>CIEINDIA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NCC Ltd.</t>
+          <t>CIE Automotive India Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3252,26 +3252,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>130.06</v>
+        <v>379</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>128.02 - 128.95 DR DEMAND</t>
+          <t>374.8 - 376.45 DR DEMAND</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>479.0 - 504.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3313,17 +3313,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RAINBOW</t>
+          <t>TITAGARH</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Rainbow Childrens Medicare Ltd.</t>
+          <t>Titagarh Rail Systems Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3332,26 +3332,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1279.8</v>
+        <v>804.85</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1255.95 - 1260.24 DR DEMAND</t>
+          <t>789.05 - 796.05 DR DEMAND</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1550.0 - 1610.0 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3393,17 +3393,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>UTIAMC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Petronet LNG Ltd.</t>
+          <t>UTI Asset Management Company Ltd.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3412,36 +3412,36 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>285.5</v>
+        <v>888.2</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>280.3 - 281.75 DR DEMAND</t>
+          <t>1039.08 - 1043.74 RD SUPPLY</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>232.67 - 245.62 DR DEMAND</t>
+          <t>841.38 - 874.76 DR DEMAND</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3473,17 +3473,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>ASTERDM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Torrent Power Ltd.</t>
+          <t>Aster DM Healthcare Ltd.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3492,26 +3492,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1242.9</v>
+        <v>684.7</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1211.5 - 1220.2 DR DEMAND</t>
+          <t>671.0 - 674.35 DR DEMAND</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1186.52 - 1241.27 DR DEMAND</t>
+          <t>516.84 - 549.74 DR DEMAND</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>3.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3553,17 +3553,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>POLYMED</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>United Spirits Ltd.</t>
+          <t>Poly Medicure Ltd.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3572,26 +3572,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1335.1</v>
+        <v>1633.8</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1301.97 - 1310.41 DR DEMAND</t>
+          <t>1607.81 - 1618.09 DR DEMAND</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1595.35 - 1664.74 RD SUPPLY</t>
+          <t>1297.34 - 1337.36 DR DEMAND</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>3.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3633,17 +3633,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CRISIL</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CRISIL Ltd.</t>
+          <t>Bharat Electronics Ltd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3652,21 +3652,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4428.6</v>
+        <v>387.4</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>4325.1 - 4356.3 DR DEMAND</t>
+          <t>397.4 - 399.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3669.91 - 3717.29 DR DEMAND</t>
+          <t>378.32 - 397.37 DR DEMAND</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3696,62 +3696,62 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>JKTYRE</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JK Tyre &amp; Industries Ltd.</t>
+          <t>NATCO Pharma Ltd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>EQUILIBRIUM</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>340.35</v>
+        <v>823.65</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>333.1 - 334.8 DR DEMAND</t>
+          <t>838.12 - 844.07 RD SUPPLY</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>803.34 - 821.13 DR DEMAND</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3771,39 +3771,39 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>CONFLICT</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>RAMCOCEM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Max Healthcare Institute Ltd.</t>
+          <t>The Ramco Cements Ltd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3812,11 +3812,11 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>940.95</v>
+        <v>848.25</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>918.17 - 923.96 DR DEMAND</t>
+          <t>951.15 - 986.61 RD SUPPLY</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3826,12 +3826,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>836.02 - 868.83 DR DEMAND</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3846,44 +3846,44 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>One 97 Communications Ltd.</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3892,31 +3892,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1656</v>
+        <v>958.75</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1624.4 - 1635.8 DR DEMAND</t>
+          <t>1108.0 - 1124.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>651.5 - 700.0 DR DEMAND</t>
+          <t>933.9 - 964.4 DR DEMAND</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3936,34 +3936,34 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TATATECH</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tata Technologies Ltd.</t>
+          <t>Torrent Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3972,36 +3972,36 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>698.8</v>
+        <v>4772</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>683.7 - 686.75 DR DEMAND</t>
+          <t>4755.5 - 4810.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>835.0 - 891.0 RD SUPPLY</t>
+          <t>3068.54 - 3119.39 DR DEMAND</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4016,34 +4016,34 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AIAENG</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AIA Engineering Ltd.</t>
+          <t>SBI Cards and Payment Services Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4052,26 +4052,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3824.4</v>
+        <v>569.4</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>3778.0 - 3805.8 DR DEMAND</t>
+          <t>698.4 - 700.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>5062.37 - 5160.6 RD SUPPLY</t>
+          <t>565.45 - 593.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4096,17 +4096,17 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1178.9</v>
+        <v>1159.8</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4181,24 +4181,24 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SCHAEFFLER</t>
+          <t>ZFCVINDIA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Schaeffler India Ltd.</t>
+          <t>ZF Commercial Vehicle Control Systems India Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4212,11 +4212,11 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3885.6</v>
+        <v>2187.4</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>3811.1 - 3860.2 DR DEMAND</t>
+          <t>2183.71 - 2194.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>3489.69 - 3548.8 DR DEMAND</t>
+          <t>2046.79 - 2067.08 DR DEMAND</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4261,29 +4261,29 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tube Investments of India Ltd.</t>
+          <t>Indian Bank</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4292,26 +4292,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2340</v>
+        <v>813</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2161.89 - 2177.97 DR DEMAND</t>
+          <t>769.25 - 772.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2161.89 - 2330.75 DR DEMAND</t>
+          <t>748.11 - 819.79 DR DEMAND</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>MEDANTA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Astral Ltd.</t>
+          <t>Global Health Ltd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4372,28 +4372,28 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1344</v>
+        <v>1300.8</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1540.5 - 1544.7 RD SUPPLY</t>
+          <t>1295.44 - 1304.54 DR DEMAND</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
+          <t>5.0 C</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>1480.9 - 1544.0 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>1309.54 - 1333.5 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>4.0 C</t>
-        </is>
-      </c>
       <c r="J50" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4421,29 +4421,29 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>NCC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capri Global Capital Ltd.</t>
+          <t>NCC Ltd.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4452,16 +4452,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>249.23</v>
+        <v>128.47</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>243.67 - 244.62 DR DEMAND</t>
+          <t>128.02 - 128.95 DR DEMAND</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4501,29 +4501,29 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Eternal Ltd.</t>
+          <t>Tata Steel Ltd.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4532,11 +4532,11 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>313.9</v>
+        <v>178.69</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>306.2 - 310.25 DR DEMAND</t>
+          <t>177.59 - 179.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4546,17 +4546,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>194.8 - 201.7 DR DEMAND</t>
+          <t>156.83 - 164.57 DR DEMAND</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4581,29 +4581,29 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>SCHAEFFLER</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Indian Hotels Co. Ltd.</t>
+          <t>Schaeffler India Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4612,36 +4612,36 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>718</v>
+        <v>3818.1</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>706.05 - 713.55 DR DEMAND</t>
+          <t>3811.1 - 3860.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>871.1 - 888.32 RD SUPPLY</t>
+          <t>3489.69 - 3548.8 DR DEMAND</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>🔴 5 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4651,39 +4651,39 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NHPC Ltd.</t>
+          <t>Chambal Fertilizers &amp; Chemicals Ltd.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4692,26 +4692,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>71.75</v>
+        <v>404.8</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>81.64 - 82.57 RD SUPPLY</t>
+          <t>487.44 - 491.19 RD SUPPLY</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>67.83 - 70.98 DR DEMAND</t>
+          <t>404.75 - 434.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4736,29 +4736,29 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RAMCOCEM</t>
+          <t>ESCORTS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The Ramco Cements Ltd.</t>
+          <t>Escorts Kubota Ltd.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4768,30 +4768,30 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>830.85</v>
+        <v>2811.7</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>951.15 - 986.61 RD SUPPLY</t>
+          <t>2855.7 - 2866.3 RD SUPPLY</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>784.7 - 825.32 DR DEMAND</t>
+          <t>2679.78 - 2709.64 DR DEMAND</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4811,17 +4811,17 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -4833,55 +4833,55 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>IGIL</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>International Gemological Institute Ltd.</t>
+          <t>Navin Fluorine International Ltd.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>311.95</v>
+        <v>8536</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>309.47 - 310.95 DR DEMAND</t>
+          <t>8584.5 - 8600.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>8688.0 - 8949.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4891,17 +4891,17 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>9.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -4913,47 +4913,47 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NATCO Pharma Ltd.</t>
+          <t>Bharti Airtel Ltd.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>821.3</v>
+        <v>1810.5</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>838.12 - 844.07 RD SUPPLY</t>
+          <t>1833.2 - 1836.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
+          <t>7.5 A</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>1726.3 - 1745.0 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
           <t>7.0 A</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>803.34 - 821.13 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>4.5 C</t>
-        </is>
-      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4971,17 +4971,17 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -4993,45 +4993,45 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>POONAWALLA</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Poonawalla Fincorp Ltd.</t>
+          <t>CCL Products (I) Ltd.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>433.4</v>
+        <v>1054.9</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>425.0 - 428.45 DR DEMAND</t>
+          <t>1073.0 - 1079.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>370.05 - 382.85 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5073,40 +5073,40 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bharat Forge Ltd.</t>
+          <t>JSW Steel Ltd.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1875</v>
+        <v>1259.6</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1830.45 - 1850.39 DR DEMAND</t>
+          <t>1272.4 - 1275.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1605.33 - 1669.53 DR DEMAND</t>
+          <t>1096.2 - 1116.09 DR DEMAND</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5131,17 +5131,17 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5153,45 +5153,45 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MRPL</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mangalore Refinery &amp; Petrochemicals Ltd.</t>
+          <t>KEI Industries Ltd.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>164.76</v>
+        <v>4557.4</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>161.2 - 162.96 DR DEMAND</t>
+          <t>4638.2 - 4652.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>96.88 - 103.61 DR DEMAND</t>
+          <t>3937.0 - 4038.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5211,17 +5211,17 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5233,35 +5233,35 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ONESOURCE</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Onesource Specialty Pharma Ltd.</t>
+          <t>Reliance Industries Ltd.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1508</v>
+        <v>1218</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1479.1 - 1501.3 DR DEMAND</t>
+          <t>1226.0 - 1227.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5291,17 +5291,17 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -5313,55 +5313,55 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>TARIL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Saregama India Ltd</t>
+          <t>Transformers and Rectifiers (India) Ltd.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>494.75</v>
+        <v>283.65</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>484.5 - 488.2 DR DEMAND</t>
+          <t>289.0 - 289.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>223.85 - 235.94 DR DEMAND</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5371,17 +5371,17 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -5393,45 +5393,45 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TITAGARH</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Titagarh Rail Systems Ltd.</t>
+          <t>Adani Power Ltd.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>805.1</v>
+        <v>202.4</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>789.05 - 796.05 DR DEMAND</t>
+          <t>204.0 - 204.49 RD SUPPLY</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>245.0 - 254.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -5473,12 +5473,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>UTIAMC</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>UTI Asset Management Company Ltd.</t>
+          <t>Angel One Ltd.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5488,30 +5488,30 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>883.7</v>
+        <v>295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1039.08 - 1043.74 RD SUPPLY</t>
+          <t>300.0 - 301.1 RD SUPPLY</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>841.38 - 874.76 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5521,27 +5521,27 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -5553,35 +5553,35 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>AWL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Shree Cement Ltd.</t>
+          <t>AWL Agri Business Ltd.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>21900</v>
+        <v>185.93</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>21550.0 - 21900.0 DR DEMAND</t>
+          <t>188.49 - 189.33 RD SUPPLY</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5606,72 +5606,72 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>BSOFT</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AU Small Finance Bank Ltd.</t>
+          <t>Birlasoft Ltd.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>987</v>
+        <v>279.45</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>984.5 - 990.0 DR DEMAND</t>
+          <t>284.15 - 284.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>830.84 - 841.88 DR DEMAND</t>
+          <t>421.73 - 438.51 RD SUPPLY</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5686,72 +5686,72 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>CREDITACC</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Bharat Electronics Ltd.</t>
+          <t>CreditAccess Grameen Ltd.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>383.1</v>
+        <v>1265.8</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>397.4 - 399.2 RD SUPPLY</t>
+          <t>1272.0 - 1278.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>378.32 - 397.37 DR DEMAND</t>
+          <t>1602.0 - 1634.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CIEINDIA</t>
+          <t>MRF</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CIE Automotive India Ltd.</t>
+          <t>MRF Ltd.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5808,32 +5808,32 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>376.35</v>
+        <v>124080</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>374.8 - 376.45 DR DEMAND</t>
+          <t>125780.0 - 126500.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>101787.0 - 105025.92 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>479.0 - 504.0 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>4.0 C</t>
-        </is>
-      </c>
       <c r="J68" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5851,67 +5851,67 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Fortis Healthcare Ltd.</t>
+          <t>Shriram Finance Ltd.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>785</v>
+        <v>965.05</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>915.0 - 918.4 RD SUPPLY</t>
+          <t>982.7 - 987.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>765.99 - 794.16 DR DEMAND</t>
+          <t>559.9 - 573.24 DR DEMAND</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -5926,72 +5926,72 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>TECHNOE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tata Steel Ltd.</t>
+          <t>Techno Electric &amp; Engineering Company Ltd.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>178</v>
+        <v>996.2</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>177.59 - 179.3 DR DEMAND</t>
+          <t>1006.2 - 1016.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>156.83 - 164.57 DR DEMAND</t>
+          <t>863.77 - 967.52 DR DEMAND</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6006,67 +6006,67 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Eicher Motors Ltd.</t>
+          <t>Titan Company Ltd.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6920</v>
+        <v>4550</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>6870.55 - 7000.19 DR DEMAND</t>
+          <t>4599.9 - 4610.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>5099.29 - 5210.66 DR DEMAND</t>
+          <t>3949.84 - 4061.57 DR DEMAND</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6086,57 +6086,57 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>POLYMED</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Poly Medicure Ltd.</t>
+          <t>Asian Paints Ltd.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1638.1</v>
+        <v>2424.2</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1635.65 - 1644.33 DR DEMAND</t>
+          <t>2444.0 - 2451.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1297.34 - 1337.36 DR DEMAND</t>
+          <t>2083.96 - 2137.91 DR DEMAND</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6171,67 +6171,67 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>GODIGIT</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>State Bank of India</t>
+          <t>Go Digit General Insurance Ltd.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>954.1</v>
+        <v>258.6</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1108.0 - 1124.5 RD SUPPLY</t>
+          <t>263.25 - 267.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>933.9 - 964.4 DR DEMAND</t>
+          <t>322.75 - 333.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -6251,67 +6251,67 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>KARURVYSYA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Torrent Pharmaceuticals Ltd.</t>
+          <t>Karur Vysya Bank Ltd.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>PVTBANK</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4767.3</v>
+        <v>325.2</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>4755.5 - 4810.0 DR DEMAND</t>
+          <t>327.95 - 328.65 RD SUPPLY</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>3068.54 - 3119.39 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6331,67 +6331,67 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Jindal Stainless Ltd.</t>
+          <t>Siemens Ltd.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>732.7</v>
+        <v>3854</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>726.0 - 735.7 DR DEMAND</t>
+          <t>3877.0 - 3881.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>2891.79 - 2920.65 DR DEMAND</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6411,147 +6411,147 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>ELGIEQUIP</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Federal Bank Ltd.</t>
+          <t>Elgi Equipments Ltd.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>318.2</v>
+        <v>599.25</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>317.12 - 318.41 DR DEMAND</t>
+          <t>608.85 - 614.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>171.04 - 175.95 DR DEMAND</t>
+          <t>452.89 - 464.98 DR DEMAND</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Vedanta Ltd.</t>
+          <t>Punjab National Bank</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>252.05</v>
+        <v>111.92</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>249.7 - 253.05 DR DEMAND</t>
+          <t>113.06 - 114.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>80.71 - 82.53 DR DEMAND</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -6571,67 +6571,67 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>FORCEMOT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ashok Leyland Ltd.</t>
+          <t>Force Motors Ltd.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>150.48</v>
+        <v>17110</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>150.3 - 151.46 DR DEMAND</t>
+          <t>17388.0 - 17430.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>207.56 - 211.81 RD SUPPLY</t>
+          <t>24271.95 - 26374.97 RD SUPPLY</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -6646,152 +6646,152 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>HONASA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Axis Bank Ltd.</t>
+          <t>Honasa Consumer Ltd.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1217.1</v>
+        <v>478.3</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1175.0 - 1186.5 DR DEMAND</t>
+          <t>483.8 - 488.71 RD SUPPLY</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1208.6 - 1229.5 DR DEMAND</t>
+          <t>483.35 - 506.65 RD SUPPLY</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>STARHEALTH</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Indian Bank</t>
+          <t>Star Health and Allied Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>793.15</v>
+        <v>550.55</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>769.25 - 772.4 DR DEMAND</t>
+          <t>560.55 - 562.85 RD SUPPLY</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>748.11 - 819.79 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -6801,87 +6801,87 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Navin Fluorine International Ltd.</t>
+          <t>Tata Consultancy Services Ltd.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>8136.5</v>
+        <v>2100</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>8110.0 - 8151.0 DR DEMAND</t>
+          <t>2135.1 - 2145.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>4173.89 - 4245.43 DR DEMAND</t>
+          <t>1966.02 - 2020.42 DR DEMAND</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6891,62 +6891,62 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Amber Enterprises India Ltd.</t>
+          <t>Adani Green Energy Ltd.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6500</v>
+        <v>1313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>6151.0 - 6170.5 DR DEMAND</t>
+          <t>1330.6 - 1346.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>6120.0 - 6549.0 DR DEMAND</t>
+          <t>765.0 - 814.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -6961,44 +6961,44 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ECLERX</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>eClerx Services Ltd.</t>
+          <t>Blue Star Ltd.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -7008,40 +7008,40 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1802.9</v>
+        <v>1571.5</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1734.04 - 1810.7 DR DEMAND</t>
+          <t>1572.0 - 1580.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1083.13 - 1256.54 DR DEMAND</t>
+          <t>1931.73 - 2019.69 RD SUPPLY</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -7051,77 +7051,77 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ENDURANCE</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Endurance Technologies Ltd.</t>
+          <t>CG Power and Industrial Solutions Ltd.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2601.4</v>
+        <v>912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2538.15 - 2615.93 DR DEMAND</t>
+          <t>794.1 - 800.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1661.59 - 1735.99 DR DEMAND</t>
+          <t>916.0 - 931.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -7131,77 +7131,77 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>VMM</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Vishal Mega Mart Ltd.</t>
+          <t>DLF Ltd.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>99.5</v>
+        <v>666.1</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>98.77 - 99.68 DR DEMAND</t>
+          <t>673.0 - 676.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>483.33 - 497.85 DR DEMAND</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -7211,39 +7211,39 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>LLOYDSME</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CCL Products (I) Ltd.</t>
+          <t>Lloyds Metals And Energy Ltd.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7252,41 +7252,41 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1056.6</v>
+        <v>1858.2</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1073.0 - 1079.5 RD SUPPLY</t>
+          <t>1890.9 - 1911.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>991.4 - 1013.1 DR DEMAND</t>
+          <t>1042.28 - 1072.36 DR DEMAND</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -7313,17 +7313,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>JAINREC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>HDFC Bank Ltd.</t>
+          <t>Jain Resource Recycling Ltd.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7332,16 +7332,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>721.2</v>
+        <v>290.15</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>735.6 - 739.65 RD SUPPLY</t>
+          <t>292.35 - 293.85 RD SUPPLY</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -7393,17 +7393,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Alkem Laboratories Ltd.</t>
+          <t>Varun Beverages Ltd.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7412,26 +7412,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5220</v>
+        <v>439.3</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>5250.0 - 5306.5 RD SUPPLY</t>
+          <t>439.3 - 443.3 RD SUPPLY</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>396.2 - 400.45 DR DEMAND</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -7441,12 +7441,12 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -7473,17 +7473,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>APOLLOTYRE</t>
+          <t>JSWINFRA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Apollo Tyres Ltd.</t>
+          <t>JSW Infrastructure Ltd.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -7492,36 +7492,36 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>404.75</v>
+        <v>363.05</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>412.9 - 429.0 RD SUPPLY</t>
+          <t>369.0 - 375.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>216.99 - 253.34 DR DEMAND</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -7553,17 +7553,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CENTRALBK</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Central Bank of India</t>
+          <t>Saregama India Ltd</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -7572,36 +7572,36 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>30</v>
+        <v>503.7</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>30.46 - 30.84 RD SUPPLY</t>
+          <t>506.55 - 518.65 RD SUPPLY</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>35.83 - 36.93 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -7633,17 +7633,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MRF</t>
+          <t>RITES</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MRF Ltd.</t>
+          <t>RITES Ltd.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -7652,26 +7652,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>123715</v>
+        <v>203.51</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>125780.0 - 126500.0 RD SUPPLY</t>
+          <t>207.23 - 211.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>101787.0 - 105025.93 DR DEMAND</t>
+          <t>214.72 - 226.44 RD SUPPLY</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>3.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -7713,17 +7713,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TECHNOE</t>
+          <t>BALRAMCHIN</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Techno Electric &amp; Engineering Company Ltd.</t>
+          <t>Balrampur Chini Mills Ltd.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -7732,41 +7732,41 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>998.6</v>
+        <v>691.3</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1006.2 - 1016.2 RD SUPPLY</t>
+          <t>695.95 - 738.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>863.77 - 967.52 DR DEMAND</t>
+          <t>415.9 - 440.91 DR DEMAND</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 5 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>2.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -7793,17 +7793,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>COHANCE</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Asian Paints Ltd.</t>
+          <t>Cohance Lifesciences Ltd.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -7812,41 +7812,41 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2407</v>
+        <v>457</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2444.0 - 2451.0 RD SUPPLY</t>
+          <t>462.35 - 467.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2083.96 - 2137.91 DR DEMAND</t>
+          <t>1229.95 - 1328.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>2.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -7873,17 +7873,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>KARURVYSYA</t>
+          <t>DEEPAKFERT</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Karur Vysya Bank Ltd.</t>
+          <t>Deepak Fertilisers &amp; Petrochemicals Corp. Ltd.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PVTBANK</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -7892,11 +7892,11 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>325.3</v>
+        <v>1385.6</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>327.95 - 328.65 RD SUPPLY</t>
+          <t>1351.0 - 1387.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7906,17 +7906,17 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>876.6 - 939.96 DR DEMAND</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7936,34 +7936,34 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Siemens Ltd.</t>
+          <t>PVR INOX Ltd.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -7972,26 +7972,26 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3804</v>
+        <v>1249.4</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>3877.0 - 3881.6 RD SUPPLY</t>
+          <t>1159.9 - 1169.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2891.79 - 2920.65 DR DEMAND</t>
+          <t>1207.7 - 1249.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -8016,34 +8016,34 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>KPIL</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Kalpataru Projects International Ltd.</t>
+          <t>REC Ltd.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8052,36 +8052,36 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1356.4</v>
+        <v>300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1381.8 - 1386.4 RD SUPPLY</t>
+          <t>299.0 - 301.75 RD SUPPLY</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1258.2 - 1289.0 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -8101,29 +8101,29 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Adani Green Energy Ltd.</t>
+          <t>Alkem Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8132,26 +8132,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1276.1</v>
+        <v>5292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>1296.6 - 1299.6 RD SUPPLY</t>
+          <t>5250.0 - 5306.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>765.0 - 814.2 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -8176,29 +8176,29 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Berger Paints India Ltd.</t>
+          <t>Kajaria Ceramics Ltd.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -8212,31 +8212,31 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>452.4</v>
+        <v>1213.8</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>458.35 - 459.0 RD SUPPLY</t>
+          <t>1175.7 - 1183.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>1181.73 - 1240.58 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
           <t>5.0 C</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>560.77 - 590.09 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>5.0 C</t>
-        </is>
-      </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -8256,29 +8256,29 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>LEMONTREE</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Lemon Tree Hotels Ltd.</t>
+          <t>Sun TV Network Ltd.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -8292,31 +8292,31 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>107.67</v>
+        <v>632.1</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>108.53 - 108.8 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>599.4 - 653.93 RD SUPPLY</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8336,34 +8336,34 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>APARINDS</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Apar Industries Ltd.</t>
+          <t>Gland Pharma Ltd.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8372,26 +8372,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>17648</v>
+        <v>3006.1</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>17804.0 - 18062.0 RD SUPPLY</t>
+          <t>2990.0 - 3024.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>13236.05 - 14298.36 DR DEMAND</t>
+          <t>1256.51 - 1376.68 DR DEMAND</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -8416,34 +8416,34 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Emcure Pharmaceuticals Ltd.</t>
+          <t>Phoenix Mills Ltd.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -8452,36 +8452,36 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1944.6</v>
+        <v>1883.5</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>1834.83 - 1851.1 DR DEMAND</t>
+          <t>1946.8 - 1954.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>1962.18 - 2044.02 RD SUPPLY</t>
+          <t>1851.05 - 1990.36 RD SUPPLY</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -8496,34 +8496,34 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>3.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LGEINDIA</t>
+          <t>POONAWALLA</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LG Electronics India Ltd.</t>
+          <t>Poonawalla Fincorp Ltd.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -8532,26 +8532,26 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1721.8</v>
+        <v>460.45</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1737.1 - 1755.0 RD SUPPLY</t>
+          <t>427.1 - 433.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>454.8 - 503.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -8576,29 +8576,29 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>3.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>CARBORUNIV</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>RITES Ltd.</t>
+          <t>Carborundum Universal Ltd.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -8612,41 +8612,41 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>209.48</v>
+        <v>1269.6</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>207.23 - 211.2 RD SUPPLY</t>
+          <t>1194.0 - 1200.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>214.72 - 226.44 RD SUPPLY</t>
+          <t>1181.58 - 1303.79 RD SUPPLY</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>2.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -8673,17 +8673,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Kajaria Ceramics Ltd.</t>
+          <t>Kotak Mahindra Bank Ltd.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -8692,26 +8692,26 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1225.1</v>
+        <v>431.9</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>1175.7 - 1183.6 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>1181.73 - 1240.58 RD SUPPLY</t>
+          <t>431.46 - 447.25 RD SUPPLY</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -8721,12 +8721,12 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>2.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -8745,326 +8745,6 @@
         </is>
       </c>
       <c r="P104" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>SUNTV</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Sun TV Network Ltd.</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>CONSUMPTION</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-      <c r="E105" t="n">
-        <v>599.9</v>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>599.4 - 653.93 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>4.5 C</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>1W UP • 20 EMA BULLISH</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>🟡 1 TEST (TESTED)</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>🔥 1.8x HIGH VOL</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>+0.0 PTS</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>4.5 / 10 SUPPLY</t>
-        </is>
-      </c>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t>SUPPLY TEST</t>
-        </is>
-      </c>
-      <c r="P105" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>PVRINOX</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>PVR INOX Ltd.</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>CONSUMPTION</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-      <c r="E106" t="n">
-        <v>1215.3</v>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>1159.9 - 1169.2 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>7.0 A</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>1207.7 - 1249.7 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>4.0 C</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>1W UP • 20 EMA BULLISH</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>🟡 1 TEST (TESTED)</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>NORMAL VOL</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>+0.0 PTS</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>4.0 / 10 SUPPLY</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>SUPPLY TEST</t>
-        </is>
-      </c>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>CARBORUNIV</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Carborundum Universal Ltd.</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-      <c r="E107" t="n">
-        <v>1239.7</v>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>1194.0 - 1200.5 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>7.0 A</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>1181.58 - 1303.79 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>2.5 C</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>1W UP • 20 EMA BULLISH</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>🔴 2 TESTS (WEAK)</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>NORMAL VOL</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>+0.0 PTS</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>2.5 / 10 SUPPLY</t>
-        </is>
-      </c>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>SUPPLY TEST</t>
-        </is>
-      </c>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Phoenix Mills Ltd.</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>REALTY</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-      <c r="E108" t="n">
-        <v>1930</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>1978.4 - 1990.6 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>5.5 B</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>1851.05 - 1990.36 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>2.5 C</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>1W UP • 20 EMA BULLISH</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>🔴 3 TESTS (WEAK)</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>NORMAL VOL</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>+0.0 PTS</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>2.5 / 10 SUPPLY</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr">
-        <is>
-          <t>SUPPLY TEST</t>
-        </is>
-      </c>
-      <c r="P108" t="inlineStr">
         <is>
           <t>IN</t>
         </is>

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P120"/>
+  <dimension ref="A1:P126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>136.35</v>
+        <v>138.86</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -593,17 +593,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IDBI</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IDBI Bank Ltd.</t>
+          <t>Tube Investments of India Ltd.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PVTBANK</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -612,26 +612,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>82.94</v>
+        <v>2220.5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>81.32 - 81.87 DR DEMAND</t>
+          <t>2161.89 - 2177.97 DR DEMAND</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>91.3 - 96.25 RD SUPPLY</t>
+          <t>2161.89 - 2330.75 DR DEMAND</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -673,17 +673,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>JKCEMENT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tube Investments of India Ltd.</t>
+          <t>J.K. Cement Ltd.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -692,26 +692,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2194.9</v>
+        <v>4895.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2161.89 - 2177.97 DR DEMAND</t>
+          <t>4810.5 - 4824.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2161.89 - 2330.75 DR DEMAND</t>
+          <t>4193.16 - 4362.57 DR DEMAND</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>11.0 / 10 SUPER COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -753,17 +753,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JKCEMENT</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J.K. Cement Ltd.</t>
+          <t>Aurobindo Pharma Ltd.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4887.5</v>
+        <v>1662.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4810.5 - 4824.5 DR DEMAND</t>
+          <t>1633.0 - 1645.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4193.16 - 4362.57 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>10.5 / 10 HIGH COMBO</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -833,17 +833,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASAHIINDIA</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Asahi India Glass Ltd.</t>
+          <t>Axis Bank Ltd.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -852,11 +852,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>937.05</v>
+        <v>1264.6</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>925.1 - 929.29 DR DEMAND</t>
+          <t>1242.2 - 1247.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -866,12 +866,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1175.0 - 1219.1 DR DEMAND</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -913,17 +913,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Castrol India Ltd.</t>
+          <t>Syrma SGS Technology Ltd.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -932,11 +932,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>193.98</v>
+        <v>1692.2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>193.15 - 193.5 DR DEMAND</t>
+          <t>1657.6 - 1680.9 DR DEMAND</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>144.37 - 156.26 DR DEMAND</t>
+          <t>1782.9 - 1822.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -993,17 +993,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>ABSLAMC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Syrma SGS Technology Ltd.</t>
+          <t>Aditya Birla Sun Life AMC Ltd.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1012,31 +1012,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1694</v>
+        <v>970.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1657.6 - 1680.9 DR DEMAND</t>
+          <t>955.16 - 963.07 DR DEMAND</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>7.5 A</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>721.52 - 740.88 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>7.0 A</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>1782.9 - 1822.6 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>6.0 B</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1073,17 +1073,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>CHOLAHLDNG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GAIL (India) Ltd.</t>
+          <t>Cholamandalam Financial Holdings Ltd.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1092,21 +1092,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>168.3</v>
+        <v>1385</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>164.53 - 165.61 DR DEMAND</t>
+          <t>1341.0 - 1361.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>133.97 - 137.31 DR DEMAND</t>
+          <t>1358.29 - 1396.78 DR DEMAND</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>78.83</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1233,17 +1233,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Indraprastha Gas Ltd.</t>
+          <t>Laurus Labs Ltd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1252,36 +1252,36 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>142.85</v>
+        <v>2036.9</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>137.77 - 140.53 DR DEMAND</t>
+          <t>1988.9 - 1997.9 DR DEMAND</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>140.28 - 144.12 DR DEMAND</t>
+          <t>510.72 - 525.52 DR DEMAND</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1291,12 +1291,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1313,17 +1313,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JSW Energy Ltd.</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1332,26 +1332,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>460.5</v>
+        <v>954.9</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>450.32 - 457.34 DR DEMAND</t>
+          <t>937.5 - 940.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>415.69 - 460.71 DR DEMAND</t>
+          <t>933.9 - 964.4 DR DEMAND</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Torrent Power Ltd.</t>
+          <t>Castrol India Ltd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1412,41 +1412,41 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1189.3</v>
+        <v>196.96</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1169.9 - 1174.4 DR DEMAND</t>
+          <t>193.15 - 193.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>5.5 B</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>144.37 - 156.26 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>1186.52 - 1241.27 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3.0 C</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1473,17 +1473,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ITC Ltd.</t>
+          <t>Hindustan Copper Ltd.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1492,26 +1492,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>261</v>
+        <v>467.65</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>254.65 - 255.9 DR DEMAND</t>
+          <t>450.0 - 462.15 DR DEMAND</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>400.8 - 406.57 RD SUPPLY</t>
+          <t>444.02 - 451.79 DR DEMAND</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1553,17 +1553,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>State Bank of India</t>
+          <t>Lodha Developers Ltd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1572,26 +1572,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>957</v>
+        <v>1059.6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>937.5 - 940.0 DR DEMAND</t>
+          <t>1047.5 - 1050.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>933.9 - 964.4 DR DEMAND</t>
+          <t>648.52 - 674.63 DR DEMAND</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1633,17 +1633,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Biocon Ltd.</t>
+          <t>Navin Fluorine International Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1652,36 +1652,36 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>351</v>
+        <v>8457</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>348.08 - 349.43 DR DEMAND</t>
+          <t>8310.0 - 8352.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>5.5 B</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>4173.89 - 4245.43 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>7.5 A</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>290.26 - 301.69 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4.0 C</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hindustan Copper Ltd.</t>
+          <t>Tata Steel Ltd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1732,11 +1732,11 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>468.05</v>
+        <v>174.49</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>450.0 - 462.15 DR DEMAND</t>
+          <t>171.66 - 172.24 DR DEMAND</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1746,12 +1746,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>444.02 - 451.79 DR DEMAND</t>
+          <t>156.83 - 164.57 DR DEMAND</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1793,17 +1793,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CHOLAHLDNG</t>
+          <t>ESCORTS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cholamandalam Financial Holdings Ltd.</t>
+          <t>Escorts Kubota Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1812,11 +1812,11 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1414.2</v>
+        <v>2689.1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1341.0 - 1361.0 DR DEMAND</t>
+          <t>2550.1 - 2667.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1358.29 - 1396.78 DR DEMAND</t>
+          <t>2679.78 - 2709.64 DR DEMAND</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1873,17 +1873,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>HDBFS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Larsen &amp; Toubro Ltd.</t>
+          <t>HDB Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1892,11 +1892,11 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3675</v>
+        <v>583.75</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3607.0 - 3625.1 DR DEMAND</t>
+          <t>579.2 - 581.75 DR DEMAND</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3256.29 - 3470.21 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1953,17 +1953,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PCBL</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PCBL Chemical Ltd.</t>
+          <t>Indraprastha Gas Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1972,21 +1972,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>312.2</v>
+        <v>145.09</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>308.15 - 309.8 DR DEMAND</t>
+          <t>137.77 - 140.53 DR DEMAND</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>223.38 - 238.62 DR DEMAND</t>
+          <t>140.28 - 144.12 DR DEMAND</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2033,17 +2033,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TRIDENT</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Trident Ltd.</t>
+          <t>Larsen &amp; Toubro Ltd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2052,28 +2052,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>22.16</v>
+        <v>3642</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>21.8 - 21.84 DR DEMAND</t>
+          <t>3607.0 - 3625.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>5.5 B</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3256.29 - 3470.21 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>7.0 A</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2091,12 +2091,12 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2113,17 +2113,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>ASAHIINDIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>InterGlobe Aviation Ltd.</t>
+          <t>Asahi India Glass Ltd.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2132,36 +2132,36 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4800.4</v>
+        <v>930.4</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>4701.5 - 4733.5 DR DEMAND</t>
+          <t>925.1 - 929.29 DR DEMAND</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5901.5 - 5970.0 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2193,17 +2193,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NLC India Ltd.</t>
+          <t>Asian Paints Ltd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2212,26 +2212,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>245.35</v>
+        <v>2344.7</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>238.83 - 241.02 DR DEMAND</t>
+          <t>2317.8 - 2331.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>217.4 - 220.48 DR DEMAND</t>
+          <t>2083.96 - 2137.91 DR DEMAND</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2273,17 +2273,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>WHIRLPOOL</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Whirlpool of India Ltd.</t>
+          <t>Oracle Financial Services Software Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2292,26 +2292,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>799.6</v>
+        <v>10420</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1004.0 - 1011.55 RD SUPPLY</t>
+          <t>10284.0 - 10360.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>766.42 - 785.01 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2353,17 +2353,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>POONAWALLA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Abbott India Ltd.</t>
+          <t>Poonawalla Fincorp Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2372,26 +2372,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>25695</v>
+        <v>437.25</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25475.0 - 25580.0 DR DEMAND</t>
+          <t>427.1 - 433.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>24406.02 - 25223.54 DR DEMAND</t>
+          <t>370.05 - 382.85 DR DEMAND</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2433,12 +2433,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bata India Ltd.</t>
+          <t>Voltas Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2452,11 +2452,11 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>615.2</v>
+        <v>1039.8</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>600.15 - 603.35 DR DEMAND</t>
+          <t>1012.5 - 1020.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>689.25 - 743.46 RD SUPPLY</t>
+          <t>1440.67 - 1533.08 RD SUPPLY</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2513,17 +2513,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CEMPRO</t>
+          <t>CHALET</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cemindia Projects Ltd.</t>
+          <t>Chalet Hotels Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2532,26 +2532,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1138.8</v>
+        <v>820.7</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1116.5 - 1122.4 DR DEMAND</t>
+          <t>803.05 - 809.65 DR DEMAND</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>474.17 - 485.07 DR DEMAND</t>
+          <t>902.92 - 938.88 RD SUPPLY</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2593,17 +2593,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>POONAWALLA</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Poonawalla Fincorp Ltd.</t>
+          <t>Ashok Leyland Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2612,26 +2612,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>440.4</v>
+        <v>145</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>427.1 - 433.4 DR DEMAND</t>
+          <t>143.5 - 144.25 DR DEMAND</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>370.05 - 382.85 DR DEMAND</t>
+          <t>207.56 - 211.81 RD SUPPLY</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2673,17 +2673,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AU Small Finance Bank Ltd.</t>
+          <t>Avenue Supermarts Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2692,26 +2692,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>991.5</v>
+        <v>3415</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>974.2 - 987.0 DR DEMAND</t>
+          <t>4432.2 - 4444.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>830.84 - 841.88 DR DEMAND</t>
+          <t>3340.0 - 3403.95 DR DEMAND</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2753,17 +2753,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Grasim Industries Ltd.</t>
+          <t>Eternal Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2772,31 +2772,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2912</v>
+        <v>316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2853.5 - 2856.8 DR DEMAND</t>
+          <t>306.2 - 310.25 DR DEMAND</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2494.13 - 2528.69 DR DEMAND</t>
+          <t>194.8 - 201.7 DR DEMAND</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2833,17 +2833,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HBLENGINE</t>
+          <t>LENSKART</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HBL Engineering Ltd.</t>
+          <t>Lenskart Solutions Ltd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2852,31 +2852,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>712.75</v>
+        <v>656.95</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>692.0 - 704.65 DR DEMAND</t>
+          <t>645.5 - 653.95 DR DEMAND</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>647.1 - 656.44 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2913,17 +2913,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SARDAEN</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sarda Energy and Minerals Ltd.</t>
+          <t>PCBL Chemical Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2932,26 +2932,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>471.9</v>
+        <v>312.95</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>308.15 - 309.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>451.37 - 469.2 DR DEMAND</t>
+          <t>223.38 - 238.62 DR DEMAND</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2993,17 +2993,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EMAMILTD</t>
+          <t>SOBHA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Emami Ltd.</t>
+          <t>Sobha Ltd.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3012,26 +3012,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>373.5</v>
+        <v>1205.1</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>366.55 - 368.45 DR DEMAND</t>
+          <t>1248.4 - 1251.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
+          <t>7.5 A</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>1125.39 - 1182.55 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
           <t>4.0 C</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>451.6 - 477.0 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>7.0 A</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3073,17 +3073,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ESCORTS</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Escorts Kubota Ltd.</t>
+          <t>AU Small Finance Bank Ltd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3092,26 +3092,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2672.2</v>
+        <v>999.5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2550.1 - 2667.3 DR DEMAND</t>
+          <t>974.2 - 987.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3268.02 - 3369.87 RD SUPPLY</t>
+          <t>830.84 - 841.88 DR DEMAND</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3153,17 +3153,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IOB</t>
+          <t>MEDANTA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Indian Overseas Bank</t>
+          <t>Global Health Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3172,26 +3172,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>30.79</v>
+        <v>1280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>30.07 - 30.38 DR DEMAND</t>
+          <t>1270.9 - 1276.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1480.9 - 1544.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3233,17 +3233,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lenskart Solutions Ltd.</t>
+          <t>Shree Cement Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3252,16 +3252,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>657.3</v>
+        <v>22185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>645.5 - 653.95 DR DEMAND</t>
+          <t>21550.0 - 21900.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3291,12 +3291,12 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3313,17 +3313,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PPLPHARMA</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Piramal Pharma Ltd.</t>
+          <t>Alkem Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3332,11 +3332,11 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>196.01</v>
+        <v>5201</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>193.75 - 194.89 DR DEMAND</t>
+          <t>5110.0 - 5150.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3346,17 +3346,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>132.3 - 136.54 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3393,17 +3393,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SOBHA</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sobha Ltd.</t>
+          <t>Amber Enterprises India Ltd.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3412,21 +3412,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1184.8</v>
+        <v>6645</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1154.1 - 1156.0 DR DEMAND</t>
+          <t>6151.0 - 6170.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1125.39 - 1182.55 DR DEMAND</t>
+          <t>6120.0 - 6549.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3473,17 +3473,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MEDANTA</t>
+          <t>FIVESTAR</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Global Health Ltd.</t>
+          <t>Five-Star Business Finance Ltd.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3492,21 +3492,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1280.2</v>
+        <v>512.3</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1270.9 - 1276.5 DR DEMAND</t>
+          <t>498.25 - 506.25 DR DEMAND</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1480.9 - 1544.0 RD SUPPLY</t>
+          <t>412.05 - 443.54 DR DEMAND</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3553,17 +3553,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Shree Cement Ltd.</t>
+          <t>Indian Hotels Co. Ltd.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3572,36 +3572,36 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>22225</v>
+        <v>725.4</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>21550.0 - 21900.0 DR DEMAND</t>
+          <t>706.05 - 713.55 DR DEMAND</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>871.1 - 888.32 RD SUPPLY</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🔴 5 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3633,17 +3633,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Alkem Laboratories Ltd.</t>
+          <t>Mazagoan Dock Shipbuilders Ltd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3652,26 +3652,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5250</v>
+        <v>2124.4</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>5110.0 - 5150.0 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1900.61 - 2111.67 DR DEMAND</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3713,17 +3713,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>PIRAMALFIN</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Amber Enterprises India Ltd.</t>
+          <t>Piramal Finance Ltd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3732,26 +3732,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6640</v>
+        <v>1951.1</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>6380.0 - 6445.0 DR DEMAND</t>
+          <t>1901.22 - 1939.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6120.0 - 6549.0 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3793,17 +3793,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>SAILIFE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Indian Hotels Co. Ltd.</t>
+          <t>Sai Life Sciences Ltd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3812,11 +3812,11 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>724.15</v>
+        <v>1432.1</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>706.05 - 713.55 DR DEMAND</t>
+          <t>1415.0 - 1422.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3826,12 +3826,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>871.1 - 888.32 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>🔴 5 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3873,17 +3873,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>JUBLINGREA</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Jubilant Ingrevia Ltd.</t>
+          <t>Tata Communications Ltd.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3892,21 +3892,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>627.5</v>
+        <v>1658.9</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>613.35 - 617.6 DR DEMAND</t>
+          <t>1640.2 - 1649.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>714.54 - 766.92 RD SUPPLY</t>
+          <t>1310.58 - 1335.75 DR DEMAND</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3953,17 +3953,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LALPATHLAB</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dr. Lal Path Labs Ltd.</t>
+          <t>Vedanta Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3972,11 +3972,11 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1910.6</v>
+        <v>250</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1885.0 - 1896.9 DR DEMAND</t>
+          <t>244.83 - 248.11 DR DEMAND</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4033,12 +4033,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>USHAMART</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mazagoan Dock Shipbuilders Ltd.</t>
+          <t>Usha Martin Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4052,26 +4052,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2120</v>
+        <v>487</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2816.13 - 2834.04 RD SUPPLY</t>
+          <t>477.8 - 481.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1900.61 - 2111.67 DR DEMAND</t>
+          <t>274.28 - 291.22 DR DEMAND</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4113,17 +4113,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>UTIAMC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tata Communications Ltd.</t>
+          <t>UTI Asset Management Company Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4132,11 +4132,11 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1672.4</v>
+        <v>876.5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1640.2 - 1649.3 DR DEMAND</t>
+          <t>1039.08 - 1043.74 RD SUPPLY</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -4146,12 +4146,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1310.58 - 1335.75 DR DEMAND</t>
+          <t>841.38 - 874.76 DR DEMAND</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4193,17 +4193,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>AFFLE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Vedanta Ltd.</t>
+          <t>Affle 3i Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4212,11 +4212,11 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>256.3</v>
+        <v>1434.1</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>249.7 - 253.05 DR DEMAND</t>
+          <t>1389.9 - 1406.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1251.3 - 1335.3 DR DEMAND</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4241,22 +4241,22 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🔴 4 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>4.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4273,17 +4273,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>USHAMART</t>
+          <t>ASTERDM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Usha Martin Ltd.</t>
+          <t>Aster DM Healthcare Ltd.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4292,26 +4292,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>486.45</v>
+        <v>675.2</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>477.8 - 481.3 DR DEMAND</t>
+          <t>671.0 - 674.35 DR DEMAND</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>274.28 - 291.22 DR DEMAND</t>
+          <t>516.84 - 549.74 DR DEMAND</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🔴 4 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>4.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4353,17 +4353,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>UTIAMC</t>
+          <t>BLUEJET</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>UTI Asset Management Company Ltd.</t>
+          <t>Blue Jet Healthcare Ltd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4372,26 +4372,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>887.6</v>
+        <v>522.45</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1039.08 - 1043.74 RD SUPPLY</t>
+          <t>507.79 - 514.92 DR DEMAND</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>841.38 - 874.76 DR DEMAND</t>
+          <t>631.68 - 646.45 RD SUPPLY</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>3.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4433,17 +4433,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BLUEJET</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Blue Jet Healthcare Ltd.</t>
+          <t>Jindal Steel Ltd.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4452,26 +4452,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>517.85</v>
+        <v>1029.2</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>507.79 - 514.92 DR DEMAND</t>
+          <t>1000.91 - 1008.99 DR DEMAND</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>631.68 - 646.45 RD SUPPLY</t>
+          <t>1008.29 - 1043.63 DR DEMAND</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4491,39 +4491,39 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>3.5 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Jindal Steel Ltd.</t>
+          <t>Bharat Electronics Ltd.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4532,26 +4532,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1031.7</v>
+        <v>382.35</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1000.91 - 1008.99 DR DEMAND</t>
+          <t>397.4 - 399.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1008.29 - 1043.63 DR DEMAND</t>
+          <t>378.32 - 397.37 DR DEMAND</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4593,17 +4593,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>LINDEINDIA</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Linde India Ltd.</t>
+          <t>InterGlobe Aviation Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4612,11 +4612,11 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6009</v>
+        <v>4718.5</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>5991.0 - 6030.0 DR DEMAND</t>
+          <t>4701.5 - 4733.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>7487.35 - 7842.09 RD SUPPLY</t>
+          <t>5901.5 - 5970.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4673,17 +4673,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bharat Electronics Ltd.</t>
+          <t>CG Power and Industrial Solutions Ltd.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4692,26 +4692,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>380</v>
+        <v>863</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>397.4 - 399.2 RD SUPPLY</t>
+          <t>794.1 - 800.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>378.32 - 397.37 DR DEMAND</t>
+          <t>814.85 - 863.4 DR DEMAND</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4753,17 +4753,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Reliance Industries Ltd.</t>
+          <t>SBI Cards and Payment Services Ltd.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4772,26 +4772,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1166.7</v>
+        <v>568</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1160.8 - 1167.7 DR DEMAND</t>
+          <t>698.4 - 700.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>565.45 - 593.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4833,17 +4833,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>ANTHEM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CG Power and Industrial Solutions Ltd.</t>
+          <t>Anthem Biosciences Ltd.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4852,31 +4852,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>854</v>
+        <v>847.75</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>794.1 - 800.0 DR DEMAND</t>
+          <t>842.2 - 862.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>814.85 - 863.4 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4913,17 +4913,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>COROMANDEL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SBI Cards and Payment Services Ltd.</t>
+          <t>Coromandel International Ltd.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4932,26 +4932,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>572.3</v>
+        <v>1747</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>698.4 - 700.4 RD SUPPLY</t>
+          <t>1963.9 - 1975.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>565.45 - 593.2 DR DEMAND</t>
+          <t>1704.84 - 1751.89 DR DEMAND</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4993,47 +4993,47 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SUMICHEM</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sumitomo Chemical India Ltd.</t>
+          <t>ICICI Bank Ltd.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>414.25</v>
+        <v>1338.6</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>421.95 - 426.85 RD SUPPLY</t>
+          <t>1329.4 - 1339.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
+          <t>4.5 C</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>1457.77 - 1476.07 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
           <t>5.0 C</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>410.56 - 419.84 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>7.0 A</t>
-        </is>
-      </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5066,24 +5066,24 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>CONFLICT</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>COROMANDEL</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Coromandel International Ltd.</t>
+          <t>GAIL (India) Ltd.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5092,26 +5092,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1723.2</v>
+        <v>166.96</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1963.9 - 1975.0 RD SUPPLY</t>
+          <t>166.44 - 167.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1704.84 - 1751.89 DR DEMAND</t>
+          <t>133.97 - 137.31 DR DEMAND</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5153,17 +5153,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FIVESTAR</t>
+          <t>RAMCOCEM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Five-Star Business Finance Ltd.</t>
+          <t>The Ramco Cements Ltd.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5172,26 +5172,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>505.2</v>
+        <v>804.15</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>498.25 - 506.25 DR DEMAND</t>
+          <t>951.15 - 986.61 RD SUPPLY</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>412.05 - 443.54 DR DEMAND</t>
+          <t>784.7 - 825.32 DR DEMAND</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5233,17 +5233,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SAMMAANCAP</t>
+          <t>TECHNOE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sammaan Capital Ltd.</t>
+          <t>Techno Electric &amp; Engineering Company Ltd.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5252,11 +5252,11 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>135.1</v>
+        <v>949.8</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>144.48 - 145.94 RD SUPPLY</t>
+          <t>1006.2 - 1016.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>134.75 - 144.61 DR DEMAND</t>
+          <t>863.77 - 967.52 DR DEMAND</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5313,17 +5313,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>PPLPHARMA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Avenue Supermarts Ltd.</t>
+          <t>Piramal Pharma Ltd.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5332,26 +5332,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3383</v>
+        <v>193.94</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>4432.2 - 4444.5 RD SUPPLY</t>
+          <t>193.75 - 194.89 DR DEMAND</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>3340.0 - 3403.95 DR DEMAND</t>
+          <t>132.3 - 136.54 DR DEMAND</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5393,17 +5393,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>RAMCOCEM</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Ramco Cements Ltd.</t>
+          <t>Torrent Power Ltd.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5412,11 +5412,11 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>809.45</v>
+        <v>1240.3</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>951.15 - 986.61 RD SUPPLY</t>
+          <t>1165.0 - 1174.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>784.7 - 825.32 DR DEMAND</t>
+          <t>1186.52 - 1241.27 DR DEMAND</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5473,17 +5473,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TECHNOE</t>
+          <t>GLAXO</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Techno Electric &amp; Engineering Company Ltd.</t>
+          <t>Glaxosmithkline Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5492,28 +5492,28 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>943.9</v>
+        <v>2538.9</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1006.2 - 1016.2 RD SUPPLY</t>
+          <t>2515.0 - 2546.9 DR DEMAND</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
+          <t>2.5 C</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>1849.2 - 1903.26 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
           <t>7.0 A</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>863.77 - 967.52 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>4.0 C</t>
-        </is>
-      </c>
       <c r="J64" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5531,12 +5531,12 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>3.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5553,45 +5553,45 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Glaxosmithkline Pharmaceuticals Ltd.</t>
+          <t>Tata Elxsi Ltd.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2536.3</v>
+        <v>3623.1</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2515.0 - 2546.9 DR DEMAND</t>
+          <t>3685.0 - 3708.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1849.2 - 1903.26 DR DEMAND</t>
+          <t>2996.0 - 3088.9 DR DEMAND</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5601,49 +5601,49 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>UCOBANK</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>UCO Bank</t>
+          <t>Adani Green Energy Ltd.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5652,31 +5652,31 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>23.61</v>
+        <v>1318.4</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>23.9 - 23.95 RD SUPPLY</t>
+          <t>1342.7 - 1377.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>32.81 - 33.64 RD SUPPLY</t>
+          <t>765.0 - 814.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>9.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -5713,17 +5713,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ABFRL</t>
+          <t>JSWCEMENT</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Aditya Birla Fashion and Retail Ltd.</t>
+          <t>JSW Cement Ltd.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5732,16 +5732,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>44.78</v>
+        <v>114.7</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>45.68 - 47.39 RD SUPPLY</t>
+          <t>115.77 - 116.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>9.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -5793,17 +5793,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BAJAJHFL</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bajaj Housing Finance Ltd.</t>
+          <t>ABB India Ltd.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5812,11 +5812,11 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>82.67</v>
+        <v>6999</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>84.08 - 84.41 RD SUPPLY</t>
+          <t>7122.5 - 7140.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>7638.5 - 7825.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5873,17 +5873,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>MINDACORP</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Bharti Airtel Ltd.</t>
+          <t>Minda Corporation Ltd.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5892,11 +5892,11 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1806.5</v>
+        <v>657.15</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1833.2 - 1836.7 RD SUPPLY</t>
+          <t>659.6 - 661.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1527.35 - 1537.83 DR DEMAND</t>
+          <t>451.85 - 473.12 DR DEMAND</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -5953,17 +5953,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Britannia Industries Ltd.</t>
+          <t>NLC India Ltd.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5972,11 +5972,11 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4801.3</v>
+        <v>257.65</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>4883.8 - 4892.5 RD SUPPLY</t>
+          <t>261.7 - 263.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5986,12 +5986,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>4374.85 - 4461.7 DR DEMAND</t>
+          <t>217.4 - 220.48 DR DEMAND</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6033,17 +6033,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DEEPAKNTR</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deepak Nitrite Ltd.</t>
+          <t>NMDC Ltd.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6052,11 +6052,11 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1622.1</v>
+        <v>71.08</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1635.8 - 1639.0 RD SUPPLY</t>
+          <t>71.99 - 72.33 RD SUPPLY</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6113,17 +6113,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MINDACORP</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Minda Corporation Ltd.</t>
+          <t>Pidilite Industries Ltd.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6132,11 +6132,11 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>651.2</v>
+        <v>1499.5</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>659.6 - 661.5 RD SUPPLY</t>
+          <t>1520.5 - 1524.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>451.85 - 473.12 DR DEMAND</t>
+          <t>1687.7 - 1707.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6193,17 +6193,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Pidilite Industries Ltd.</t>
+          <t>360 ONE WAM Ltd.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6212,26 +6212,26 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1497.6</v>
+        <v>1063</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1520.5 - 1524.6 RD SUPPLY</t>
+          <t>1077.5 - 1080.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1687.7 - 1707.5 RD SUPPLY</t>
+          <t>1185.06 - 1260.04 RD SUPPLY</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -6273,17 +6273,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ZENTEC</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Zen Technologies Ltd.</t>
+          <t>Aditya Birla Capital Ltd.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6292,26 +6292,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1652.7</v>
+        <v>378.9</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1682.4 - 1695.0 RD SUPPLY</t>
+          <t>385.6 - 386.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>943.53 - 1043.28 DR DEMAND</t>
+          <t>287.7 - 292.25 DR DEMAND</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -6353,12 +6353,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BSE Ltd.</t>
+          <t>Bajaj Finserv Ltd.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6372,11 +6372,11 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3375.4</v>
+        <v>1721.7</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>3417.0 - 3452.7 RD SUPPLY</t>
+          <t>1755.7 - 1758.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>3000.0 - 3089.9 DR DEMAND</t>
+          <t>1991.7 - 2073.13 RD SUPPLY</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -6433,17 +6433,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>INDIACEM</t>
+          <t>BAJAJHFL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>India Cements Ltd.</t>
+          <t>Bajaj Housing Finance Ltd.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6452,11 +6452,11 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>299.4</v>
+        <v>84.55</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>303.05 - 305.0 RD SUPPLY</t>
+          <t>85.58 - 86.45 RD SUPPLY</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6466,12 +6466,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>400.0 - 416.4 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6513,17 +6513,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Capri Global Capital Ltd.</t>
+          <t>Grasim Industries Ltd.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6532,31 +6532,31 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>248.9</v>
+        <v>2873</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>250.74 - 252.0 RD SUPPLY</t>
+          <t>2899.4 - 2919.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>2494.13 - 2528.7 DR DEMAND</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -6593,17 +6593,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>INDIACEM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HDFC Life Insurance Company Ltd.</t>
+          <t>India Cements Ltd.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6612,28 +6612,28 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>560</v>
+        <v>295.65</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>561.0 - 561.95 RD SUPPLY</t>
+          <t>300.65 - 302.15 RD SUPPLY</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>400.0 - 416.4 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
           <t>6.5 B</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>811.41 - 817.84 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>4.0 C</t>
-        </is>
-      </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -6673,12 +6673,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank Ltd.</t>
+          <t>IndusInd Bank Ltd.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6692,31 +6692,31 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>439</v>
+        <v>866</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>440.0 - 441.5 RD SUPPLY</t>
+          <t>877.6 - 883.05 RD SUPPLY</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>431.46 - 447.25 RD SUPPLY</t>
+          <t>605.02 - 647.95 DR DEMAND</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -6753,17 +6753,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>RAINBOW</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LT Foods Ltd.</t>
+          <t>Rainbow Childrens Medicare Ltd.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -6772,31 +6772,31 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>414.25</v>
+        <v>1246.7</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>418.4 - 421.9 RD SUPPLY</t>
+          <t>1270.7 - 1288.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>285.59 - 341.87 DR DEMAND</t>
+          <t>1550.0 - 1610.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -6833,17 +6833,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Ltd.</t>
+          <t>Steel Authority of India Ltd.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -6852,31 +6852,31 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3308</v>
+        <v>170</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>3362.6 - 3374.6 RD SUPPLY</t>
+          <t>172.77 - 174.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>202.55 - 206.99 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
           <t>7.5 A</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>2559.23 - 2685.62 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>9.0 A+</t>
-        </is>
-      </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -6913,17 +6913,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Radico Khaitan Ltd</t>
+          <t>Computer Age Management Services Ltd.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -6932,31 +6932,31 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4540</v>
+        <v>694</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>4601.9 - 4614.1 RD SUPPLY</t>
+          <t>701.0 - 704.45 RD SUPPLY</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>591.51 - 613.37 DR DEMAND</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -6993,17 +6993,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Supreme Industries Ltd.</t>
+          <t>Capri Global Capital Ltd.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7012,11 +7012,11 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3506.9</v>
+        <v>247.91</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>3567.7 - 3631.8 RD SUPPLY</t>
+          <t>250.74 - 252.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -7073,12 +7073,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>ABFRL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Trent Ltd.</t>
+          <t>Aditya Birla Fashion and Retail Ltd.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7092,36 +7092,36 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2987.8</v>
+        <v>45.28</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2989.9 - 3020.6 RD SUPPLY</t>
+          <t>45.68 - 47.39 RD SUPPLY</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2545.8 - 2615.0 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7153,17 +7153,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>CENTRALBK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>KEI Industries Ltd.</t>
+          <t>Central Bank of India</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7172,11 +7172,11 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4640.6</v>
+        <v>31.18</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>4722.5 - 4760.0 RD SUPPLY</t>
+          <t>31.63 - 31.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>3937.0 - 4038.0 DR DEMAND</t>
+          <t>35.83 - 36.93 RD SUPPLY</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7201,12 +7201,12 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7233,17 +7233,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LGEINDIA</t>
+          <t>INDGN</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>LG Electronics India Ltd.</t>
+          <t>Indegene Ltd.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7252,11 +7252,11 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1758</v>
+        <v>596.9</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1782.0 - 1790.0 RD SUPPLY</t>
+          <t>607.1 - 612.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>412.19 - 432.7 DR DEMAND</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -7313,17 +7313,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FORCEMOT</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Force Motors Ltd.</t>
+          <t>KEI Industries Ltd.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7332,26 +7332,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>17170</v>
+        <v>4648</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>17388.0 - 17430.0 RD SUPPLY</t>
+          <t>4722.5 - 4760.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>24271.95 - 26374.97 RD SUPPLY</t>
+          <t>3937.0 - 4038.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -7393,17 +7393,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GESHIP</t>
+          <t>LALPATHLAB</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Great Eastern Shipping Co. Ltd.</t>
+          <t>Dr. Lal Path Labs Ltd.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7412,26 +7412,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1542</v>
+        <v>1938</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1565.0 - 1570.5 RD SUPPLY</t>
+          <t>1969.7 - 2002.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>762.54 - 775.16 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -7473,12 +7473,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>UCOBANK</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Bank of Maharashtra</t>
+          <t>UCO Bank</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -7492,36 +7492,36 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>83.73999999999999</v>
+        <v>23.96</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>84.15 - 84.5 RD SUPPLY</t>
+          <t>24.12 - 24.17 RD SUPPLY</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
+          <t>6.0 B</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>32.81 - 33.64 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
           <t>6.5 B</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>91.75 - 94.5 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>6.5 B</t>
-        </is>
-      </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -7553,17 +7553,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>THELEELA</t>
+          <t>ANURAS</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Leela Palaces Hotels &amp; Resorts Ltd.</t>
+          <t>Anupam Rasayan India Ltd.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -7572,36 +7572,36 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>601.25</v>
+        <v>1187</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>604.45 - 607.25 RD SUPPLY</t>
+          <t>1207.7 - 1219.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>599.85 - 631.19 DR DEMAND</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -7633,17 +7633,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>GESHIP</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>APL Apollo Tubes Ltd.</t>
+          <t>Great Eastern Shipping Co. Ltd.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -7652,26 +7652,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2185</v>
+        <v>1543.1</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026.2 - 2040.0 DR DEMAND</t>
+          <t>1567.9 - 1577.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2226.02 - 2292.57 RD SUPPLY</t>
+          <t>762.54 - 775.16 DR DEMAND</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -7713,17 +7713,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CARTRADE</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cartrade Tech Ltd.</t>
+          <t>Bank of Maharashtra</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -7732,26 +7732,26 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3152.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>3177.1 - 3189.0 RD SUPPLY</t>
+          <t>84.15 - 84.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1485.0 - 1525.0 DR DEMAND</t>
+          <t>91.75 - 94.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -7793,17 +7793,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LEMONTREE</t>
+          <t>AARTIIND</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Lemon Tree Hotels Ltd.</t>
+          <t>Aarti Industries Ltd.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -7812,11 +7812,11 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>111.86</v>
+        <v>497.9</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>112.71 - 113.55 RD SUPPLY</t>
+          <t>502.7 - 503.75 RD SUPPLY</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>525.95 - 550.66 RD SUPPLY</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7873,17 +7873,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Syngene International Ltd.</t>
+          <t>Angel One Ltd.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -7892,36 +7892,36 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>379.55</v>
+        <v>306.05</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>385.15 - 387.05 RD SUPPLY</t>
+          <t>306.45 - 310.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>711.99 - 726.54 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7953,17 +7953,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>DCMSHRIRAM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CCL Products (I) Ltd.</t>
+          <t>DCM Shriram Ltd.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -7972,21 +7972,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1070.7</v>
+        <v>1033.3</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1073.0 - 1079.5 RD SUPPLY</t>
+          <t>1044.55 - 1088.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>991.4 - 1013.1 DR DEMAND</t>
+          <t>1227.63 - 1319.98 RD SUPPLY</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -7996,17 +7996,17 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -8033,17 +8033,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>FINCABLES</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DLF Ltd.</t>
+          <t>Finolex Cables Ltd.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8052,26 +8052,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>664.8</v>
+        <v>1446.3</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>673.0 - 676.5 RD SUPPLY</t>
+          <t>1474.5 - 1480.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>483.33 - 497.85 DR DEMAND</t>
+          <t>949.44 - 980.62 DR DEMAND</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -8113,17 +8113,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STARHEALTH</t>
+          <t>FLUOROCHEM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Star Health and Allied Insurance Company Ltd.</t>
+          <t>Gujarat Fluorochemicals Ltd.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8132,26 +8132,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>560.1</v>
+        <v>4632.1</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>560.55 - 562.85 RD SUPPLY</t>
+          <t>3338.79 - 3344.99 DR DEMAND</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>4706.78 - 4955.62 RD SUPPLY</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -8193,17 +8193,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ABDL</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Allied Blenders and Distillers Ltd.</t>
+          <t>HDFC Bank Ltd.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8212,11 +8212,11 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>718.45</v>
+        <v>710.7</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>719.6 - 727.85 RD SUPPLY</t>
+          <t>711.45 - 714.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -8226,17 +8226,17 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>378.82 - 400.58 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -8273,17 +8273,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AWL</t>
+          <t>LEMONTREE</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>AWL Agri Business Ltd.</t>
+          <t>Lemon Tree Hotels Ltd.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -8292,16 +8292,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>184.91</v>
+        <v>111.46</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>188.49 - 189.33 RD SUPPLY</t>
+          <t>112.71 - 113.55 RD SUPPLY</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -8353,17 +8353,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CENTRALBK</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Central Bank of India</t>
+          <t>Nestle India Ltd.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8372,26 +8372,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>30.39</v>
+        <v>1383.2</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>30.46 - 30.84 RD SUPPLY</t>
+          <t>1384.5 - 1397.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>35.83 - 36.93 RD SUPPLY</t>
+          <t>1292.9 - 1301.9 DR DEMAND</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -8401,12 +8401,12 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -8433,17 +8433,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kalyan Jewellers India Ltd.</t>
+          <t>REC Ltd.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -8452,31 +8452,31 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>571</v>
+        <v>311.8</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>571.8 - 581.2 RD SUPPLY</t>
+          <t>314.0 - 315.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>760.91 - 789.86 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>4.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -8513,17 +8513,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>FSN E-Commerce Ventures Ltd.</t>
+          <t>DLF Ltd.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -8532,26 +8532,26 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>338</v>
+        <v>666.9</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>341.25 - 346.45 RD SUPPLY</t>
+          <t>673.0 - 676.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>232.05 - 235.0 DR DEMAND</t>
+          <t>483.33 - 497.85 DR DEMAND</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>4.5 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -8593,17 +8593,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>LTFOODS</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Punjab National Bank</t>
+          <t>LT Foods Ltd.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -8612,26 +8612,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>116.55</v>
+        <v>418.05</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>118.45 - 118.74 RD SUPPLY</t>
+          <t>418.4 - 421.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>80.71 - 82.53 DR DEMAND</t>
+          <t>285.59 - 341.86 DR DEMAND</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -8673,17 +8673,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>ZENTEC</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Saregama India Ltd</t>
+          <t>Zen Technologies Ltd.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -8692,31 +8692,31 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>501.15</v>
+        <v>1649.3</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>506.55 - 518.65 RD SUPPLY</t>
+          <t>1682.4 - 1695.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>943.53 - 1043.28 DR DEMAND</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -8753,12 +8753,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>AWL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Navin Fluorine International Ltd.</t>
+          <t>AWL Agri Business Ltd.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -8772,36 +8772,36 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>8468</v>
+        <v>188.21</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>8584.5 - 8600.0 RD SUPPLY</t>
+          <t>188.49 - 189.33 RD SUPPLY</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>4173.89 - 4245.43 DR DEMAND</t>
+          <t>172.6 - 176.61 DR DEMAND</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>3.5 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -8833,12 +8833,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>IDBI</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>City Union Bank Ltd.</t>
+          <t>IDBI Bank Ltd.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -8852,26 +8852,26 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>234.53</v>
+        <v>90.39</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>235.93 - 243.1 RD SUPPLY</t>
+          <t>81.32 - 81.87 DR DEMAND</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>177.59 - 189.81 DR DEMAND</t>
+          <t>91.3 - 96.25 RD SUPPLY</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>3.0 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -8913,17 +8913,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>KALYANKJIL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>LIC Housing Finance Ltd.</t>
+          <t>Kalyan Jewellers India Ltd.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -8936,22 +8936,22 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>574.07 - 586.43 RD SUPPLY</t>
+          <t>571.8 - 581.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>449.87 - 485.5 DR DEMAND</t>
+          <t>760.91 - 789.86 RD SUPPLY</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -8961,7 +8961,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>🔴 5 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2.5 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -8993,12 +8993,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FIRSTCRY</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Brainbees Solutions Ltd.</t>
+          <t>Trent Ltd.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -9012,36 +9012,36 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>178.03</v>
+        <v>2971</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>178.01 - 178.85 RD SUPPLY</t>
+          <t>2989.9 - 3020.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>2545.8 - 2615.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -9056,34 +9056,34 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>HDFC Bank Ltd.</t>
+          <t>Clean Science and Technology Ltd.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9092,36 +9092,36 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>714</v>
+        <v>818.6</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>711.45 - 714.7 RD SUPPLY</t>
+          <t>824.8 - 830.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1538.62 - 1583.15 RD SUPPLY</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -9136,34 +9136,34 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>3.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CREDITACC</t>
+          <t>FORCEMOT</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CreditAccess Grameen Ltd.</t>
+          <t>Force Motors Ltd.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9172,26 +9172,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1278.4</v>
+        <v>17270</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>1272.0 - 1278.8 RD SUPPLY</t>
+          <t>17388.0 - 17430.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>1602.0 - 1634.0 RD SUPPLY</t>
+          <t>24271.95 - 26374.97 RD SUPPLY</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -9216,34 +9216,34 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>3.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>LTTS</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Angel One Ltd.</t>
+          <t>L&amp;T Technology Services Ltd.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9252,26 +9252,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>310</v>
+        <v>3613.4</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>306.45 - 310.0 RD SUPPLY</t>
+          <t>3652.7 - 3708.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>3051.8 - 3199.1 DR DEMAND</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -9281,12 +9281,12 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -9296,34 +9296,34 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>3.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Bank of Baroda</t>
+          <t>Radico Khaitan Ltd</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -9332,36 +9332,36 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>238.43</v>
+        <v>4554.1</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>238.13 - 238.51 RD SUPPLY</t>
+          <t>4601.9 - 4614.1 RD SUPPLY</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>178.57 - 184.54 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -9376,34 +9376,34 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>3.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>CARBORUNIV</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Indian Railway Finance Corporation Ltd.</t>
+          <t>Carborundum Universal Ltd.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -9412,36 +9412,36 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>79.62</v>
+        <v>1171</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>79.28 - 81.5 RD SUPPLY</t>
+          <t>990.84 - 995.43 DR DEMAND</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1181.58 - 1303.79 RD SUPPLY</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -9456,29 +9456,29 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>2.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Kajaria Ceramics Ltd.</t>
+          <t>FSN E-Commerce Ventures Ltd.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -9492,28 +9492,28 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1226.7</v>
+        <v>336.5</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>1175.7 - 1183.6 DR DEMAND</t>
+          <t>341.25 - 346.45 RD SUPPLY</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
+          <t>2.5 C</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>232.05 - 235.0 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
           <t>7.0 A</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>1181.73 - 1240.58 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>5.0 C</t>
-        </is>
-      </c>
       <c r="J114" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
@@ -9521,7 +9521,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -9536,17 +9536,17 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>2.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
@@ -9572,7 +9572,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>636.05</v>
+        <v>653.1</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -9633,17 +9633,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>TARIL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Varun Beverages Ltd.</t>
+          <t>Transformers and Rectifiers (India) Ltd.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -9652,41 +9652,41 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>442</v>
+        <v>349.5</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>439.3 - 443.3 RD SUPPLY</t>
+          <t>346.99 - 350.28 RD SUPPLY</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>396.2 - 400.45 DR DEMAND</t>
+          <t>223.85 - 235.94 DR DEMAND</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -9713,17 +9713,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BHARTIHEXA</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Bharti Hexacom Ltd.</t>
+          <t>Colgate Palmolive (India) Ltd.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -9732,36 +9732,36 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1548.7</v>
+        <v>1826.4</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>1546.1 - 1567.4 RD SUPPLY</t>
+          <t>1826.4 - 1868.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>1359.2 - 1404.0 DR DEMAND</t>
+          <t>2228.23 - 2274.78 RD SUPPLY</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -9776,7 +9776,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>3.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -9793,17 +9793,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BALRAMCHIN</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Ltd.</t>
+          <t>Indian Railway Finance Corporation Ltd.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -9812,36 +9812,36 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>720.2</v>
+        <v>79.75</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>695.95 - 738.95 RD SUPPLY</t>
+          <t>79.28 - 81.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>638.0 - 660.0 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2.5 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -9873,17 +9873,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CARBORUNIV</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Carborundum Universal Ltd.</t>
+          <t>Kajaria Ceramics Ltd.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -9892,26 +9892,26 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1184.7</v>
+        <v>1224.6</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>990.84 - 995.43 DR DEMAND</t>
+          <t>1175.7 - 1183.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>1181.58 - 1303.79 RD SUPPLY</t>
+          <t>1181.73 - 1240.58 RD SUPPLY</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -9936,7 +9936,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2.5 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -9953,78 +9953,558 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
+          <t>SUPREMEIND</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Supreme Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>3607</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>3567.7 - 3631.8 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>5.0 C</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>— NO ACTIVE ZONE —</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>🟡 1 TEST (TESTED)</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>🔥 1.8x HIGH VOL</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>5.0 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Punjab National Bank</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>PSUBANK</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>118.45 - 118.74 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>4.0 C</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>80.71 - 82.53 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>6.0 B</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>🟡 1 TEST (TESTED)</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>4.0 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Varun Beverages Ltd.</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>442.65</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>439.3 - 443.3 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>2.5 C</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>396.2 - 400.45 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>5.5 B</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>1W DOWN • 20 EMA BEARISH</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>🔴 4 TESTS (WEAK)</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>3.5 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>SAREGAMA</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Saregama India Ltd</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>CONSUMPTION</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>510.6</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>506.55 - 518.65 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>3.0 C</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>— NO ACTIVE ZONE —</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>🔴 2 TESTS (WEAK)</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>3.0 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd.</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>713.85</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>695.95 - 738.95 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>2.5 C</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>638.0 - 660.0 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>🔴 4 TESTS (WEAK)</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>2.5 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Kotak Mahindra Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>BANK</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>438.05</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>— NO ACTIVE ZONE —</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>431.46 - 447.25 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>2.5 C</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>🔴 2 TESTS (WEAK)</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>2.5 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
           <t>PHOENIXLTD</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>Phoenix Mills Ltd.</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>REALTY</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D126" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
       </c>
-      <c r="E120" t="n">
-        <v>1902.6</v>
-      </c>
-      <c r="F120" t="inlineStr">
+      <c r="E126" t="n">
+        <v>1887.3</v>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>1946.8 - 1954.9 RD SUPPLY</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="G126" t="inlineStr">
         <is>
           <t>8.0 A</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="H126" t="inlineStr">
         <is>
           <t>1851.05 - 1990.36 RD SUPPLY</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
+      <c r="I126" t="inlineStr">
         <is>
           <t>2.5 C</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr">
+      <c r="J126" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
+      <c r="K126" t="inlineStr">
         <is>
           <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>NORMAL VOL</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr">
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
         <is>
           <t>+0.0 PTS</t>
         </is>
       </c>
-      <c r="N120" t="inlineStr">
+      <c r="N126" t="inlineStr">
         <is>
           <t>2.5 / 10 SUPPLY</t>
         </is>
       </c>
-      <c r="O120" t="inlineStr">
+      <c r="O126" t="inlineStr">
         <is>
           <t>SUPPLY TEST</t>
         </is>
       </c>
-      <c r="P120" t="inlineStr">
+      <c r="P126" t="inlineStr">
         <is>
           <t>IN</t>
         </is>

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P126"/>
+  <dimension ref="A1:P133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>138.86</v>
+        <v>135.85</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -593,17 +593,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>IDBI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tube Investments of India Ltd.</t>
+          <t>IDBI Bank Ltd.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>PVTBANK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -612,26 +612,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2220.5</v>
+        <v>83.45</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2161.89 - 2177.97 DR DEMAND</t>
+          <t>81.32 - 81.87 DR DEMAND</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2161.89 - 2330.75 DR DEMAND</t>
+          <t>91.3 - 96.25 RD SUPPLY</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -673,17 +673,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JKCEMENT</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J.K. Cement Ltd.</t>
+          <t>Shriram Finance Ltd.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -692,26 +692,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4895.5</v>
+        <v>943.8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4810.5 - 4824.5 DR DEMAND</t>
+          <t>920.0 - 929.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4193.16 - 4362.57 DR DEMAND</t>
+          <t>559.9 - 573.24 DR DEMAND</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>10.5 / 10 HIGH COMBO</t>
+          <t>11.0 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -753,17 +753,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>JKCEMENT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Ltd.</t>
+          <t>J.K. Cement Ltd.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1662.9</v>
+        <v>4899</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1633.0 - 1645.0 DR DEMAND</t>
+          <t>4810.5 - 4824.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>4193.16 - 4362.57 DR DEMAND</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -833,17 +833,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Axis Bank Ltd.</t>
+          <t>Aegis Logistics Ltd.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -852,11 +852,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1264.6</v>
+        <v>1410.6</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1242.2 - 1247.0 DR DEMAND</t>
+          <t>1364.8 - 1392.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -866,12 +866,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1175.0 - 1219.1 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -913,17 +913,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Syrma SGS Technology Ltd.</t>
+          <t>Tube Investments of India Ltd.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -932,36 +932,36 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1692.2</v>
+        <v>2184.6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1657.6 - 1680.9 DR DEMAND</t>
+          <t>2161.89 - 2177.97 DR DEMAND</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1782.9 - 1822.6 RD SUPPLY</t>
+          <t>2161.89 - 2330.75 DR DEMAND</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>970.5</v>
+        <v>981.6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1385</v>
+        <v>1377.6</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>78.73999999999999</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1233,17 +1233,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Laurus Labs Ltd.</t>
+          <t>Computer Age Management Services Ltd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2036.9</v>
+        <v>704.85</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1988.9 - 1997.9 DR DEMAND</t>
+          <t>691.45 - 694.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>510.72 - 525.52 DR DEMAND</t>
+          <t>591.51 - 613.37 DR DEMAND</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1313,17 +1313,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>DATAPATTNS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>State Bank of India</t>
+          <t>Data Patterns (India) Ltd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>954.9</v>
+        <v>4038.9</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>937.5 - 940.0 DR DEMAND</t>
+          <t>3890.52 - 3981.32 DR DEMAND</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>933.9 - 964.4 DR DEMAND</t>
+          <t>1344.18 - 1430.33 DR DEMAND</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>GESHIP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Castrol India Ltd.</t>
+          <t>Great Eastern Shipping Co. Ltd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1412,26 +1412,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>196.96</v>
+        <v>1484.1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>193.15 - 193.5 DR DEMAND</t>
+          <t>1458.0 - 1462.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>144.37 - 156.26 DR DEMAND</t>
+          <t>762.54 - 775.16 DR DEMAND</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1473,17 +1473,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>INDGN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hindustan Copper Ltd.</t>
+          <t>Indegene Ltd.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1492,31 +1492,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>467.65</v>
+        <v>591.2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>450.0 - 462.15 DR DEMAND</t>
+          <t>567.55 - 579.9 DR DEMAND</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>444.02 - 451.79 DR DEMAND</t>
+          <t>412.19 - 432.7 DR DEMAND</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1553,17 +1553,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lodha Developers Ltd.</t>
+          <t>Kfin Technologies Ltd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1572,28 +1572,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1059.6</v>
+        <v>894</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1047.5 - 1050.0 DR DEMAND</t>
+          <t>875.0 - 879.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1329.97 - 1360.84 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>6.5 B</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>648.52 - 674.63 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>6.5 B</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1633,17 +1633,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Navin Fluorine International Ltd.</t>
+          <t>Laurus Labs Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1652,26 +1652,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>8457</v>
+        <v>2018.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>8310.0 - 8352.5 DR DEMAND</t>
+          <t>1988.9 - 1997.9 DR DEMAND</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4173.89 - 4245.43 DR DEMAND</t>
+          <t>510.72 - 525.52 DR DEMAND</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1713,17 +1713,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>APARINDS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tata Steel Ltd.</t>
+          <t>Apar Industries Ltd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1732,36 +1732,36 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>174.49</v>
+        <v>16914</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>171.66 - 172.24 DR DEMAND</t>
+          <t>16442.91 - 16754.83 DR DEMAND</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>156.83 - 164.57 DR DEMAND</t>
+          <t>13236.05 - 14298.36 DR DEMAND</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1793,17 +1793,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ESCORTS</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Escorts Kubota Ltd.</t>
+          <t>Castrol India Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1812,31 +1812,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2689.1</v>
+        <v>196.23</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2550.1 - 2667.3 DR DEMAND</t>
+          <t>193.15 - 193.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2679.78 - 2709.64 DR DEMAND</t>
+          <t>144.37 - 156.26 DR DEMAND</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1873,17 +1873,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HDBFS</t>
+          <t>CIEINDIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HDB Financial Services Ltd.</t>
+          <t>CIE Automotive India Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1892,26 +1892,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>583.75</v>
+        <v>376.6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>579.2 - 581.75 DR DEMAND</t>
+          <t>368.3 - 370.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>479.0 - 504.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1953,17 +1953,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Indraprastha Gas Ltd.</t>
+          <t>Lodha Developers Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1972,26 +1972,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>145.09</v>
+        <v>1061.8</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>137.77 - 140.53 DR DEMAND</t>
+          <t>1047.5 - 1050.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>140.28 - 144.12 DR DEMAND</t>
+          <t>648.52 - 674.63 DR DEMAND</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2033,17 +2033,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Larsen &amp; Toubro Ltd.</t>
+          <t>NHPC Ltd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2052,26 +2052,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3642</v>
+        <v>72.7</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>3607.0 - 3625.1 DR DEMAND</t>
+          <t>71.1 - 71.65 DR DEMAND</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3256.29 - 3470.21 DR DEMAND</t>
+          <t>67.83 - 70.98 DR DEMAND</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2113,17 +2113,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASAHIINDIA</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Asahi India Glass Ltd.</t>
+          <t>Syrma SGS Technology Ltd.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2132,26 +2132,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>930.4</v>
+        <v>1687.3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>925.1 - 929.29 DR DEMAND</t>
+          <t>1670.3 - 1685.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1782.9 - 1822.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2193,17 +2193,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Asian Paints Ltd.</t>
+          <t>Aurobindo Pharma Ltd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2212,11 +2212,11 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2344.7</v>
+        <v>1677.9</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2317.8 - 2331.0 DR DEMAND</t>
+          <t>1647.1 - 1653.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2226,17 +2226,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2083.96 - 2137.91 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2273,17 +2273,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>EIDPARRY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Oracle Financial Services Software Ltd.</t>
+          <t>E.I.D. Parry (India) Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2292,11 +2292,11 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>10420</v>
+        <v>701.95</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>10284.0 - 10360.0 DR DEMAND</t>
+          <t>688.7 - 690.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>639.0 - 660.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2353,17 +2353,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>POONAWALLA</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Poonawalla Fincorp Ltd.</t>
+          <t>Indraprastha Gas Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2372,26 +2372,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>437.25</v>
+        <v>145.14</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>427.1 - 433.4 DR DEMAND</t>
+          <t>137.77 - 140.53 DR DEMAND</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>370.05 - 382.85 DR DEMAND</t>
+          <t>140.28 - 144.12 DR DEMAND</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2433,17 +2433,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>J&amp;KBANK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Voltas Ltd.</t>
+          <t>Jammu &amp; Kashmir Bank Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2452,11 +2452,11 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1039.8</v>
+        <v>137.45</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1012.5 - 1020.0 DR DEMAND</t>
+          <t>135.02 - 135.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1440.67 - 1533.08 RD SUPPLY</t>
+          <t>108.0 - 110.01 DR DEMAND</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2513,17 +2513,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CHALET</t>
+          <t>M&amp;MFIN</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chalet Hotels Ltd.</t>
+          <t>Mahindra &amp; Mahindra Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2532,26 +2532,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>820.7</v>
+        <v>316.15</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>803.05 - 809.65 DR DEMAND</t>
+          <t>309.2 - 310.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>902.92 - 938.88 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2593,17 +2593,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>SJVN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ashok Leyland Ltd.</t>
+          <t>SJVN Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2612,26 +2612,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>145</v>
+        <v>55.39</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>143.5 - 144.25 DR DEMAND</t>
+          <t>54.26 - 54.56 DR DEMAND</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>207.56 - 211.81 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2673,12 +2673,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>TRIDENT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Avenue Supermarts Ltd.</t>
+          <t>Trident Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2692,26 +2692,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3415</v>
+        <v>22.09</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4432.2 - 4444.5 RD SUPPLY</t>
+          <t>21.8 - 21.84 DR DEMAND</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3340.0 - 3403.95 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2753,17 +2753,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>GRAPHITE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Eternal Ltd.</t>
+          <t>Graphite India Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2772,26 +2772,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>316</v>
+        <v>767.2</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>306.2 - 310.25 DR DEMAND</t>
+          <t>756.9 - 763.95 DR DEMAND</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>194.8 - 201.7 DR DEMAND</t>
+          <t>551.99 - 610.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2833,12 +2833,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lenskart Solutions Ltd.</t>
+          <t>InterGlobe Aviation Ltd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2852,36 +2852,36 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>656.95</v>
+        <v>4778.3</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>645.5 - 653.95 DR DEMAND</t>
+          <t>4701.5 - 4733.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>5901.5 - 5970.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2913,17 +2913,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PCBL</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PCBL Chemical Ltd.</t>
+          <t>Larsen &amp; Toubro Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2932,26 +2932,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>312.95</v>
+        <v>3632</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>308.15 - 309.8 DR DEMAND</t>
+          <t>3607.0 - 3625.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>223.38 - 238.62 DR DEMAND</t>
+          <t>3256.29 - 3470.21 DR DEMAND</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2993,17 +2993,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SOBHA</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sobha Ltd.</t>
+          <t>Asian Paints Ltd.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3012,26 +3012,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1205.1</v>
+        <v>2350</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1248.4 - 1251.0 RD SUPPLY</t>
+          <t>2317.8 - 2331.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1125.39 - 1182.55 DR DEMAND</t>
+          <t>2083.96 - 2137.91 DR DEMAND</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3073,17 +3073,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AU Small Finance Bank Ltd.</t>
+          <t>Cipla Ltd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3092,26 +3092,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>999.5</v>
+        <v>1328</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>974.2 - 987.0 DR DEMAND</t>
+          <t>1302.7 - 1311.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>830.84 - 841.88 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3153,12 +3153,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MEDANTA</t>
+          <t>PFIZER</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Global Health Ltd.</t>
+          <t>Pfizer Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3172,26 +3172,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1280</v>
+        <v>3810.8</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1270.9 - 1276.5 DR DEMAND</t>
+          <t>3731.0 - 3750.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1480.9 - 1544.0 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3233,17 +3233,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>POONAWALLA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Shree Cement Ltd.</t>
+          <t>Poonawalla Fincorp Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3252,26 +3252,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>22185</v>
+        <v>441.3</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>21550.0 - 21900.0 DR DEMAND</t>
+          <t>427.1 - 433.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>370.05 - 382.85 DR DEMAND</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3313,17 +3313,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Alkem Laboratories Ltd.</t>
+          <t>Sun Pharmaceutical Industries Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3332,26 +3332,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5201</v>
+        <v>1764</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>5110.0 - 5150.0 DR DEMAND</t>
+          <t>1725.5 - 1736.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1569.37 - 1580.86 DR DEMAND</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3393,17 +3393,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>COROMANDEL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Amber Enterprises India Ltd.</t>
+          <t>Coromandel International Ltd.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3412,26 +3412,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6645</v>
+        <v>1765.3</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>6151.0 - 6170.5 DR DEMAND</t>
+          <t>1963.9 - 1975.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6120.0 - 6549.0 DR DEMAND</t>
+          <t>1704.84 - 1751.89 DR DEMAND</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3473,12 +3473,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FIVESTAR</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Five-Star Business Finance Ltd.</t>
+          <t>CRISIL Ltd.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3492,21 +3492,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>512.3</v>
+        <v>4415.5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>498.25 - 506.25 DR DEMAND</t>
+          <t>4251.3 - 4337.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>412.05 - 443.54 DR DEMAND</t>
+          <t>3669.91 - 3717.29 DR DEMAND</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3553,17 +3553,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>ESCORTS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Indian Hotels Co. Ltd.</t>
+          <t>Escorts Kubota Ltd.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3572,36 +3572,36 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>725.4</v>
+        <v>2726.6</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>706.05 - 713.55 DR DEMAND</t>
+          <t>2550.1 - 2667.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>871.1 - 888.32 RD SUPPLY</t>
+          <t>2679.78 - 2709.64 DR DEMAND</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>🔴 5 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3633,12 +3633,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>HBLENGINE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mazagoan Dock Shipbuilders Ltd.</t>
+          <t>HBL Engineering Ltd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3652,26 +3652,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2124.4</v>
+        <v>710.45</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>692.0 - 704.65 DR DEMAND</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1900.61 - 2111.67 DR DEMAND</t>
+          <t>647.1 - 656.44 DR DEMAND</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3713,17 +3713,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PIRAMALFIN</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Piramal Finance Ltd.</t>
+          <t>GAIL (India) Ltd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3732,26 +3732,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1951.1</v>
+        <v>169.35</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1901.22 - 1939.2 DR DEMAND</t>
+          <t>166.44 - 167.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>133.97 - 137.31 DR DEMAND</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3793,17 +3793,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SAILIFE</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sai Life Sciences Ltd.</t>
+          <t>Indian Bank</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3812,31 +3812,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1432.1</v>
+        <v>835</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1415.0 - 1422.2 DR DEMAND</t>
+          <t>769.25 - 772.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>748.11 - 819.79 DR DEMAND</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3873,17 +3873,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>IOB</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tata Communications Ltd.</t>
+          <t>Indian Overseas Bank</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3892,11 +3892,11 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1658.9</v>
+        <v>30.74</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1640.2 - 1649.3 DR DEMAND</t>
+          <t>30.07 - 30.38 DR DEMAND</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1310.58 - 1335.75 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3926,17 +3926,17 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3953,17 +3953,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>SOBHA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vedanta Ltd.</t>
+          <t>Sobha Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3972,26 +3972,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>250</v>
+        <v>1190.8</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>244.83 - 248.11 DR DEMAND</t>
+          <t>1248.4 - 1251.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1125.39 - 1182.55 DR DEMAND</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4033,17 +4033,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>USHAMART</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Usha Martin Ltd.</t>
+          <t>AU Small Finance Bank Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4052,26 +4052,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>487</v>
+        <v>1002.7</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>477.8 - 481.3 DR DEMAND</t>
+          <t>974.2 - 987.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>274.28 - 291.22 DR DEMAND</t>
+          <t>830.84 - 841.88 DR DEMAND</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4113,17 +4113,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>UTIAMC</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>UTI Asset Management Company Ltd.</t>
+          <t>Navin Fluorine International Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4132,31 +4132,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>876.5</v>
+        <v>8247.5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1039.08 - 1043.74 RD SUPPLY</t>
+          <t>8110.0 - 8151.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>841.38 - 874.76 DR DEMAND</t>
+          <t>4173.89 - 4245.43 DR DEMAND</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4193,17 +4193,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AFFLE</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Affle 3i Ltd.</t>
+          <t>Shree Cement Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4212,26 +4212,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1434.1</v>
+        <v>22315</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1389.9 - 1406.7 DR DEMAND</t>
+          <t>21550.0 - 21900.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1251.3 - 1335.3 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>4.0 / 10 SOLID</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4273,17 +4273,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ASTERDM</t>
+          <t>BELRISE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Aster DM Healthcare Ltd.</t>
+          <t>Belrise Industries Ltd.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4292,11 +4292,11 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>675.2</v>
+        <v>229.9</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>671.0 - 674.35 DR DEMAND</t>
+          <t>225.27 - 226.36 DR DEMAND</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>516.84 - 549.74 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>4.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4353,17 +4353,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BLUEJET</t>
+          <t>FIVESTAR</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Blue Jet Healthcare Ltd.</t>
+          <t>Five-Star Business Finance Ltd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4372,21 +4372,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>522.45</v>
+        <v>513.25</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>507.79 - 514.92 DR DEMAND</t>
+          <t>498.25 - 506.25 DR DEMAND</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>631.68 - 646.45 RD SUPPLY</t>
+          <t>412.05 - 443.54 DR DEMAND</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>3.5 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4433,17 +4433,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>PIRAMALFIN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Jindal Steel Ltd.</t>
+          <t>Piramal Finance Ltd.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4452,26 +4452,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1029.2</v>
+        <v>1974.7</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1000.91 - 1008.99 DR DEMAND</t>
+          <t>1901.22 - 1939.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1008.29 - 1043.63 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4496,34 +4496,34 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bharat Electronics Ltd.</t>
+          <t>KEI Industries Ltd.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4532,26 +4532,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>382.35</v>
+        <v>4571.2</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>397.4 - 399.2 RD SUPPLY</t>
+          <t>4495.0 - 4557.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>378.32 - 397.37 DR DEMAND</t>
+          <t>3937.0 - 4038.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4576,34 +4576,34 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>USHAMART</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>InterGlobe Aviation Ltd.</t>
+          <t>Usha Martin Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4612,26 +4612,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4718.5</v>
+        <v>482.9</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>4701.5 - 4733.5 DR DEMAND</t>
+          <t>477.8 - 481.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>5901.5 - 5970.0 RD SUPPLY</t>
+          <t>274.28 - 291.22 DR DEMAND</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4651,39 +4651,39 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>AFFLE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CG Power and Industrial Solutions Ltd.</t>
+          <t>Affle 3i Ltd.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4692,26 +4692,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>863</v>
+        <v>1428.5</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>794.1 - 800.0 DR DEMAND</t>
+          <t>1389.9 - 1406.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>814.85 - 863.4 DR DEMAND</t>
+          <t>1251.3 - 1335.3 DR DEMAND</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 4 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4731,39 +4731,39 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>4.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>BLUEJET</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SBI Cards and Payment Services Ltd.</t>
+          <t>Blue Jet Healthcare Ltd.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4772,26 +4772,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>568</v>
+        <v>519.45</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>698.4 - 700.4 RD SUPPLY</t>
+          <t>507.79 - 514.92 DR DEMAND</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>565.45 - 593.2 DR DEMAND</t>
+          <t>631.68 - 646.45 RD SUPPLY</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4811,39 +4811,39 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>3.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ANTHEM</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Anthem Biosciences Ltd.</t>
+          <t>Hindustan Copper Ltd.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4852,31 +4852,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>847.75</v>
+        <v>453.05</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>842.2 - 862.3 DR DEMAND</t>
+          <t>450.0 - 462.15 DR DEMAND</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>444.02 - 451.79 DR DEMAND</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4913,17 +4913,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>COROMANDEL</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Coromandel International Ltd.</t>
+          <t>Jindal Steel Ltd.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4932,26 +4932,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1747</v>
+        <v>1030</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1963.9 - 1975.0 RD SUPPLY</t>
+          <t>1000.91 - 1008.99 DR DEMAND</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1704.84 - 1751.89 DR DEMAND</t>
+          <t>1008.29 - 1043.63 DR DEMAND</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4961,12 +4961,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4993,17 +4993,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ICICI Bank Ltd.</t>
+          <t>Bharat Electronics Ltd.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5012,26 +5012,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1338.6</v>
+        <v>380.4</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1329.4 - 1339.0 DR DEMAND</t>
+          <t>397.4 - 399.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1457.77 - 1476.07 RD SUPPLY</t>
+          <t>378.32 - 397.37 DR DEMAND</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5073,17 +5073,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GAIL (India) Ltd.</t>
+          <t>Varun Beverages Ltd.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5092,26 +5092,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>166.96</v>
+        <v>429.25</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>166.44 - 167.5 DR DEMAND</t>
+          <t>428.95 - 430.55 DR DEMAND</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>133.97 - 137.31 DR DEMAND</t>
+          <t>396.2 - 400.45 DR DEMAND</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5153,12 +5153,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>RAMCOCEM</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Ramco Cements Ltd.</t>
+          <t>Welspun Corp Ltd.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5172,31 +5172,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>804.15</v>
+        <v>2486.9</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>951.15 - 986.61 RD SUPPLY</t>
+          <t>2450.0 - 2497.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>784.7 - 825.32 DR DEMAND</t>
+          <t>658.55 - 760.86 DR DEMAND</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5233,17 +5233,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TECHNOE</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Techno Electric &amp; Engineering Company Ltd.</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5252,26 +5252,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>949.8</v>
+        <v>960</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1006.2 - 1016.2 RD SUPPLY</t>
+          <t>937.5 - 940.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>863.77 - 967.52 DR DEMAND</t>
+          <t>933.9 - 964.4 DR DEMAND</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5313,17 +5313,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PPLPHARMA</t>
+          <t>ASAHIINDIA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Piramal Pharma Ltd.</t>
+          <t>Asahi India Glass Ltd.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5332,11 +5332,11 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>193.94</v>
+        <v>925.9</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>193.75 - 194.89 DR DEMAND</t>
+          <t>925.1 - 929.29 DR DEMAND</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5346,17 +5346,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>132.3 - 136.54 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5393,17 +5393,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Torrent Power Ltd.</t>
+          <t>CG Power and Industrial Solutions Ltd.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5412,26 +5412,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1240.3</v>
+        <v>818</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1165.0 - 1174.4 DR DEMAND</t>
+          <t>794.1 - 800.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1186.52 - 1241.27 DR DEMAND</t>
+          <t>814.85 - 863.4 DR DEMAND</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5473,17 +5473,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Glaxosmithkline Pharmaceuticals Ltd.</t>
+          <t>SBI Cards and Payment Services Ltd.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5492,26 +5492,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2538.9</v>
+        <v>573.2</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2515.0 - 2546.9 DR DEMAND</t>
+          <t>698.4 - 700.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1849.2 - 1903.26 DR DEMAND</t>
+          <t>565.45 - 593.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5531,12 +5531,12 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>3.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5553,45 +5553,45 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>SAMMAANCAP</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tata Elxsi Ltd.</t>
+          <t>Sammaan Capital Ltd.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3623.1</v>
+        <v>136.98</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>3685.0 - 3708.0 RD SUPPLY</t>
+          <t>125.66 - 126.44 DR DEMAND</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2996.0 - 3088.9 DR DEMAND</t>
+          <t>134.75 - 144.61 DR DEMAND</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5611,77 +5611,77 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Adani Green Energy Ltd.</t>
+          <t>Avenue Supermarts Ltd.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1318.4</v>
+        <v>3378.4</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1342.7 - 1377.8 RD SUPPLY</t>
+          <t>4432.2 - 4444.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>765.0 - 814.2 DR DEMAND</t>
+          <t>3340.0 - 3403.95 DR DEMAND</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5691,67 +5691,67 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>9.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>JSWCEMENT</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JSW Cement Ltd.</t>
+          <t>PCBL Chemical Ltd.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>114.7</v>
+        <v>308.9</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>115.77 - 116.4 RD SUPPLY</t>
+          <t>308.15 - 309.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>223.38 - 238.62 DR DEMAND</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5771,77 +5771,77 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>9.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>PPLPHARMA</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ABB India Ltd.</t>
+          <t>Piramal Pharma Ltd.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6999</v>
+        <v>194.43</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>7122.5 - 7140.5 RD SUPPLY</t>
+          <t>193.75 - 194.89 DR DEMAND</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>7638.5 - 7825.0 RD SUPPLY</t>
+          <t>132.3 - 136.54 DR DEMAND</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5851,67 +5851,67 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MINDACORP</t>
+          <t>RAMCOCEM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Minda Corporation Ltd.</t>
+          <t>The Ramco Cements Ltd.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>657.15</v>
+        <v>786.9</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>659.6 - 661.5 RD SUPPLY</t>
+          <t>951.15 - 986.61 RD SUPPLY</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>451.85 - 473.12 DR DEMAND</t>
+          <t>784.7 - 825.32 DR DEMAND</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5931,67 +5931,67 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>TECHNOE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NLC India Ltd.</t>
+          <t>Techno Electric &amp; Engineering Company Ltd.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>257.65</v>
+        <v>945.2</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>261.7 - 263.5 RD SUPPLY</t>
+          <t>1006.2 - 1016.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>217.4 - 220.48 DR DEMAND</t>
+          <t>863.77 - 967.52 DR DEMAND</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6011,57 +6011,57 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>LALPATHLAB</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NMDC Ltd.</t>
+          <t>Dr. Lal Path Labs Ltd.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>71.08</v>
+        <v>1885.1</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>71.99 - 72.33 RD SUPPLY</t>
+          <t>1870.0 - 1890.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6076,12 +6076,12 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 4 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -6091,67 +6091,67 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>MEDANTA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Pidilite Industries Ltd.</t>
+          <t>Global Health Ltd.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1499.5</v>
+        <v>1275.5</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1520.5 - 1524.6 RD SUPPLY</t>
+          <t>1270.9 - 1276.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1687.7 - 1707.5 RD SUPPLY</t>
+          <t>1480.9 - 1544.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -6171,67 +6171,67 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>360 ONE WAM Ltd.</t>
+          <t>Mazagoan Dock Shipbuilders Ltd.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1063</v>
+        <v>2105</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1077.5 - 1080.9 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1185.06 - 1260.04 RD SUPPLY</t>
+          <t>1900.61 - 2111.67 DR DEMAND</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -6251,67 +6251,67 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Aditya Birla Capital Ltd.</t>
+          <t>Torrent Power Ltd.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>378.9</v>
+        <v>1238.6</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>385.6 - 386.5 RD SUPPLY</t>
+          <t>1165.0 - 1174.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>287.7 - 292.25 DR DEMAND</t>
+          <t>1186.52 - 1241.27 DR DEMAND</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6331,67 +6331,67 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Bajaj Finserv Ltd.</t>
+          <t>Vedanta Ltd.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1721.7</v>
+        <v>245.9</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1755.7 - 1758.0 RD SUPPLY</t>
+          <t>244.83 - 248.11 DR DEMAND</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1991.7 - 2073.13 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6411,34 +6411,34 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BAJAJHFL</t>
+          <t>UTIAMC</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Bajaj Housing Finance Ltd.</t>
+          <t>UTI Asset Management Company Ltd.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6448,30 +6448,30 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>84.55</v>
+        <v>874.35</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>85.58 - 86.45 RD SUPPLY</t>
+          <t>1039.08 - 1043.74 RD SUPPLY</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>841.38 - 874.76 DR DEMAND</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -6491,67 +6491,67 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Grasim Industries Ltd.</t>
+          <t>Alkem Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2873</v>
+        <v>5120.5</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2899.4 - 2919.5 RD SUPPLY</t>
+          <t>5110.0 - 5150.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2494.13 - 2528.7 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6571,69 +6571,69 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>4.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>INDIACEM</t>
+          <t>GLAXO</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>India Cements Ltd.</t>
+          <t>Glaxosmithkline Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>295.65</v>
+        <v>2524.7</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>300.65 - 302.15 RD SUPPLY</t>
+          <t>2515.0 - 2546.9 DR DEMAND</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
+          <t>2.5 C</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>1849.2 - 1903.26 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
           <t>7.0 A</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>400.0 - 416.4 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>6.5 B</t>
-        </is>
-      </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6651,34 +6651,34 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>3.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>IndusInd Bank Ltd.</t>
+          <t>HDFC Bank Ltd.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6692,26 +6692,26 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>866</v>
+        <v>726.85</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>877.6 - 883.05 RD SUPPLY</t>
+          <t>731.95 - 734.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>605.02 - 647.95 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -6753,17 +6753,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>RAINBOW</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Rainbow Childrens Medicare Ltd.</t>
+          <t>ITC Ltd.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -6772,28 +6772,28 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1246.7</v>
+        <v>263.9</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1270.7 - 1288.7 RD SUPPLY</t>
+          <t>267.2 - 268.05 RD SUPPLY</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
+          <t>8.5 A</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>400.8 - 406.57 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
           <t>7.0 A</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>1550.0 - 1610.0 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>6.0 B</t>
-        </is>
-      </c>
       <c r="J80" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -6833,17 +6833,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Steel Authority of India Ltd.</t>
+          <t>Phoenix Mills Ltd.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -6852,31 +6852,31 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>170</v>
+        <v>1917.2</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>172.77 - 174.0 RD SUPPLY</t>
+          <t>1946.8 - 1954.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>202.55 - 206.99 RD SUPPLY</t>
+          <t>1851.05 - 1990.36 RD SUPPLY</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -6913,12 +6913,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Computer Age Management Services Ltd.</t>
+          <t>Bajaj Finance Ltd.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6932,26 +6932,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>694</v>
+        <v>965.25</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>701.0 - 704.45 RD SUPPLY</t>
+          <t>982.75 - 986.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>591.51 - 613.37 DR DEMAND</t>
+          <t>783.09 - 796.65 DR DEMAND</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -6993,12 +6993,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Capri Global Capital Ltd.</t>
+          <t>HDFC Asset Management Company Ltd.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -7012,11 +7012,11 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>247.91</v>
+        <v>2415</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>250.74 - 252.0 RD SUPPLY</t>
+          <t>2448.3 - 2454.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -7026,17 +7026,17 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>2223.3 - 2280.7 DR DEMAND</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -7073,17 +7073,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ABFRL</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Aditya Birla Fashion and Retail Ltd.</t>
+          <t>Hindustan Petroleum Corporation Ltd.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7092,26 +7092,26 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>45.28</v>
+        <v>348.5</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>45.68 - 47.39 RD SUPPLY</t>
+          <t>351.0 - 351.75 RD SUPPLY</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>263.73 - 269.42 DR DEMAND</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7153,17 +7153,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CENTRALBK</t>
+          <t>JAINREC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Central Bank of India</t>
+          <t>Jain Resource Recycling Ltd.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7172,26 +7172,26 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>31.18</v>
+        <v>292.8</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>31.63 - 31.8 RD SUPPLY</t>
+          <t>295.15 - 300.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>35.83 - 36.93 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -7233,17 +7233,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Indegene Ltd.</t>
+          <t>NMDC Ltd.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7252,31 +7252,31 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>596.9</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>607.1 - 612.0 RD SUPPLY</t>
+          <t>71.99 - 72.33 RD SUPPLY</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>412.19 - 432.7 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -7313,17 +7313,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>KEI Industries Ltd.</t>
+          <t>Pidilite Industries Ltd.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7332,26 +7332,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4648</v>
+        <v>1505</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>4722.5 - 4760.0 RD SUPPLY</t>
+          <t>1520.5 - 1524.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>3937.0 - 4038.0 DR DEMAND</t>
+          <t>1687.7 - 1707.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -7393,17 +7393,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>LALPATHLAB</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Dr. Lal Path Labs Ltd.</t>
+          <t>Reliance Industries Ltd.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7412,16 +7412,16 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1938</v>
+        <v>1215</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1969.7 - 2002.5 RD SUPPLY</t>
+          <t>1226.0 - 1227.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -7473,17 +7473,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>UCOBANK</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>UCO Bank</t>
+          <t>Abbott India Ltd.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -7492,26 +7492,26 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>23.96</v>
+        <v>26070</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>24.12 - 24.17 RD SUPPLY</t>
+          <t>26295.0 - 26550.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>32.81 - 33.64 RD SUPPLY</t>
+          <t>24406.02 - 25223.54 DR DEMAND</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -7553,17 +7553,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ANURAS</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Anupam Rasayan India Ltd.</t>
+          <t>Aditya Birla Capital Ltd.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -7572,26 +7572,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1187</v>
+        <v>382.25</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1207.7 - 1219.0 RD SUPPLY</t>
+          <t>385.6 - 386.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>599.85 - 631.19 DR DEMAND</t>
+          <t>287.7 - 292.25 DR DEMAND</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -7633,17 +7633,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>GESHIP</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Great Eastern Shipping Co. Ltd.</t>
+          <t>Bajaj Finserv Ltd.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -7652,31 +7652,31 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1543.1</v>
+        <v>1732</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1567.9 - 1577.0 RD SUPPLY</t>
+          <t>1755.7 - 1758.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>762.54 - 775.16 DR DEMAND</t>
+          <t>1991.7 - 2073.13 RD SUPPLY</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -7713,17 +7713,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>DOMS</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Bank of Maharashtra</t>
+          <t>DOMS Industries Ltd.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -7732,31 +7732,31 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>83.09999999999999</v>
+        <v>2124.8</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>84.15 - 84.5 RD SUPPLY</t>
+          <t>2141.5 - 2147.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>91.75 - 94.5 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -7793,17 +7793,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AARTIIND</t>
+          <t>INDIACEM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Aarti Industries Ltd.</t>
+          <t>India Cements Ltd.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -7812,36 +7812,36 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>497.9</v>
+        <v>297.4</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>502.7 - 503.75 RD SUPPLY</t>
+          <t>300.65 - 302.15 RD SUPPLY</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>525.95 - 550.66 RD SUPPLY</t>
+          <t>400.0 - 416.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -7873,17 +7873,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Angel One Ltd.</t>
+          <t>NATCO Pharma Ltd.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -7892,16 +7892,16 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>306.05</v>
+        <v>784.95</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>306.45 - 310.0 RD SUPPLY</t>
+          <t>800.55 - 804.75 RD SUPPLY</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -7953,17 +7953,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DCMSHRIRAM</t>
+          <t>RAINBOW</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DCM Shriram Ltd.</t>
+          <t>Rainbow Childrens Medicare Ltd.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -7972,31 +7972,31 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1033.3</v>
+        <v>1246.6</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1044.55 - 1088.2 RD SUPPLY</t>
+          <t>1270.7 - 1288.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>1550.0 - 1610.0 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>1227.63 - 1319.98 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>7.0 A</t>
-        </is>
-      </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -8033,17 +8033,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FINCABLES</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Finolex Cables Ltd.</t>
+          <t>Steel Authority of India Ltd.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8052,31 +8052,31 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1446.3</v>
+        <v>170.29</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1474.5 - 1480.0 RD SUPPLY</t>
+          <t>172.77 - 174.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>949.44 - 980.62 DR DEMAND</t>
+          <t>202.55 - 206.99 RD SUPPLY</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -8113,17 +8113,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FLUOROCHEM</t>
+          <t>VTL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Gujarat Fluorochemicals Ltd.</t>
+          <t>Vardhman Textiles Ltd.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8132,31 +8132,31 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4632.1</v>
+        <v>539</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>3338.79 - 3344.99 DR DEMAND</t>
+          <t>549.4 - 557.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>4706.78 - 4955.62 RD SUPPLY</t>
+          <t>614.54 - 641.56 RD SUPPLY</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -8193,17 +8193,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>HDFC Bank Ltd.</t>
+          <t>Capri Global Capital Ltd.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8212,16 +8212,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>710.7</v>
+        <v>247.15</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>711.45 - 714.7 RD SUPPLY</t>
+          <t>250.74 - 252.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -8236,12 +8236,12 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -8273,17 +8273,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>LEMONTREE</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Lemon Tree Hotels Ltd.</t>
+          <t>HDFC Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -8292,31 +8292,31 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>111.46</v>
+        <v>550.55</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>112.71 - 113.55 RD SUPPLY</t>
+          <t>561.0 - 561.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>811.41 - 817.84 RD SUPPLY</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -8353,17 +8353,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>HONAUT</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Nestle India Ltd.</t>
+          <t>Honeywell Automation India Ltd.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8372,26 +8372,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1383.2</v>
+        <v>32380</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1384.5 - 1397.0 RD SUPPLY</t>
+          <t>32925.0 - 33020.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1292.9 - 1301.9 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -8401,12 +8401,12 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -8433,17 +8433,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>OLAELEC</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>REC Ltd.</t>
+          <t>Ola Electric Mobility Ltd.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -8452,16 +8452,16 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>311.8</v>
+        <v>35.17</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>314.0 - 315.5 RD SUPPLY</t>
+          <t>35.88 - 36.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -8513,17 +8513,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>ABFRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>DLF Ltd.</t>
+          <t>Aditya Birla Fashion and Retail Ltd.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -8532,36 +8532,36 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>666.9</v>
+        <v>44.86</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>673.0 - 676.5 RD SUPPLY</t>
+          <t>45.68 - 47.39 RD SUPPLY</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>483.33 - 497.85 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -8593,12 +8593,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>AWL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LT Foods Ltd.</t>
+          <t>AWL Agri Business Ltd.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -8612,28 +8612,28 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>418.05</v>
+        <v>190.54</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>418.4 - 421.9 RD SUPPLY</t>
+          <t>194.38 - 195.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>172.6 - 176.61 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
           <t>5.5 B</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>285.59 - 341.86 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>5.5 B</t>
-        </is>
-      </c>
       <c r="J103" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -8673,17 +8673,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ZENTEC</t>
+          <t>ZENSARTECH</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Zen Technologies Ltd.</t>
+          <t>Zensar Technolgies Ltd.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -8692,11 +8692,11 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1649.3</v>
+        <v>504.45</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>1682.4 - 1695.0 RD SUPPLY</t>
+          <t>416.15 - 422.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -8706,22 +8706,22 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>943.53 - 1043.28 DR DEMAND</t>
+          <t>510.15 - 553.1 RD SUPPLY</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -8753,17 +8753,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AWL</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>AWL Agri Business Ltd.</t>
+          <t>Adani Green Energy Ltd.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -8772,28 +8772,28 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>188.21</v>
+        <v>1307.1</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>188.49 - 189.33 RD SUPPLY</t>
+          <t>1330.6 - 1346.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
+          <t>5.5 B</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>765.0 - 814.2 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
           <t>4.0 C</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>172.6 - 176.61 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>5.5 B</t>
-        </is>
-      </c>
       <c r="J105" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -8833,17 +8833,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>IDBI</t>
+          <t>ASTERDM</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>IDBI Bank Ltd.</t>
+          <t>Aster DM Healthcare Ltd.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PVTBANK</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -8852,31 +8852,31 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>90.39</v>
+        <v>682.65</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>81.32 - 81.87 DR DEMAND</t>
+          <t>689.85 - 706.3 RD SUPPLY</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>91.3 - 96.25 RD SUPPLY</t>
+          <t>516.84 - 549.74 DR DEMAND</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>4.5 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -8913,12 +8913,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>THELEELA</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Kalyan Jewellers India Ltd.</t>
+          <t>Leela Palaces Hotels &amp; Resorts Ltd.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -8932,26 +8932,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>564</v>
+        <v>596.5</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>571.8 - 581.2 RD SUPPLY</t>
+          <t>604.45 - 607.25 RD SUPPLY</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>760.91 - 789.86 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>4.5 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -8993,12 +8993,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>CHALET</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Trent Ltd.</t>
+          <t>Chalet Hotels Ltd.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -9012,26 +9012,26 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2971</v>
+        <v>842.6</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2989.9 - 3020.6 RD SUPPLY</t>
+          <t>848.0 - 851.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2545.8 - 2615.0 DR DEMAND</t>
+          <t>902.92 - 938.88 RD SUPPLY</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>4.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -9073,17 +9073,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Clean Science and Technology Ltd.</t>
+          <t>Grasim Industries Ltd.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9092,36 +9092,36 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>818.6</v>
+        <v>2885.9</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>824.8 - 830.8 RD SUPPLY</t>
+          <t>2899.4 - 2919.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>1538.62 - 1583.15 RD SUPPLY</t>
+          <t>2494.13 - 2528.7 DR DEMAND</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>3.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -9153,17 +9153,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FORCEMOT</t>
+          <t>LEMONTREE</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Force Motors Ltd.</t>
+          <t>Lemon Tree Hotels Ltd.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9172,41 +9172,41 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>17270</v>
+        <v>112.5</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>17388.0 - 17430.0 RD SUPPLY</t>
+          <t>112.71 - 113.55 RD SUPPLY</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>24271.95 - 26374.97 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>3.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -9233,17 +9233,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>LTTS</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>REC Ltd.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9252,41 +9252,41 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3613.4</v>
+        <v>309.75</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>3652.7 - 3708.0 RD SUPPLY</t>
+          <t>314.0 - 315.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>3051.8 - 3199.1 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>3.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -9313,17 +9313,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>SCI</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Radico Khaitan Ltd</t>
+          <t>Shipping Corporation of India Ltd.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -9332,16 +9332,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4554.1</v>
+        <v>284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>4601.9 - 4614.1 RD SUPPLY</t>
+          <t>289.0 - 292.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>3.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -9393,17 +9393,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CARBORUNIV</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Carborundum Universal Ltd.</t>
+          <t>Indian Railway Finance Corporation Ltd.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -9412,36 +9412,36 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1171</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>990.84 - 995.43 DR DEMAND</t>
+          <t>79.28 - 81.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>1181.58 - 1303.79 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2.5 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -9473,17 +9473,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>UCOBANK</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>FSN E-Commerce Ventures Ltd.</t>
+          <t>UCO Bank</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -9492,41 +9492,41 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>336.5</v>
+        <v>23.56</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>341.25 - 346.45 RD SUPPLY</t>
+          <t>24.04 - 24.12 RD SUPPLY</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>232.05 - 235.0 DR DEMAND</t>
+          <t>32.81 - 33.64 RD SUPPLY</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2.5 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -9553,17 +9553,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Sun TV Network Ltd.</t>
+          <t>360 ONE WAM Ltd.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -9572,36 +9572,36 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>653.1</v>
+        <v>1073</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>608.6 - 613.0 DR DEMAND</t>
+          <t>1077.5 - 1080.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>603.75 - 653.93 RD SUPPLY</t>
+          <t>1185.06 - 1260.04 RD SUPPLY</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -9616,29 +9616,29 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>TARIL</t>
+          <t>RITES</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Transformers and Rectifiers (India) Ltd.</t>
+          <t>RITES Ltd.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -9652,26 +9652,26 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>349.5</v>
+        <v>214.27</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>346.99 - 350.28 RD SUPPLY</t>
+          <t>191.25 - 192.31 DR DEMAND</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>223.85 - 235.94 DR DEMAND</t>
+          <t>214.72 - 226.44 RD SUPPLY</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -9696,34 +9696,34 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Colgate Palmolive (India) Ltd.</t>
+          <t>Trent Ltd.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -9732,31 +9732,31 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1826.4</v>
+        <v>2949.7</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>1826.4 - 1868.9 RD SUPPLY</t>
+          <t>2989.9 - 3020.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2228.23 - 2274.78 RD SUPPLY</t>
+          <t>2545.8 - 2615.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -9776,34 +9776,34 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Indian Railway Finance Corporation Ltd.</t>
+          <t>DLF Ltd.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -9812,31 +9812,31 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>79.75</v>
+        <v>670.5</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>79.28 - 81.5 RD SUPPLY</t>
+          <t>673.0 - 676.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>483.33 - 497.85 DR DEMAND</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -9856,29 +9856,29 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Kajaria Ceramics Ltd.</t>
+          <t>Indian Hotels Co. Ltd.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -9892,26 +9892,26 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1224.6</v>
+        <v>741.45</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>1175.7 - 1183.6 DR DEMAND</t>
+          <t>751.2 - 757.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>1181.73 - 1240.58 RD SUPPLY</t>
+          <t>871.1 - 888.32 RD SUPPLY</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 4 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -9936,34 +9936,34 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>3.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>COHANCE</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Supreme Industries Ltd.</t>
+          <t>Cohance Lifesciences Ltd.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -9972,26 +9972,26 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3607</v>
+        <v>459.95</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>3567.7 - 3631.8 RD SUPPLY</t>
+          <t>462.35 - 467.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1229.95 - 1328.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -10016,34 +10016,34 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>2.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Punjab National Bank</t>
+          <t>FSN E-Commerce Ventures Ltd.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -10052,26 +10052,26 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>118.5</v>
+        <v>338.4</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>118.45 - 118.74 RD SUPPLY</t>
+          <t>341.25 - 346.45 RD SUPPLY</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>80.71 - 82.53 DR DEMAND</t>
+          <t>232.05 - 235.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -10081,7 +10081,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -10096,34 +10096,34 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>2.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Varun Beverages Ltd.</t>
+          <t>Tata Elxsi Ltd.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -10132,41 +10132,41 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>442.65</v>
+        <v>3700</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>439.3 - 443.3 RD SUPPLY</t>
+          <t>3685.0 - 3708.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>396.2 - 400.45 DR DEMAND</t>
+          <t>2996.0 - 3088.9 DR DEMAND</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>3.5 / 10 SUPPLY</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -10193,17 +10193,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>APOLLOTYRE</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Saregama India Ltd</t>
+          <t>Apollo Tyres Ltd.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10212,16 +10212,16 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>510.6</v>
+        <v>413.9</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>506.55 - 518.65 RD SUPPLY</t>
+          <t>412.9 - 429.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -10236,17 +10236,17 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>3.0 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -10273,17 +10273,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BALRAMCHIN</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Ltd.</t>
+          <t>Sun TV Network Ltd.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -10292,26 +10292,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>713.85</v>
+        <v>629.15</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>695.95 - 738.95 RD SUPPLY</t>
+          <t>608.6 - 613.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>638.0 - 660.0 DR DEMAND</t>
+          <t>603.75 - 653.93 RD SUPPLY</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2.5 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -10353,17 +10353,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank Ltd.</t>
+          <t>Narayana Hrudayalaya Ltd.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -10372,36 +10372,36 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>438.05</v>
+        <v>1725.4</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1724.4 - 1746.3 RD SUPPLY</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>431.46 - 447.25 RD SUPPLY</t>
+          <t>2170.07 - 2359.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2.5 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -10433,17 +10433,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Phoenix Mills Ltd.</t>
+          <t>Kajaria Ceramics Ltd.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -10452,59 +10452,619 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1887.3</v>
+        <v>1215</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>1946.8 - 1954.9 RD SUPPLY</t>
+          <t>1175.7 - 1183.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>1851.05 - 1990.36 RD SUPPLY</t>
+          <t>1181.73 - 1240.58 RD SUPPLY</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
+          <t>5.0 C</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>🟡 1 TEST (TESTED)</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>5.0 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>SUPREMEIND</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Supreme Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>3616</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>3567.7 - 3631.8 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>5.0 C</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>— NO ACTIVE ZONE —</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>🟡 1 TEST (TESTED)</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>5.0 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>BSE Ltd.</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>FINSERVICE</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>3428</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>3417.0 - 3452.7 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>4.5 C</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>3000.0 - 3089.9 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>7.5 A</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>🟡 1 TEST (TESTED)</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>4.5 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ZENTEC</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Zen Technologies Ltd.</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>1695</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>1682.4 - 1695.0 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>4.5 C</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>943.53 - 1043.28 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>6.0 B</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>🟡 1 TEST (TESTED)</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>4.5 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>AARTIIND</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Aarti Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>505.05</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>503.05 - 510.93 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>3.0 C</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>459.3 - 475.7 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>6.5 B</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>🔴 2 TESTS (WEAK)</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>3.0 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>LTFOODS</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>LT Foods Ltd.</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>419.6</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>418.4 - 421.9 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>3.0 C</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>285.59 - 341.87 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>5.5 B</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>🔴 2 TESTS (WEAK)</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>3.0 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>LTTS</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>L&amp;T Technology Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>3686.8</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>3652.7 - 3708.0 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>3.0 C</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>3051.8 - 3199.1 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>6.5 B</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>🔴 3 TESTS (WEAK)</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>🔥 2.5x VOL EXPLOSION</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>3.0 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd.</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>726</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>695.95 - 738.95 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
           <t>2.5 C</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr">
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>638.0 - 660.0 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>🔴 3 TESTS (WEAK)</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>NORMAL VOL</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr">
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>🔴 4 TESTS (WEAK)</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t>+0.0 PTS</t>
         </is>
       </c>
-      <c r="N126" t="inlineStr">
+      <c r="N133" t="inlineStr">
         <is>
           <t>2.5 / 10 SUPPLY</t>
         </is>
       </c>
-      <c r="O126" t="inlineStr">
+      <c r="O133" t="inlineStr">
         <is>
           <t>SUPPLY TEST</t>
         </is>
       </c>
-      <c r="P126" t="inlineStr">
+      <c r="P133" t="inlineStr">
         <is>
           <t>IN</t>
         </is>

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P133"/>
+  <dimension ref="A1:P134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,17 +513,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CESC Ltd.</t>
+          <t>Aegis Logistics Ltd.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -532,31 +532,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>135.85</v>
+        <v>1366.7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>128.31 - 128.73 DR DEMAND</t>
+          <t>1364.8 - 1392.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>133.19 - 139.44 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -593,17 +593,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IDBI</t>
+          <t>CHOLAHLDNG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IDBI Bank Ltd.</t>
+          <t>Cholamandalam Financial Holdings Ltd.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PVTBANK</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -612,26 +612,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>83.45</v>
+        <v>1360</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>81.32 - 81.87 DR DEMAND</t>
+          <t>1341.0 - 1361.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>91.3 - 96.25 RD SUPPLY</t>
+          <t>1358.29 - 1396.78 DR DEMAND</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -641,12 +641,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -656,34 +656,34 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>11.0 / 10 SUPER COMBO</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>BUY READY</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Shriram Finance Ltd.</t>
+          <t>CESC Ltd.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -692,26 +692,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>943.8</v>
+        <v>135.9</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>920.0 - 929.0 DR DEMAND</t>
+          <t>128.31 - 128.73 DR DEMAND</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>559.9 - 573.24 DR DEMAND</t>
+          <t>133.19 - 139.44 DR DEMAND</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -736,34 +736,34 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>11.0 / 10 SUPER COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>BUY READY</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JKCEMENT</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J.K. Cement Ltd.</t>
+          <t>Aurobindo Pharma Ltd.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4899</v>
+        <v>1666.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4810.5 - 4824.5 DR DEMAND</t>
+          <t>1633.0 - 1645.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4193.16 - 4362.57 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>10.5 / 10 HIGH COMBO</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -833,17 +833,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AEGISLOG</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aegis Logistics Ltd.</t>
+          <t>Tube Investments of India Ltd.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -852,36 +852,36 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1410.6</v>
+        <v>2197.3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1364.8 - 1392.0 DR DEMAND</t>
+          <t>2161.89 - 2177.97 DR DEMAND</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>2161.89 - 2330.75 DR DEMAND</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -913,17 +913,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>CREDITACC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tube Investments of India Ltd.</t>
+          <t>CreditAccess Grameen Ltd.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -932,21 +932,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2184.6</v>
+        <v>1233.2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2161.89 - 2177.97 DR DEMAND</t>
+          <t>1209.1 - 1216.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2161.89 - 2330.75 DR DEMAND</t>
+          <t>1602.0 - 1634.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -993,17 +993,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ABSLAMC</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aditya Birla Sun Life AMC Ltd.</t>
+          <t>GAIL (India) Ltd.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1012,11 +1012,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>981.6</v>
+        <v>168.1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>955.16 - 963.07 DR DEMAND</t>
+          <t>164.53 - 165.61 DR DEMAND</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>721.52 - 740.88 DR DEMAND</t>
+          <t>133.97 - 137.31 DR DEMAND</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1073,17 +1073,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CHOLAHLDNG</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cholamandalam Financial Holdings Ltd.</t>
+          <t>Indraprastha Gas Ltd.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1092,21 +1092,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1377.6</v>
+        <v>143.06</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1341.0 - 1361.0 DR DEMAND</t>
+          <t>137.77 - 140.53 DR DEMAND</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1358.29 - 1396.78 DR DEMAND</t>
+          <t>140.28 - 144.12 DR DEMAND</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1153,17 +1153,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IDFC First Bank Ltd.</t>
+          <t>Computer Age Management Services Ltd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1172,26 +1172,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>79.06999999999999</v>
+        <v>700</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>77.24 - 77.59 DR DEMAND</t>
+          <t>691.45 - 694.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>57.91 - 58.68 DR DEMAND</t>
+          <t>591.51 - 613.37 DR DEMAND</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1233,12 +1233,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Computer Age Management Services Ltd.</t>
+          <t>Kfin Technologies Ltd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>704.85</v>
+        <v>887</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>691.45 - 694.0 DR DEMAND</t>
+          <t>875.0 - 879.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>591.51 - 613.37 DR DEMAND</t>
+          <t>1329.97 - 1360.84 RD SUPPLY</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1313,17 +1313,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DATAPATTNS</t>
+          <t>RKFORGE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Data Patterns (India) Ltd.</t>
+          <t>Ramkrishna Forgings Ltd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1332,31 +1332,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4038.9</v>
+        <v>691.45</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3890.52 - 3981.32 DR DEMAND</t>
+          <t>675.0 - 678.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1344.18 - 1430.33 DR DEMAND</t>
+          <t>459.41 - 465.85 DR DEMAND</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GESHIP</t>
+          <t>CIEINDIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Great Eastern Shipping Co. Ltd.</t>
+          <t>CIE Automotive India Ltd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1412,21 +1412,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1484.1</v>
+        <v>377.2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1458.0 - 1462.0 DR DEMAND</t>
+          <t>368.3 - 370.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>762.54 - 775.16 DR DEMAND</t>
+          <t>479.0 - 504.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1473,17 +1473,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Indegene Ltd.</t>
+          <t>Glenmark Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1492,31 +1492,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>591.2</v>
+        <v>2226.7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>567.55 - 579.9 DR DEMAND</t>
+          <t>2181.2 - 2192.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>412.19 - 432.7 DR DEMAND</t>
+          <t>1331.41 - 1376.45 DR DEMAND</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1553,17 +1553,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kfin Technologies Ltd.</t>
+          <t>Jindal Steel Ltd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1572,21 +1572,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>894</v>
+        <v>1045.2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>875.0 - 879.0 DR DEMAND</t>
+          <t>1000.91 - 1008.99 DR DEMAND</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1329.97 - 1360.84 RD SUPPLY</t>
+          <t>1008.29 - 1043.63 DR DEMAND</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1633,17 +1633,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Laurus Labs Ltd.</t>
+          <t>Lodha Developers Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1652,31 +1652,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2018.5</v>
+        <v>1058.7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1988.9 - 1997.9 DR DEMAND</t>
+          <t>1047.5 - 1050.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>510.72 - 525.52 DR DEMAND</t>
+          <t>648.52 - 674.63 DR DEMAND</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1713,17 +1713,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>APARINDS</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Apar Industries Ltd.</t>
+          <t>Tata Steel Ltd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1732,41 +1732,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>16914</v>
+        <v>175.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>16442.91 - 16754.83 DR DEMAND</t>
+          <t>171.66 - 172.24 DR DEMAND</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>13236.05 - 14298.36 DR DEMAND</t>
+          <t>156.83 - 164.57 DR DEMAND</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1793,17 +1793,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>NCC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Castrol India Ltd.</t>
+          <t>NCC Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1812,36 +1812,36 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>196.23</v>
+        <v>125.66</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>193.15 - 193.5 DR DEMAND</t>
+          <t>123.08 - 123.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>144.37 - 156.26 DR DEMAND</t>
+          <t>163.99 - 169.16 RD SUPPLY</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1873,17 +1873,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CIEINDIA</t>
+          <t>REDINGTON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CIE Automotive India Ltd.</t>
+          <t>Redington Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1892,31 +1892,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>376.6</v>
+        <v>383.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>368.3 - 370.1 DR DEMAND</t>
+          <t>377.95 - 380.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>479.0 - 504.0 RD SUPPLY</t>
+          <t>407.0 - 419.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1953,17 +1953,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>TRIDENT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lodha Developers Ltd.</t>
+          <t>Trident Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1972,26 +1972,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1061.8</v>
+        <v>22.27</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1047.5 - 1050.0 DR DEMAND</t>
+          <t>21.8 - 21.84 DR DEMAND</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>648.52 - 674.63 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2033,17 +2033,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>GRAPHITE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NHPC Ltd.</t>
+          <t>Graphite India Ltd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2052,36 +2052,36 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>72.7</v>
+        <v>770.25</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>71.1 - 71.65 DR DEMAND</t>
+          <t>756.9 - 763.95 DR DEMAND</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>67.83 - 70.98 DR DEMAND</t>
+          <t>551.99 - 610.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2113,17 +2113,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>INTELLECT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Syrma SGS Technology Ltd.</t>
+          <t>Intellect Design Arena Ltd.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2132,36 +2132,36 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1687.3</v>
+        <v>646.4</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1670.3 - 1685.1 DR DEMAND</t>
+          <t>632.0 - 633.75 DR DEMAND</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1782.9 - 1822.6 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2193,17 +2193,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Ltd.</t>
+          <t>Cipla Ltd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2212,11 +2212,11 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1677.9</v>
+        <v>1325.1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1647.1 - 1653.2 DR DEMAND</t>
+          <t>1302.7 - 1311.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2273,17 +2273,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EIDPARRY</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>E.I.D. Parry (India) Ltd.</t>
+          <t>Jubilant Foodworks Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2292,11 +2292,11 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>701.95</v>
+        <v>417.95</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>688.7 - 690.2 DR DEMAND</t>
+          <t>408.55 - 410.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>639.0 - 660.0 DR DEMAND</t>
+          <t>496.0 - 527.85 RD SUPPLY</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2353,17 +2353,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Indraprastha Gas Ltd.</t>
+          <t>Mankind Pharma Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2372,21 +2372,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>145.14</v>
+        <v>2275.5</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>137.77 - 140.53 DR DEMAND</t>
+          <t>2242.1 - 2246.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>140.28 - 144.12 DR DEMAND</t>
+          <t>1909.7 - 2005.8 DR DEMAND</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2433,17 +2433,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J&amp;KBANK</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir Bank Ltd.</t>
+          <t>Sun Pharmaceutical Industries Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2452,11 +2452,11 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>137.45</v>
+        <v>1758.8</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>135.02 - 135.5 DR DEMAND</t>
+          <t>1725.5 - 1736.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>108.0 - 110.01 DR DEMAND</t>
+          <t>1569.37 - 1580.86 DR DEMAND</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2513,17 +2513,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>M&amp;MFIN</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Financial Services Ltd.</t>
+          <t>Voltas Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2532,11 +2532,11 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>316.15</v>
+        <v>1029.1</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>309.2 - 310.5 DR DEMAND</t>
+          <t>1012.5 - 1020.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1440.67 - 1533.08 RD SUPPLY</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2593,17 +2593,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SJVN</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SJVN Ltd.</t>
+          <t>Clean Science and Technology Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2612,26 +2612,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>55.39</v>
+        <v>783.8</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>54.26 - 54.56 DR DEMAND</t>
+          <t>766.0 - 775.75 DR DEMAND</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1538.62 - 1583.15 RD SUPPLY</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2673,17 +2673,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TRIDENT</t>
+          <t>COROMANDEL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Trident Ltd.</t>
+          <t>Coromandel International Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2692,11 +2692,11 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>22.09</v>
+        <v>1758.6</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>21.8 - 21.84 DR DEMAND</t>
+          <t>1963.9 - 1975.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1704.84 - 1751.89 DR DEMAND</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2753,12 +2753,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GRAPHITE</t>
+          <t>ESCORTS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Graphite India Ltd.</t>
+          <t>Escorts Kubota Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2772,11 +2772,11 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>767.2</v>
+        <v>2751</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>756.9 - 763.95 DR DEMAND</t>
+          <t>2550.1 - 2667.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2786,17 +2786,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>551.99 - 610.0 DR DEMAND</t>
+          <t>2679.78 - 2709.64 DR DEMAND</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2833,17 +2833,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>InterGlobe Aviation Ltd.</t>
+          <t>Godrej Consumer Products Ltd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2852,26 +2852,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4778.3</v>
+        <v>855</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4701.5 - 4733.5 DR DEMAND</t>
+          <t>840.5 - 848.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>5901.5 - 5970.0 RD SUPPLY</t>
+          <t>1066.21 - 1111.86 RD SUPPLY</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2913,17 +2913,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Larsen &amp; Toubro Ltd.</t>
+          <t>Jio Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2932,21 +2932,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3632</v>
+        <v>216.25</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>3607.0 - 3625.1 DR DEMAND</t>
+          <t>212.31 - 213.45 DR DEMAND</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3256.29 - 3470.21 DR DEMAND</t>
+          <t>259.39 - 267.57 RD SUPPLY</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2993,17 +2993,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>M&amp;MFIN</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Asian Paints Ltd.</t>
+          <t>Mahindra &amp; Mahindra Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3012,26 +3012,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2350</v>
+        <v>311.55</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2317.8 - 2331.0 DR DEMAND</t>
+          <t>309.2 - 310.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2083.96 - 2137.91 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3073,17 +3073,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>RRKABEL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cipla Ltd.</t>
+          <t>R R Kabel Ltd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3092,26 +3092,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1328</v>
+        <v>2388</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1302.7 - 1311.6 DR DEMAND</t>
+          <t>2330.2 - 2378.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1287.45 - 1370.25 DR DEMAND</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3121,22 +3121,22 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3153,17 +3153,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PFIZER</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pfizer Ltd.</t>
+          <t>Shriram Finance Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3172,26 +3172,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3810.8</v>
+        <v>939.95</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>3731.0 - 3750.0 DR DEMAND</t>
+          <t>920.0 - 929.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>559.9 - 573.24 DR DEMAND</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3233,17 +3233,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>POONAWALLA</t>
+          <t>PPLPHARMA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Poonawalla Fincorp Ltd.</t>
+          <t>Piramal Pharma Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3252,31 +3252,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>441.3</v>
+        <v>197.73</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>427.1 - 433.4 DR DEMAND</t>
+          <t>193.75 - 194.89 DR DEMAND</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>370.05 - 382.85 DR DEMAND</t>
+          <t>132.3 - 136.54 DR DEMAND</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3291,12 +3291,12 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3313,17 +3313,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>SOBHA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries Ltd.</t>
+          <t>Sobha Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3332,26 +3332,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1764</v>
+        <v>1188.4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1725.5 - 1736.0 DR DEMAND</t>
+          <t>1248.4 - 1251.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1569.37 - 1580.86 DR DEMAND</t>
+          <t>1125.39 - 1182.55 DR DEMAND</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3361,22 +3361,22 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3393,17 +3393,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>COROMANDEL</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Coromandel International Ltd.</t>
+          <t>Asian Paints Ltd.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3412,21 +3412,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1765.3</v>
+        <v>2331.9</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1963.9 - 1975.0 RD SUPPLY</t>
+          <t>2317.8 - 2331.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1704.84 - 1751.89 DR DEMAND</t>
+          <t>2083.96 - 2137.91 DR DEMAND</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3473,17 +3473,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CRISIL</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CRISIL Ltd.</t>
+          <t>Navin Fluorine International Ltd.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3492,36 +3492,36 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4415.5</v>
+        <v>8167</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>4251.3 - 4337.2 DR DEMAND</t>
+          <t>8110.0 - 8151.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3669.91 - 3717.29 DR DEMAND</t>
+          <t>4173.89 - 4245.43 DR DEMAND</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3553,17 +3553,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ESCORTS</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Escorts Kubota Ltd.</t>
+          <t>Amber Enterprises India Ltd.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3572,26 +3572,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2726.6</v>
+        <v>6668</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2550.1 - 2667.3 DR DEMAND</t>
+          <t>6151.0 - 6170.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2679.78 - 2709.64 DR DEMAND</t>
+          <t>6120.0 - 6549.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3633,17 +3633,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HBLENGINE</t>
+          <t>PFIZER</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HBL Engineering Ltd.</t>
+          <t>Pfizer Ltd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3652,26 +3652,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>710.45</v>
+        <v>3814</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>692.0 - 704.65 DR DEMAND</t>
+          <t>3731.0 - 3750.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>647.1 - 656.44 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3691,12 +3691,12 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3713,17 +3713,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>PIRAMALFIN</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GAIL (India) Ltd.</t>
+          <t>Piramal Finance Ltd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3732,26 +3732,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>169.35</v>
+        <v>1950.3</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>166.44 - 167.5 DR DEMAND</t>
+          <t>1901.22 - 1939.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>133.97 - 137.31 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3793,17 +3793,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>ZEEL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Indian Bank</t>
+          <t>Zee Entertainment Enterprises Ltd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3812,11 +3812,11 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>835</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>769.25 - 772.4 DR DEMAND</t>
+          <t>80.0 - 83.66 RD SUPPLY</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>748.11 - 819.79 DR DEMAND</t>
+          <t>66.41 - 70.46 DR DEMAND</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3841,22 +3841,22 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3873,17 +3873,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IOB</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Indian Overseas Bank</t>
+          <t>Larsen &amp; Toubro Ltd.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3892,26 +3892,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>30.74</v>
+        <v>3627.1</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>30.07 - 30.38 DR DEMAND</t>
+          <t>3607.0 - 3625.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>3256.29 - 3470.21 DR DEMAND</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3953,17 +3953,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SOBHA</t>
+          <t>GLAXO</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sobha Ltd.</t>
+          <t>Glaxosmithkline Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3972,26 +3972,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1190.8</v>
+        <v>2566.1</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1248.4 - 1251.0 RD SUPPLY</t>
+          <t>2515.0 - 2546.9 DR DEMAND</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1125.39 - 1182.55 DR DEMAND</t>
+          <t>1849.2 - 1903.26 DR DEMAND</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>4.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4033,17 +4033,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>BLUEJET</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AU Small Finance Bank Ltd.</t>
+          <t>Blue Jet Healthcare Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4052,26 +4052,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1002.7</v>
+        <v>520.65</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>974.2 - 987.0 DR DEMAND</t>
+          <t>507.79 - 514.92 DR DEMAND</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>830.84 - 841.88 DR DEMAND</t>
+          <t>631.68 - 646.45 RD SUPPLY</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>3.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4113,17 +4113,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Navin Fluorine International Ltd.</t>
+          <t>Hindustan Copper Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4132,36 +4132,36 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>8247.5</v>
+        <v>458.45</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>8110.0 - 8151.0 DR DEMAND</t>
+          <t>450.0 - 462.15 DR DEMAND</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>4173.89 - 4245.43 DR DEMAND</t>
+          <t>444.02 - 451.79 DR DEMAND</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4176,34 +4176,34 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Shree Cement Ltd.</t>
+          <t>NHPC Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4212,26 +4212,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>22315</v>
+        <v>71.44</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>21550.0 - 21900.0 DR DEMAND</t>
+          <t>71.1 - 71.65 DR DEMAND</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>67.83 - 70.98 DR DEMAND</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4256,34 +4256,34 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BELRISE</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Belrise Industries Ltd.</t>
+          <t>IDFC First Bank Ltd.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4292,26 +4292,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229.9</v>
+        <v>78.08</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>225.27 - 226.36 DR DEMAND</t>
+          <t>78.01 - 78.34 DR DEMAND</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>57.91 - 58.68 DR DEMAND</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FIVESTAR</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Five-Star Business Finance Ltd.</t>
+          <t>Varun Beverages Ltd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4372,26 +4372,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>513.25</v>
+        <v>430.5</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>498.25 - 506.25 DR DEMAND</t>
+          <t>428.95 - 430.55 DR DEMAND</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>412.05 - 443.54 DR DEMAND</t>
+          <t>396.2 - 400.45 DR DEMAND</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4416,34 +4416,34 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PIRAMALFIN</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Piramal Finance Ltd.</t>
+          <t>Avenue Supermarts Ltd.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4452,26 +4452,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1974.7</v>
+        <v>3342</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1901.22 - 1939.2 DR DEMAND</t>
+          <t>4432.2 - 4444.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>3340.0 - 3403.95 DR DEMAND</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4491,39 +4491,39 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>KEI Industries Ltd.</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4532,26 +4532,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4571.2</v>
+        <v>962.6</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>4495.0 - 4557.4 DR DEMAND</t>
+          <t>937.5 - 940.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>3937.0 - 4038.0 DR DEMAND</t>
+          <t>933.9 - 964.4 DR DEMAND</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4576,29 +4576,29 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>USHAMART</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Usha Martin Ltd.</t>
+          <t>CG Power and Industrial Solutions Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4612,26 +4612,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>482.9</v>
+        <v>846</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>477.8 - 481.3 DR DEMAND</t>
+          <t>794.1 - 800.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>274.28 - 291.22 DR DEMAND</t>
+          <t>814.85 - 863.4 DR DEMAND</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4656,34 +4656,34 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AFFLE</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Affle 3i Ltd.</t>
+          <t>Anant Raj Ltd.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4692,26 +4692,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1428.5</v>
+        <v>511.75</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1389.9 - 1406.7 DR DEMAND</t>
+          <t>510.41 - 512.91 DR DEMAND</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1251.3 - 1335.3 DR DEMAND</t>
+          <t>855.56 - 945.21 RD SUPPLY</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4721,49 +4721,49 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>4.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BLUEJET</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Blue Jet Healthcare Ltd.</t>
+          <t>PCBL Chemical Ltd.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4772,21 +4772,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>519.45</v>
+        <v>309.3</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>507.79 - 514.92 DR DEMAND</t>
+          <t>308.15 - 309.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>631.68 - 646.45 RD SUPPLY</t>
+          <t>223.38 - 238.62 DR DEMAND</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4811,39 +4811,39 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>3.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>RAMCOCEM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Hindustan Copper Ltd.</t>
+          <t>The Ramco Cements Ltd.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4852,26 +4852,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>453.05</v>
+        <v>805.4</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>450.0 - 462.15 DR DEMAND</t>
+          <t>779.5 - 786.9 DR DEMAND</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>444.02 - 451.79 DR DEMAND</t>
+          <t>784.7 - 825.32 DR DEMAND</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4913,17 +4913,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>TECHNOE</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Jindal Steel Ltd.</t>
+          <t>Techno Electric &amp; Engineering Company Ltd.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4932,28 +4932,28 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1030</v>
+        <v>946.6</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1000.91 - 1008.99 DR DEMAND</t>
+          <t>1006.2 - 1016.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>863.77 - 967.52 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
           <t>4.0 C</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>1008.29 - 1043.63 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>6.5 B</t>
-        </is>
-      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4993,17 +4993,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>FIVESTAR</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bharat Electronics Ltd.</t>
+          <t>Five-Star Business Finance Ltd.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5012,21 +5012,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>380.4</v>
+        <v>506.15</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>397.4 - 399.2 RD SUPPLY</t>
+          <t>498.25 - 506.25 DR DEMAND</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>378.32 - 397.37 DR DEMAND</t>
+          <t>412.05 - 443.54 DR DEMAND</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5073,17 +5073,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Varun Beverages Ltd.</t>
+          <t>Mazagoan Dock Shipbuilders Ltd.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5092,26 +5092,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>429.25</v>
+        <v>2092</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>428.95 - 430.55 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>396.2 - 400.45 DR DEMAND</t>
+          <t>1900.61 - 2111.67 DR DEMAND</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5153,17 +5153,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>WELCORP</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Welspun Corp Ltd.</t>
+          <t>Torrent Power Ltd.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5172,36 +5172,36 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2486.9</v>
+        <v>1226.3</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2450.0 - 2497.5 DR DEMAND</t>
+          <t>1165.0 - 1174.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>658.55 - 760.86 DR DEMAND</t>
+          <t>1186.52 - 1241.27 DR DEMAND</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5233,17 +5233,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>State Bank of India</t>
+          <t>Vedanta Ltd.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5252,26 +5252,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>960</v>
+        <v>246.1</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>937.5 - 940.0 DR DEMAND</t>
+          <t>244.83 - 248.11 DR DEMAND</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>933.9 - 964.4 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5313,17 +5313,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ASAHIINDIA</t>
+          <t>UTIAMC</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Asahi India Glass Ltd.</t>
+          <t>UTI Asset Management Company Ltd.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5332,11 +5332,11 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>925.9</v>
+        <v>869.9</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>925.1 - 929.29 DR DEMAND</t>
+          <t>1039.08 - 1043.74 RD SUPPLY</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5346,22 +5346,22 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>841.38 - 874.76 DR DEMAND</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5393,17 +5393,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>ASTERDM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CG Power and Industrial Solutions Ltd.</t>
+          <t>Aster DM Healthcare Ltd.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5412,26 +5412,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>818</v>
+        <v>674.35</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>794.1 - 800.0 DR DEMAND</t>
+          <t>671.0 - 674.35 DR DEMAND</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>814.85 - 863.4 DR DEMAND</t>
+          <t>516.84 - 549.74 DR DEMAND</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5441,22 +5441,22 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 4 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>4.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5473,45 +5473,45 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SBI Cards and Payment Services Ltd.</t>
+          <t>HDFC Bank Ltd.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>573.2</v>
+        <v>728.85</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>698.4 - 700.4 RD SUPPLY</t>
+          <t>731.95 - 734.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>565.45 - 593.2 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5531,67 +5531,67 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SAMMAANCAP</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sammaan Capital Ltd.</t>
+          <t>ITC Ltd.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>136.98</v>
+        <v>263.5</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>125.66 - 126.44 DR DEMAND</t>
+          <t>267.2 - 268.05 RD SUPPLY</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>134.75 - 144.61 DR DEMAND</t>
+          <t>400.8 - 406.57 RD SUPPLY</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5601,77 +5601,77 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>JSWCEMENT</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Avenue Supermarts Ltd.</t>
+          <t>JSW Cement Ltd.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3378.4</v>
+        <v>114.71</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>4432.2 - 4444.5 RD SUPPLY</t>
+          <t>115.77 - 116.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>3340.0 - 3403.95 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5691,67 +5691,67 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>9.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PCBL</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PCBL Chemical Ltd.</t>
+          <t>Bajaj Finance Ltd.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>308.9</v>
+        <v>982.1</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>308.15 - 309.8 DR DEMAND</t>
+          <t>982.75 - 986.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>223.38 - 238.62 DR DEMAND</t>
+          <t>783.09 - 796.65 DR DEMAND</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5771,77 +5771,77 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PPLPHARMA</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Piramal Pharma Ltd.</t>
+          <t>Hindustan Petroleum Corporation Ltd.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>194.43</v>
+        <v>346</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>193.75 - 194.89 DR DEMAND</t>
+          <t>351.0 - 351.75 RD SUPPLY</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>132.3 - 136.54 DR DEMAND</t>
+          <t>263.73 - 269.42 DR DEMAND</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5851,67 +5851,67 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>RAMCOCEM</t>
+          <t>IGIL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The Ramco Cements Ltd.</t>
+          <t>International Gemological Institute Ltd.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>786.9</v>
+        <v>326.7</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>951.15 - 986.61 RD SUPPLY</t>
+          <t>330.55 - 332.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>784.7 - 825.32 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5931,67 +5931,67 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TECHNOE</t>
+          <t>ITCHOTELS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Techno Electric &amp; Engineering Company Ltd.</t>
+          <t>ITC Hotels Ltd.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>945.2</v>
+        <v>162.48</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1006.2 - 1016.2 RD SUPPLY</t>
+          <t>164.13 - 164.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>863.77 - 967.52 DR DEMAND</t>
+          <t>180.5 - 188.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6011,57 +6011,57 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>LALPATHLAB</t>
+          <t>JAINREC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dr. Lal Path Labs Ltd.</t>
+          <t>Jain Resource Recycling Ltd.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1885.1</v>
+        <v>289.8</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1870.0 - 1890.6 DR DEMAND</t>
+          <t>295.15 - 300.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6076,12 +6076,12 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -6091,67 +6091,67 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MEDANTA</t>
+          <t>MINDACORP</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Global Health Ltd.</t>
+          <t>Minda Corporation Ltd.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1275.5</v>
+        <v>649.85</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1270.9 - 1276.5 DR DEMAND</t>
+          <t>659.6 - 661.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1480.9 - 1544.0 RD SUPPLY</t>
+          <t>451.85 - 473.12 DR DEMAND</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -6171,67 +6171,67 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Mazagoan Dock Shipbuilders Ltd.</t>
+          <t>NLC India Ltd.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2105</v>
+        <v>253.35</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>257.65 - 258.25 RD SUPPLY</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1900.61 - 2111.67 DR DEMAND</t>
+          <t>217.4 - 220.48 DR DEMAND</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -6251,34 +6251,34 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Torrent Power Ltd.</t>
+          <t>NMDC Ltd.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -6288,30 +6288,30 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1238.6</v>
+        <v>71.69</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1165.0 - 1174.4 DR DEMAND</t>
+          <t>71.99 - 72.33 RD SUPPLY</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1186.52 - 1241.27 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6331,67 +6331,67 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Vedanta Ltd.</t>
+          <t>Pidilite Industries Ltd.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>245.9</v>
+        <v>1502.8</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>244.83 - 248.11 DR DEMAND</t>
+          <t>1520.5 - 1524.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1687.7 - 1707.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6411,67 +6411,67 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>UTIAMC</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>UTI Asset Management Company Ltd.</t>
+          <t>Reliance Industries Ltd.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>874.35</v>
+        <v>1211.2</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1039.08 - 1043.74 RD SUPPLY</t>
+          <t>1226.0 - 1227.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>841.38 - 874.76 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -6481,44 +6481,44 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Alkem Laboratories Ltd.</t>
+          <t>Abbott India Ltd.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6528,30 +6528,30 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5120.5</v>
+        <v>26170</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>5110.0 - 5150.0 DR DEMAND</t>
+          <t>26295.0 - 26550.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>24406.02 - 25223.54 DR DEMAND</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6571,62 +6571,62 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>4.0 / 10 SOLID</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Glaxosmithkline Pharmaceuticals Ltd.</t>
+          <t>Aditya Birla Capital Ltd.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2524.7</v>
+        <v>379.4</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2515.0 - 2546.9 DR DEMAND</t>
+          <t>385.6 - 386.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>1849.2 - 1903.26 DR DEMAND</t>
+          <t>287.7 - 292.25 DR DEMAND</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6651,34 +6651,34 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>3.5 / 10 SOLID</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HDFC Bank Ltd.</t>
+          <t>AU Small Finance Bank Ltd.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6692,26 +6692,26 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>726.85</v>
+        <v>989.4</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>731.95 - 734.2 RD SUPPLY</t>
+          <t>1002.8 - 1015.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>830.84 - 841.88 DR DEMAND</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -6753,17 +6753,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ITC Ltd.</t>
+          <t>Bajaj Finserv Ltd.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -6772,26 +6772,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>263.9</v>
+        <v>1729</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>267.2 - 268.05 RD SUPPLY</t>
+          <t>1755.7 - 1758.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>400.8 - 406.57 RD SUPPLY</t>
+          <t>1991.7 - 2073.13 RD SUPPLY</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -6833,17 +6833,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Phoenix Mills Ltd.</t>
+          <t>Chambal Fertilizers &amp; Chemicals Ltd.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -6852,31 +6852,31 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1917.2</v>
+        <v>388.1</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1946.8 - 1954.9 RD SUPPLY</t>
+          <t>393.0 - 398.25 RD SUPPLY</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>1851.05 - 1990.36 RD SUPPLY</t>
+          <t>670.14 - 717.72 RD SUPPLY</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -6913,17 +6913,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>DOMS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Bajaj Finance Ltd.</t>
+          <t>DOMS Industries Ltd.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -6932,26 +6932,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>965.25</v>
+        <v>2104.5</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>982.75 - 986.5 RD SUPPLY</t>
+          <t>2141.5 - 2147.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>783.09 - 796.65 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -6993,17 +6993,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>EIDPARRY</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HDFC Asset Management Company Ltd.</t>
+          <t>E.I.D. Parry (India) Ltd.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7012,21 +7012,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2415</v>
+        <v>694.15</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2448.3 - 2454.0 RD SUPPLY</t>
+          <t>702.8 - 706.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2223.3 - 2280.7 DR DEMAND</t>
+          <t>639.0 - 660.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -7073,17 +7073,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Hindustan Petroleum Corporation Ltd.</t>
+          <t>IndusInd Bank Ltd.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7092,21 +7092,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>348.5</v>
+        <v>877</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>351.0 - 351.75 RD SUPPLY</t>
+          <t>887.9 - 891.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>263.73 - 269.42 DR DEMAND</t>
+          <t>605.02 - 647.95 DR DEMAND</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7153,17 +7153,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>JAINREC</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Jain Resource Recycling Ltd.</t>
+          <t>NATCO Pharma Ltd.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7172,16 +7172,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>292.8</v>
+        <v>785.05</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>295.15 - 300.9 RD SUPPLY</t>
+          <t>800.55 - 804.75 RD SUPPLY</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -7233,17 +7233,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>RAINBOW</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>NMDC Ltd.</t>
+          <t>Rainbow Childrens Medicare Ltd.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7252,26 +7252,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>70.81999999999999</v>
+        <v>1248.9</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>71.99 - 72.33 RD SUPPLY</t>
+          <t>1270.7 - 1288.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1550.0 - 1610.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -7313,17 +7313,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Pidilite Industries Ltd.</t>
+          <t>Steel Authority of India Ltd.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7332,28 +7332,28 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1505</v>
+        <v>170.95</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1520.5 - 1524.6 RD SUPPLY</t>
+          <t>172.77 - 174.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>202.55 - 206.99 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
           <t>7.5 A</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>1687.7 - 1707.5 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>8.5 A</t>
-        </is>
-      </c>
       <c r="J87" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -7376,7 +7376,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -7393,17 +7393,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Reliance Industries Ltd.</t>
+          <t>SBI Cards and Payment Services Ltd.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7412,28 +7412,28 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1215</v>
+        <v>564.2</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1226.0 - 1227.4 RD SUPPLY</t>
+          <t>573.2 - 578.75 RD SUPPLY</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>771.7 - 797.71 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
           <t>7.5 A</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J88" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -7473,17 +7473,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>VTL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Abbott India Ltd.</t>
+          <t>Vardhman Textiles Ltd.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -7492,11 +7492,11 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>26070</v>
+        <v>531.9</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>26295.0 - 26550.0 RD SUPPLY</t>
+          <t>540.0 - 543.1 RD SUPPLY</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>24406.02 - 25223.54 DR DEMAND</t>
+          <t>614.54 - 641.56 RD SUPPLY</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -7553,12 +7553,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Aditya Birla Capital Ltd.</t>
+          <t>Capri Global Capital Ltd.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -7572,31 +7572,31 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>382.25</v>
+        <v>247.56</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>385.6 - 386.5 RD SUPPLY</t>
+          <t>250.74 - 252.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>287.7 - 292.25 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -7633,12 +7633,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Bajaj Finserv Ltd.</t>
+          <t>HDFC Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -7652,26 +7652,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1732</v>
+        <v>553</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1755.7 - 1758.0 RD SUPPLY</t>
+          <t>561.0 - 561.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1991.7 - 2073.13 RD SUPPLY</t>
+          <t>811.41 - 817.84 RD SUPPLY</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -7713,17 +7713,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DOMS</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>DOMS Industries Ltd.</t>
+          <t>Jindal Stainless Ltd.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -7732,16 +7732,16 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2124.8</v>
+        <v>736.55</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2141.5 - 2147.0 RD SUPPLY</t>
+          <t>751.0 - 759.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -7793,17 +7793,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>INDIACEM</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>India Cements Ltd.</t>
+          <t>Phoenix Mills Ltd.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -7812,31 +7812,31 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>297.4</v>
+        <v>1896.9</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>300.65 - 302.15 RD SUPPLY</t>
+          <t>1924.0 - 1935.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>400.0 - 416.4 RD SUPPLY</t>
+          <t>1851.05 - 1990.36 RD SUPPLY</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -7873,17 +7873,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>NATCO Pharma Ltd.</t>
+          <t>Punjab National Bank</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -7892,31 +7892,31 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>784.95</v>
+        <v>116.3</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>800.55 - 804.75 RD SUPPLY</t>
+          <t>118.55 - 119.64 RD SUPPLY</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>80.71 - 82.53 DR DEMAND</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -7953,17 +7953,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>RAINBOW</t>
+          <t>ABFRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Rainbow Childrens Medicare Ltd.</t>
+          <t>Aditya Birla Fashion and Retail Ltd.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -7972,26 +7972,26 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1246.6</v>
+        <v>44.83</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1270.7 - 1288.7 RD SUPPLY</t>
+          <t>45.68 - 47.39 RD SUPPLY</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1550.0 - 1610.0 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -8033,17 +8033,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>INDGN</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Steel Authority of India Ltd.</t>
+          <t>Indegene Ltd.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8052,11 +8052,11 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>170.29</v>
+        <v>598.3</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>172.77 - 174.0 RD SUPPLY</t>
+          <t>607.1 - 612.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -8066,17 +8066,17 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>202.55 - 206.99 RD SUPPLY</t>
+          <t>412.19 - 432.7 DR DEMAND</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -8113,17 +8113,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>VTL</t>
+          <t>UCOBANK</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Vardhman Textiles Ltd.</t>
+          <t>UCO Bank</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8132,26 +8132,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>539</v>
+        <v>23.73</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>549.4 - 557.0 RD SUPPLY</t>
+          <t>24.12 - 24.17 RD SUPPLY</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>614.54 - 641.56 RD SUPPLY</t>
+          <t>32.81 - 33.64 RD SUPPLY</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -8193,17 +8193,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Capri Global Capital Ltd.</t>
+          <t>Zydus Lifesciences Ltd.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8212,26 +8212,26 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>247.15</v>
+        <v>1123</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>250.74 - 252.0 RD SUPPLY</t>
+          <t>1140.2 - 1150.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>855.18 - 875.51 DR DEMAND</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -8273,12 +8273,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>AAVAS</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>HDFC Life Insurance Company Ltd.</t>
+          <t>Aavas Financiers Ltd.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -8292,26 +8292,26 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>550.55</v>
+        <v>1195.2</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>561.0 - 561.95 RD SUPPLY</t>
+          <t>1219.4 - 1228.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>811.41 - 817.84 RD SUPPLY</t>
+          <t>1060.4 - 1078.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -8353,17 +8353,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>HONAUT</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Honeywell Automation India Ltd.</t>
+          <t>Coforge Ltd.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8372,31 +8372,31 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>32380</v>
+        <v>1951.9</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>32925.0 - 33020.0 RD SUPPLY</t>
+          <t>1837.2 - 1846.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>1985.3 - 2021.2 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
           <t>6.5 B</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -8433,17 +8433,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>OLAELEC</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ola Electric Mobility Ltd.</t>
+          <t>Narayana Hrudayalaya Ltd.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -8452,28 +8452,28 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>35.17</v>
+        <v>1719.4</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>35.88 - 36.4 RD SUPPLY</t>
+          <t>1724.4 - 1746.3 RD SUPPLY</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
+          <t>5.5 B</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2170.07 - 2359.4 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
           <t>6.5 B</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J101" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -8481,7 +8481,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -8513,17 +8513,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ABFRL</t>
+          <t>NUVOCO</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Aditya Birla Fashion and Retail Ltd.</t>
+          <t>Nuvoco Vistas Corporation Ltd.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -8532,36 +8532,36 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>44.86</v>
+        <v>341.15</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>45.68 - 47.39 RD SUPPLY</t>
+          <t>344.75 - 348.75 RD SUPPLY</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>349.75 - 398.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -8593,17 +8593,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AWL</t>
+          <t>GABRIEL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>AWL Agri Business Ltd.</t>
+          <t>Gabriel India Ltd.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -8612,28 +8612,28 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>190.54</v>
+        <v>1448.9</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>194.38 - 195.5 RD SUPPLY</t>
+          <t>1475.5 - 1495.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
+          <t>6.0 B</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>1268.2 - 1338.3 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
           <t>7.0 A</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>172.6 - 176.61 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>5.5 B</t>
-        </is>
-      </c>
       <c r="J103" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -8673,17 +8673,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ZENSARTECH</t>
+          <t>INDIACEM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Zensar Technolgies Ltd.</t>
+          <t>India Cements Ltd.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -8692,36 +8692,36 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>504.45</v>
+        <v>302.3</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>416.15 - 422.4 DR DEMAND</t>
+          <t>303.05 - 305.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>510.15 - 553.1 RD SUPPLY</t>
+          <t>400.0 - 416.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -8753,17 +8753,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Adani Green Energy Ltd.</t>
+          <t>REC Ltd.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -8772,26 +8772,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1307.1</v>
+        <v>307.8</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>1330.6 - 1346.8 RD SUPPLY</t>
+          <t>314.0 - 315.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>765.0 - 814.2 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -8833,17 +8833,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ASTERDM</t>
+          <t>SCI</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Aster DM Healthcare Ltd.</t>
+          <t>Shipping Corporation of India Ltd.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -8852,36 +8852,36 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>682.65</v>
+        <v>284.9</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>689.85 - 706.3 RD SUPPLY</t>
+          <t>289.0 - 292.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>516.84 - 549.74 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -8913,17 +8913,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>THELEELA</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Leela Palaces Hotels &amp; Resorts Ltd.</t>
+          <t>Wipro Ltd.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -8932,28 +8932,28 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>596.5</v>
+        <v>184.4</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>604.45 - 607.25 RD SUPPLY</t>
+          <t>187.53 - 188.37 RD SUPPLY</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
+          <t>6.0 B</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>156.79 - 158.5 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
           <t>6.5 B</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J107" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -8993,17 +8993,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CHALET</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Chalet Hotels Ltd.</t>
+          <t>BSE Ltd.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9012,31 +9012,31 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>842.6</v>
+        <v>3363</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>848.0 - 851.95 RD SUPPLY</t>
+          <t>3417.0 - 3452.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>902.92 - 938.88 RD SUPPLY</t>
+          <t>3000.0 - 3089.9 DR DEMAND</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -9073,17 +9073,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>ZENSARTECH</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Grasim Industries Ltd.</t>
+          <t>Zensar Technolgies Ltd.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9092,31 +9092,31 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2885.9</v>
+        <v>507.75</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2899.4 - 2919.5 RD SUPPLY</t>
+          <t>416.15 - 422.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2494.13 - 2528.7 DR DEMAND</t>
+          <t>510.15 - 553.1 RD SUPPLY</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -9153,17 +9153,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>LEMONTREE</t>
+          <t>ZENTEC</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Lemon Tree Hotels Ltd.</t>
+          <t>Zen Technologies Ltd.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9172,41 +9172,41 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>112.5</v>
+        <v>1655.6</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>112.71 - 113.55 RD SUPPLY</t>
+          <t>1682.4 - 1695.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
+          <t>4.5 C</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>943.53 - 1043.28 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -9233,12 +9233,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>REC Ltd.</t>
+          <t>360 ONE WAM Ltd.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -9252,26 +9252,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>309.75</v>
+        <v>1075</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>314.0 - 315.5 RD SUPPLY</t>
+          <t>1077.5 - 1080.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1185.06 - 1260.04 RD SUPPLY</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -9313,17 +9313,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SCI</t>
+          <t>APOLLOTYRE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Shipping Corporation of India Ltd.</t>
+          <t>Apollo Tyres Ltd.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -9332,16 +9332,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>284</v>
+        <v>408.85</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>289.0 - 292.0 RD SUPPLY</t>
+          <t>412.9 - 429.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -9356,12 +9356,12 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -9393,17 +9393,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>BSOFT</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Indian Railway Finance Corporation Ltd.</t>
+          <t>Birlasoft Ltd.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -9412,11 +9412,11 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>78.90000000000001</v>
+        <v>318.2</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>79.28 - 81.5 RD SUPPLY</t>
+          <t>323.62 - 325.69 RD SUPPLY</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -9426,17 +9426,17 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>421.73 - 438.51 RD SUPPLY</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -9473,17 +9473,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>UCOBANK</t>
+          <t>KARURVYSYA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>UCO Bank</t>
+          <t>Karur Vysya Bank Ltd.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>PVTBANK</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -9492,11 +9492,11 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>23.56</v>
+        <v>355.65</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>24.04 - 24.12 RD SUPPLY</t>
+          <t>356.85 - 358.65 RD SUPPLY</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -9506,17 +9506,17 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>32.81 - 33.64 RD SUPPLY</t>
+          <t>311.4 - 323.7 DR DEMAND</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -9553,17 +9553,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>360 ONE WAM Ltd.</t>
+          <t>Trent Ltd.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -9572,31 +9572,31 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1073</v>
+        <v>2958.7</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>1077.5 - 1080.9 RD SUPPLY</t>
+          <t>2989.9 - 3020.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>1185.06 - 1260.04 RD SUPPLY</t>
+          <t>2545.8 - 2615.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -9633,17 +9633,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>POONAWALLA</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>RITES Ltd.</t>
+          <t>Poonawalla Fincorp Ltd.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -9652,41 +9652,41 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>214.27</v>
+        <v>448.95</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>191.25 - 192.31 DR DEMAND</t>
+          <t>427.1 - 433.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>214.72 - 226.44 RD SUPPLY</t>
+          <t>454.8 - 503.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -9713,17 +9713,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>AARTIIND</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Trent Ltd.</t>
+          <t>Aarti Industries Ltd.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -9732,26 +9732,26 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2949.7</v>
+        <v>503</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2989.9 - 3020.6 RD SUPPLY</t>
+          <t>503.05 - 510.93 RD SUPPLY</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2545.8 - 2615.0 DR DEMAND</t>
+          <t>459.3 - 475.7 DR DEMAND</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -9761,12 +9761,12 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -9776,7 +9776,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>4.5 / 10 SUPPLY</t>
+          <t>3.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -9793,17 +9793,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>GROWW</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>DLF Ltd.</t>
+          <t>Billionbrains Garage Ventures Ltd.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -9812,26 +9812,26 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>670.5</v>
+        <v>200.85</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>673.0 - 676.5 RD SUPPLY</t>
+          <t>203.01 - 205.21 RD SUPPLY</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>483.33 - 497.85 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>3.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -9873,17 +9873,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>LTFOODS</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Indian Hotels Co. Ltd.</t>
+          <t>LT Foods Ltd.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -9892,11 +9892,11 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>741.45</v>
+        <v>417.65</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>751.2 - 757.4 RD SUPPLY</t>
+          <t>418.4 - 421.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>871.1 - 888.32 RD SUPPLY</t>
+          <t>285.59 - 341.86 DR DEMAND</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -9953,17 +9953,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>COHANCE</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Cohance Lifesciences Ltd.</t>
+          <t>Saregama India Ltd</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -9972,26 +9972,26 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>459.95</v>
+        <v>504</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>462.35 - 467.2 RD SUPPLY</t>
+          <t>506.55 - 518.65 RD SUPPLY</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>1229.95 - 1328.0 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2.5 / 10 SUPPLY</t>
+          <t>3.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -10033,17 +10033,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>FSN E-Commerce Ventures Ltd.</t>
+          <t>Radico Khaitan Ltd</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -10052,11 +10052,11 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>338.4</v>
+        <v>4473.4</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>341.25 - 346.45 RD SUPPLY</t>
+          <t>4557.1 - 4600.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -10066,12 +10066,12 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>232.05 - 235.0 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -10113,17 +10113,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Tata Elxsi Ltd.</t>
+          <t>Sun TV Network Ltd.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -10132,26 +10132,26 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3700</v>
+        <v>638</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>3685.0 - 3708.0 RD SUPPLY</t>
+          <t>608.6 - 613.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2996.0 - 3088.9 DR DEMAND</t>
+          <t>603.75 - 653.93 RD SUPPLY</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -10193,17 +10193,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>APOLLOTYRE</t>
+          <t>BATAINDIA</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Apollo Tyres Ltd.</t>
+          <t>Bata India Ltd.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10212,26 +10212,26 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>413.9</v>
+        <v>638.65</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>412.9 - 429.0 RD SUPPLY</t>
+          <t>637.2 - 644.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>689.25 - 743.46 RD SUPPLY</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -10273,12 +10273,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>CHALET</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Sun TV Network Ltd.</t>
+          <t>Chalet Hotels Ltd.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -10292,26 +10292,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>629.15</v>
+        <v>850.25</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>608.6 - 613.0 DR DEMAND</t>
+          <t>848.0 - 851.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>603.75 - 653.93 RD SUPPLY</t>
+          <t>902.92 - 938.88 RD SUPPLY</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -10353,17 +10353,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>LEMONTREE</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Narayana Hrudayalaya Ltd.</t>
+          <t>Lemon Tree Hotels Ltd.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -10372,36 +10372,36 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1725.4</v>
+        <v>113.42</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>1724.4 - 1746.3 RD SUPPLY</t>
+          <t>112.71 - 113.55 RD SUPPLY</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2170.07 - 2359.4 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -10433,17 +10433,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Kajaria Ceramics Ltd.</t>
+          <t>Indian Railway Finance Corporation Ltd.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -10452,31 +10452,31 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1215</v>
+        <v>80.25</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>1175.7 - 1183.6 DR DEMAND</t>
+          <t>79.28 - 81.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>1181.73 - 1240.58 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -10513,17 +10513,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Supreme Industries Ltd.</t>
+          <t>Tech Mahindra Ltd.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -10532,26 +10532,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>3616</v>
+        <v>1790</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>3567.7 - 3631.8 RD SUPPLY</t>
+          <t>1442.5 - 1471.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1698.95 - 1807.04 RD SUPPLY</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -10593,12 +10593,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>AIIL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>BSE Ltd.</t>
+          <t>Authum Investment &amp; Infrastructure Ltd.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -10612,26 +10612,26 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3428</v>
+        <v>571.9</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>3417.0 - 3452.7 RD SUPPLY</t>
+          <t>568.95 - 579.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>3000.0 - 3089.9 DR DEMAND</t>
+          <t>629.8 - 683.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -10641,12 +10641,12 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>4.5 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -10673,17 +10673,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ZENTEC</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Zen Technologies Ltd.</t>
+          <t>Kajaria Ceramics Ltd.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -10692,26 +10692,26 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1695</v>
+        <v>1211</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>1682.4 - 1695.0 RD SUPPLY</t>
+          <t>1175.7 - 1183.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>943.53 - 1043.28 DR DEMAND</t>
+          <t>1181.73 - 1240.58 RD SUPPLY</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>4.5 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -10753,17 +10753,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AARTIIND</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Aarti Industries Ltd.</t>
+          <t>Supreme Industries Ltd.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -10772,26 +10772,26 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>505.05</v>
+        <v>3595.5</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>503.05 - 510.93 RD SUPPLY</t>
+          <t>3567.7 - 3631.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>459.3 - 475.7 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -10816,7 +10816,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>3.0 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -10833,17 +10833,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>LT Foods Ltd.</t>
+          <t>DLF Ltd.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -10852,26 +10852,26 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>419.6</v>
+        <v>675</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>418.4 - 421.9 RD SUPPLY</t>
+          <t>673.0 - 676.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>285.59 - 341.87 DR DEMAND</t>
+          <t>483.33 - 497.85 DR DEMAND</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>3.0 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -10913,17 +10913,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>LTTS</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>FSN E-Commerce Ventures Ltd.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -10932,11 +10932,11 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3686.8</v>
+        <v>345</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>3652.7 - 3708.0 RD SUPPLY</t>
+          <t>341.25 - 346.45 RD SUPPLY</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>3051.8 - 3199.1 DR DEMAND</t>
+          <t>232.05 - 235.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -10966,7 +10966,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -11012,7 +11012,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>726</v>
+        <v>721.15</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11065,6 +11065,86 @@
         </is>
       </c>
       <c r="P133" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>COHANCE</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Cohance Lifesciences Ltd.</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>HEALTHCARE</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>464.05</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>462.35 - 467.2 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>2.5 C</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>1229.95 - 1328.0 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>4.0 C</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>🔴 2 TESTS (WEAK)</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>2.5 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
         <is>
           <t>IN</t>
         </is>

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P127"/>
+  <dimension ref="A1:P126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,12 +513,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JMFINANCIL</t>
+          <t>HOMEFIRST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JM Financial Ltd.</t>
+          <t>Home First Finance Company India Ltd.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -532,26 +532,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>113.96</v>
+        <v>1021.3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>112.77 - 116.19 DR DEMAND</t>
+          <t>1018.5 - 1029.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>110.31 - 111.89 DR DEMAND</t>
+          <t>889.54 - 900.59 DR DEMAND</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>10.5 / 10 HIGH COMBO</t>
+          <t>11.0 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -593,17 +593,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kirloskar Oil Eng Ltd.</t>
+          <t>Axis Bank Ltd.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -612,11 +612,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1908.7</v>
+        <v>1212</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1905.97 - 1910.96 DR DEMAND</t>
+          <t>1175.0 - 1186.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -626,12 +626,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>539.93 - 571.37 DR DEMAND</t>
+          <t>1208.6 - 1229.5 DR DEMAND</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -673,17 +673,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Axis Bank Ltd.</t>
+          <t>Cummins India Ltd.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -692,26 +692,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1210</v>
+        <v>4460</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1175.0 - 1186.5 DR DEMAND</t>
+          <t>4357.85 - 4480.83 DR DEMAND</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1208.6 - 1229.5 DR DEMAND</t>
+          <t>4357.85 - 4463.08 DR DEMAND</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -736,29 +736,29 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>11.0 / 10 SUPER COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>BUY READY</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HOMEFIRST</t>
+          <t>JMFINANCIL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Home First Finance Company India Ltd.</t>
+          <t>JM Financial Ltd.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -772,26 +772,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1039.2</v>
+        <v>110.97</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1018.5 - 1029.7 DR DEMAND</t>
+          <t>129.02 - 129.65 RD SUPPLY</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>889.54 - 900.59 DR DEMAND</t>
+          <t>110.31 - 111.89 DR DEMAND</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -816,34 +816,34 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>11.0 / 10 SUPER COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>BUY READY</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FINCABLES</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Finolex Cables Ltd.</t>
+          <t>JSW Energy Ltd.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -852,26 +852,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202.4</v>
+        <v>463.9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1178.11 - 1182.78 DR DEMAND</t>
+          <t>457.5 - 460.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>949.44 - 980.62 DR DEMAND</t>
+          <t>415.69 - 460.71 DR DEMAND</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>10.5 / 10 HIGH COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -913,17 +913,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LALPATHLAB</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dr. Lal Path Labs Ltd.</t>
+          <t>ITC Ltd.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -932,31 +932,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1836.1</v>
+        <v>258.9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1785.35 - 1800.31 DR DEMAND</t>
+          <t>253.15 - 255.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>400.8 - 406.57 RD SUPPLY</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>10.5 / 10 HIGH COMBO</t>
+          <t>11.0 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -993,17 +993,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>M&amp;MFIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jindal Steel Ltd.</t>
+          <t>Mahindra &amp; Mahindra Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1012,26 +1012,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1028</v>
+        <v>287.6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1000.91 - 1008.99 DR DEMAND</t>
+          <t>282.35 - 284.84 DR DEMAND</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1008.29 - 1043.63 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>11.0 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1073,17 +1073,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PINELABS</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pine Labs Ltd.</t>
+          <t>Nestle India Ltd.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1092,26 +1092,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>158.42</v>
+        <v>1189.9</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>155.1 - 156.5 DR DEMAND</t>
+          <t>1384.5 - 1397.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1153.85 - 1169.18 DR DEMAND</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>11.0 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1153,17 +1153,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Indraprastha Gas Ltd.</t>
+          <t>ICICI Bank Ltd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1172,36 +1172,36 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>142.31</v>
+        <v>1398.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>137.77 - 140.53 DR DEMAND</t>
+          <t>1375.1 - 1379.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>140.28 - 144.12 DR DEMAND</t>
+          <t>1291.0 - 1316.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1233,17 +1233,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>RITES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nestle India Ltd.</t>
+          <t>RITES Ltd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1252,26 +1252,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1223.9</v>
+        <v>196.09</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1216.25 - 1220.23 DR DEMAND</t>
+          <t>191.25 - 192.31 DR DEMAND</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1153.85 - 1169.18 DR DEMAND</t>
+          <t>214.72 - 226.44 RD SUPPLY</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1313,17 +1313,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RRKABEL</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R R Kabel Ltd.</t>
+          <t>Amber Enterprises India Ltd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1332,11 +1332,11 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2327.8</v>
+        <v>6180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2284.0 - 2291.3 DR DEMAND</t>
+          <t>6151.0 - 6170.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1287.45 - 1370.25 DR DEMAND</t>
+          <t>6120.0 - 6549.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Acutaas Chemicals Ltd.</t>
+          <t>Hindustan Aeronautics Ltd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1412,11 +1412,11 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3152.4</v>
+        <v>4875</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3116.6 - 3132.5 DR DEMAND</t>
+          <t>4765.2 - 4790.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1568.83 - 1703.63 DR DEMAND</t>
+          <t>3004.72 - 3046.3 DR DEMAND</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1473,17 +1473,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>BEML</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>APL Apollo Tubes Ltd.</t>
+          <t>BEML Ltd.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1492,26 +1492,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2066.8</v>
+        <v>1907.7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026.2 - 2040.0 DR DEMAND</t>
+          <t>1875.6 - 1894.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1683.51 - 1712.3 DR DEMAND</t>
+          <t>1159.43 - 1211.03 DR DEMAND</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1553,12 +1553,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWL</t>
+          <t>BALRAMCHIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AWL Agri Business Ltd.</t>
+          <t>Balrampur Chini Mills Ltd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1572,31 +1572,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>179.66</v>
+        <v>654.75</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>174.69 - 176.18 DR DEMAND</t>
+          <t>638.0 - 649.05 DR DEMAND</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>415.9 - 440.91 DR DEMAND</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1633,17 +1633,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BAYERCROP</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bayer Cropscience Ltd.</t>
+          <t>Gland Pharma Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1652,11 +1652,11 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3437.3</v>
+        <v>2850.4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3366.3 - 3381.6 DR DEMAND</t>
+          <t>2792.4 - 2826.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1666,17 +1666,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1256.51 - 1376.68 DR DEMAND</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1850.2</v>
+        <v>1828.3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5882.5</v>
+        <v>5900.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>11200</v>
+        <v>11170</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1953,17 +1953,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RKFORGE</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ramkrishna Forgings Ltd.</t>
+          <t>United Spirits Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1972,11 +1972,11 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>635.75</v>
+        <v>1284.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>623.3 - 626.4 DR DEMAND</t>
+          <t>1256.42 - 1261.78 DR DEMAND</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>459.41 - 465.85 DR DEMAND</t>
+          <t>1595.35 - 1664.73 RD SUPPLY</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2033,17 +2033,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>CARTRADE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Castrol India Ltd.</t>
+          <t>Cartrade Tech Ltd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2052,26 +2052,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>196.19</v>
+        <v>2840</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>193.15 - 193.5 DR DEMAND</t>
+          <t>2739.8 - 2806.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>144.37 - 156.26 DR DEMAND</t>
+          <t>1485.0 - 1525.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2194.1</v>
+        <v>2198.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2193,17 +2193,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tata Steel Ltd.</t>
+          <t>HDFC Bank Ltd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2212,11 +2212,11 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>172.45</v>
+        <v>694.05</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>171.66 - 172.24 DR DEMAND</t>
+          <t>686.2 - 687.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>156.83 - 164.57 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2273,17 +2273,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>WOCKPHARMA</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Wockhardt Ltd.</t>
+          <t>FSN E-Commerce Ventures Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2292,31 +2292,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1877.2</v>
+        <v>321.9</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1833.3 - 1846.2 DR DEMAND</t>
+          <t>316.0 - 317.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1154.4 - 1292.0 DR DEMAND</t>
+          <t>232.05 - 235.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2353,12 +2353,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>SUMICHEM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Zydus Wellness Ltd.</t>
+          <t>Sumitomo Chemical India Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2372,11 +2372,11 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>492</v>
+        <v>370.5</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>482.0 - 483.8 DR DEMAND</t>
+          <t>361.73 - 363.57 DR DEMAND</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>297.16 - 310.71 DR DEMAND</t>
+          <t>649.43 - 663.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2433,17 +2433,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Adani Green Energy Ltd.</t>
+          <t>Tata Steel Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2452,26 +2452,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1258.5</v>
+        <v>172.33</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1223.6 - 1235.0 DR DEMAND</t>
+          <t>171.66 - 172.24 DR DEMAND</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>765.0 - 814.2 DR DEMAND</t>
+          <t>156.83 - 164.57 DR DEMAND</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2513,17 +2513,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Enterprise Ltd.</t>
+          <t>Adani Green Energy Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2532,26 +2532,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>7600</v>
+        <v>1250</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>7501.27 - 7544.22 DR DEMAND</t>
+          <t>1223.6 - 1235.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>765.0 - 814.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2593,17 +2593,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Ltd.</t>
+          <t>Apollo Hospitals Enterprise Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2612,11 +2612,11 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1578.8</v>
+        <v>7604.5</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1536.8 - 1554.7 DR DEMAND</t>
+          <t>7501.27 - 7544.22 DR DEMAND</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1070</v>
+        <v>1052.5</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2753,17 +2753,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IIFL</t>
+          <t>CENTRALBK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IIFL Finance Ltd.</t>
+          <t>Central Bank of India</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2772,11 +2772,11 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>584.7</v>
+        <v>30.01</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>566.3 - 579.15 DR DEMAND</t>
+          <t>29.32 - 29.62 DR DEMAND</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>35.83 - 36.93 RD SUPPLY</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2833,17 +2833,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>J&amp;KBANK</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir Bank Ltd.</t>
+          <t>Eternal Ltd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2852,28 +2852,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>135.5</v>
+        <v>304.45</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>133.7 - 134.33 DR DEMAND</t>
+          <t>300.05 - 302.45 DR DEMAND</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>194.8 - 201.7 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>108.0 - 110.01 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>7.0 A</t>
-        </is>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -2886,12 +2886,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2913,17 +2913,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PCBL</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PCBL Chemical Ltd.</t>
+          <t>Hindalco Industries Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2932,11 +2932,11 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>293.1</v>
+        <v>885.6</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>290.94 - 292.91 DR DEMAND</t>
+          <t>857.15 - 869.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>223.38 - 238.62 DR DEMAND</t>
+          <t>766.15 - 804.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2993,17 +2993,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BALRAMCHIN</t>
+          <t>J&amp;KBANK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Ltd.</t>
+          <t>Jammu &amp; Kashmir Bank Ltd.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3012,41 +3012,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>680.95</v>
+        <v>135.08</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>675.5 - 678.15 DR DEMAND</t>
+          <t>133.7 - 134.33 DR DEMAND</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>415.9 - 440.91 DR DEMAND</t>
+          <t>108.0 - 110.01 DR DEMAND</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3073,17 +3073,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>CEMPRO</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tata Consumer Products Ltd.</t>
+          <t>Cemindia Projects Ltd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3092,26 +3092,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>970.65</v>
+        <v>1132.4</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>960.9 - 963.1 DR DEMAND</t>
+          <t>1116.5 - 1122.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>869.05 - 898.68 DR DEMAND</t>
+          <t>474.17 - 485.07 DR DEMAND</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3121,12 +3121,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3153,17 +3153,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>FORCEMOT</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Varun Beverages Ltd.</t>
+          <t>Force Motors Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3172,26 +3172,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>408.4</v>
+        <v>16768</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>439.3 - 443.3 RD SUPPLY</t>
+          <t>16520.0 - 16650.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>396.2 - 400.45 DR DEMAND</t>
+          <t>24271.95 - 26374.97 RD SUPPLY</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3233,17 +3233,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ZFCVINDIA</t>
+          <t>KALYANKJIL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ZF Commercial Vehicle Control Systems India Ltd.</t>
+          <t>Kalyan Jewellers India Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3252,26 +3252,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2096.3</v>
+        <v>530.4</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2341.0 - 2352.9 RD SUPPLY</t>
+          <t>522.5 - 528.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2046.79 - 2067.08 DR DEMAND</t>
+          <t>760.91 - 789.86 RD SUPPLY</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3291,12 +3291,12 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3313,17 +3313,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>KPIL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Abbott India Ltd.</t>
+          <t>Kalpataru Projects International Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3332,26 +3332,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>25680</v>
+        <v>1302.8</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25475.0 - 25580.0 DR DEMAND</t>
+          <t>1258.2 - 1265.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>24406.02 - 25223.54 DR DEMAND</t>
+          <t>1258.2 - 1289.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3393,17 +3393,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FORCEMOT</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Force Motors Ltd.</t>
+          <t>Patanjali Foods Ltd.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3412,11 +3412,11 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>16885</v>
+        <v>354.95</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>16520.0 - 16650.0 DR DEMAND</t>
+          <t>350.0 - 354.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>24271.95 - 26374.97 RD SUPPLY</t>
+          <t>598.95 - 605.96 RD SUPPLY</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3473,12 +3473,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HDFC Asset Management Company Ltd.</t>
+          <t>Angel One Ltd.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3492,26 +3492,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2311.4</v>
+        <v>291.25</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2276.2 - 2296.9 DR DEMAND</t>
+          <t>286.72 - 290.61 DR DEMAND</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1711.28 - 1742.62 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3553,17 +3553,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KPIL</t>
+          <t>CHALET</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kalpataru Projects International Ltd.</t>
+          <t>Chalet Hotels Ltd.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3572,26 +3572,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1301.1</v>
+        <v>819.2</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1258.2 - 1265.5 DR DEMAND</t>
+          <t>803.05 - 809.65 DR DEMAND</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1258.2 - 1289.0 DR DEMAND</t>
+          <t>902.92 - 938.88 RD SUPPLY</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3633,17 +3633,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MEDANTA</t>
+          <t>COROMANDEL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Global Health Ltd.</t>
+          <t>Coromandel International Ltd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3652,26 +3652,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1232.4</v>
+        <v>1776.6</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1205.67 - 1209.97 DR DEMAND</t>
+          <t>1963.9 - 1975.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1480.9 - 1544.0 RD SUPPLY</t>
+          <t>1704.84 - 1751.89 DR DEMAND</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3691,12 +3691,12 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3713,17 +3713,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PAGEIND</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Page Industries Ltd.</t>
+          <t>GAIL (India) Ltd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3732,28 +3732,28 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>34870</v>
+        <v>168.49</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>34000.0 - 34275.0 DR DEMAND</t>
+          <t>164.53 - 165.61 DR DEMAND</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>4.5 C</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>133.97 - 137.31 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3793,12 +3793,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Patanjali Foods Ltd.</t>
+          <t>Godrej Consumer Products Ltd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3812,26 +3812,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>357</v>
+        <v>860.2</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>350.0 - 354.8 DR DEMAND</t>
+          <t>840.5 - 848.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>598.95 - 605.96 RD SUPPLY</t>
+          <t>1066.21 - 1111.86 RD SUPPLY</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3873,17 +3873,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SCHAEFFLER</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Schaeffler India Ltd.</t>
+          <t>Grasim Industries Ltd.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3892,21 +3892,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3554.6</v>
+        <v>2894.4</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>4217.6 - 4260.0 RD SUPPLY</t>
+          <t>2853.5 - 2856.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>3489.69 - 3548.8 DR DEMAND</t>
+          <t>2494.13 - 2528.69 DR DEMAND</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3953,17 +3953,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>JKCEMENT</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Angel One Ltd.</t>
+          <t>J.K. Cement Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3972,11 +3972,11 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>293.2</v>
+        <v>4858.5</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>288.1 - 292.0 DR DEMAND</t>
+          <t>4810.5 - 4824.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>4193.16 - 4362.57 DR DEMAND</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4033,17 +4033,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Godrej Consumer Products Ltd.</t>
+          <t>Kfin Technologies Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4052,11 +4052,11 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>859</v>
+        <v>842.4</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>840.5 - 848.0 DR DEMAND</t>
+          <t>815.7 - 832.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1066.21 - 1111.86 RD SUPPLY</t>
+          <t>1329.97 - 1360.84 RD SUPPLY</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4113,17 +4113,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Grasim Industries Ltd.</t>
+          <t>Laurus Labs Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4132,11 +4132,11 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2889.1</v>
+        <v>2002.5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2853.5 - 2856.8 DR DEMAND</t>
+          <t>1988.9 - 1997.9 DR DEMAND</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -4146,17 +4146,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2494.13 - 2528.69 DR DEMAND</t>
+          <t>510.72 - 525.52 DR DEMAND</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4193,17 +4193,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>JINDALSAW</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Jindal Saw Ltd.</t>
+          <t>Pidilite Industries Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4212,11 +4212,11 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>270.4</v>
+        <v>1481.2</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>260.6 - 270.05 DR DEMAND</t>
+          <t>1462.0 - 1477.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>310.0 - 320.0 RD SUPPLY</t>
+          <t>1687.7 - 1707.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4273,17 +4273,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kfin Technologies Ltd.</t>
+          <t>UNO Minda Ltd.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4292,11 +4292,11 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>848.8</v>
+        <v>1068.1</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>826.8 - 836.62 DR DEMAND</t>
+          <t>1031.3 - 1057.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1329.97 - 1360.84 RD SUPPLY</t>
+          <t>1022.67 - 1037.63 DR DEMAND</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4353,17 +4353,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Laurus Labs Ltd.</t>
+          <t>APL Apollo Tubes Ltd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4372,31 +4372,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2012.5</v>
+        <v>2052.4</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1988.9 - 1997.9 DR DEMAND</t>
+          <t>2026.2 - 2040.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>510.72 - 525.52 DR DEMAND</t>
+          <t>1683.51 - 1712.3 DR DEMAND</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4433,17 +4433,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NIVABUPA</t>
+          <t>AWL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Niva Bupa Health Insurance Company Ltd.</t>
+          <t>AWL Agri Business Ltd.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4452,16 +4452,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>73.53</v>
+        <v>178.51</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>72.15 - 72.98 DR DEMAND</t>
+          <t>174.69 - 176.18 DR DEMAND</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4513,17 +4513,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pidilite Industries Ltd.</t>
+          <t>CESC Ltd.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4532,26 +4532,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1484.9</v>
+        <v>129.96</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1462.0 - 1477.7 DR DEMAND</t>
+          <t>128.31 - 128.73 DR DEMAND</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1687.7 - 1707.5 RD SUPPLY</t>
+          <t>111.02 - 121.56 DR DEMAND</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4593,17 +4593,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Torrent Power Ltd.</t>
+          <t>GE Vernova T&amp;D India Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4612,26 +4612,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1181.9</v>
+        <v>3740</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1165.0 - 1174.4 DR DEMAND</t>
+          <t>3640.99 - 3715.9 DR DEMAND</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1742.27 - 1817.8 RD SUPPLY</t>
+          <t>1267.83 - 1314.33 DR DEMAND</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4673,17 +4673,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>UNO Minda Ltd.</t>
+          <t>NHPC Ltd.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4692,26 +4692,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1064.9</v>
+        <v>72.38</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1031.3 - 1057.7 DR DEMAND</t>
+          <t>70.56 - 70.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1022.67 - 1037.63 DR DEMAND</t>
+          <t>67.83 - 70.98 DR DEMAND</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4753,17 +4753,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Eternal Ltd.</t>
+          <t>Shree Cement Ltd.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4772,11 +4772,11 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>312.35</v>
+        <v>22330</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>306.2 - 310.25 DR DEMAND</t>
+          <t>21550.0 - 21900.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4786,22 +4786,22 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>194.8 - 201.7 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4833,17 +4833,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>SOBHA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Hindustan Zinc Ltd.</t>
+          <t>Sobha Ltd.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4852,28 +4852,28 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>525</v>
+        <v>1196.1</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>516.85 - 518.05 DR DEMAND</t>
+          <t>1248.4 - 1251.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
+          <t>7.5 A</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>1125.39 - 1182.55 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
           <t>4.0 C</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>475.32 - 493.14 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>7.0 A</t>
-        </is>
-      </c>
       <c r="J56" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4913,17 +4913,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>TENNIND</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Indegene Ltd.</t>
+          <t>Tenneco Clean Air India Ltd.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4932,11 +4932,11 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>580.5</v>
+        <v>450.3</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>567.55 - 579.9 DR DEMAND</t>
+          <t>438.05 - 443.95 DR DEMAND</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4946,17 +4946,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>412.19 - 432.7 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4993,17 +4993,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TENNIND</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tenneco Clean Air India Ltd.</t>
+          <t>Varun Beverages Ltd.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5012,26 +5012,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>447.85</v>
+        <v>400.8</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>438.05 - 443.95 DR DEMAND</t>
+          <t>439.3 - 443.3 RD SUPPLY</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
+          <t>2.5 C</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>396.2 - 400.45 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
           <t>4.0 C</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5073,12 +5073,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>JSWDULUX</t>
+          <t>3MINDIA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JSW Dulux Ltd.</t>
+          <t>3M India Ltd.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5092,21 +5092,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2994.8</v>
+        <v>29770</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>3229.9 - 3249.0 RD SUPPLY</t>
+          <t>34890.0 - 35095.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2862.0 - 2938.8 DR DEMAND</t>
+          <t>28319.86 - 29690.02 DR DEMAND</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5153,17 +5153,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>POONAWALLA</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Poonawalla Fincorp Ltd.</t>
+          <t>Abbott India Ltd.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5172,26 +5172,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>437.3</v>
+        <v>25360</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>427.1 - 433.4 DR DEMAND</t>
+          <t>26295.0 - 26550.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>370.05 - 382.85 DR DEMAND</t>
+          <t>24406.02 - 25223.54 DR DEMAND</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -5233,17 +5233,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Shree Cement Ltd.</t>
+          <t>Bharat Forge Ltd.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5252,11 +5252,11 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>22310</v>
+        <v>1741</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>21550.0 - 21900.0 DR DEMAND</t>
+          <t>1718.88 - 1734.14 DR DEMAND</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1605.33 - 1669.53 DR DEMAND</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5313,17 +5313,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>PAGEIND</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries Ltd.</t>
+          <t>Page Industries Ltd.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5332,11 +5332,11 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1745.1</v>
+        <v>34425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1725.5 - 1736.0 DR DEMAND</t>
+          <t>34000.0 - 34275.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1569.37 - 1580.86 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5393,17 +5393,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TRAVELFOOD</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Travel Food Services Ltd.</t>
+          <t>One 97 Communications Ltd.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5412,36 +5412,36 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1166.2</v>
+        <v>1661.4</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1158.76 - 1165.7 DR DEMAND</t>
+          <t>1624.4 - 1635.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>651.5 - 700.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -5473,17 +5473,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3MINDIA</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>3M India Ltd.</t>
+          <t>Sun Pharmaceutical Industries Ltd.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5492,26 +5492,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>30240</v>
+        <v>1758</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>34890.0 - 35095.0 RD SUPPLY</t>
+          <t>1725.5 - 1736.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>28319.86 - 29690.02 DR DEMAND</t>
+          <t>1569.37 - 1580.86 DR DEMAND</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5553,12 +5553,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>WOCKPHARMA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cipla Ltd.</t>
+          <t>Wockhardt Ltd.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5572,28 +5572,28 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1314</v>
+        <v>1855.5</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1302.7 - 1311.6 DR DEMAND</t>
+          <t>1833.3 - 1846.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
+          <t>4.5 C</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>1154.4 - 1292.0 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
           <t>4.0 C</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J65" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5633,17 +5633,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Larsen &amp; Toubro Ltd.</t>
+          <t>Cipla Ltd.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5652,26 +5652,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3636</v>
+        <v>1330.9</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>3607.0 - 3625.1 DR DEMAND</t>
+          <t>1302.7 - 1311.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>3256.29 - 3470.21 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5713,17 +5713,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>IKS</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Mankind Pharma Ltd.</t>
+          <t>Inventurus Knowledge Solutions Ltd.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5732,11 +5732,11 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2285.5</v>
+        <v>1648</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2242.1 - 2246.0 DR DEMAND</t>
+          <t>1620.3 - 1632.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1909.7 - 2005.8 DR DEMAND</t>
+          <t>1858.0 - 1933.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5793,17 +5793,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TATATECH</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tata Technologies Ltd.</t>
+          <t>Larsen &amp; Toubro Ltd.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5812,26 +5812,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>692.1</v>
+        <v>3638.3</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>683.7 - 686.75 DR DEMAND</t>
+          <t>3607.0 - 3625.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>835.0 - 891.0 RD SUPPLY</t>
+          <t>3256.29 - 3470.21 DR DEMAND</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5873,17 +5873,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Ltd.</t>
+          <t>Mankind Pharma Ltd.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5892,36 +5892,36 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1117.3</v>
+        <v>2275.6</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1094.12 - 1098.81 DR DEMAND</t>
+          <t>2242.1 - 2246.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>855.18 - 875.51 DR DEMAND</t>
+          <t>1909.7 - 2005.8 DR DEMAND</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>146.74</v>
+        <v>146.03</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6033,17 +6033,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>IOB</t>
+          <t>PIRAMALFIN</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Indian Overseas Bank</t>
+          <t>Piramal Finance Ltd.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6052,11 +6052,11 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>30.39</v>
+        <v>1952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>30.07 - 30.38 DR DEMAND</t>
+          <t>1901.22 - 1939.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -6113,17 +6113,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NAVA</t>
+          <t>TATATECH</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nava Ltd.</t>
+          <t>Tata Technologies Ltd.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6132,26 +6132,26 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>522.4</v>
+        <v>689.35</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>507.31 - 509.34 DR DEMAND</t>
+          <t>683.7 - 686.75 DR DEMAND</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>497.01 - 517.17 DR DEMAND</t>
+          <t>835.0 - 891.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>3.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -6193,17 +6193,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FIRSTCRY</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Brainbees Solutions Ltd.</t>
+          <t>IndusInd Bank Ltd.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6212,26 +6212,26 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>170.86</v>
+        <v>850.5</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>168.15 - 170.82 DR DEMAND</t>
+          <t>845.7 - 851.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>605.02 - 647.95 DR DEMAND</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -6251,39 +6251,39 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>4.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PFIZER</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Pfizer Ltd.</t>
+          <t>Jindal Steel Ltd.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6292,26 +6292,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3754.7</v>
+        <v>1037</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>3731.0 - 3750.0 DR DEMAND</t>
+          <t>1000.91 - 1008.99 DR DEMAND</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1008.29 - 1043.63 DR DEMAND</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6331,39 +6331,39 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>4.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BEML</t>
+          <t>KPRMILL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BEML Ltd.</t>
+          <t>K.P.R. Mill Ltd.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6372,26 +6372,26 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1888.3</v>
+        <v>1023.7</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1875.6 - 1894.7 DR DEMAND</t>
+          <t>885.21 - 891.84 DR DEMAND</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1159.43 - 1211.03 DR DEMAND</t>
+          <t>1015.0 - 1049.8 DR DEMAND</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -6433,17 +6433,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CIEINDIA</t>
+          <t>IIFL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CIE Automotive India Ltd.</t>
+          <t>IIFL Finance Ltd.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6452,26 +6452,26 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>369.55</v>
+        <v>567.9</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>368.3 - 370.1 DR DEMAND</t>
+          <t>566.3 - 579.15 DR DEMAND</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>479.0 - 504.0 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -6513,17 +6513,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>IndusInd Bank Ltd.</t>
+          <t>PCBL Chemical Ltd.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6532,26 +6532,26 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>849.55</v>
+        <v>292.5</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>845.7 - 851.0 DR DEMAND</t>
+          <t>290.94 - 292.91 DR DEMAND</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>605.02 - 647.95 DR DEMAND</t>
+          <t>223.38 - 238.62 DR DEMAND</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -6593,45 +6593,45 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cummins India Ltd.</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>EQUILIBRIUM</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4440</v>
+        <v>970</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>4357.85 - 4480.83 DR DEMAND</t>
+          <t>981.9 - 983.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>4357.85 - 4463.08 DR DEMAND</t>
+          <t>933.9 - 964.4 DR DEMAND</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6651,12 +6651,12 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -6666,19 +6666,19 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CONFLICT</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>NCC</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NCC Ltd.</t>
+          <t>CG Power and Industrial Solutions Ltd.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6692,26 +6692,26 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>123.2</v>
+        <v>817.1</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>123.08 - 123.5 DR DEMAND</t>
+          <t>794.1 - 800.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>163.99 - 169.16 RD SUPPLY</t>
+          <t>814.85 - 863.4 DR DEMAND</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -6772,16 +6772,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>464.15</v>
+        <v>456.25</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>462.0 - 471.9 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -6833,55 +6833,55 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Bharat Heavy Electricals Ltd.</t>
+          <t>SBI Cards and Payment Services Ltd.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>EQUILIBRIUM</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>410.2</v>
+        <v>566.3</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>406.0 - 410.6 DR DEMAND</t>
+          <t>573.2 - 578.75 RD SUPPLY</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>204.46 - 207.34 DR DEMAND</t>
+          <t>565.45 - 593.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -6906,52 +6906,52 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CONFLICT</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>SCHAEFFLER</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>State Bank of India</t>
+          <t>Schaeffler India Ltd.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>963</v>
+        <v>3527.3</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>981.9 - 983.8 RD SUPPLY</t>
+          <t>4217.6 - 4260.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>933.9 - 964.4 DR DEMAND</t>
+          <t>3489.69 - 3548.8 DR DEMAND</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -6971,12 +6971,12 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -6986,19 +6986,19 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>CONFLICT</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>DATAPATTNS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CG Power and Industrial Solutions Ltd.</t>
+          <t>Data Patterns (India) Ltd.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -7012,26 +7012,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>821</v>
+        <v>3901.6</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>794.1 - 800.0 DR DEMAND</t>
+          <t>3890.52 - 3981.32 DR DEMAND</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>814.85 - 863.4 DR DEMAND</t>
+          <t>1344.18 - 1430.33 DR DEMAND</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -7073,12 +7073,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>EIDPARRY</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Colgate Palmolive (India) Ltd.</t>
+          <t>E.I.D. Parry (India) Ltd.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7092,26 +7092,26 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1720</v>
+        <v>647.4</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1716.1 - 1735.0 DR DEMAND</t>
+          <t>702.8 - 706.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2228.23 - 2274.78 RD SUPPLY</t>
+          <t>639.0 - 660.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7153,17 +7153,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DATAPATTNS</t>
+          <t>ENDURANCE</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Data Patterns (India) Ltd.</t>
+          <t>Endurance Technologies Ltd.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7172,11 +7172,11 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3916.9</v>
+        <v>2329.7</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>3890.52 - 3981.32 DR DEMAND</t>
+          <t>2322.64 - 2344.55 DR DEMAND</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1344.18 - 1430.33 DR DEMAND</t>
+          <t>1661.59 - 1735.99 DR DEMAND</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -7233,17 +7233,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EIDPARRY</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>E.I.D. Parry (India) Ltd.</t>
+          <t>Jio Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7252,26 +7252,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>657.1</v>
+        <v>210.8</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>702.8 - 706.5 RD SUPPLY</t>
+          <t>210.52 - 212.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
+          <t>4.5 C</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>259.39 - 267.57 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
           <t>7.0 A</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>639.0 - 660.0 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>4.5 C</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -7313,17 +7313,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ENDURANCE</t>
+          <t>MMTC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Endurance Technologies Ltd.</t>
+          <t>MMTC Ltd.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7332,21 +7332,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2340.6</v>
+        <v>52.06</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2322.64 - 2344.55 DR DEMAND</t>
+          <t>50.1 - 52.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1661.59 - 1735.99 DR DEMAND</t>
+          <t>50.1 - 52.1 DR DEMAND</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -7393,40 +7393,40 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ESCORTS</t>
+          <t>NBCC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Escorts Kubota Ltd.</t>
+          <t>NBCC (India) Ltd.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2720.4</v>
+        <v>70.5</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2751.0 - 2761.2 RD SUPPLY</t>
+          <t>89.63 - 90.03 RD SUPPLY</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2679.78 - 2709.64 DR DEMAND</t>
+          <t>69.86 - 71.89 DR DEMAND</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -7466,24 +7466,24 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>CONFLICT</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Jio Financial Services Ltd.</t>
+          <t>Hindustan Zinc Ltd.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -7492,21 +7492,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>211.39</v>
+        <v>518</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>210.52 - 212.0 DR DEMAND</t>
+          <t>516.85 - 518.05 DR DEMAND</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>259.39 - 267.57 RD SUPPLY</t>
+          <t>475.32 - 493.14 DR DEMAND</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -7553,17 +7553,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>KPRMILL</t>
+          <t>HUDCO</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>K.P.R. Mill Ltd.</t>
+          <t>Housing &amp; Urban Development Corporation Ltd.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -7572,11 +7572,11 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1029.8</v>
+        <v>151.77</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>885.21 - 891.84 DR DEMAND</t>
+          <t>199.29 - 202.09 RD SUPPLY</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -7586,12 +7586,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1015.0 - 1049.8 DR DEMAND</t>
+          <t>151.47 - 157.32 DR DEMAND</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -7611,12 +7611,12 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -7633,17 +7633,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>IDBI</t>
+          <t>TECHNOE</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>IDBI Bank Ltd.</t>
+          <t>Techno Electric &amp; Engineering Company Ltd.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>PVTBANK</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -7652,26 +7652,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>80.44</v>
+        <v>869.4</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>80.17 - 80.53 DR DEMAND</t>
+          <t>1006.2 - 1016.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>863.77 - 967.52 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
           <t>4.0 C</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>91.3 - 96.25 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>5.0 C</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -7713,17 +7713,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>NBCC</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>NBCC (India) Ltd.</t>
+          <t>KEI Industries Ltd.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -7732,26 +7732,26 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>71.45</v>
+        <v>3873</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>89.63 - 90.03 RD SUPPLY</t>
+          <t>4722.5 - 4760.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>69.86 - 71.89 DR DEMAND</t>
+          <t>3724.29 - 3949.9 DR DEMAND</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -7761,12 +7761,12 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -7793,17 +7793,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TECHNOE</t>
+          <t>POONAWALLA</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Techno Electric &amp; Engineering Company Ltd.</t>
+          <t>Poonawalla Fincorp Ltd.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -7812,26 +7812,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>885.7</v>
+        <v>432.45</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1006.2 - 1016.2 RD SUPPLY</t>
+          <t>427.1 - 433.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>863.77 - 967.52 DR DEMAND</t>
+          <t>370.05 - 382.85 DR DEMAND</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -7873,17 +7873,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AFFLE</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Affle 3i Ltd.</t>
+          <t>AU Small Finance Bank Ltd.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -7892,11 +7892,11 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1395.3</v>
+        <v>953.9</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1389.9 - 1406.7 DR DEMAND</t>
+          <t>952.48 - 957.77 DR DEMAND</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7906,12 +7906,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1331.25 - 1400.25 DR DEMAND</t>
+          <t>830.84 - 841.88 DR DEMAND</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7931,12 +7931,12 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -7953,17 +7953,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ESCORTS</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Asian Paints Ltd.</t>
+          <t>Escorts Kubota Ltd.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -7972,26 +7972,26 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2319.4</v>
+        <v>2636.9</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2317.8 - 2331.0 DR DEMAND</t>
+          <t>2550.1 - 2667.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2083.96 - 2137.91 DR DEMAND</t>
+          <t>3268.02 - 3369.87 RD SUPPLY</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -8033,17 +8033,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Amber Enterprises India Ltd.</t>
+          <t>Indraprastha Gas Ltd.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8052,26 +8052,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6340</v>
+        <v>140.01</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>6151.0 - 6170.5 DR DEMAND</t>
+          <t>137.77 - 140.53 DR DEMAND</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>6120.0 - 6549.0 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -8113,17 +8113,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AU Small Finance Bank Ltd.</t>
+          <t>Mazagoan Dock Shipbuilders Ltd.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8132,28 +8132,28 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>954</v>
+        <v>1922.3</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>952.48 - 957.77 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>1900.61 - 2111.67 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
           <t>3.0 C</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>830.84 - 841.88 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>8.0 A</t>
-        </is>
-      </c>
       <c r="J97" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -8193,17 +8193,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>IKS</t>
+          <t>NAVA</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Inventurus Knowledge Solutions Ltd.</t>
+          <t>Nava Ltd.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8212,26 +8212,26 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1631.7</v>
+        <v>499.4</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>1620.3 - 1632.0 DR DEMAND</t>
+          <t>625.16 - 632.05 RD SUPPLY</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1858.0 - 1933.0 RD SUPPLY</t>
+          <t>497.01 - 517.17 DR DEMAND</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -8273,30 +8273,30 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Kajaria Ceramics Ltd.</t>
+          <t>Torrent Power Ltd.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1189.8</v>
+        <v>1204</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1175.7 - 1183.6 DR DEMAND</t>
+          <t>1165.0 - 1174.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -8306,22 +8306,22 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1181.73 - 1240.58 RD SUPPLY</t>
+          <t>1186.52 - 1241.27 DR DEMAND</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -8346,24 +8346,24 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>CONFLICT</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>ZEEL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Mazagoan Dock Shipbuilders Ltd.</t>
+          <t>Zee Entertainment Enterprises Ltd.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8372,26 +8372,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1997.5</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>80.0 - 83.66 RD SUPPLY</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1900.61 - 2111.67 DR DEMAND</t>
+          <t>66.41 - 70.46 DR DEMAND</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -8433,17 +8433,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>UTIAMC</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GAIL (India) Ltd.</t>
+          <t>UTI Asset Management Company Ltd.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -8452,28 +8452,28 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>167.2</v>
+        <v>851.15</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>166.44 - 167.5 DR DEMAND</t>
+          <t>1039.08 - 1043.74 RD SUPPLY</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
+          <t>4.0 C</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>841.38 - 874.76 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
           <t>2.5 C</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>133.97 - 137.31 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>6.0 B</t>
-        </is>
-      </c>
       <c r="J101" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -8481,12 +8481,12 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8513,17 +8513,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>HUDCO</t>
+          <t>AFFLE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Housing &amp; Urban Development Corporation Ltd.</t>
+          <t>Affle 3i Ltd.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -8532,26 +8532,26 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>154.34</v>
+        <v>1362.8</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>199.29 - 202.09 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>151.47 - 157.32 DR DEMAND</t>
+          <t>1331.25 - 1400.25 DR DEMAND</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>4.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -8593,40 +8593,40 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>UTIAMC</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>UTI Asset Management Company Ltd.</t>
+          <t>Phoenix Mills Ltd.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>869.8</v>
+        <v>1909.9</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>1039.08 - 1043.74 RD SUPPLY</t>
+          <t>1946.8 - 1954.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>841.38 - 874.76 DR DEMAND</t>
+          <t>1851.05 - 1990.36 RD SUPPLY</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -8651,39 +8651,39 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ITC Ltd.</t>
+          <t>Ipca Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -8692,11 +8692,11 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>262</v>
+        <v>1903.5</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>267.2 - 268.05 RD SUPPLY</t>
+          <t>1913.1 - 1930.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -8706,17 +8706,17 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>400.8 - 406.57 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -8753,17 +8753,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CRISIL</t>
+          <t>ITCHOTELS</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CRISIL Ltd.</t>
+          <t>ITC Hotels Ltd.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -8772,21 +8772,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4586.4</v>
+        <v>161.83</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>4650.6 - 4706.2 RD SUPPLY</t>
+          <t>164.13 - 164.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>3669.91 - 3717.29 DR DEMAND</t>
+          <t>180.5 - 188.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8833,17 +8833,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>AADHARHFC</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Reliance Industries Ltd.</t>
+          <t>Aadhar Housing Finance Ltd.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -8852,16 +8852,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1209</v>
+        <v>459.3</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>1226.0 - 1227.4 RD SUPPLY</t>
+          <t>468.35 - 470.25 RD SUPPLY</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -8913,17 +8913,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Oracle Financial Services Software Ltd.</t>
+          <t>NATCO Pharma Ltd.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -8932,11 +8932,11 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>10263</v>
+        <v>785.15</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>10386.0 - 10535.0 RD SUPPLY</t>
+          <t>800.85 - 809.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8993,17 +8993,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PIRAMALFIN</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Piramal Finance Ltd.</t>
+          <t>Steel Authority of India Ltd.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9012,11 +9012,11 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2019</v>
+        <v>169.75</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2040.9 - 2055.2 RD SUPPLY</t>
+          <t>172.77 - 174.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -9026,12 +9026,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>202.55 - 206.99 RD SUPPLY</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -9073,17 +9073,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Steel Authority of India Ltd.</t>
+          <t>CRISIL Ltd.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9092,11 +9092,11 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>169.5</v>
+        <v>4777.2</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>172.77 - 174.0 RD SUPPLY</t>
+          <t>4470.0 - 4511.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>202.55 - 206.99 RD SUPPLY</t>
+          <t>4821.8 - 4872.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -9153,17 +9153,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>APOLLOTYRE</t>
+          <t>INDGN</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Apollo Tyres Ltd.</t>
+          <t>Indegene Ltd.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9172,36 +9172,36 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>410.05</v>
+        <v>588.1</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>417.65 - 419.45 RD SUPPLY</t>
+          <t>598.3 - 600.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>412.19 - 432.7 DR DEMAND</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -9233,17 +9233,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Coforge Ltd.</t>
+          <t>Sun TV Network Ltd.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9252,26 +9252,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1951</v>
+        <v>600.3</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>1837.2 - 1846.6 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>1985.3 - 2021.2 RD SUPPLY</t>
+          <t>603.75 - 653.93 RD SUPPLY</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -9313,17 +9313,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>JSWCEMENT</t>
+          <t>JAINREC</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>JSW Cement Ltd.</t>
+          <t>Jain Resource Recycling Ltd.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -9332,16 +9332,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>114.75</v>
+        <v>289.6</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>115.77 - 116.4 RD SUPPLY</t>
+          <t>295.15 - 300.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -9393,17 +9393,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Tata Elxsi Ltd.</t>
+          <t>Zydus Lifesciences Ltd.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -9412,26 +9412,26 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3848.6</v>
+        <v>1135</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>3858.0 - 3867.2 RD SUPPLY</t>
+          <t>1140.2 - 1150.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2996.0 - 3088.9 DR DEMAND</t>
+          <t>855.18 - 875.51 DR DEMAND</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -9473,17 +9473,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Hindustan Petroleum Corporation Ltd.</t>
+          <t>Narayana Hrudayalaya Ltd.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -9492,21 +9492,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>347.3</v>
+        <v>1693.2</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>351.0 - 351.75 RD SUPPLY</t>
+          <t>1724.4 - 1746.3 RD SUPPLY</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>263.73 - 269.42 DR DEMAND</t>
+          <t>2170.07 - 2359.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -9553,17 +9553,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ZENSARTECH</t>
+          <t>JSWCEMENT</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Zensar Technolgies Ltd.</t>
+          <t>JSW Cement Ltd.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -9572,31 +9572,31 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>509.35</v>
+        <v>114.69</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>416.15 - 422.4 DR DEMAND</t>
+          <t>115.77 - 116.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>510.15 - 553.1 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -9633,17 +9633,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Supreme Industries Ltd.</t>
+          <t>Kajaria Ceramics Ltd.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -9652,31 +9652,31 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3554.2</v>
+        <v>1159.6</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>3567.7 - 3631.8 RD SUPPLY</t>
+          <t>1055.21 - 1067.25 DR DEMAND</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
+          <t>2.5 C</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>1181.73 - 1240.58 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
           <t>5.0 C</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -9713,17 +9713,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Bank of Baroda</t>
+          <t>Tata Elxsi Ltd.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -9732,36 +9732,36 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>237.38</v>
+        <v>3846.8</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>238.13 - 238.51 RD SUPPLY</t>
+          <t>3858.0 - 3867.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>178.57 - 184.54 DR DEMAND</t>
+          <t>2996.0 - 3088.9 DR DEMAND</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -9776,7 +9776,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>4.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -9793,12 +9793,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>LEMONTREE</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Bata India Ltd.</t>
+          <t>Lemon Tree Hotels Ltd.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -9812,26 +9812,26 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>631.1</v>
+        <v>110.95</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>637.2 - 644.0 RD SUPPLY</t>
+          <t>112.71 - 113.55 RD SUPPLY</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>689.25 - 743.46 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>4.5 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -9873,17 +9873,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>ZENSARTECH</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>DLF Ltd.</t>
+          <t>Zensar Technolgies Ltd.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -9892,26 +9892,26 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>664</v>
+        <v>501.2</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>673.0 - 676.5 RD SUPPLY</t>
+          <t>416.15 - 422.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>483.33 - 497.85 DR DEMAND</t>
+          <t>510.15 - 553.1 RD SUPPLY</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -9936,7 +9936,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -9953,17 +9953,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>COHANCE</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Cohance Lifesciences Ltd.</t>
+          <t>Bank of Baroda</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -9972,31 +9972,31 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>461.8</v>
+        <v>236.42</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>462.35 - 467.2 RD SUPPLY</t>
+          <t>238.13 - 238.51 RD SUPPLY</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>1229.95 - 1328.0 RD SUPPLY</t>
+          <t>178.57 - 184.54 DR DEMAND</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2.5 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -10033,17 +10033,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>BATAINDIA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Ipca Laboratories Ltd.</t>
+          <t>Bata India Ltd.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -10052,41 +10052,41 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1918.9</v>
+        <v>636.5</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>1913.1 - 1930.0 RD SUPPLY</t>
+          <t>637.2 - 644.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>689.25 - 743.46 RD SUPPLY</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -10096,34 +10096,34 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Sun TV Network Ltd.</t>
+          <t>DLF Ltd.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -10132,26 +10132,26 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>627.15</v>
+        <v>663.25</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>608.6 - 613.0 DR DEMAND</t>
+          <t>673.0 - 676.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>603.75 - 653.93 RD SUPPLY</t>
+          <t>483.33 - 497.85 DR DEMAND</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -10176,29 +10176,29 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>COHANCE</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Narayana Hrudayalaya Ltd.</t>
+          <t>Cohance Lifesciences Ltd.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -10212,36 +10212,36 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1725</v>
+        <v>453.85</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>1724.4 - 1746.3 RD SUPPLY</t>
+          <t>462.35 - 467.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2170.07 - 2359.4 RD SUPPLY</t>
+          <t>1229.95 - 1328.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -10256,34 +10256,34 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>2.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>TTML</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Wipro Ltd.</t>
+          <t>Tata Teleservices (Maharashtra) Ltd.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -10292,26 +10292,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>189.17</v>
+        <v>38.01</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>189.0 - 189.81 RD SUPPLY</t>
+          <t>36.64 - 38.25 RD SUPPLY</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>156.79 - 158.5 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>437.8</v>
+        <v>437</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10433,17 +10433,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Phoenix Mills Ltd.</t>
+          <t>Saregama India Ltd</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -10452,36 +10452,36 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1874.4</v>
+        <v>508.9</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>1924.0 - 1935.0 RD SUPPLY</t>
+          <t>506.55 - 518.65 RD SUPPLY</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>1851.05 - 1990.36 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>3.5 / 10 SUPPLY</t>
+          <t>3.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -10505,86 +10505,6 @@
         </is>
       </c>
       <c r="P126" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>SAREGAMA</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Saregama India Ltd</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>CONSUMPTION</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-      <c r="E127" t="n">
-        <v>510.4</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>506.55 - 518.65 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>3.0 C</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>1W UP • 20 EMA BULLISH</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>🔴 2 TESTS (WEAK)</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>NORMAL VOL</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>+0.0 PTS</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr">
-        <is>
-          <t>3.0 / 10 SUPPLY</t>
-        </is>
-      </c>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>SUPPLY TEST</t>
-        </is>
-      </c>
-      <c r="P127" t="inlineStr">
         <is>
           <t>IN</t>
         </is>

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P126"/>
+  <dimension ref="A1:P93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,17 +513,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HOMEFIRST</t>
+          <t>PWL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Home First Finance Company India Ltd.</t>
+          <t>Physicswallah Ltd.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -532,11 +532,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1021.3</v>
+        <v>119.95</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1018.5 - 1029.7 DR DEMAND</t>
+          <t>117.71 - 120.17 DR DEMAND</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>889.54 - 900.59 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -571,12 +571,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>11.0 / 10 SUPER COMBO</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -593,17 +593,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Axis Bank Ltd.</t>
+          <t>Engineers India Ltd.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -612,11 +612,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1212</v>
+        <v>242.5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1175.0 - 1186.5 DR DEMAND</t>
+          <t>241.51 - 244.94 DR DEMAND</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -626,12 +626,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1208.6 - 1229.5 DR DEMAND</t>
+          <t>217.65 - 220.56 DR DEMAND</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -673,17 +673,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cummins India Ltd.</t>
+          <t>Axis Bank Ltd.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -692,26 +692,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4460</v>
+        <v>1217.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4357.85 - 4480.83 DR DEMAND</t>
+          <t>1175.0 - 1186.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4357.85 - 4463.08 DR DEMAND</t>
+          <t>1208.6 - 1229.5 DR DEMAND</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -753,17 +753,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JMFINANCIL</t>
+          <t>BALRAMCHIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JM Financial Ltd.</t>
+          <t>Balrampur Chini Mills Ltd.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>110.97</v>
+        <v>639.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>129.02 - 129.65 RD SUPPLY</t>
+          <t>638.0 - 649.05 DR DEMAND</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>110.31 - 111.89 DR DEMAND</t>
+          <t>415.9 - 440.91 DR DEMAND</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -833,17 +833,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JSW Energy Ltd.</t>
+          <t>Hindustan Unilever Ltd.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -852,26 +852,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>463.9</v>
+        <v>1814.7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>457.5 - 460.5 DR DEMAND</t>
+          <t>1814.4 - 1820.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>415.69 - 460.71 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -896,34 +896,34 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>11.5 / 10 SUPER COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>BUY READY</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ITC Ltd.</t>
+          <t>KEI Industries Ltd.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -932,21 +932,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>258.9</v>
+        <v>3725</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>253.15 - 255.0 DR DEMAND</t>
+          <t>4722.5 - 4760.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>400.8 - 406.57 RD SUPPLY</t>
+          <t>3724.29 - 3949.9 DR DEMAND</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -976,34 +976,34 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>11.0 / 10 SUPER COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>BUY READY</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M&amp;MFIN</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Financial Services Ltd.</t>
+          <t>Bandhan Bank Ltd.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1012,26 +1012,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>287.6</v>
+        <v>149.89</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>282.35 - 284.84 DR DEMAND</t>
+          <t>146.33 - 147.85 DR DEMAND</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>178.25 - 193.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>11.0 / 10 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1073,17 +1073,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>ELECON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nestle India Ltd.</t>
+          <t>Elecon Engineering Co. Ltd.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1092,26 +1092,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1189.9</v>
+        <v>416.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1384.5 - 1397.0 RD SUPPLY</t>
+          <t>406.76 - 408.41 DR DEMAND</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1153.85 - 1169.18 DR DEMAND</t>
+          <t>630.11 - 667.79 RD SUPPLY</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>11.0 / 10 SUPER COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1153,17 +1153,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ICICI Bank Ltd.</t>
+          <t>Jindal Steel Ltd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1172,36 +1172,36 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1398.5</v>
+        <v>1015.9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1375.1 - 1379.0 DR DEMAND</t>
+          <t>1000.91 - 1008.99 DR DEMAND</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1291.0 - 1316.0 DR DEMAND</t>
+          <t>1008.29 - 1043.63 DR DEMAND</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>10.5 / 10 HIGH COMBO</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1233,17 +1233,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RITES Ltd.</t>
+          <t>Indraprastha Gas Ltd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1252,26 +1252,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>196.09</v>
+        <v>141.71</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>191.25 - 192.31 DR DEMAND</t>
+          <t>137.77 - 140.53 DR DEMAND</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>214.72 - 226.44 RD SUPPLY</t>
+          <t>140.28 - 144.12 DR DEMAND</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1281,12 +1281,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>10.5 / 10 HIGH COMBO</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1313,17 +1313,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Amber Enterprises India Ltd.</t>
+          <t>Life Insurance Corporation of India</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1332,11 +1332,11 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6180</v>
+        <v>381.5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6151.0 - 6170.5 DR DEMAND</t>
+          <t>378.2 - 379.25 DR DEMAND</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6120.0 - 6549.0 DR DEMAND</t>
+          <t>344.89 - 357.04 DR DEMAND</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hindustan Aeronautics Ltd.</t>
+          <t>Multi Commodity Exchange of India Ltd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1412,31 +1412,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4875</v>
+        <v>3020.3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4765.2 - 4790.0 DR DEMAND</t>
+          <t>2952.86 - 2965.73 DR DEMAND</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3004.72 - 3046.3 DR DEMAND</t>
+          <t>2559.23 - 2685.62 DR DEMAND</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1473,17 +1473,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BEML</t>
+          <t>APARINDS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BEML Ltd.</t>
+          <t>Apar Industries Ltd.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1492,36 +1492,36 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1907.7</v>
+        <v>14379</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1875.6 - 1894.7 DR DEMAND</t>
+          <t>13354.64 - 13396.49 DR DEMAND</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1159.43 - 1211.03 DR DEMAND</t>
+          <t>13236.05 - 14298.36 DR DEMAND</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1553,12 +1553,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BALRAMCHIN</t>
+          <t>BAYERCROP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Ltd.</t>
+          <t>Bayer Cropscience Ltd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1572,31 +1572,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>654.75</v>
+        <v>3383.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>638.0 - 649.05 DR DEMAND</t>
+          <t>3366.3 - 3381.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>415.9 - 440.91 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1633,17 +1633,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gland Pharma Ltd.</t>
+          <t>CG Power and Industrial Solutions Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1652,11 +1652,11 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2850.4</v>
+        <v>813.35</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2792.4 - 2826.6 DR DEMAND</t>
+          <t>794.1 - 800.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1666,17 +1666,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1256.51 - 1376.68 DR DEMAND</t>
+          <t>534.85 - 567.71 DR DEMAND</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1713,17 +1713,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hindustan Unilever Ltd.</t>
+          <t>Gland Pharma Ltd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1732,11 +1732,11 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1828.3</v>
+        <v>2826.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1814.4 - 1820.7 DR DEMAND</t>
+          <t>2792.4 - 2826.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1256.51 - 1376.68 DR DEMAND</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1793,12 +1793,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LINDEINDIA</t>
+          <t>HSCL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Linde India Ltd.</t>
+          <t>Himadri Speciality Chemical Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1812,11 +1812,11 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5900.5</v>
+        <v>492</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>5816.14 - 5836.6 DR DEMAND</t>
+          <t>482.0 - 488.34 DR DEMAND</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7487.35 - 7842.09 RD SUPPLY</t>
+          <t>417.93 - 437.01 DR DEMAND</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1873,17 +1873,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>KPIL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Maruti Suzuki India Ltd.</t>
+          <t>Kalpataru Projects International Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1892,26 +1892,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>11170</v>
+        <v>1291.6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>11136.0 - 11150.0 DR DEMAND</t>
+          <t>1258.2 - 1265.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>6.5 B</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1258.2 - 1289.0 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>7.0 A</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>14709.27 - 15305.29 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>8.5 A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1953,17 +1953,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>United Spirits Ltd.</t>
+          <t>Maruti Suzuki India Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1972,11 +1972,11 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1284.5</v>
+        <v>11230</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1256.42 - 1261.78 DR DEMAND</t>
+          <t>11136.0 - 11150.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1595.35 - 1664.73 RD SUPPLY</t>
+          <t>14709.27 - 15305.29 RD SUPPLY</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2033,17 +2033,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CARTRADE</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cartrade Tech Ltd.</t>
+          <t>PCBL Chemical Ltd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2052,31 +2052,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2840</v>
+        <v>274.85</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2739.8 - 2806.0 DR DEMAND</t>
+          <t>271.9 - 273.93 DR DEMAND</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1485.0 - 1525.0 DR DEMAND</t>
+          <t>223.38 - 238.62 DR DEMAND</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2086,17 +2086,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2113,17 +2113,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Glenmark Pharmaceuticals Ltd.</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2132,26 +2132,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2198.5</v>
+        <v>958.6</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2181.2 - 2192.2 DR DEMAND</t>
+          <t>937.5 - 940.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1331.41 - 1376.45 DR DEMAND</t>
+          <t>933.9 - 964.4 DR DEMAND</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2193,17 +2193,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HDFC Bank Ltd.</t>
+          <t>Castrol India Ltd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2212,41 +2212,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>694.05</v>
+        <v>194.64</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>686.2 - 687.1 DR DEMAND</t>
+          <t>193.15 - 193.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>144.37 - 156.26 DR DEMAND</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2273,17 +2273,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FSN E-Commerce Ventures Ltd.</t>
+          <t>ICICI Bank Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2292,21 +2292,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>321.9</v>
+        <v>1394.2</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>316.0 - 317.0 DR DEMAND</t>
+          <t>1375.1 - 1379.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>232.05 - 235.0 DR DEMAND</t>
+          <t>1291.0 - 1316.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2353,17 +2353,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SUMICHEM</t>
+          <t>KAYNES</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sumitomo Chemical India Ltd.</t>
+          <t>Kaynes Technology India Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2372,11 +2372,11 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>370.5</v>
+        <v>3187.9</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>361.73 - 363.57 DR DEMAND</t>
+          <t>3130.0 - 3155.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>649.43 - 663.4 RD SUPPLY</t>
+          <t>4070.0 - 4538.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2433,17 +2433,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tata Steel Ltd.</t>
+          <t>Britannia Industries Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2452,26 +2452,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>172.33</v>
+        <v>4537.9</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>171.66 - 172.24 DR DEMAND</t>
+          <t>5382.5 - 5388.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>156.83 - 164.57 DR DEMAND</t>
+          <t>4374.85 - 4461.7 DR DEMAND</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2513,17 +2513,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>FIVESTAR</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Adani Green Energy Ltd.</t>
+          <t>Five-Star Business Finance Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2532,26 +2532,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1250</v>
+        <v>448.4</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1223.6 - 1235.0 DR DEMAND</t>
+          <t>352.47 - 354.71 DR DEMAND</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>6.5 B</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>412.05 - 443.54 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
           <t>6.0 B</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>765.0 - 814.2 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>4.0 C</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2593,17 +2593,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Enterprise Ltd.</t>
+          <t>HDFC Bank Ltd.</t>
         </is>
       </c>
   